--- a/Assets/Data/Tables/Skill.xlsx
+++ b/Assets/Data/Tables/Skill.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -473,12 +473,13 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,30 +510,35 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>maxLevel</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>unlockPrice</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>requires</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>#memo</t>
         </is>
@@ -566,30 +572,35 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>long</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>int[]</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -619,30 +630,35 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
+          <t>최대 레벨 (비우면 1)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
           <t>해금 가격</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>해금 재화 (Gold / Mycelite)</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>선행 스킬 index (쉼표로 구분)</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>아이콘 경로 (Resources 기준)</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>인게임 설명</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>기획 메모 (게임에서 읽지 않음)</t>
         </is>

--- a/Assets/Data/Tables/Skill.xlsx
+++ b/Assets/Data/Tables/Skill.xlsx
@@ -38,7 +38,7 @@
       <color rgb="00404040"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -65,8 +65,28 @@
         <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8E1E1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -88,11 +108,25 @@
         <color rgb="00B8A68C"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -100,6 +134,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,204 +509,9099 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:S138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="48" customWidth="1" min="18" max="18"/>
+    <col width="52" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>branch</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>rarity</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>startLevel</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>maxLevel</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>ability</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>abilityBase</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>abilityValue</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>maxLevel</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>param</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>unlockPrice</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>requires</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="R1" s="5" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="S1" s="6" t="inlineStr">
         <is>
           <t>#memo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>SkillBranch</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>SkillTag</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>int[]</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="R2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>고유 번호 (3001~3999)</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>영문 식별자 (코드·리소스용, 표 안에서 유일)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="S2" s="7" t="n"/>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>고유 번호 (3001~3999). 시작 3001 / 식용 3101~ / 약용 3201~ / 독성 3301~</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>영문 식별자 = group_시작레벨 (표 안에서 고유)</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>인게임 이름</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>능력 종류 키</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>능력 수치</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>최대 레벨 (비우면 1)</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>해금 가격</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>가지 (Start / Edible / Medicinal / Toxic)</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>레어도 0~19 (유저 비공개, 클수록 바깥)</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>태그 (SlideBar / Gain / Stage / Skill / Harvester)</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>같은 스킬 계열 키</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>이 노드가 계열의 몇 레벨부터인지 (비우면 1)</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>이 노드에서 올릴 수 있는 레벨 수 (비우면 1)</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>능력 종류 키 (효과 코드가 찾는 값)</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>배웠으면 한 번 더하는 값</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>레벨당 더하는 값 (비율은 0.1 = 10%)</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>레벨과 무관한 고정 수치 (해석은 ability마다)</t>
+        </is>
+      </c>
+      <c r="N3" s="8" t="inlineStr">
+        <is>
+          <t>해금 가격 (미정)</t>
+        </is>
+      </c>
+      <c r="O3" s="8" t="inlineStr">
         <is>
           <t>해금 재화 (Gold / Mycelite)</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>선행 스킬 index (쉼표로 구분)</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="P3" s="8" t="inlineStr">
+        <is>
+          <t>선행 스킬 index (쉼표 구분, 트리 연결 미정)</t>
+        </is>
+      </c>
+      <c r="Q3" s="8" t="inlineStr">
         <is>
           <t>아이콘 경로 (Resources 기준)</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="R3" s="8" t="inlineStr">
         <is>
           <t>인게임 설명</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="S3" s="8" t="inlineStr">
         <is>
           <t>기획 메모 (게임에서 읽지 않음)</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="n">
+        <v>3001</v>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>hunt_ready_1</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>사냥 준비</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>hunt_ready</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>start_attack_buff</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="n"/>
+      <c r="L4" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" s="9" t="n"/>
+      <c r="O4" s="9" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P4" s="9" t="n"/>
+      <c r="Q4" s="9" t="n"/>
+      <c r="R4" s="9" t="inlineStr">
+        <is>
+          <t>공격력 +2 (3초) 버프 / Lv</t>
+        </is>
+      </c>
+      <c r="S4" s="9" t="inlineStr">
+        <is>
+          <t>첫 레벨업은 골드, 이후 균사석 — currency 한 칸이라 가격 구조 정해지면 열 추가 필요. param = 버프 지속(초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="n">
+        <v>3101</v>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>efficient_hunt_1</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>효율적 사냥</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>efficient_hunt</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>score_rate</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="n"/>
+      <c r="L5" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="10" t="n"/>
+      <c r="O5" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="n"/>
+      <c r="Q5" s="10" t="n"/>
+      <c r="R5" s="10" t="inlineStr">
+        <is>
+          <t>획득 점수 +10% / Lv</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n">
+        <v>3102</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>bargain_1</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>흥정 기술</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>bargain</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>gold_conversion</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="n"/>
+      <c r="L6" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M6" s="10" t="n"/>
+      <c r="N6" s="10" t="n"/>
+      <c r="O6" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P6" s="10" t="n"/>
+      <c r="Q6" s="10" t="n"/>
+      <c r="R6" s="10" t="inlineStr">
+        <is>
+          <t>점수 골드 전환율 +10%</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n">
+        <v>3103</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>wide_view_1</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>넓은 시야</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>wide_view</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>colony_count</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="10" t="n"/>
+      <c r="R7" s="10" t="inlineStr">
+        <is>
+          <t>군락지 수 +1 (3 → 4)</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>3104</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>more_mushrooms_1</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>더 많은 버섯</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>more_mushrooms</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>colony_single_mushroom</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="10" t="n"/>
+      <c r="N8" s="10" t="n"/>
+      <c r="O8" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P8" s="10" t="n"/>
+      <c r="Q8" s="10" t="n"/>
+      <c r="R8" s="10" t="inlineStr">
+        <is>
+          <t>군락지 주변 단일 버섯 +1 (3 → 4)</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>3105</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>quick_hands_1</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>재빠른 손길</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>quick_hands</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>normal_yield</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P9" s="10" t="n"/>
+      <c r="Q9" s="10" t="n"/>
+      <c r="R9" s="10" t="inlineStr">
+        <is>
+          <t>일반 버섯 수확량 +5%</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>3106</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>epic_rumor_1</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>희귀한 버섯 소문</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>epic_rumor</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>epic_spawn</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="10" t="n"/>
+      <c r="O10" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P10" s="10" t="n"/>
+      <c r="Q10" s="10" t="n"/>
+      <c r="R10" s="10" t="inlineStr">
+        <is>
+          <t>에픽 버섯 스폰율 +10% / +15% / +20%</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>Lv.1 10, Lv.2 15, Lv.3 20 → base 5% + 5%/Lv</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n">
+        <v>3107</v>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>quick_hands_2</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>재빠른 손길</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>quick_hands</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>normal_yield</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="10" t="n"/>
+      <c r="O11" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P11" s="10" t="n"/>
+      <c r="Q11" s="10" t="n"/>
+      <c r="R11" s="10" t="inlineStr">
+        <is>
+          <t>일반 버섯 수확량 +10%</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>원문 % = 누적값으로 보고 차이(+5%)만 더함</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>3108</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>bargain_2</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>흥정 기술</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>bargain</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>gold_conversion</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M12" s="10" t="n"/>
+      <c r="N12" s="10" t="n"/>
+      <c r="O12" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P12" s="10" t="n"/>
+      <c r="Q12" s="10" t="n"/>
+      <c r="R12" s="10" t="inlineStr">
+        <is>
+          <t>점수 골드 전환율 +15%</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n">
+        <v>3109</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>fast_flood_1</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>고속 범람</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>fast_flood</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>colony_respawn</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="10" t="n"/>
+      <c r="O13" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="10" t="n"/>
+      <c r="R13" s="10" t="inlineStr">
+        <is>
+          <t>군락지 리스폰 −1초 (7 → 6)</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
+        <v>3110</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>bargain_3</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>흥정 기술</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>bargain</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>gold_conversion</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="10" t="n"/>
+      <c r="O14" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P14" s="10" t="n"/>
+      <c r="Q14" s="10" t="n"/>
+      <c r="R14" s="10" t="inlineStr">
+        <is>
+          <t>점수 골드 전환율 +20%</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n">
+        <v>3111</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>fast_flood_2</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>고속 범람</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>fast_flood</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>colony_respawn</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="n"/>
+      <c r="L15" s="10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M15" s="10" t="n"/>
+      <c r="N15" s="10" t="n"/>
+      <c r="O15" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P15" s="10" t="n"/>
+      <c r="Q15" s="10" t="n"/>
+      <c r="R15" s="10" t="inlineStr">
+        <is>
+          <t>군락지 리스폰 −1초 (6 → 5)</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>3112</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>flex_1</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>플렉스</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>triple_score_chance</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="n"/>
+      <c r="L16" s="10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M16" s="10" t="n"/>
+      <c r="N16" s="10" t="n"/>
+      <c r="O16" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P16" s="10" t="n"/>
+      <c r="Q16" s="10" t="n"/>
+      <c r="R16" s="10" t="inlineStr">
+        <is>
+          <t>점수 3배 확률 +3%</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n">
+        <v>3113</v>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>wide_view_2</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>넓은 시야</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>wide_view</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>colony_count</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="n"/>
+      <c r="L17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="10" t="n"/>
+      <c r="N17" s="10" t="n"/>
+      <c r="O17" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P17" s="10" t="n"/>
+      <c r="Q17" s="10" t="n"/>
+      <c r="R17" s="10" t="inlineStr">
+        <is>
+          <t>군락지 수 +1 (4 → 5)</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n">
+        <v>3114</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>delicate_hands_1</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>섬세한 손길</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>delicate_hands</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>epic_yield</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="n"/>
+      <c r="L18" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M18" s="10" t="n"/>
+      <c r="N18" s="10" t="n"/>
+      <c r="O18" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P18" s="10" t="n"/>
+      <c r="Q18" s="10" t="n"/>
+      <c r="R18" s="10" t="inlineStr">
+        <is>
+          <t>에픽 버섯 수확량 +5%</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n">
+        <v>3115</v>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>more_mushrooms_2</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>더 많은 버섯</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>more_mushrooms</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>colony_single_mushroom</t>
+        </is>
+      </c>
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="10" t="n"/>
+      <c r="N19" s="10" t="n"/>
+      <c r="O19" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P19" s="10" t="n"/>
+      <c r="Q19" s="10" t="n"/>
+      <c r="R19" s="10" t="inlineStr">
+        <is>
+          <t>군락지 주변 단일 버섯 +1 (4 → 5)</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
+        <v>3116</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>quick_hands_3</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>재빠른 손길</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>quick_hands</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>normal_yield</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="n"/>
+      <c r="L20" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M20" s="10" t="n"/>
+      <c r="N20" s="10" t="n"/>
+      <c r="O20" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P20" s="10" t="n"/>
+      <c r="Q20" s="10" t="n"/>
+      <c r="R20" s="10" t="inlineStr">
+        <is>
+          <t>일반 버섯 수확량 +15%</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n">
+        <v>3117</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>wide_view_3</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>넓은 시야</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>wide_view</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>colony_count</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="n"/>
+      <c r="L21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="10" t="n"/>
+      <c r="N21" s="10" t="n"/>
+      <c r="O21" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P21" s="10" t="n"/>
+      <c r="Q21" s="10" t="n"/>
+      <c r="R21" s="10" t="inlineStr">
+        <is>
+          <t>군락지 수 +1 (5 → 6)</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>3118</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>flex_2</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>플렉스</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>triple_score_chance</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="n"/>
+      <c r="L22" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M22" s="10" t="n"/>
+      <c r="N22" s="10" t="n"/>
+      <c r="O22" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P22" s="10" t="n"/>
+      <c r="Q22" s="10" t="n"/>
+      <c r="R22" s="10" t="inlineStr">
+        <is>
+          <t>점수 3배 확률 +5%</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>3119</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>more_mushrooms_3</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>더 많은 버섯</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>more_mushrooms</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>colony_single_mushroom</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="n"/>
+      <c r="L23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="10" t="n"/>
+      <c r="N23" s="10" t="n"/>
+      <c r="O23" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P23" s="10" t="n"/>
+      <c r="Q23" s="10" t="n"/>
+      <c r="R23" s="10" t="inlineStr">
+        <is>
+          <t>군락지 주변 단일 버섯 +1 (5 → 6)</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>3120</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>efficient_hunt_4</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>효율적 사냥</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>efficient_hunt</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>score_rate</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="n"/>
+      <c r="L24" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M24" s="10" t="n"/>
+      <c r="N24" s="10" t="n"/>
+      <c r="O24" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P24" s="10" t="n"/>
+      <c r="Q24" s="10" t="n"/>
+      <c r="R24" s="10" t="inlineStr">
+        <is>
+          <t>획득 점수 +40%</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>3121</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>epic_rumor_4</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>희귀한 버섯 소문</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>epic_rumor</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>epic_spawn</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="n"/>
+      <c r="L25" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M25" s="10" t="n"/>
+      <c r="N25" s="10" t="n"/>
+      <c r="O25" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P25" s="10" t="n"/>
+      <c r="Q25" s="10" t="n"/>
+      <c r="R25" s="10" t="inlineStr">
+        <is>
+          <t>에픽 버섯 스폰율 +25%</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>3122</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>regular_customer_1</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>단골 손님</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>regular_customer</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>gold_conversion</t>
+        </is>
+      </c>
+      <c r="K26" s="10" t="n"/>
+      <c r="L26" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M26" s="10" t="n"/>
+      <c r="N26" s="10" t="n"/>
+      <c r="O26" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P26" s="10" t="n"/>
+      <c r="Q26" s="10" t="n"/>
+      <c r="R26" s="10" t="inlineStr">
+        <is>
+          <t>점수 골드 전환율 +30%</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>흥정 기술의 상위. 누적값 기준 차이 +10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n">
+        <v>3123</v>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>sky_view_1</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>하늘의 시야</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>sky_view</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>colony_count</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="n"/>
+      <c r="L27" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" s="10" t="n"/>
+      <c r="N27" s="10" t="n"/>
+      <c r="O27" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P27" s="10" t="n"/>
+      <c r="Q27" s="10" t="n"/>
+      <c r="R27" s="10" t="inlineStr">
+        <is>
+          <t>군락지 수 +2 (6 → 8)</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>넓은 시야의 상위</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>3124</v>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>delicate_hands_2</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>섬세한 손길</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>delicate_hands</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>epic_yield</t>
+        </is>
+      </c>
+      <c r="K28" s="10" t="n"/>
+      <c r="L28" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M28" s="10" t="n"/>
+      <c r="N28" s="10" t="n"/>
+      <c r="O28" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P28" s="10" t="n"/>
+      <c r="Q28" s="10" t="n"/>
+      <c r="R28" s="10" t="inlineStr">
+        <is>
+          <t>에픽 버섯 수확량 +10%</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>3125</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>flex_3</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>플렉스</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>triple_score_chance</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="n"/>
+      <c r="L29" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M29" s="10" t="n"/>
+      <c r="N29" s="10" t="n"/>
+      <c r="O29" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P29" s="10" t="n"/>
+      <c r="Q29" s="10" t="n"/>
+      <c r="R29" s="10" t="inlineStr">
+        <is>
+          <t>점수 3배 확률 +7%</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>3126</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>sky_view_2</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>하늘의 시야</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>sky_view</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>colony_count</t>
+        </is>
+      </c>
+      <c r="K30" s="10" t="n"/>
+      <c r="L30" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M30" s="10" t="n"/>
+      <c r="N30" s="10" t="n"/>
+      <c r="O30" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P30" s="10" t="n"/>
+      <c r="Q30" s="10" t="n"/>
+      <c r="R30" s="10" t="inlineStr">
+        <is>
+          <t>군락지 수 +2 (8 → 10)</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>넓은 시야의 상위</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>3127</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>unique_legend_1</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>굉장한 버섯 전설</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>unique_legend</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>unique_spawn</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="n"/>
+      <c r="L31" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M31" s="10" t="n"/>
+      <c r="N31" s="10" t="n"/>
+      <c r="O31" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P31" s="10" t="n"/>
+      <c r="Q31" s="10" t="n"/>
+      <c r="R31" s="10" t="inlineStr">
+        <is>
+          <t>유니크 버섯 스폰율 +5%</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
+        <v>3128</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>delicate_hands_3</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>섬세한 손길</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>delicate_hands</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>epic_yield</t>
+        </is>
+      </c>
+      <c r="K32" s="10" t="n"/>
+      <c r="L32" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M32" s="10" t="n"/>
+      <c r="N32" s="10" t="n"/>
+      <c r="O32" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P32" s="10" t="n"/>
+      <c r="Q32" s="10" t="n"/>
+      <c r="R32" s="10" t="inlineStr">
+        <is>
+          <t>에픽 버섯 수확량 +15%</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>3129</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>divine_hands_1</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>신들린 손길</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>divine_hands</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>unique_yield</t>
+        </is>
+      </c>
+      <c r="K33" s="10" t="n"/>
+      <c r="L33" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M33" s="10" t="n"/>
+      <c r="N33" s="10" t="n"/>
+      <c r="O33" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P33" s="10" t="n"/>
+      <c r="Q33" s="10" t="n"/>
+      <c r="R33" s="10" t="inlineStr">
+        <is>
+          <t>유니크 버섯 수확량 +5%</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n">
+        <v>3130</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>fast_flood_3</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>고속 범람</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>fast_flood</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>colony_respawn</t>
+        </is>
+      </c>
+      <c r="K34" s="10" t="n"/>
+      <c r="L34" s="10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M34" s="10" t="n"/>
+      <c r="N34" s="10" t="n"/>
+      <c r="O34" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P34" s="10" t="n"/>
+      <c r="Q34" s="10" t="n"/>
+      <c r="R34" s="10" t="inlineStr">
+        <is>
+          <t>군락지 리스폰 −2초 (5 → 3)</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n">
+        <v>3131</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>golden_myth_1</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>일확천금의 신화</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>golden_myth</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>golden_spawn</t>
+        </is>
+      </c>
+      <c r="K35" s="10" t="n"/>
+      <c r="L35" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M35" s="10" t="n"/>
+      <c r="N35" s="10" t="n"/>
+      <c r="O35" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P35" s="10" t="n"/>
+      <c r="Q35" s="10" t="n"/>
+      <c r="R35" s="10" t="inlineStr">
+        <is>
+          <t>황금 변종 스폰율 +1%</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n">
+        <v>3132</v>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>divine_hands_2</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>신들린 손길</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>divine_hands</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>unique_yield</t>
+        </is>
+      </c>
+      <c r="K36" s="10" t="n"/>
+      <c r="L36" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M36" s="10" t="n"/>
+      <c r="N36" s="10" t="n"/>
+      <c r="O36" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P36" s="10" t="n"/>
+      <c r="Q36" s="10" t="n"/>
+      <c r="R36" s="10" t="inlineStr">
+        <is>
+          <t>유니크 버섯 수확량 +10%</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n">
+        <v>3133</v>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>hidden_master_1</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>은둔 고수</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>hidden_master</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>legendary_yield</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="n"/>
+      <c r="L37" s="10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M37" s="10" t="n"/>
+      <c r="N37" s="10" t="n"/>
+      <c r="O37" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P37" s="10" t="n"/>
+      <c r="Q37" s="10" t="n"/>
+      <c r="R37" s="10" t="inlineStr">
+        <is>
+          <t>보스 전용 레전더리 버섯 수확량 +3%</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="n">
+        <v>3134</v>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>unique_legend_2</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>굉장한 버섯 전설</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>unique_legend</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>unique_spawn</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="n"/>
+      <c r="L38" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M38" s="10" t="n"/>
+      <c r="N38" s="10" t="n"/>
+      <c r="O38" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P38" s="10" t="n"/>
+      <c r="Q38" s="10" t="n"/>
+      <c r="R38" s="10" t="inlineStr">
+        <is>
+          <t>유니크 버섯 스폰율 +10%</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="n">
+        <v>3135</v>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>unique_legend_3</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>굉장한 버섯 전설</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>unique_legend</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>unique_spawn</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="n"/>
+      <c r="L39" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M39" s="10" t="n"/>
+      <c r="N39" s="10" t="n"/>
+      <c r="O39" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P39" s="10" t="n"/>
+      <c r="Q39" s="10" t="n"/>
+      <c r="R39" s="10" t="inlineStr">
+        <is>
+          <t>유니크 버섯 스폰율 +15%</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +5%. 원문은 Lv.2와 같은 레어도 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="n">
+        <v>3136</v>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>golden_myth_2</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>일확천금의 신화</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>golden_myth</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>golden_spawn</t>
+        </is>
+      </c>
+      <c r="K40" s="10" t="n"/>
+      <c r="L40" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M40" s="10" t="n"/>
+      <c r="N40" s="10" t="n"/>
+      <c r="O40" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P40" s="10" t="n"/>
+      <c r="Q40" s="10" t="n"/>
+      <c r="R40" s="10" t="inlineStr">
+        <is>
+          <t>황금 변종 스폰율 +3%</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="n">
+        <v>3137</v>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>hidden_master_2</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>은둔 고수</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>hidden_master</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>legendary_yield</t>
+        </is>
+      </c>
+      <c r="K41" s="10" t="n"/>
+      <c r="L41" s="10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M41" s="10" t="n"/>
+      <c r="N41" s="10" t="n"/>
+      <c r="O41" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P41" s="10" t="n"/>
+      <c r="Q41" s="10" t="n"/>
+      <c r="R41" s="10" t="inlineStr">
+        <is>
+          <t>보스 전용 레전더리 버섯 수확량 +6%</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="n">
+        <v>3138</v>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>regular_customer_2</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>단골 손님</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>regular_customer</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>gold_conversion</t>
+        </is>
+      </c>
+      <c r="K42" s="10" t="n"/>
+      <c r="L42" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M42" s="10" t="n"/>
+      <c r="N42" s="10" t="n"/>
+      <c r="O42" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P42" s="10" t="n"/>
+      <c r="Q42" s="10" t="n"/>
+      <c r="R42" s="10" t="inlineStr">
+        <is>
+          <t>점수 골드 전환율 +40%</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>흥정 기술의 상위. 누적값 기준 차이 +10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="n">
+        <v>3139</v>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>sky_view_3</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>하늘의 시야</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>sky_view</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I43" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>colony_count</t>
+        </is>
+      </c>
+      <c r="K43" s="10" t="n"/>
+      <c r="L43" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M43" s="10" t="n"/>
+      <c r="N43" s="10" t="n"/>
+      <c r="O43" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P43" s="10" t="n"/>
+      <c r="Q43" s="10" t="n"/>
+      <c r="R43" s="10" t="inlineStr">
+        <is>
+          <t>군락지 수 +2 (10 → 12)</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>넓은 시야의 상위</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="n">
+        <v>3140</v>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>divine_hands_3</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>신들린 손길</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>divine_hands</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I44" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>unique_yield</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="n"/>
+      <c r="L44" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M44" s="10" t="n"/>
+      <c r="N44" s="10" t="n"/>
+      <c r="O44" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P44" s="10" t="n"/>
+      <c r="Q44" s="10" t="n"/>
+      <c r="R44" s="10" t="inlineStr">
+        <is>
+          <t>유니크 버섯 수확량 +15%</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="n">
+        <v>3141</v>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>efficient_hunt_5</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>효율적 사냥</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>efficient_hunt</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I45" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="10" t="inlineStr">
+        <is>
+          <t>score_rate</t>
+        </is>
+      </c>
+      <c r="K45" s="10" t="n"/>
+      <c r="L45" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M45" s="10" t="n"/>
+      <c r="N45" s="10" t="n"/>
+      <c r="O45" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P45" s="10" t="n"/>
+      <c r="Q45" s="10" t="n"/>
+      <c r="R45" s="10" t="inlineStr">
+        <is>
+          <t>획득 점수 +50%</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="n">
+        <v>3142</v>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>golden_myth_3</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>일확천금의 신화</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>golden_myth</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>golden_spawn</t>
+        </is>
+      </c>
+      <c r="K46" s="10" t="n"/>
+      <c r="L46" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M46" s="10" t="n"/>
+      <c r="N46" s="10" t="n"/>
+      <c r="O46" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P46" s="10" t="n"/>
+      <c r="Q46" s="10" t="n"/>
+      <c r="R46" s="10" t="inlineStr">
+        <is>
+          <t>황금 변종 스폰율 +5%</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="n">
+        <v>3143</v>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>grandpa_legend_1</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>할아버지의 전설</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
+        <is>
+          <t>grandpa_legend</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J47" s="10" t="inlineStr">
+        <is>
+          <t>final_rush_bonus</t>
+        </is>
+      </c>
+      <c r="K47" s="10" t="n"/>
+      <c r="L47" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M47" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="N47" s="10" t="n"/>
+      <c r="O47" s="10" t="inlineStr">
+        <is>
+          <t>Mycelite</t>
+        </is>
+      </c>
+      <c r="P47" s="10" t="n"/>
+      <c r="Q47" s="10" t="n"/>
+      <c r="R47" s="10" t="inlineStr">
+        <is>
+          <t>라운드 마지막 5초 점수·수확량 +10% / Lv</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>param = 마지막 몇 초</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="n">
+        <v>3144</v>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>god_eye_1</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>신의 눈</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>god_eye</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>colony_count</t>
+        </is>
+      </c>
+      <c r="K48" s="10" t="n"/>
+      <c r="L48" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M48" s="10" t="n"/>
+      <c r="N48" s="10" t="n"/>
+      <c r="O48" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P48" s="10" t="n"/>
+      <c r="Q48" s="10" t="n"/>
+      <c r="R48" s="10" t="inlineStr">
+        <is>
+          <t>군락지 수 +3 (12 → 15)</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>넓은 시야의 상위</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="n">
+        <v>3145</v>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>hidden_master_3</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>은둔 고수</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>hidden_master</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I49" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="10" t="inlineStr">
+        <is>
+          <t>legendary_yield</t>
+        </is>
+      </c>
+      <c r="K49" s="10" t="n"/>
+      <c r="L49" s="10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M49" s="10" t="n"/>
+      <c r="N49" s="10" t="n"/>
+      <c r="O49" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P49" s="10" t="n"/>
+      <c r="Q49" s="10" t="n"/>
+      <c r="R49" s="10" t="inlineStr">
+        <is>
+          <t>보스 전용 레전더리 버섯 수확량 +9%</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="n">
+        <v>3146</v>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>regular_customer_3</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>단골 손님</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>Edible</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>Gain</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>regular_customer</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I50" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>gold_conversion</t>
+        </is>
+      </c>
+      <c r="K50" s="10" t="n"/>
+      <c r="L50" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M50" s="10" t="n"/>
+      <c r="N50" s="10" t="n"/>
+      <c r="O50" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P50" s="10" t="n"/>
+      <c r="Q50" s="10" t="n"/>
+      <c r="R50" s="10" t="inlineStr">
+        <is>
+          <t>점수 골드 전환율 +50%</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>흥정 기술의 상위. 누적값 기준 차이 +10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="n">
+        <v>3201</v>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>spring_1</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>스프링</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>spring</t>
+        </is>
+      </c>
+      <c r="H51" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>buff_haste_duration</t>
+        </is>
+      </c>
+      <c r="K51" s="11" t="n"/>
+      <c r="L51" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M51" s="11" t="n"/>
+      <c r="N51" s="11" t="n"/>
+      <c r="O51" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P51" s="11" t="n"/>
+      <c r="Q51" s="11" t="n"/>
+      <c r="R51" s="11" t="inlineStr">
+        <is>
+          <t>가속(3초) 버프</t>
+        </is>
+      </c>
+      <c r="S51" s="11" t="inlineStr">
+        <is>
+          <t>value = 지속(초), 다음 노드는 +1초씩</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="n">
+        <v>3202</v>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>pierce_1</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>관통</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>pierce</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>buff_pierce_duration</t>
+        </is>
+      </c>
+      <c r="K52" s="11" t="n"/>
+      <c r="L52" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M52" s="11" t="n"/>
+      <c r="N52" s="11" t="n"/>
+      <c r="O52" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P52" s="11" t="n"/>
+      <c r="Q52" s="11" t="n"/>
+      <c r="R52" s="11" t="inlineStr">
+        <is>
+          <t>관통(3초) 버프</t>
+        </is>
+      </c>
+      <c r="S52" s="11" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="n">
+        <v>3203</v>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>spring_2</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>스프링</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>spring</t>
+        </is>
+      </c>
+      <c r="H53" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="11" t="inlineStr">
+        <is>
+          <t>buff_haste_duration</t>
+        </is>
+      </c>
+      <c r="K53" s="11" t="n"/>
+      <c r="L53" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" s="11" t="n"/>
+      <c r="N53" s="11" t="n"/>
+      <c r="O53" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P53" s="11" t="n"/>
+      <c r="Q53" s="11" t="n"/>
+      <c r="R53" s="11" t="inlineStr">
+        <is>
+          <t>가속(4초) 버프</t>
+        </is>
+      </c>
+      <c r="S53" s="11" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="n">
+        <v>3204</v>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>restoration_1</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>환경 복원</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>restoration</t>
+        </is>
+      </c>
+      <c r="H54" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="11" t="inlineStr">
+        <is>
+          <t>field_restoration</t>
+        </is>
+      </c>
+      <c r="K54" s="11" t="n"/>
+      <c r="L54" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" s="11" t="n"/>
+      <c r="N54" s="11" t="n"/>
+      <c r="O54" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P54" s="11" t="n"/>
+      <c r="Q54" s="11" t="n"/>
+      <c r="R54" s="11" t="inlineStr">
+        <is>
+          <t>필드에 그루터기 추가</t>
+        </is>
+      </c>
+      <c r="S54" s="11" t="inlineStr">
+        <is>
+          <t>value = 단계 (1 그루터기 / 2 꽃밭 / 3 도토리 점등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="n">
+        <v>3205</v>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>poison_cure_1</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>이독제독</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="G55" s="11" t="inlineStr">
+        <is>
+          <t>poison_cure</t>
+        </is>
+      </c>
+      <c r="H55" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="11" t="inlineStr">
+        <is>
+          <t>poison_strike_chance</t>
+        </is>
+      </c>
+      <c r="K55" s="11" t="n"/>
+      <c r="L55" s="11" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M55" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N55" s="11" t="n"/>
+      <c r="O55" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P55" s="11" t="n"/>
+      <c r="Q55" s="11" t="n"/>
+      <c r="R55" s="11" t="inlineStr">
+        <is>
+          <t>단일 버섯 획득 시 3% 확률로 다음 타격 피해 +200%</t>
+        </is>
+      </c>
+      <c r="S55" s="11" t="inlineStr">
+        <is>
+          <t>param = 피해 증가 (2 = +200%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="n">
+        <v>3206</v>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>fever_1</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>피버까지 피버</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>fever</t>
+        </is>
+      </c>
+      <c r="H56" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
+          <t>buff_fever_duration</t>
+        </is>
+      </c>
+      <c r="K56" s="11" t="n"/>
+      <c r="L56" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M56" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N56" s="11" t="n"/>
+      <c r="O56" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P56" s="11" t="n"/>
+      <c r="Q56" s="11" t="n"/>
+      <c r="R56" s="11" t="inlineStr">
+        <is>
+          <t>[피버] 버프 3초 · 콤보 계수 +50%</t>
+        </is>
+      </c>
+      <c r="S56" s="11" t="inlineStr">
+        <is>
+          <t>param = 콤보 계수 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="n">
+        <v>3207</v>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>spring_3</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>스프링</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>spring</t>
+        </is>
+      </c>
+      <c r="H57" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I57" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="11" t="inlineStr">
+        <is>
+          <t>buff_haste_duration</t>
+        </is>
+      </c>
+      <c r="K57" s="11" t="n"/>
+      <c r="L57" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" s="11" t="n"/>
+      <c r="N57" s="11" t="n"/>
+      <c r="O57" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P57" s="11" t="n"/>
+      <c r="Q57" s="11" t="n"/>
+      <c r="R57" s="11" t="inlineStr">
+        <is>
+          <t>가속(5초) 버프</t>
+        </is>
+      </c>
+      <c r="S57" s="11" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="n">
+        <v>3208</v>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>poison_cure_2</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>이독제독</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>poison_cure</t>
+        </is>
+      </c>
+      <c r="H58" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" s="11" t="inlineStr">
+        <is>
+          <t>poison_strike_chance</t>
+        </is>
+      </c>
+      <c r="K58" s="11" t="n"/>
+      <c r="L58" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M58" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N58" s="11" t="n"/>
+      <c r="O58" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P58" s="11" t="n"/>
+      <c r="Q58" s="11" t="n"/>
+      <c r="R58" s="11" t="inlineStr">
+        <is>
+          <t>단일 버섯 획득 시 4% 확률로 다음 타격 피해 +200%</t>
+        </is>
+      </c>
+      <c r="S58" s="11" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="n">
+        <v>3209</v>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>chain_lightning_1</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>연속 번개</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="G59" s="11" t="inlineStr">
+        <is>
+          <t>chain_lightning</t>
+        </is>
+      </c>
+      <c r="H59" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="11" t="inlineStr">
+        <is>
+          <t>chain_lightning_chance</t>
+        </is>
+      </c>
+      <c r="K59" s="11" t="n"/>
+      <c r="L59" s="11" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M59" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N59" s="11" t="n"/>
+      <c r="O59" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P59" s="11" t="n"/>
+      <c r="Q59" s="11" t="n"/>
+      <c r="R59" s="11" t="inlineStr">
+        <is>
+          <t>군락 파괴 시 3% 확률로 랜덤 군락에 번개(공격력 30%)</t>
+        </is>
+      </c>
+      <c r="S59" s="11" t="inlineStr">
+        <is>
+          <t>param = 번개 피해 (공격력 비율)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="n">
+        <v>3210</v>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>homing_1</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>유도</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>homing</t>
+        </is>
+      </c>
+      <c r="H60" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="11" t="inlineStr">
+        <is>
+          <t>buff_homing_duration</t>
+        </is>
+      </c>
+      <c r="K60" s="11" t="n"/>
+      <c r="L60" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M60" s="11" t="n"/>
+      <c r="N60" s="11" t="n"/>
+      <c r="O60" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P60" s="11" t="n"/>
+      <c r="Q60" s="11" t="n"/>
+      <c r="R60" s="11" t="inlineStr">
+        <is>
+          <t>유도(3초) 버프</t>
+        </is>
+      </c>
+      <c r="S60" s="11" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="n">
+        <v>3211</v>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>pierce_2</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>관통</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>pierce</t>
+        </is>
+      </c>
+      <c r="H61" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I61" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" s="11" t="inlineStr">
+        <is>
+          <t>buff_pierce_duration</t>
+        </is>
+      </c>
+      <c r="K61" s="11" t="n"/>
+      <c r="L61" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" s="11" t="n"/>
+      <c r="N61" s="11" t="n"/>
+      <c r="O61" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P61" s="11" t="n"/>
+      <c r="Q61" s="11" t="n"/>
+      <c r="R61" s="11" t="inlineStr">
+        <is>
+          <t>관통(4초) 버프</t>
+        </is>
+      </c>
+      <c r="S61" s="11" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="n">
+        <v>3212</v>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>pierce_3</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>관통</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
+          <t>pierce</t>
+        </is>
+      </c>
+      <c r="H62" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I62" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="11" t="inlineStr">
+        <is>
+          <t>buff_pierce_duration</t>
+        </is>
+      </c>
+      <c r="K62" s="11" t="n"/>
+      <c r="L62" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" s="11" t="n"/>
+      <c r="N62" s="11" t="n"/>
+      <c r="O62" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P62" s="11" t="n"/>
+      <c r="Q62" s="11" t="n"/>
+      <c r="R62" s="11" t="inlineStr">
+        <is>
+          <t>관통(5초) 버프</t>
+        </is>
+      </c>
+      <c r="S62" s="11" t="inlineStr">
+        <is>
+          <t>원문은 Lv.2와 같은 레어도 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="n">
+        <v>3213</v>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>molt_1</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>탈피</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>molt</t>
+        </is>
+      </c>
+      <c r="H63" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="11" t="inlineStr">
+        <is>
+          <t>debuff_cleanse_chance</t>
+        </is>
+      </c>
+      <c r="K63" s="11" t="n"/>
+      <c r="L63" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M63" s="11" t="n"/>
+      <c r="N63" s="11" t="n"/>
+      <c r="O63" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P63" s="11" t="n"/>
+      <c r="Q63" s="11" t="n"/>
+      <c r="R63" s="11" t="inlineStr">
+        <is>
+          <t>군락 충돌로 디버프를 얻으면 10% 확률로 해제</t>
+        </is>
+      </c>
+      <c r="S63" s="11" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="n">
+        <v>3214</v>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>poison_cure_3</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>이독제독</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>poison_cure</t>
+        </is>
+      </c>
+      <c r="H64" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I64" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" s="11" t="inlineStr">
+        <is>
+          <t>poison_strike_chance</t>
+        </is>
+      </c>
+      <c r="K64" s="11" t="n"/>
+      <c r="L64" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M64" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N64" s="11" t="n"/>
+      <c r="O64" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P64" s="11" t="n"/>
+      <c r="Q64" s="11" t="n"/>
+      <c r="R64" s="11" t="inlineStr">
+        <is>
+          <t>단일 버섯 획득 시 5% 확률로 다음 타격 피해 +200%</t>
+        </is>
+      </c>
+      <c r="S64" s="11" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="n">
+        <v>3215</v>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>restoration_2</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>환경 복원</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>restoration</t>
+        </is>
+      </c>
+      <c r="H65" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I65" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="11" t="inlineStr">
+        <is>
+          <t>field_restoration</t>
+        </is>
+      </c>
+      <c r="K65" s="11" t="n"/>
+      <c r="L65" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M65" s="11" t="n"/>
+      <c r="N65" s="11" t="n"/>
+      <c r="O65" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P65" s="11" t="n"/>
+      <c r="Q65" s="11" t="n"/>
+      <c r="R65" s="11" t="inlineStr">
+        <is>
+          <t>필드에 꽃밭 추가</t>
+        </is>
+      </c>
+      <c r="S65" s="11" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="n">
+        <v>3216</v>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>healing_hand_1</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>할아버지 손은 약손</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G66" s="11" t="inlineStr">
+        <is>
+          <t>healing_hand</t>
+        </is>
+      </c>
+      <c r="H66" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" s="11" t="inlineStr">
+        <is>
+          <t>buff_heal_duration</t>
+        </is>
+      </c>
+      <c r="K66" s="11" t="n"/>
+      <c r="L66" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M66" s="11" t="n"/>
+      <c r="N66" s="11" t="n"/>
+      <c r="O66" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P66" s="11" t="n"/>
+      <c r="Q66" s="11" t="n"/>
+      <c r="R66" s="11" t="inlineStr">
+        <is>
+          <t>포자 디버프 제거 + 약손(3초)</t>
+        </is>
+      </c>
+      <c r="S66" s="11" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="n">
+        <v>3217</v>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>homing_2</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>유도</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="F67" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G67" s="11" t="inlineStr">
+        <is>
+          <t>homing</t>
+        </is>
+      </c>
+      <c r="H67" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I67" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" s="11" t="inlineStr">
+        <is>
+          <t>buff_homing_duration</t>
+        </is>
+      </c>
+      <c r="K67" s="11" t="n"/>
+      <c r="L67" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M67" s="11" t="n"/>
+      <c r="N67" s="11" t="n"/>
+      <c r="O67" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P67" s="11" t="n"/>
+      <c r="Q67" s="11" t="n"/>
+      <c r="R67" s="11" t="inlineStr">
+        <is>
+          <t>유도(4초) 버프</t>
+        </is>
+      </c>
+      <c r="S67" s="11" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="n">
+        <v>3218</v>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>molt_2</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>탈피</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G68" s="11" t="inlineStr">
+        <is>
+          <t>molt</t>
+        </is>
+      </c>
+      <c r="H68" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I68" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" s="11" t="inlineStr">
+        <is>
+          <t>debuff_cleanse_chance</t>
+        </is>
+      </c>
+      <c r="K68" s="11" t="n"/>
+      <c r="L68" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M68" s="11" t="n"/>
+      <c r="N68" s="11" t="n"/>
+      <c r="O68" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P68" s="11" t="n"/>
+      <c r="Q68" s="11" t="n"/>
+      <c r="R68" s="11" t="inlineStr">
+        <is>
+          <t>군락 충돌로 디버프를 얻으면 20% 확률로 해제</t>
+        </is>
+      </c>
+      <c r="S68" s="11" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="n">
+        <v>3219</v>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>whirlwind_1</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>회오리</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>whirlwind</t>
+        </is>
+      </c>
+      <c r="H69" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" s="11" t="inlineStr">
+        <is>
+          <t>whirlwind_chance</t>
+        </is>
+      </c>
+      <c r="K69" s="11" t="n"/>
+      <c r="L69" s="11" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M69" s="11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N69" s="11" t="n"/>
+      <c r="O69" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P69" s="11" t="n"/>
+      <c r="Q69" s="11" t="n"/>
+      <c r="R69" s="11" t="inlineStr">
+        <is>
+          <t>군락 충돌 시 3% 확률로 3초 지속 피해(공격력 5%)</t>
+        </is>
+      </c>
+      <c r="S69" s="11" t="inlineStr">
+        <is>
+          <t>param = 초당 피해 (공격력 비율). 지속 시간도 3/4/5초로 오르는데 칸이 하나라 계열 레벨 + 2초로 계산 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="n">
+        <v>3220</v>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>elder_wisdom_1</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>노인의 지혜</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G70" s="11" t="inlineStr">
+        <is>
+          <t>elder_wisdom</t>
+        </is>
+      </c>
+      <c r="H70" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" s="11" t="inlineStr">
+        <is>
+          <t>buff_wisdom_rate</t>
+        </is>
+      </c>
+      <c r="K70" s="11" t="n"/>
+      <c r="L70" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M70" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="N70" s="11" t="n"/>
+      <c r="O70" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P70" s="11" t="n"/>
+      <c r="Q70" s="11" t="n"/>
+      <c r="R70" s="11" t="inlineStr">
+        <is>
+          <t>[지혜] 버프 3초 · 수확기 스킬 발동률 +1%</t>
+        </is>
+      </c>
+      <c r="S70" s="11" t="inlineStr">
+        <is>
+          <t>param = 버프 지속(초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="n">
+        <v>3221</v>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>elder_wisdom_2</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>노인의 지혜</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G71" s="11" t="inlineStr">
+        <is>
+          <t>elder_wisdom</t>
+        </is>
+      </c>
+      <c r="H71" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I71" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" s="11" t="inlineStr">
+        <is>
+          <t>buff_wisdom_rate</t>
+        </is>
+      </c>
+      <c r="K71" s="11" t="n"/>
+      <c r="L71" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M71" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="N71" s="11" t="n"/>
+      <c r="O71" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P71" s="11" t="n"/>
+      <c r="Q71" s="11" t="n"/>
+      <c r="R71" s="11" t="inlineStr">
+        <is>
+          <t>[지혜] 버프 3초 · 수확기 스킬 발동률 +2%</t>
+        </is>
+      </c>
+      <c r="S71" s="11" t="inlineStr">
+        <is>
+          <t>원문은 Lv.1과 같은 레어도 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="n">
+        <v>3222</v>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>fever_2</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>피버까지 피버</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="F72" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G72" s="11" t="inlineStr">
+        <is>
+          <t>fever</t>
+        </is>
+      </c>
+      <c r="H72" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I72" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" s="11" t="inlineStr">
+        <is>
+          <t>buff_fever_duration</t>
+        </is>
+      </c>
+      <c r="K72" s="11" t="n"/>
+      <c r="L72" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N72" s="11" t="n"/>
+      <c r="O72" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P72" s="11" t="n"/>
+      <c r="Q72" s="11" t="n"/>
+      <c r="R72" s="11" t="inlineStr">
+        <is>
+          <t>[피버] 버프 4초 · 콤보 계수 +50%</t>
+        </is>
+      </c>
+      <c r="S72" s="11" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="n">
+        <v>3223</v>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>spore_burst_1</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>포자 폭발</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>spore_burst</t>
+        </is>
+      </c>
+      <c r="H73" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>spore_burst_chance</t>
+        </is>
+      </c>
+      <c r="K73" s="11" t="n"/>
+      <c r="L73" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M73" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N73" s="11" t="n"/>
+      <c r="O73" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P73" s="11" t="n"/>
+      <c r="Q73" s="11" t="n"/>
+      <c r="R73" s="11" t="inlineStr">
+        <is>
+          <t>군락 충돌 시 1% 확률로 전체 피해(공격력 10%)</t>
+        </is>
+      </c>
+      <c r="S73" s="11" t="inlineStr">
+        <is>
+          <t>param = 피해 (공격력 비율)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="n">
+        <v>3224</v>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>spore_burst_2</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>포자 폭발</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="G74" s="11" t="inlineStr">
+        <is>
+          <t>spore_burst</t>
+        </is>
+      </c>
+      <c r="H74" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I74" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" s="11" t="inlineStr">
+        <is>
+          <t>spore_burst_chance</t>
+        </is>
+      </c>
+      <c r="K74" s="11" t="n"/>
+      <c r="L74" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M74" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N74" s="11" t="n"/>
+      <c r="O74" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P74" s="11" t="n"/>
+      <c r="Q74" s="11" t="n"/>
+      <c r="R74" s="11" t="inlineStr">
+        <is>
+          <t>군락 충돌 시 2% 확률로 전체 피해(공격력 10%)</t>
+        </is>
+      </c>
+      <c r="S74" s="11" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="n">
+        <v>3225</v>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>homing_3</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>유도</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F75" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G75" s="11" t="inlineStr">
+        <is>
+          <t>homing</t>
+        </is>
+      </c>
+      <c r="H75" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I75" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" s="11" t="inlineStr">
+        <is>
+          <t>buff_homing_duration</t>
+        </is>
+      </c>
+      <c r="K75" s="11" t="n"/>
+      <c r="L75" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M75" s="11" t="n"/>
+      <c r="N75" s="11" t="n"/>
+      <c r="O75" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P75" s="11" t="n"/>
+      <c r="Q75" s="11" t="n"/>
+      <c r="R75" s="11" t="inlineStr">
+        <is>
+          <t>유도(5초) 버프</t>
+        </is>
+      </c>
+      <c r="S75" s="11" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="n">
+        <v>3226</v>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>molt_3</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>탈피</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F76" s="11" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G76" s="11" t="inlineStr">
+        <is>
+          <t>molt</t>
+        </is>
+      </c>
+      <c r="H76" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I76" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" s="11" t="inlineStr">
+        <is>
+          <t>debuff_cleanse_chance</t>
+        </is>
+      </c>
+      <c r="K76" s="11" t="n"/>
+      <c r="L76" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M76" s="11" t="n"/>
+      <c r="N76" s="11" t="n"/>
+      <c r="O76" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P76" s="11" t="n"/>
+      <c r="Q76" s="11" t="n"/>
+      <c r="R76" s="11" t="inlineStr">
+        <is>
+          <t>군락 충돌로 디버프를 얻으면 30% 확률로 해제</t>
+        </is>
+      </c>
+      <c r="S76" s="11" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="n">
+        <v>3227</v>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>restoration_3</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>환경 복원</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F77" s="11" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G77" s="11" t="inlineStr">
+        <is>
+          <t>restoration</t>
+        </is>
+      </c>
+      <c r="H77" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I77" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" s="11" t="inlineStr">
+        <is>
+          <t>field_restoration</t>
+        </is>
+      </c>
+      <c r="K77" s="11" t="n"/>
+      <c r="L77" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" s="11" t="n"/>
+      <c r="N77" s="11" t="n"/>
+      <c r="O77" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P77" s="11" t="n"/>
+      <c r="Q77" s="11" t="n"/>
+      <c r="R77" s="11" t="inlineStr">
+        <is>
+          <t>필드에 도토리 점등 추가</t>
+        </is>
+      </c>
+      <c r="S77" s="11" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="n">
+        <v>3228</v>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>split_1</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>분열</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F78" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G78" s="11" t="inlineStr">
+        <is>
+          <t>split</t>
+        </is>
+      </c>
+      <c r="H78" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" s="11" t="inlineStr">
+        <is>
+          <t>buff_split_duration</t>
+        </is>
+      </c>
+      <c r="K78" s="11" t="n"/>
+      <c r="L78" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M78" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N78" s="11" t="n"/>
+      <c r="O78" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P78" s="11" t="n"/>
+      <c r="Q78" s="11" t="n"/>
+      <c r="R78" s="11" t="inlineStr">
+        <is>
+          <t>10% 확률로 분열(3초) 버프</t>
+        </is>
+      </c>
+      <c r="S78" s="11" t="inlineStr">
+        <is>
+          <t>param = 발동 확률</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="n">
+        <v>3229</v>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>whirlwind_2</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>회오리</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F79" s="11" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="G79" s="11" t="inlineStr">
+        <is>
+          <t>whirlwind</t>
+        </is>
+      </c>
+      <c r="H79" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I79" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" s="11" t="inlineStr">
+        <is>
+          <t>whirlwind_chance</t>
+        </is>
+      </c>
+      <c r="K79" s="11" t="n"/>
+      <c r="L79" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M79" s="11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N79" s="11" t="n"/>
+      <c r="O79" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P79" s="11" t="n"/>
+      <c r="Q79" s="11" t="n"/>
+      <c r="R79" s="11" t="inlineStr">
+        <is>
+          <t>군락 충돌 시 4% 확률로 4초 지속 피해(공격력 5%)</t>
+        </is>
+      </c>
+      <c r="S79" s="11" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="n">
+        <v>3230</v>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>elder_wisdom_3</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>노인의 지혜</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F80" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G80" s="11" t="inlineStr">
+        <is>
+          <t>elder_wisdom</t>
+        </is>
+      </c>
+      <c r="H80" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I80" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="11" t="inlineStr">
+        <is>
+          <t>buff_wisdom_rate</t>
+        </is>
+      </c>
+      <c r="K80" s="11" t="n"/>
+      <c r="L80" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M80" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="N80" s="11" t="n"/>
+      <c r="O80" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P80" s="11" t="n"/>
+      <c r="Q80" s="11" t="n"/>
+      <c r="R80" s="11" t="inlineStr">
+        <is>
+          <t>[지혜] 버프 3초 · 수확기 스킬 발동률 +3%</t>
+        </is>
+      </c>
+      <c r="S80" s="11" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="n">
+        <v>3231</v>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>healing_hand_2</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>할아버지 손은 약손</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G81" s="11" t="inlineStr">
+        <is>
+          <t>healing_hand</t>
+        </is>
+      </c>
+      <c r="H81" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I81" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="11" t="inlineStr">
+        <is>
+          <t>buff_heal_duration</t>
+        </is>
+      </c>
+      <c r="K81" s="11" t="n"/>
+      <c r="L81" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" s="11" t="n"/>
+      <c r="N81" s="11" t="n"/>
+      <c r="O81" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P81" s="11" t="n"/>
+      <c r="Q81" s="11" t="n"/>
+      <c r="R81" s="11" t="inlineStr">
+        <is>
+          <t>포자 디버프 제거 + 약손(4초)</t>
+        </is>
+      </c>
+      <c r="S81" s="11" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="n">
+        <v>3232</v>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>chain_lightning_2</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>연속 번개</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="F82" s="11" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="G82" s="11" t="inlineStr">
+        <is>
+          <t>chain_lightning</t>
+        </is>
+      </c>
+      <c r="H82" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I82" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" s="11" t="inlineStr">
+        <is>
+          <t>chain_lightning_chance</t>
+        </is>
+      </c>
+      <c r="K82" s="11" t="n"/>
+      <c r="L82" s="11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M82" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N82" s="11" t="n"/>
+      <c r="O82" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P82" s="11" t="n"/>
+      <c r="Q82" s="11" t="n"/>
+      <c r="R82" s="11" t="inlineStr">
+        <is>
+          <t>군락 파괴 시 5% 확률로 랜덤 군락에 번개(공격력 30%)</t>
+        </is>
+      </c>
+      <c r="S82" s="11" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="11" t="n">
+        <v>3233</v>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>healing_hand_3</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>할아버지 손은 약손</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G83" s="11" t="inlineStr">
+        <is>
+          <t>healing_hand</t>
+        </is>
+      </c>
+      <c r="H83" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I83" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" s="11" t="inlineStr">
+        <is>
+          <t>buff_heal_duration</t>
+        </is>
+      </c>
+      <c r="K83" s="11" t="n"/>
+      <c r="L83" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" s="11" t="n"/>
+      <c r="N83" s="11" t="n"/>
+      <c r="O83" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P83" s="11" t="n"/>
+      <c r="Q83" s="11" t="n"/>
+      <c r="R83" s="11" t="inlineStr">
+        <is>
+          <t>포자 디버프 제거 + 약손(5초)</t>
+        </is>
+      </c>
+      <c r="S83" s="11" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="11" t="n">
+        <v>3234</v>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>chain_lightning_3</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>연속 번개</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E84" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="F84" s="11" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="G84" s="11" t="inlineStr">
+        <is>
+          <t>chain_lightning</t>
+        </is>
+      </c>
+      <c r="H84" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I84" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" s="11" t="inlineStr">
+        <is>
+          <t>chain_lightning_chance</t>
+        </is>
+      </c>
+      <c r="K84" s="11" t="n"/>
+      <c r="L84" s="11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M84" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N84" s="11" t="n"/>
+      <c r="O84" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P84" s="11" t="n"/>
+      <c r="Q84" s="11" t="n"/>
+      <c r="R84" s="11" t="inlineStr">
+        <is>
+          <t>군락 파괴 시 7% 확률로 랜덤 위치에 번개(공격력 30%)</t>
+        </is>
+      </c>
+      <c r="S84" s="11" t="inlineStr">
+        <is>
+          <t>확인 필요: 원문 Lv.3만 "랜덤 위치", Lv.1·2는 "랜덤 군락"</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="11" t="n">
+        <v>3235</v>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>legendary_grandpa_1</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>전설의 할아버지</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="F85" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G85" s="11" t="inlineStr">
+        <is>
+          <t>legendary_grandpa</t>
+        </is>
+      </c>
+      <c r="H85" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J85" s="11" t="inlineStr">
+        <is>
+          <t>opening_buff_chance</t>
+        </is>
+      </c>
+      <c r="K85" s="11" t="n"/>
+      <c r="L85" s="11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M85" s="11" t="n"/>
+      <c r="N85" s="11" t="n"/>
+      <c r="O85" s="11" t="inlineStr">
+        <is>
+          <t>Mycelite</t>
+        </is>
+      </c>
+      <c r="P85" s="11" t="n"/>
+      <c r="Q85" s="11" t="n"/>
+      <c r="R85" s="11" t="inlineStr">
+        <is>
+          <t>게임 시작 시 보유 버프 스킬 즉시 발동 확률 +2% / Lv</t>
+        </is>
+      </c>
+      <c r="S85" s="11" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="11" t="n">
+        <v>3236</v>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>split_2</t>
+        </is>
+      </c>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t>분열</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="F86" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G86" s="11" t="inlineStr">
+        <is>
+          <t>split</t>
+        </is>
+      </c>
+      <c r="H86" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I86" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" s="11" t="inlineStr">
+        <is>
+          <t>buff_split_duration</t>
+        </is>
+      </c>
+      <c r="K86" s="11" t="n"/>
+      <c r="L86" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N86" s="11" t="n"/>
+      <c r="O86" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P86" s="11" t="n"/>
+      <c r="Q86" s="11" t="n"/>
+      <c r="R86" s="11" t="inlineStr">
+        <is>
+          <t>10% 확률로 분열(4초) 버프</t>
+        </is>
+      </c>
+      <c r="S86" s="11" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="11" t="n">
+        <v>3237</v>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>split_3</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>분열</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>split</t>
+        </is>
+      </c>
+      <c r="H87" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I87" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" s="11" t="inlineStr">
+        <is>
+          <t>buff_split_duration</t>
+        </is>
+      </c>
+      <c r="K87" s="11" t="n"/>
+      <c r="L87" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M87" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N87" s="11" t="n"/>
+      <c r="O87" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P87" s="11" t="n"/>
+      <c r="Q87" s="11" t="n"/>
+      <c r="R87" s="11" t="inlineStr">
+        <is>
+          <t>10% 확률로 분열(5초) 버프</t>
+        </is>
+      </c>
+      <c r="S87" s="11" t="inlineStr">
+        <is>
+          <t>원문은 Lv.2와 같은 레어도 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="11" t="n">
+        <v>3238</v>
+      </c>
+      <c r="B88" s="11" t="inlineStr">
+        <is>
+          <t>spore_burst_3</t>
+        </is>
+      </c>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t>포자 폭발</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E88" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="F88" s="11" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="G88" s="11" t="inlineStr">
+        <is>
+          <t>spore_burst</t>
+        </is>
+      </c>
+      <c r="H88" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I88" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" s="11" t="inlineStr">
+        <is>
+          <t>spore_burst_chance</t>
+        </is>
+      </c>
+      <c r="K88" s="11" t="n"/>
+      <c r="L88" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M88" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N88" s="11" t="n"/>
+      <c r="O88" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P88" s="11" t="n"/>
+      <c r="Q88" s="11" t="n"/>
+      <c r="R88" s="11" t="inlineStr">
+        <is>
+          <t>군락 충돌 시 3% 확률로 전체 피해(공격력 10%)</t>
+        </is>
+      </c>
+      <c r="S88" s="11" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="11" t="n">
+        <v>3239</v>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>whirlwind_3</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>회오리</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="F89" s="11" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="G89" s="11" t="inlineStr">
+        <is>
+          <t>whirlwind</t>
+        </is>
+      </c>
+      <c r="H89" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I89" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" s="11" t="inlineStr">
+        <is>
+          <t>whirlwind_chance</t>
+        </is>
+      </c>
+      <c r="K89" s="11" t="n"/>
+      <c r="L89" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M89" s="11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N89" s="11" t="n"/>
+      <c r="O89" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P89" s="11" t="n"/>
+      <c r="Q89" s="11" t="n"/>
+      <c r="R89" s="11" t="inlineStr">
+        <is>
+          <t>군락 충돌 시 5% 확률로 5초 지속 피해(공격력 5%)</t>
+        </is>
+      </c>
+      <c r="S89" s="11" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="11" t="n">
+        <v>3240</v>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>fever_3</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>피버까지 피버</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>Medicinal</t>
+        </is>
+      </c>
+      <c r="E90" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="F90" s="11" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G90" s="11" t="inlineStr">
+        <is>
+          <t>fever</t>
+        </is>
+      </c>
+      <c r="H90" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I90" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" s="11" t="inlineStr">
+        <is>
+          <t>buff_fever_duration</t>
+        </is>
+      </c>
+      <c r="K90" s="11" t="n"/>
+      <c r="L90" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M90" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N90" s="11" t="n"/>
+      <c r="O90" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P90" s="11" t="n"/>
+      <c r="Q90" s="11" t="n"/>
+      <c r="R90" s="11" t="inlineStr">
+        <is>
+          <t>[피버] 버프 5초 · 콤보 계수 +50%</t>
+        </is>
+      </c>
+      <c r="S90" s="11" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="n">
+        <v>3301</v>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>sharpen_1</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>날 갈기</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G91" s="12" t="inlineStr">
+        <is>
+          <t>sharpen</t>
+        </is>
+      </c>
+      <c r="H91" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" s="12" t="inlineStr">
+        <is>
+          <t>harvester_damage</t>
+        </is>
+      </c>
+      <c r="K91" s="12" t="n"/>
+      <c r="L91" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M91" s="12" t="n"/>
+      <c r="N91" s="12" t="n"/>
+      <c r="O91" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P91" s="12" t="n"/>
+      <c r="Q91" s="12" t="n"/>
+      <c r="R91" s="12" t="inlineStr">
+        <is>
+          <t>공격력 +2 (1 → 3)</t>
+        </is>
+      </c>
+      <c r="S91" s="12" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="n">
+        <v>3302</v>
+      </c>
+      <c r="B92" s="12" t="inlineStr">
+        <is>
+          <t>combo_1</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>콤보 계수</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t>combo</t>
+        </is>
+      </c>
+      <c r="H92" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="12" t="inlineStr">
+        <is>
+          <t>combo_rate</t>
+        </is>
+      </c>
+      <c r="K92" s="12" t="n"/>
+      <c r="L92" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M92" s="12" t="n"/>
+      <c r="N92" s="12" t="n"/>
+      <c r="O92" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P92" s="12" t="n"/>
+      <c r="Q92" s="12" t="n"/>
+      <c r="R92" s="12" t="inlineStr">
+        <is>
+          <t>콤보 계수 +20%</t>
+        </is>
+      </c>
+      <c r="S92" s="12" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="n">
+        <v>3303</v>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>wind_path_1</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>바람의 길</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F93" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G93" s="12" t="inlineStr">
+        <is>
+          <t>wind_path</t>
+        </is>
+      </c>
+      <c r="H93" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" s="12" t="inlineStr">
+        <is>
+          <t>harvester_speed</t>
+        </is>
+      </c>
+      <c r="K93" s="12" t="n"/>
+      <c r="L93" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M93" s="12" t="n"/>
+      <c r="N93" s="12" t="n"/>
+      <c r="O93" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P93" s="12" t="n"/>
+      <c r="Q93" s="12" t="n"/>
+      <c r="R93" s="12" t="inlineStr">
+        <is>
+          <t>수확기 속도 +10%</t>
+        </is>
+      </c>
+      <c r="S93" s="12" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="n">
+        <v>3304</v>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>crit_1</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>치명 공격</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F94" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G94" s="12" t="inlineStr">
+        <is>
+          <t>crit</t>
+        </is>
+      </c>
+      <c r="H94" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" s="12" t="inlineStr">
+        <is>
+          <t>crit_chance</t>
+        </is>
+      </c>
+      <c r="K94" s="12" t="n"/>
+      <c r="L94" s="12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M94" s="12" t="n"/>
+      <c r="N94" s="12" t="n"/>
+      <c r="O94" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P94" s="12" t="n"/>
+      <c r="Q94" s="12" t="n"/>
+      <c r="R94" s="12" t="inlineStr">
+        <is>
+          <t>치명타 확률 2%</t>
+        </is>
+      </c>
+      <c r="S94" s="12" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="n">
+        <v>3305</v>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>big_hug_1</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>한가득 포옹</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" s="12" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G95" s="12" t="inlineStr">
+        <is>
+          <t>big_hug</t>
+        </is>
+      </c>
+      <c r="H95" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" s="12" t="inlineStr">
+        <is>
+          <t>bar_length</t>
+        </is>
+      </c>
+      <c r="K95" s="12" t="n"/>
+      <c r="L95" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M95" s="12" t="n"/>
+      <c r="N95" s="12" t="n"/>
+      <c r="O95" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P95" s="12" t="n"/>
+      <c r="Q95" s="12" t="n"/>
+      <c r="R95" s="12" t="inlineStr">
+        <is>
+          <t>바 길이 +20%</t>
+        </is>
+      </c>
+      <c r="S95" s="12" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="n">
+        <v>3306</v>
+      </c>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>sharpen_2</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>날 갈기</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F96" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G96" s="12" t="inlineStr">
+        <is>
+          <t>sharpen</t>
+        </is>
+      </c>
+      <c r="H96" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I96" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" s="12" t="inlineStr">
+        <is>
+          <t>harvester_damage</t>
+        </is>
+      </c>
+      <c r="K96" s="12" t="n"/>
+      <c r="L96" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M96" s="12" t="n"/>
+      <c r="N96" s="12" t="n"/>
+      <c r="O96" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P96" s="12" t="n"/>
+      <c r="Q96" s="12" t="n"/>
+      <c r="R96" s="12" t="inlineStr">
+        <is>
+          <t>공격력 +2 (3 → 5)</t>
+        </is>
+      </c>
+      <c r="S96" s="12" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="12" t="n">
+        <v>3307</v>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>scorched_1</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>초토화</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F97" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G97" s="12" t="inlineStr">
+        <is>
+          <t>scorched</t>
+        </is>
+      </c>
+      <c r="H97" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" s="12" t="inlineStr">
+        <is>
+          <t>harvester_size</t>
+        </is>
+      </c>
+      <c r="K97" s="12" t="n"/>
+      <c r="L97" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M97" s="12" t="n"/>
+      <c r="N97" s="12" t="n"/>
+      <c r="O97" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P97" s="12" t="n"/>
+      <c r="Q97" s="12" t="n"/>
+      <c r="R97" s="12" t="inlineStr">
+        <is>
+          <t>수확기 크기 +10%</t>
+        </is>
+      </c>
+      <c r="S97" s="12" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="12" t="n">
+        <v>3308</v>
+      </c>
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t>scorched_2</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>초토화</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F98" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G98" s="12" t="inlineStr">
+        <is>
+          <t>scorched</t>
+        </is>
+      </c>
+      <c r="H98" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I98" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" s="12" t="inlineStr">
+        <is>
+          <t>harvester_size</t>
+        </is>
+      </c>
+      <c r="K98" s="12" t="n"/>
+      <c r="L98" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M98" s="12" t="n"/>
+      <c r="N98" s="12" t="n"/>
+      <c r="O98" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P98" s="12" t="n"/>
+      <c r="Q98" s="12" t="n"/>
+      <c r="R98" s="12" t="inlineStr">
+        <is>
+          <t>수확기 크기 +20%</t>
+        </is>
+      </c>
+      <c r="S98" s="12" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +10%. 원문은 Lv.1과 같은 레어도 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="n">
+        <v>3309</v>
+      </c>
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t>sharpen_3</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>날 갈기</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F99" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G99" s="12" t="inlineStr">
+        <is>
+          <t>sharpen</t>
+        </is>
+      </c>
+      <c r="H99" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I99" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" s="12" t="inlineStr">
+        <is>
+          <t>harvester_damage</t>
+        </is>
+      </c>
+      <c r="K99" s="12" t="n"/>
+      <c r="L99" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M99" s="12" t="n"/>
+      <c r="N99" s="12" t="n"/>
+      <c r="O99" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P99" s="12" t="n"/>
+      <c r="Q99" s="12" t="n"/>
+      <c r="R99" s="12" t="inlineStr">
+        <is>
+          <t>공격력 +2 (5 → 7)</t>
+        </is>
+      </c>
+      <c r="S99" s="12" t="inlineStr">
+        <is>
+          <t>확인 필요: 원문은 "+3 (5 → 7)", 화살표 기준 +2로 넣음</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="n">
+        <v>3310</v>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>big_hug_2</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>한가득 포옹</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F100" s="12" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G100" s="12" t="inlineStr">
+        <is>
+          <t>big_hug</t>
+        </is>
+      </c>
+      <c r="H100" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I100" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" s="12" t="inlineStr">
+        <is>
+          <t>bar_length</t>
+        </is>
+      </c>
+      <c r="K100" s="12" t="n"/>
+      <c r="L100" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M100" s="12" t="n"/>
+      <c r="N100" s="12" t="n"/>
+      <c r="O100" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P100" s="12" t="n"/>
+      <c r="Q100" s="12" t="n"/>
+      <c r="R100" s="12" t="inlineStr">
+        <is>
+          <t>바 길이 +30%</t>
+        </is>
+      </c>
+      <c r="S100" s="12" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="12" t="n">
+        <v>3311</v>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>scorched_3</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>초토화</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F101" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G101" s="12" t="inlineStr">
+        <is>
+          <t>scorched</t>
+        </is>
+      </c>
+      <c r="H101" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I101" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J101" s="12" t="inlineStr">
+        <is>
+          <t>harvester_size</t>
+        </is>
+      </c>
+      <c r="K101" s="12" t="n"/>
+      <c r="L101" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M101" s="12" t="n"/>
+      <c r="N101" s="12" t="n"/>
+      <c r="O101" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P101" s="12" t="n"/>
+      <c r="Q101" s="12" t="n"/>
+      <c r="R101" s="12" t="inlineStr">
+        <is>
+          <t>수확기 크기 +30%</t>
+        </is>
+      </c>
+      <c r="S101" s="12" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="12" t="n">
+        <v>3312</v>
+      </c>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>wind_path_2</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>바람의 길</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F102" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G102" s="12" t="inlineStr">
+        <is>
+          <t>wind_path</t>
+        </is>
+      </c>
+      <c r="H102" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I102" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" s="12" t="inlineStr">
+        <is>
+          <t>harvester_speed</t>
+        </is>
+      </c>
+      <c r="K102" s="12" t="n"/>
+      <c r="L102" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M102" s="12" t="n"/>
+      <c r="N102" s="12" t="n"/>
+      <c r="O102" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P102" s="12" t="n"/>
+      <c r="Q102" s="12" t="n"/>
+      <c r="R102" s="12" t="inlineStr">
+        <is>
+          <t>수확기 속도 +20%</t>
+        </is>
+      </c>
+      <c r="S102" s="12" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="12" t="n">
+        <v>3313</v>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>crit_2</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>치명 공격</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F103" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G103" s="12" t="inlineStr">
+        <is>
+          <t>crit</t>
+        </is>
+      </c>
+      <c r="H103" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I103" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" s="12" t="inlineStr">
+        <is>
+          <t>crit_chance</t>
+        </is>
+      </c>
+      <c r="K103" s="12" t="n"/>
+      <c r="L103" s="12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M103" s="12" t="n"/>
+      <c r="N103" s="12" t="n"/>
+      <c r="O103" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P103" s="12" t="n"/>
+      <c r="Q103" s="12" t="n"/>
+      <c r="R103" s="12" t="inlineStr">
+        <is>
+          <t>치명타 확률 4%</t>
+        </is>
+      </c>
+      <c r="S103" s="12" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="12" t="n">
+        <v>3314</v>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>orbit_blade_1</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>회전 칼날</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F104" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G104" s="12" t="inlineStr">
+        <is>
+          <t>orbit_blade</t>
+        </is>
+      </c>
+      <c r="H104" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I104" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J104" s="12" t="inlineStr">
+        <is>
+          <t>orbit_harvester_count</t>
+        </is>
+      </c>
+      <c r="K104" s="12" t="n"/>
+      <c r="L104" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M104" s="12" t="n"/>
+      <c r="N104" s="12" t="n"/>
+      <c r="O104" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P104" s="12" t="n"/>
+      <c r="Q104" s="12" t="n"/>
+      <c r="R104" s="12" t="inlineStr">
+        <is>
+          <t>회전 꼬마 수확기 +1 (0 → 1)</t>
+        </is>
+      </c>
+      <c r="S104" s="12" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="n">
+        <v>3315</v>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>big_hug_3</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>한가득 포옹</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F105" s="12" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G105" s="12" t="inlineStr">
+        <is>
+          <t>big_hug</t>
+        </is>
+      </c>
+      <c r="H105" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I105" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" s="12" t="inlineStr">
+        <is>
+          <t>bar_length</t>
+        </is>
+      </c>
+      <c r="K105" s="12" t="n"/>
+      <c r="L105" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M105" s="12" t="n"/>
+      <c r="N105" s="12" t="n"/>
+      <c r="O105" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P105" s="12" t="n"/>
+      <c r="Q105" s="12" t="n"/>
+      <c r="R105" s="12" t="inlineStr">
+        <is>
+          <t>바 길이 +50%</t>
+        </is>
+      </c>
+      <c r="S105" s="12" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="12" t="n">
+        <v>3316</v>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>boss_damage_1</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>보스 피해</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F106" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G106" s="12" t="inlineStr">
+        <is>
+          <t>boss_damage</t>
+        </is>
+      </c>
+      <c r="H106" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J106" s="12" t="inlineStr">
+        <is>
+          <t>boss_damage</t>
+        </is>
+      </c>
+      <c r="K106" s="12" t="n"/>
+      <c r="L106" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M106" s="12" t="n"/>
+      <c r="N106" s="12" t="n"/>
+      <c r="O106" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P106" s="12" t="n"/>
+      <c r="Q106" s="12" t="n"/>
+      <c r="R106" s="12" t="inlineStr">
+        <is>
+          <t>보스 피해 +20%</t>
+        </is>
+      </c>
+      <c r="S106" s="12" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="12" t="n">
+        <v>3317</v>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>combo_2</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>콤보 계수</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F107" s="12" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G107" s="12" t="inlineStr">
+        <is>
+          <t>combo</t>
+        </is>
+      </c>
+      <c r="H107" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I107" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" s="12" t="inlineStr">
+        <is>
+          <t>combo_rate</t>
+        </is>
+      </c>
+      <c r="K107" s="12" t="n"/>
+      <c r="L107" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M107" s="12" t="n"/>
+      <c r="N107" s="12" t="n"/>
+      <c r="O107" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P107" s="12" t="n"/>
+      <c r="Q107" s="12" t="n"/>
+      <c r="R107" s="12" t="inlineStr">
+        <is>
+          <t>콤보 계수 +40%</t>
+        </is>
+      </c>
+      <c r="S107" s="12" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="12" t="n">
+        <v>3318</v>
+      </c>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>veteran_1</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>노장의 체력</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F108" s="12" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G108" s="12" t="inlineStr">
+        <is>
+          <t>veteran</t>
+        </is>
+      </c>
+      <c r="H108" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" s="12" t="inlineStr">
+        <is>
+          <t>round_time</t>
+        </is>
+      </c>
+      <c r="K108" s="12" t="n"/>
+      <c r="L108" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M108" s="12" t="n"/>
+      <c r="N108" s="12" t="n"/>
+      <c r="O108" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P108" s="12" t="n"/>
+      <c r="Q108" s="12" t="n"/>
+      <c r="R108" s="12" t="inlineStr">
+        <is>
+          <t>지속 시간 +3초 (15 → 18)</t>
+        </is>
+      </c>
+      <c r="S108" s="12" t="inlineStr">
+        <is>
+          <t>확인 필요: 원문은 "+2초 (15 → 18)", 화살표 기준 +3으로 넣음</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="n">
+        <v>3319</v>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>crit_3</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>치명 공격</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F109" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G109" s="12" t="inlineStr">
+        <is>
+          <t>crit</t>
+        </is>
+      </c>
+      <c r="H109" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I109" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" s="12" t="inlineStr">
+        <is>
+          <t>crit_chance</t>
+        </is>
+      </c>
+      <c r="K109" s="12" t="n"/>
+      <c r="L109" s="12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M109" s="12" t="n"/>
+      <c r="N109" s="12" t="n"/>
+      <c r="O109" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P109" s="12" t="n"/>
+      <c r="Q109" s="12" t="n"/>
+      <c r="R109" s="12" t="inlineStr">
+        <is>
+          <t>치명타 확률 6%</t>
+        </is>
+      </c>
+      <c r="S109" s="12" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="12" t="n">
+        <v>3320</v>
+      </c>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>sharpen_4</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>날 갈기</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G110" s="12" t="inlineStr">
+        <is>
+          <t>sharpen</t>
+        </is>
+      </c>
+      <c r="H110" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I110" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J110" s="12" t="inlineStr">
+        <is>
+          <t>harvester_damage</t>
+        </is>
+      </c>
+      <c r="K110" s="12" t="n"/>
+      <c r="L110" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M110" s="12" t="n"/>
+      <c r="N110" s="12" t="n"/>
+      <c r="O110" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P110" s="12" t="n"/>
+      <c r="Q110" s="12" t="n"/>
+      <c r="R110" s="12" t="inlineStr">
+        <is>
+          <t>공격력 +3 (7 → 10)</t>
+        </is>
+      </c>
+      <c r="S110" s="12" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="n">
+        <v>3321</v>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>boss_damage_2</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>보스 피해</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="F111" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G111" s="12" t="inlineStr">
+        <is>
+          <t>boss_damage</t>
+        </is>
+      </c>
+      <c r="H111" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I111" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" s="12" t="inlineStr">
+        <is>
+          <t>boss_damage</t>
+        </is>
+      </c>
+      <c r="K111" s="12" t="n"/>
+      <c r="L111" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M111" s="12" t="n"/>
+      <c r="N111" s="12" t="n"/>
+      <c r="O111" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P111" s="12" t="n"/>
+      <c r="Q111" s="12" t="n"/>
+      <c r="R111" s="12" t="inlineStr">
+        <is>
+          <t>보스 피해 +40%</t>
+        </is>
+      </c>
+      <c r="S111" s="12" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="12" t="n">
+        <v>3322</v>
+      </c>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>clone_1</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>분신술</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="F112" s="12" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G112" s="12" t="inlineStr">
+        <is>
+          <t>clone</t>
+        </is>
+      </c>
+      <c r="H112" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J112" s="12" t="inlineStr">
+        <is>
+          <t>clone_bar_duration</t>
+        </is>
+      </c>
+      <c r="K112" s="12" t="n"/>
+      <c r="L112" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M112" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N112" s="12" t="n"/>
+      <c r="O112" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P112" s="12" t="n"/>
+      <c r="Q112" s="12" t="n"/>
+      <c r="R112" s="12" t="inlineStr">
+        <is>
+          <t>10% 확률로 3초 분신 바</t>
+        </is>
+      </c>
+      <c r="S112" s="12" t="inlineStr">
+        <is>
+          <t>param = 발동 확률</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="n">
+        <v>3323</v>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>veteran_2</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>노장의 체력</t>
+        </is>
+      </c>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="F113" s="12" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G113" s="12" t="inlineStr">
+        <is>
+          <t>veteran</t>
+        </is>
+      </c>
+      <c r="H113" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I113" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J113" s="12" t="inlineStr">
+        <is>
+          <t>round_time</t>
+        </is>
+      </c>
+      <c r="K113" s="12" t="n"/>
+      <c r="L113" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M113" s="12" t="n"/>
+      <c r="N113" s="12" t="n"/>
+      <c r="O113" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P113" s="12" t="n"/>
+      <c r="Q113" s="12" t="n"/>
+      <c r="R113" s="12" t="inlineStr">
+        <is>
+          <t>지속 시간 +3초 (18 → 21)</t>
+        </is>
+      </c>
+      <c r="S113" s="12" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="12" t="n">
+        <v>3324</v>
+      </c>
+      <c r="B114" s="12" t="inlineStr">
+        <is>
+          <t>wind_path_3</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>바람의 길</t>
+        </is>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E114" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="F114" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G114" s="12" t="inlineStr">
+        <is>
+          <t>wind_path</t>
+        </is>
+      </c>
+      <c r="H114" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I114" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J114" s="12" t="inlineStr">
+        <is>
+          <t>harvester_speed</t>
+        </is>
+      </c>
+      <c r="K114" s="12" t="n"/>
+      <c r="L114" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M114" s="12" t="n"/>
+      <c r="N114" s="12" t="n"/>
+      <c r="O114" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P114" s="12" t="n"/>
+      <c r="Q114" s="12" t="n"/>
+      <c r="R114" s="12" t="inlineStr">
+        <is>
+          <t>수확기 속도 +30%</t>
+        </is>
+      </c>
+      <c r="S114" s="12" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="n">
+        <v>3325</v>
+      </c>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t>combo_3</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>콤보 계수</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F115" s="12" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G115" s="12" t="inlineStr">
+        <is>
+          <t>combo</t>
+        </is>
+      </c>
+      <c r="H115" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I115" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" s="12" t="inlineStr">
+        <is>
+          <t>combo_rate</t>
+        </is>
+      </c>
+      <c r="K115" s="12" t="n"/>
+      <c r="L115" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M115" s="12" t="n"/>
+      <c r="N115" s="12" t="n"/>
+      <c r="O115" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P115" s="12" t="n"/>
+      <c r="Q115" s="12" t="n"/>
+      <c r="R115" s="12" t="inlineStr">
+        <is>
+          <t>콤보 계수 +60%</t>
+        </is>
+      </c>
+      <c r="S115" s="12" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="12" t="n">
+        <v>3326</v>
+      </c>
+      <c r="B116" s="12" t="inlineStr">
+        <is>
+          <t>orbit_blade_2</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>회전 칼날</t>
+        </is>
+      </c>
+      <c r="D116" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F116" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G116" s="12" t="inlineStr">
+        <is>
+          <t>orbit_blade</t>
+        </is>
+      </c>
+      <c r="H116" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I116" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" s="12" t="inlineStr">
+        <is>
+          <t>orbit_harvester_count</t>
+        </is>
+      </c>
+      <c r="K116" s="12" t="n"/>
+      <c r="L116" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" s="12" t="n"/>
+      <c r="N116" s="12" t="n"/>
+      <c r="O116" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P116" s="12" t="n"/>
+      <c r="Q116" s="12" t="n"/>
+      <c r="R116" s="12" t="inlineStr">
+        <is>
+          <t>회전 꼬마 수확기 +1 (1 → 2)</t>
+        </is>
+      </c>
+      <c r="S116" s="12" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="n">
+        <v>3327</v>
+      </c>
+      <c r="B117" s="12" t="inlineStr">
+        <is>
+          <t>orbit_whirl_1</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>회전 회오리</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F117" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G117" s="12" t="inlineStr">
+        <is>
+          <t>orbit_whirl</t>
+        </is>
+      </c>
+      <c r="H117" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J117" s="12" t="inlineStr">
+        <is>
+          <t>orbit_harvester_damage</t>
+        </is>
+      </c>
+      <c r="K117" s="12" t="n"/>
+      <c r="L117" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M117" s="12" t="n"/>
+      <c r="N117" s="12" t="n"/>
+      <c r="O117" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P117" s="12" t="n"/>
+      <c r="Q117" s="12" t="n"/>
+      <c r="R117" s="12" t="inlineStr">
+        <is>
+          <t>회전 꼬마 수확기 공격력 5%</t>
+        </is>
+      </c>
+      <c r="S117" s="12" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="12" t="n">
+        <v>3328</v>
+      </c>
+      <c r="B118" s="12" t="inlineStr">
+        <is>
+          <t>boss_damage_3</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>보스 피해</t>
+        </is>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F118" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G118" s="12" t="inlineStr">
+        <is>
+          <t>boss_damage</t>
+        </is>
+      </c>
+      <c r="H118" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I118" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" s="12" t="inlineStr">
+        <is>
+          <t>boss_damage</t>
+        </is>
+      </c>
+      <c r="K118" s="12" t="n"/>
+      <c r="L118" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M118" s="12" t="n"/>
+      <c r="N118" s="12" t="n"/>
+      <c r="O118" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P118" s="12" t="n"/>
+      <c r="Q118" s="12" t="n"/>
+      <c r="R118" s="12" t="inlineStr">
+        <is>
+          <t>보스 피해 +60%</t>
+        </is>
+      </c>
+      <c r="S118" s="12" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="n">
+        <v>3329</v>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>clone_2</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>분신술</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F119" s="12" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G119" s="12" t="inlineStr">
+        <is>
+          <t>clone</t>
+        </is>
+      </c>
+      <c r="H119" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I119" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" s="12" t="inlineStr">
+        <is>
+          <t>clone_bar_duration</t>
+        </is>
+      </c>
+      <c r="K119" s="12" t="n"/>
+      <c r="L119" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M119" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N119" s="12" t="n"/>
+      <c r="O119" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P119" s="12" t="n"/>
+      <c r="Q119" s="12" t="n"/>
+      <c r="R119" s="12" t="inlineStr">
+        <is>
+          <t>10% 확률로 4초 분신 바</t>
+        </is>
+      </c>
+      <c r="S119" s="12" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="12" t="n">
+        <v>3330</v>
+      </c>
+      <c r="B120" s="12" t="inlineStr">
+        <is>
+          <t>combo_4</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>콤보 계수</t>
+        </is>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E120" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F120" s="12" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G120" s="12" t="inlineStr">
+        <is>
+          <t>combo</t>
+        </is>
+      </c>
+      <c r="H120" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I120" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" s="12" t="inlineStr">
+        <is>
+          <t>combo_rate</t>
+        </is>
+      </c>
+      <c r="K120" s="12" t="n"/>
+      <c r="L120" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M120" s="12" t="n"/>
+      <c r="N120" s="12" t="n"/>
+      <c r="O120" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P120" s="12" t="n"/>
+      <c r="Q120" s="12" t="n"/>
+      <c r="R120" s="12" t="inlineStr">
+        <is>
+          <t>콤보 계수 +80%</t>
+        </is>
+      </c>
+      <c r="S120" s="12" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="12" t="n">
+        <v>3331</v>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>crit_smash_1</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>치명 박살</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F121" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G121" s="12" t="inlineStr">
+        <is>
+          <t>crit_smash</t>
+        </is>
+      </c>
+      <c r="H121" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I121" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" s="12" t="inlineStr">
+        <is>
+          <t>crit_damage</t>
+        </is>
+      </c>
+      <c r="K121" s="12" t="n"/>
+      <c r="L121" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M121" s="12" t="n"/>
+      <c r="N121" s="12" t="n"/>
+      <c r="O121" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P121" s="12" t="n"/>
+      <c r="Q121" s="12" t="n"/>
+      <c r="R121" s="12" t="inlineStr">
+        <is>
+          <t>치명타 피해 100%</t>
+        </is>
+      </c>
+      <c r="S121" s="12" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="12" t="n">
+        <v>3332</v>
+      </c>
+      <c r="B122" s="12" t="inlineStr">
+        <is>
+          <t>crit_4</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>치명 공격</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="F122" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G122" s="12" t="inlineStr">
+        <is>
+          <t>crit</t>
+        </is>
+      </c>
+      <c r="H122" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I122" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J122" s="12" t="inlineStr">
+        <is>
+          <t>crit_chance</t>
+        </is>
+      </c>
+      <c r="K122" s="12" t="n"/>
+      <c r="L122" s="12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M122" s="12" t="n"/>
+      <c r="N122" s="12" t="n"/>
+      <c r="O122" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P122" s="12" t="n"/>
+      <c r="Q122" s="12" t="n"/>
+      <c r="R122" s="12" t="inlineStr">
+        <is>
+          <t>치명타 확률 8%</t>
+        </is>
+      </c>
+      <c r="S122" s="12" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="12" t="n">
+        <v>3333</v>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>veteran_3</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>노장의 체력</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="F123" s="12" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G123" s="12" t="inlineStr">
+        <is>
+          <t>veteran</t>
+        </is>
+      </c>
+      <c r="H123" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I123" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" s="12" t="inlineStr">
+        <is>
+          <t>round_time</t>
+        </is>
+      </c>
+      <c r="K123" s="12" t="n"/>
+      <c r="L123" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M123" s="12" t="n"/>
+      <c r="N123" s="12" t="n"/>
+      <c r="O123" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P123" s="12" t="n"/>
+      <c r="Q123" s="12" t="n"/>
+      <c r="R123" s="12" t="inlineStr">
+        <is>
+          <t>지속 시간 +3초 (21 → 24)</t>
+        </is>
+      </c>
+      <c r="S123" s="12" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="12" t="n">
+        <v>3334</v>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t>veteran_4</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>노장의 체력</t>
+        </is>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="F124" s="12" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G124" s="12" t="inlineStr">
+        <is>
+          <t>veteran</t>
+        </is>
+      </c>
+      <c r="H124" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I124" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J124" s="12" t="inlineStr">
+        <is>
+          <t>round_time</t>
+        </is>
+      </c>
+      <c r="K124" s="12" t="n"/>
+      <c r="L124" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M124" s="12" t="n"/>
+      <c r="N124" s="12" t="n"/>
+      <c r="O124" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P124" s="12" t="n"/>
+      <c r="Q124" s="12" t="n"/>
+      <c r="R124" s="12" t="inlineStr">
+        <is>
+          <t>지속 시간 +3초 (24 → 27)</t>
+        </is>
+      </c>
+      <c r="S124" s="12" t="inlineStr">
+        <is>
+          <t>원문은 Lv.3과 같은 레어도 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="12" t="n">
+        <v>3335</v>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>boss_damage_4</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>보스 피해</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F125" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G125" s="12" t="inlineStr">
+        <is>
+          <t>boss_damage</t>
+        </is>
+      </c>
+      <c r="H125" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I125" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" s="12" t="inlineStr">
+        <is>
+          <t>boss_damage</t>
+        </is>
+      </c>
+      <c r="K125" s="12" t="n"/>
+      <c r="L125" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M125" s="12" t="n"/>
+      <c r="N125" s="12" t="n"/>
+      <c r="O125" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P125" s="12" t="n"/>
+      <c r="Q125" s="12" t="n"/>
+      <c r="R125" s="12" t="inlineStr">
+        <is>
+          <t>보스 피해 +80%</t>
+        </is>
+      </c>
+      <c r="S125" s="12" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="12" t="n">
+        <v>3336</v>
+      </c>
+      <c r="B126" s="12" t="inlineStr">
+        <is>
+          <t>combo_5</t>
+        </is>
+      </c>
+      <c r="C126" s="12" t="inlineStr">
+        <is>
+          <t>콤보 계수</t>
+        </is>
+      </c>
+      <c r="D126" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E126" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F126" s="12" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G126" s="12" t="inlineStr">
+        <is>
+          <t>combo</t>
+        </is>
+      </c>
+      <c r="H126" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I126" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J126" s="12" t="inlineStr">
+        <is>
+          <t>combo_rate</t>
+        </is>
+      </c>
+      <c r="K126" s="12" t="n"/>
+      <c r="L126" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M126" s="12" t="n"/>
+      <c r="N126" s="12" t="n"/>
+      <c r="O126" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P126" s="12" t="n"/>
+      <c r="Q126" s="12" t="n"/>
+      <c r="R126" s="12" t="inlineStr">
+        <is>
+          <t>콤보 계수 +100%</t>
+        </is>
+      </c>
+      <c r="S126" s="12" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="12" t="n">
+        <v>3337</v>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>orbit_whirl_2</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>회전 회오리</t>
+        </is>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F127" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G127" s="12" t="inlineStr">
+        <is>
+          <t>orbit_whirl</t>
+        </is>
+      </c>
+      <c r="H127" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I127" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J127" s="12" t="inlineStr">
+        <is>
+          <t>orbit_harvester_damage</t>
+        </is>
+      </c>
+      <c r="K127" s="12" t="n"/>
+      <c r="L127" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M127" s="12" t="n"/>
+      <c r="N127" s="12" t="n"/>
+      <c r="O127" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P127" s="12" t="n"/>
+      <c r="Q127" s="12" t="n"/>
+      <c r="R127" s="12" t="inlineStr">
+        <is>
+          <t>회전 꼬마 수확기 공격력 10%</t>
+        </is>
+      </c>
+      <c r="S127" s="12" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="12" t="n">
+        <v>3338</v>
+      </c>
+      <c r="B128" s="12" t="inlineStr">
+        <is>
+          <t>sharpen_5</t>
+        </is>
+      </c>
+      <c r="C128" s="12" t="inlineStr">
+        <is>
+          <t>날 갈기</t>
+        </is>
+      </c>
+      <c r="D128" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E128" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F128" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G128" s="12" t="inlineStr">
+        <is>
+          <t>sharpen</t>
+        </is>
+      </c>
+      <c r="H128" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I128" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J128" s="12" t="inlineStr">
+        <is>
+          <t>harvester_damage</t>
+        </is>
+      </c>
+      <c r="K128" s="12" t="n"/>
+      <c r="L128" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M128" s="12" t="n"/>
+      <c r="N128" s="12" t="n"/>
+      <c r="O128" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P128" s="12" t="n"/>
+      <c r="Q128" s="12" t="n"/>
+      <c r="R128" s="12" t="inlineStr">
+        <is>
+          <t>공격력 +5 (10 → 15)</t>
+        </is>
+      </c>
+      <c r="S128" s="12" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="12" t="n">
+        <v>3339</v>
+      </c>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>artisan_tools_1</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>장인의 도구</t>
+        </is>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F129" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G129" s="12" t="inlineStr">
+        <is>
+          <t>artisan_tools</t>
+        </is>
+      </c>
+      <c r="H129" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J129" s="12" t="inlineStr">
+        <is>
+          <t>harvester_slot</t>
+        </is>
+      </c>
+      <c r="K129" s="12" t="n"/>
+      <c r="L129" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M129" s="12" t="n"/>
+      <c r="N129" s="12" t="n"/>
+      <c r="O129" s="12" t="inlineStr">
+        <is>
+          <t>Mycelite</t>
+        </is>
+      </c>
+      <c r="P129" s="12" t="n"/>
+      <c r="Q129" s="12" t="n"/>
+      <c r="R129" s="12" t="inlineStr">
+        <is>
+          <t>수확기 개수 +1 / Lv (최대 5개 장착)</t>
+        </is>
+      </c>
+      <c r="S129" s="12" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="12" t="n">
+        <v>3340</v>
+      </c>
+      <c r="B130" s="12" t="inlineStr">
+        <is>
+          <t>boss_damage_5</t>
+        </is>
+      </c>
+      <c r="C130" s="12" t="inlineStr">
+        <is>
+          <t>보스 피해</t>
+        </is>
+      </c>
+      <c r="D130" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E130" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F130" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G130" s="12" t="inlineStr">
+        <is>
+          <t>boss_damage</t>
+        </is>
+      </c>
+      <c r="H130" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I130" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J130" s="12" t="inlineStr">
+        <is>
+          <t>boss_damage</t>
+        </is>
+      </c>
+      <c r="K130" s="12" t="n"/>
+      <c r="L130" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M130" s="12" t="n"/>
+      <c r="N130" s="12" t="n"/>
+      <c r="O130" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P130" s="12" t="n"/>
+      <c r="Q130" s="12" t="n"/>
+      <c r="R130" s="12" t="inlineStr">
+        <is>
+          <t>보스 피해 +100%</t>
+        </is>
+      </c>
+      <c r="S130" s="12" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="12" t="n">
+        <v>3341</v>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>clone_3</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>분신술</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F131" s="12" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G131" s="12" t="inlineStr">
+        <is>
+          <t>clone</t>
+        </is>
+      </c>
+      <c r="H131" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I131" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J131" s="12" t="inlineStr">
+        <is>
+          <t>clone_bar_duration</t>
+        </is>
+      </c>
+      <c r="K131" s="12" t="n"/>
+      <c r="L131" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M131" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N131" s="12" t="n"/>
+      <c r="O131" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P131" s="12" t="n"/>
+      <c r="Q131" s="12" t="n"/>
+      <c r="R131" s="12" t="inlineStr">
+        <is>
+          <t>10% 확률로 5초 분신 바</t>
+        </is>
+      </c>
+      <c r="S131" s="12" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="12" t="n">
+        <v>3342</v>
+      </c>
+      <c r="B132" s="12" t="inlineStr">
+        <is>
+          <t>crit_5</t>
+        </is>
+      </c>
+      <c r="C132" s="12" t="inlineStr">
+        <is>
+          <t>치명 공격</t>
+        </is>
+      </c>
+      <c r="D132" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E132" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F132" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G132" s="12" t="inlineStr">
+        <is>
+          <t>crit</t>
+        </is>
+      </c>
+      <c r="H132" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I132" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" s="12" t="inlineStr">
+        <is>
+          <t>crit_chance</t>
+        </is>
+      </c>
+      <c r="K132" s="12" t="n"/>
+      <c r="L132" s="12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M132" s="12" t="n"/>
+      <c r="N132" s="12" t="n"/>
+      <c r="O132" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P132" s="12" t="n"/>
+      <c r="Q132" s="12" t="n"/>
+      <c r="R132" s="12" t="inlineStr">
+        <is>
+          <t>치명타 확률 10%</t>
+        </is>
+      </c>
+      <c r="S132" s="12" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="12" t="n">
+        <v>3343</v>
+      </c>
+      <c r="B133" s="12" t="inlineStr">
+        <is>
+          <t>mirror_clone_1</t>
+        </is>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>거울 분신술</t>
+        </is>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F133" s="12" t="inlineStr">
+        <is>
+          <t>SlideBar</t>
+        </is>
+      </c>
+      <c r="G133" s="12" t="inlineStr">
+        <is>
+          <t>mirror_clone</t>
+        </is>
+      </c>
+      <c r="H133" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I133" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J133" s="12" t="inlineStr">
+        <is>
+          <t>clone_bar_count</t>
+        </is>
+      </c>
+      <c r="K133" s="12" t="n"/>
+      <c r="L133" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M133" s="12" t="n"/>
+      <c r="N133" s="12" t="n"/>
+      <c r="O133" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P133" s="12" t="n"/>
+      <c r="Q133" s="12" t="n"/>
+      <c r="R133" s="12" t="inlineStr">
+        <is>
+          <t>분신 바 +1 (1 → 2)</t>
+        </is>
+      </c>
+      <c r="S133" s="12" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="12" t="n">
+        <v>3344</v>
+      </c>
+      <c r="B134" s="12" t="inlineStr">
+        <is>
+          <t>orbit_blade_3</t>
+        </is>
+      </c>
+      <c r="C134" s="12" t="inlineStr">
+        <is>
+          <t>회전 칼날</t>
+        </is>
+      </c>
+      <c r="D134" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E134" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F134" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G134" s="12" t="inlineStr">
+        <is>
+          <t>orbit_blade</t>
+        </is>
+      </c>
+      <c r="H134" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I134" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J134" s="12" t="inlineStr">
+        <is>
+          <t>orbit_harvester_count</t>
+        </is>
+      </c>
+      <c r="K134" s="12" t="n"/>
+      <c r="L134" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M134" s="12" t="n"/>
+      <c r="N134" s="12" t="n"/>
+      <c r="O134" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P134" s="12" t="n"/>
+      <c r="Q134" s="12" t="n"/>
+      <c r="R134" s="12" t="inlineStr">
+        <is>
+          <t>회전 꼬마 수확기 +1 (2 → 3)</t>
+        </is>
+      </c>
+      <c r="S134" s="12" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="12" t="n">
+        <v>3345</v>
+      </c>
+      <c r="B135" s="12" t="inlineStr">
+        <is>
+          <t>orbit_whirl_3</t>
+        </is>
+      </c>
+      <c r="C135" s="12" t="inlineStr">
+        <is>
+          <t>회전 회오리</t>
+        </is>
+      </c>
+      <c r="D135" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F135" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G135" s="12" t="inlineStr">
+        <is>
+          <t>orbit_whirl</t>
+        </is>
+      </c>
+      <c r="H135" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I135" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J135" s="12" t="inlineStr">
+        <is>
+          <t>orbit_harvester_damage</t>
+        </is>
+      </c>
+      <c r="K135" s="12" t="n"/>
+      <c r="L135" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M135" s="12" t="n"/>
+      <c r="N135" s="12" t="n"/>
+      <c r="O135" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P135" s="12" t="n"/>
+      <c r="Q135" s="12" t="n"/>
+      <c r="R135" s="12" t="inlineStr">
+        <is>
+          <t>회전 꼬마 수확기 공격력 15%</t>
+        </is>
+      </c>
+      <c r="S135" s="12" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="12" t="n">
+        <v>3346</v>
+      </c>
+      <c r="B136" s="12" t="inlineStr">
+        <is>
+          <t>crit_smash_2</t>
+        </is>
+      </c>
+      <c r="C136" s="12" t="inlineStr">
+        <is>
+          <t>치명 박살</t>
+        </is>
+      </c>
+      <c r="D136" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E136" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="F136" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G136" s="12" t="inlineStr">
+        <is>
+          <t>crit_smash</t>
+        </is>
+      </c>
+      <c r="H136" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I136" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J136" s="12" t="inlineStr">
+        <is>
+          <t>crit_damage</t>
+        </is>
+      </c>
+      <c r="K136" s="12" t="n"/>
+      <c r="L136" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M136" s="12" t="n"/>
+      <c r="N136" s="12" t="n"/>
+      <c r="O136" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P136" s="12" t="n"/>
+      <c r="Q136" s="12" t="n"/>
+      <c r="R136" s="12" t="inlineStr">
+        <is>
+          <t>치명타 피해 120%</t>
+        </is>
+      </c>
+      <c r="S136" s="12" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="12" t="n">
+        <v>3347</v>
+      </c>
+      <c r="B137" s="12" t="inlineStr">
+        <is>
+          <t>crit_smash_3</t>
+        </is>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>치명 박살</t>
+        </is>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F137" s="12" t="inlineStr">
+        <is>
+          <t>Harvester</t>
+        </is>
+      </c>
+      <c r="G137" s="12" t="inlineStr">
+        <is>
+          <t>crit_smash</t>
+        </is>
+      </c>
+      <c r="H137" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I137" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J137" s="12" t="inlineStr">
+        <is>
+          <t>crit_damage</t>
+        </is>
+      </c>
+      <c r="K137" s="12" t="n"/>
+      <c r="L137" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M137" s="12" t="n"/>
+      <c r="N137" s="12" t="n"/>
+      <c r="O137" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P137" s="12" t="n"/>
+      <c r="Q137" s="12" t="n"/>
+      <c r="R137" s="12" t="inlineStr">
+        <is>
+          <t>치명타 피해 150%</t>
+        </is>
+      </c>
+      <c r="S137" s="12" t="inlineStr">
+        <is>
+          <t>누적값 기준 차이 +30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="12" t="n">
+        <v>3348</v>
+      </c>
+      <c r="B138" s="12" t="inlineStr">
+        <is>
+          <t>veteran_5</t>
+        </is>
+      </c>
+      <c r="C138" s="12" t="inlineStr">
+        <is>
+          <t>노장의 체력</t>
+        </is>
+      </c>
+      <c r="D138" s="12" t="inlineStr">
+        <is>
+          <t>Toxic</t>
+        </is>
+      </c>
+      <c r="E138" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F138" s="12" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G138" s="12" t="inlineStr">
+        <is>
+          <t>veteran</t>
+        </is>
+      </c>
+      <c r="H138" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I138" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" s="12" t="inlineStr">
+        <is>
+          <t>round_time</t>
+        </is>
+      </c>
+      <c r="K138" s="12" t="n"/>
+      <c r="L138" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M138" s="12" t="n"/>
+      <c r="N138" s="12" t="n"/>
+      <c r="O138" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P138" s="12" t="n"/>
+      <c r="Q138" s="12" t="n"/>
+      <c r="R138" s="12" t="inlineStr">
+        <is>
+          <t>지속 시간 +3초 (27 → 30)</t>
+        </is>
+      </c>
+      <c r="S138" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/Data/Tables/Skill.xlsx
+++ b/Assets/Data/Tables/Skill.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S138"/>
+  <dimension ref="A1:U138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -521,8 +521,8 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
@@ -581,50 +581,60 @@
       </c>
       <c r="J1" s="5" t="inlineStr">
         <is>
+          <t>lane</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
           <t>ability</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>abilityBase</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>abilityValue</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>param</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>unlockPrice</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="P1" s="5" t="inlineStr">
+      <c r="R1" s="5" t="inlineStr">
         <is>
           <t>requires</t>
         </is>
       </c>
-      <c r="Q1" s="5" t="inlineStr">
+      <c r="S1" s="5" t="inlineStr">
         <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="T1" s="5" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="S1" s="6" t="inlineStr">
+      <c r="U1" s="6" t="inlineStr">
         <is>
           <t>#memo</t>
         </is>
@@ -678,50 +688,60 @@
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="P2" s="7" t="inlineStr">
+      <c r="R2" s="7" t="inlineStr">
         <is>
           <t>int[]</t>
         </is>
       </c>
-      <c r="Q2" s="7" t="inlineStr">
+      <c r="S2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="R2" s="7" t="inlineStr">
+      <c r="T2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="S2" s="7" t="n"/>
+      <c r="U2" s="7" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
@@ -771,50 +791,60 @@
       </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
+          <t>세로 줄 (0~4, 왼쪽부터). 시작 노드는 2</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>가로 줄 (0 = 맨 아래 시작 노드, 위로 갈수록 큼)</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
           <t>능력 종류 키 (효과 코드가 찾는 값)</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr">
         <is>
           <t>배웠으면 한 번 더하는 값</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="N3" s="8" t="inlineStr">
         <is>
           <t>레벨당 더하는 값 (비율은 0.1 = 10%)</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="O3" s="8" t="inlineStr">
         <is>
           <t>레벨과 무관한 고정 수치 (해석은 ability마다)</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="P3" s="8" t="inlineStr">
         <is>
           <t>해금 가격 (미정)</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="Q3" s="8" t="inlineStr">
         <is>
           <t>해금 재화 (Gold / Mycelite)</t>
         </is>
       </c>
-      <c r="P3" s="8" t="inlineStr">
+      <c r="R3" s="8" t="inlineStr">
         <is>
           <t>선행 스킬 index (쉼표 구분, 트리 연결 미정)</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="S3" s="8" t="inlineStr">
         <is>
           <t>아이콘 경로 (Resources 기준)</t>
         </is>
       </c>
-      <c r="R3" s="8" t="inlineStr">
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>인게임 설명</t>
         </is>
       </c>
-      <c r="S3" s="8" t="inlineStr">
+      <c r="U3" s="8" t="inlineStr">
         <is>
           <t>기획 메모 (게임에서 읽지 않음)</t>
         </is>
@@ -858,32 +888,38 @@
       <c r="I4" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="J4" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>start_attack_buff</t>
         </is>
       </c>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="9" t="n">
+      <c r="M4" s="9" t="n"/>
+      <c r="N4" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="O4" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="N4" s="9" t="n"/>
-      <c r="O4" s="9" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P4" s="9" t="n"/>
-      <c r="Q4" s="9" t="n"/>
-      <c r="R4" s="9" t="inlineStr">
+      <c r="Q4" s="9" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="R4" s="9" t="n"/>
+      <c r="S4" s="9" t="n"/>
+      <c r="T4" s="9" t="inlineStr">
         <is>
           <t>공격력 +2 (3초) 버프 / Lv</t>
         </is>
       </c>
-      <c r="S4" s="9" t="inlineStr">
+      <c r="U4" s="9" t="inlineStr">
         <is>
           <t>첫 레벨업은 골드, 이후 균사석 — currency 한 칸이라 가격 구조 정해지면 열 추가 필요. param = 버프 지속(초)</t>
         </is>
@@ -927,30 +963,40 @@
       <c r="I5" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="10" t="inlineStr">
+      <c r="J5" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
         <is>
           <t>score_rate</t>
         </is>
       </c>
-      <c r="K5" s="10" t="n"/>
-      <c r="L5" s="10" t="n">
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="M5" s="10" t="n"/>
-      <c r="N5" s="10" t="n"/>
-      <c r="O5" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O5" s="10" t="n"/>
       <c r="P5" s="10" t="n"/>
-      <c r="Q5" s="10" t="n"/>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R5" s="10" t="inlineStr">
         <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="n"/>
+      <c r="T5" s="10" t="inlineStr">
+        <is>
           <t>획득 점수 +10% / Lv</t>
         </is>
       </c>
-      <c r="S5" s="10" t="n"/>
+      <c r="U5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="n">
@@ -990,30 +1036,40 @@
       <c r="I6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="10" t="inlineStr">
+      <c r="J6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
         <is>
           <t>gold_conversion</t>
         </is>
       </c>
-      <c r="K6" s="10" t="n"/>
-      <c r="L6" s="10" t="n">
+      <c r="M6" s="10" t="n"/>
+      <c r="N6" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="M6" s="10" t="n"/>
-      <c r="N6" s="10" t="n"/>
-      <c r="O6" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O6" s="10" t="n"/>
       <c r="P6" s="10" t="n"/>
-      <c r="Q6" s="10" t="n"/>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R6" s="10" t="inlineStr">
         <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="n"/>
+      <c r="T6" s="10" t="inlineStr">
+        <is>
           <t>점수 골드 전환율 +10%</t>
         </is>
       </c>
-      <c r="S6" s="10" t="n"/>
+      <c r="U6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="n">
@@ -1053,30 +1109,40 @@
       <c r="I7" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="10" t="inlineStr">
+      <c r="J7" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
         <is>
           <t>colony_count</t>
         </is>
       </c>
-      <c r="K7" s="10" t="n"/>
-      <c r="L7" s="10" t="n">
-        <v>1</v>
-      </c>
       <c r="M7" s="10" t="n"/>
-      <c r="N7" s="10" t="n"/>
-      <c r="O7" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="10" t="n"/>
       <c r="P7" s="10" t="n"/>
-      <c r="Q7" s="10" t="n"/>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R7" s="10" t="inlineStr">
         <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="n"/>
+      <c r="T7" s="10" t="inlineStr">
+        <is>
           <t>군락지 수 +1 (3 → 4)</t>
         </is>
       </c>
-      <c r="S7" s="10" t="n"/>
+      <c r="U7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="n">
@@ -1116,30 +1182,40 @@
       <c r="I8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="10" t="inlineStr">
+      <c r="J8" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
         <is>
           <t>colony_single_mushroom</t>
         </is>
       </c>
-      <c r="K8" s="10" t="n"/>
-      <c r="L8" s="10" t="n">
-        <v>1</v>
-      </c>
       <c r="M8" s="10" t="n"/>
-      <c r="N8" s="10" t="n"/>
-      <c r="O8" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="10" t="n"/>
       <c r="P8" s="10" t="n"/>
-      <c r="Q8" s="10" t="n"/>
+      <c r="Q8" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R8" s="10" t="inlineStr">
         <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="n"/>
+      <c r="T8" s="10" t="inlineStr">
+        <is>
           <t>군락지 주변 단일 버섯 +1 (3 → 4)</t>
         </is>
       </c>
-      <c r="S8" s="10" t="n"/>
+      <c r="U8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="n">
@@ -1179,30 +1255,40 @@
       <c r="I9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="10" t="inlineStr">
+      <c r="J9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
         <is>
           <t>normal_yield</t>
         </is>
       </c>
-      <c r="K9" s="10" t="n"/>
-      <c r="L9" s="10" t="n">
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="M9" s="10" t="n"/>
-      <c r="N9" s="10" t="n"/>
-      <c r="O9" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O9" s="10" t="n"/>
       <c r="P9" s="10" t="n"/>
-      <c r="Q9" s="10" t="n"/>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R9" s="10" t="inlineStr">
         <is>
+          <t>3306</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="n"/>
+      <c r="T9" s="10" t="inlineStr">
+        <is>
           <t>일반 버섯 수확량 +5%</t>
         </is>
       </c>
-      <c r="S9" s="10" t="n"/>
+      <c r="U9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n">
@@ -1242,32 +1328,42 @@
       <c r="I10" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="10" t="inlineStr">
+      <c r="J10" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
         <is>
           <t>epic_spawn</t>
         </is>
       </c>
-      <c r="K10" s="10" t="n">
+      <c r="M10" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="L10" s="10" t="n">
+      <c r="N10" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="M10" s="10" t="n"/>
-      <c r="N10" s="10" t="n"/>
-      <c r="O10" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O10" s="10" t="n"/>
       <c r="P10" s="10" t="n"/>
-      <c r="Q10" s="10" t="n"/>
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R10" s="10" t="inlineStr">
         <is>
+          <t>3206</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="n"/>
+      <c r="T10" s="10" t="inlineStr">
+        <is>
           <t>에픽 버섯 스폰율 +10% / +15% / +20%</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="U10" s="10" t="inlineStr">
         <is>
           <t>Lv.1 10, Lv.2 15, Lv.3 20 → base 5% + 5%/Lv</t>
         </is>
@@ -1311,30 +1407,40 @@
       <c r="I11" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="10" t="inlineStr">
+      <c r="J11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
         <is>
           <t>normal_yield</t>
         </is>
       </c>
-      <c r="K11" s="10" t="n"/>
-      <c r="L11" s="10" t="n">
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="M11" s="10" t="n"/>
-      <c r="N11" s="10" t="n"/>
-      <c r="O11" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O11" s="10" t="n"/>
       <c r="P11" s="10" t="n"/>
-      <c r="Q11" s="10" t="n"/>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R11" s="10" t="inlineStr">
         <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="n"/>
+      <c r="T11" s="10" t="inlineStr">
+        <is>
           <t>일반 버섯 수확량 +10%</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="U11" s="10" t="inlineStr">
         <is>
           <t>원문 % = 누적값으로 보고 차이(+5%)만 더함</t>
         </is>
@@ -1378,30 +1484,40 @@
       <c r="I12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="10" t="inlineStr">
+      <c r="J12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
         <is>
           <t>gold_conversion</t>
         </is>
       </c>
-      <c r="K12" s="10" t="n"/>
-      <c r="L12" s="10" t="n">
+      <c r="M12" s="10" t="n"/>
+      <c r="N12" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="M12" s="10" t="n"/>
-      <c r="N12" s="10" t="n"/>
-      <c r="O12" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O12" s="10" t="n"/>
       <c r="P12" s="10" t="n"/>
-      <c r="Q12" s="10" t="n"/>
+      <c r="Q12" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R12" s="10" t="inlineStr">
         <is>
+          <t>3311</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="n"/>
+      <c r="T12" s="10" t="inlineStr">
+        <is>
           <t>점수 골드 전환율 +15%</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="U12" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -1445,30 +1561,40 @@
       <c r="I13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="10" t="inlineStr">
+      <c r="J13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
         <is>
           <t>colony_respawn</t>
         </is>
       </c>
-      <c r="K13" s="10" t="n"/>
-      <c r="L13" s="10" t="n">
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="10" t="n">
         <v>-1</v>
       </c>
-      <c r="M13" s="10" t="n"/>
-      <c r="N13" s="10" t="n"/>
-      <c r="O13" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O13" s="10" t="n"/>
       <c r="P13" s="10" t="n"/>
-      <c r="Q13" s="10" t="n"/>
+      <c r="Q13" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R13" s="10" t="inlineStr">
         <is>
+          <t>3210</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="n"/>
+      <c r="T13" s="10" t="inlineStr">
+        <is>
           <t>군락지 리스폰 −1초 (7 → 6)</t>
         </is>
       </c>
-      <c r="S13" s="10" t="n"/>
+      <c r="U13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n">
@@ -1508,30 +1634,40 @@
       <c r="I14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="10" t="inlineStr">
+      <c r="J14" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L14" s="10" t="inlineStr">
         <is>
           <t>gold_conversion</t>
         </is>
       </c>
-      <c r="K14" s="10" t="n"/>
-      <c r="L14" s="10" t="n">
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="M14" s="10" t="n"/>
-      <c r="N14" s="10" t="n"/>
-      <c r="O14" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O14" s="10" t="n"/>
       <c r="P14" s="10" t="n"/>
-      <c r="Q14" s="10" t="n"/>
+      <c r="Q14" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R14" s="10" t="inlineStr">
         <is>
+          <t>3108</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="n"/>
+      <c r="T14" s="10" t="inlineStr">
+        <is>
           <t>점수 골드 전환율 +20%</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="U14" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -1575,30 +1711,40 @@
       <c r="I15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="10" t="inlineStr">
+      <c r="J15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="L15" s="10" t="inlineStr">
         <is>
           <t>colony_respawn</t>
         </is>
       </c>
-      <c r="K15" s="10" t="n"/>
-      <c r="L15" s="10" t="n">
+      <c r="M15" s="10" t="n"/>
+      <c r="N15" s="10" t="n">
         <v>-1</v>
       </c>
-      <c r="M15" s="10" t="n"/>
-      <c r="N15" s="10" t="n"/>
-      <c r="O15" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O15" s="10" t="n"/>
       <c r="P15" s="10" t="n"/>
-      <c r="Q15" s="10" t="n"/>
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R15" s="10" t="inlineStr">
         <is>
+          <t>3110</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="n"/>
+      <c r="T15" s="10" t="inlineStr">
+        <is>
           <t>군락지 리스폰 −1초 (6 → 5)</t>
         </is>
       </c>
-      <c r="S15" s="10" t="n"/>
+      <c r="U15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
@@ -1638,30 +1784,40 @@
       <c r="I16" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J16" s="10" t="inlineStr">
+      <c r="J16" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="L16" s="10" t="inlineStr">
         <is>
           <t>triple_score_chance</t>
         </is>
       </c>
-      <c r="K16" s="10" t="n"/>
-      <c r="L16" s="10" t="n">
+      <c r="M16" s="10" t="n"/>
+      <c r="N16" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="M16" s="10" t="n"/>
-      <c r="N16" s="10" t="n"/>
-      <c r="O16" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O16" s="10" t="n"/>
       <c r="P16" s="10" t="n"/>
-      <c r="Q16" s="10" t="n"/>
+      <c r="Q16" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R16" s="10" t="inlineStr">
         <is>
+          <t>3215</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="n"/>
+      <c r="T16" s="10" t="inlineStr">
+        <is>
           <t>점수 3배 확률 +3%</t>
         </is>
       </c>
-      <c r="S16" s="10" t="n"/>
+      <c r="U16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n">
@@ -1701,30 +1857,40 @@
       <c r="I17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="10" t="inlineStr">
+      <c r="J17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
         <is>
           <t>colony_count</t>
         </is>
       </c>
-      <c r="K17" s="10" t="n"/>
-      <c r="L17" s="10" t="n">
-        <v>1</v>
-      </c>
       <c r="M17" s="10" t="n"/>
-      <c r="N17" s="10" t="n"/>
-      <c r="O17" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="10" t="n"/>
       <c r="P17" s="10" t="n"/>
-      <c r="Q17" s="10" t="n"/>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R17" s="10" t="inlineStr">
         <is>
+          <t>3111</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="n"/>
+      <c r="T17" s="10" t="inlineStr">
+        <is>
           <t>군락지 수 +1 (4 → 5)</t>
         </is>
       </c>
-      <c r="S17" s="10" t="n"/>
+      <c r="U17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
@@ -1764,30 +1930,40 @@
       <c r="I18" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="10" t="inlineStr">
+      <c r="J18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
         <is>
           <t>epic_yield</t>
         </is>
       </c>
-      <c r="K18" s="10" t="n"/>
-      <c r="L18" s="10" t="n">
+      <c r="M18" s="10" t="n"/>
+      <c r="N18" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="M18" s="10" t="n"/>
-      <c r="N18" s="10" t="n"/>
-      <c r="O18" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O18" s="10" t="n"/>
       <c r="P18" s="10" t="n"/>
-      <c r="Q18" s="10" t="n"/>
+      <c r="Q18" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R18" s="10" t="inlineStr">
         <is>
+          <t>3113</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="n"/>
+      <c r="T18" s="10" t="inlineStr">
+        <is>
           <t>에픽 버섯 수확량 +5%</t>
         </is>
       </c>
-      <c r="S18" s="10" t="n"/>
+      <c r="U18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n">
@@ -1827,30 +2003,40 @@
       <c r="I19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="10" t="inlineStr">
+      <c r="J19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="L19" s="10" t="inlineStr">
         <is>
           <t>colony_single_mushroom</t>
         </is>
       </c>
-      <c r="K19" s="10" t="n"/>
-      <c r="L19" s="10" t="n">
-        <v>1</v>
-      </c>
       <c r="M19" s="10" t="n"/>
-      <c r="N19" s="10" t="n"/>
-      <c r="O19" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="10" t="n"/>
       <c r="P19" s="10" t="n"/>
-      <c r="Q19" s="10" t="n"/>
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R19" s="10" t="inlineStr">
         <is>
+          <t>3319</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="n"/>
+      <c r="T19" s="10" t="inlineStr">
+        <is>
           <t>군락지 주변 단일 버섯 +1 (4 → 5)</t>
         </is>
       </c>
-      <c r="S19" s="10" t="n"/>
+      <c r="U19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
@@ -1890,30 +2076,40 @@
       <c r="I20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J20" s="10" t="inlineStr">
+      <c r="J20" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
         <is>
           <t>normal_yield</t>
         </is>
       </c>
-      <c r="K20" s="10" t="n"/>
-      <c r="L20" s="10" t="n">
+      <c r="M20" s="10" t="n"/>
+      <c r="N20" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="M20" s="10" t="n"/>
-      <c r="N20" s="10" t="n"/>
-      <c r="O20" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O20" s="10" t="n"/>
       <c r="P20" s="10" t="n"/>
-      <c r="Q20" s="10" t="n"/>
+      <c r="Q20" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R20" s="10" t="inlineStr">
         <is>
+          <t>3218</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="n"/>
+      <c r="T20" s="10" t="inlineStr">
+        <is>
           <t>일반 버섯 수확량 +15%</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="U20" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -1957,30 +2153,40 @@
       <c r="I21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J21" s="10" t="inlineStr">
+      <c r="J21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="L21" s="10" t="inlineStr">
         <is>
           <t>colony_count</t>
         </is>
       </c>
-      <c r="K21" s="10" t="n"/>
-      <c r="L21" s="10" t="n">
-        <v>1</v>
-      </c>
       <c r="M21" s="10" t="n"/>
-      <c r="N21" s="10" t="n"/>
-      <c r="O21" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="10" t="n"/>
       <c r="P21" s="10" t="n"/>
-      <c r="Q21" s="10" t="n"/>
+      <c r="Q21" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R21" s="10" t="inlineStr">
         <is>
+          <t>3114</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="n"/>
+      <c r="T21" s="10" t="inlineStr">
+        <is>
           <t>군락지 수 +1 (5 → 6)</t>
         </is>
       </c>
-      <c r="S21" s="10" t="n"/>
+      <c r="U21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
@@ -2020,30 +2226,40 @@
       <c r="I22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="10" t="inlineStr">
+      <c r="J22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="L22" s="10" t="inlineStr">
         <is>
           <t>triple_score_chance</t>
         </is>
       </c>
-      <c r="K22" s="10" t="n"/>
-      <c r="L22" s="10" t="n">
+      <c r="M22" s="10" t="n"/>
+      <c r="N22" s="10" t="n">
         <v>0.02</v>
       </c>
-      <c r="M22" s="10" t="n"/>
-      <c r="N22" s="10" t="n"/>
-      <c r="O22" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O22" s="10" t="n"/>
       <c r="P22" s="10" t="n"/>
-      <c r="Q22" s="10" t="n"/>
+      <c r="Q22" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R22" s="10" t="inlineStr">
         <is>
+          <t>3117</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="n"/>
+      <c r="T22" s="10" t="inlineStr">
+        <is>
           <t>점수 3배 확률 +5%</t>
         </is>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="U22" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -2087,30 +2303,40 @@
       <c r="I23" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J23" s="10" t="inlineStr">
+      <c r="J23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="L23" s="10" t="inlineStr">
         <is>
           <t>colony_single_mushroom</t>
         </is>
       </c>
-      <c r="K23" s="10" t="n"/>
-      <c r="L23" s="10" t="n">
-        <v>1</v>
-      </c>
       <c r="M23" s="10" t="n"/>
-      <c r="N23" s="10" t="n"/>
-      <c r="O23" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="10" t="n"/>
       <c r="P23" s="10" t="n"/>
-      <c r="Q23" s="10" t="n"/>
+      <c r="Q23" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R23" s="10" t="inlineStr">
         <is>
+          <t>3322</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="n"/>
+      <c r="T23" s="10" t="inlineStr">
+        <is>
           <t>군락지 주변 단일 버섯 +1 (5 → 6)</t>
         </is>
       </c>
-      <c r="S23" s="10" t="n"/>
+      <c r="U23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
@@ -2150,30 +2376,40 @@
       <c r="I24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J24" s="10" t="inlineStr">
+      <c r="J24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
         <is>
           <t>score_rate</t>
         </is>
       </c>
-      <c r="K24" s="10" t="n"/>
-      <c r="L24" s="10" t="n">
+      <c r="M24" s="10" t="n"/>
+      <c r="N24" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="M24" s="10" t="n"/>
-      <c r="N24" s="10" t="n"/>
-      <c r="O24" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O24" s="10" t="n"/>
       <c r="P24" s="10" t="n"/>
-      <c r="Q24" s="10" t="n"/>
+      <c r="Q24" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R24" s="10" t="inlineStr">
         <is>
+          <t>3118</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="n"/>
+      <c r="T24" s="10" t="inlineStr">
+        <is>
           <t>획득 점수 +40%</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="U24" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%</t>
         </is>
@@ -2217,30 +2453,40 @@
       <c r="I25" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J25" s="10" t="inlineStr">
+      <c r="J25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="L25" s="10" t="inlineStr">
         <is>
           <t>epic_spawn</t>
         </is>
       </c>
-      <c r="K25" s="10" t="n"/>
-      <c r="L25" s="10" t="n">
+      <c r="M25" s="10" t="n"/>
+      <c r="N25" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="M25" s="10" t="n"/>
-      <c r="N25" s="10" t="n"/>
-      <c r="O25" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O25" s="10" t="n"/>
       <c r="P25" s="10" t="n"/>
-      <c r="Q25" s="10" t="n"/>
+      <c r="Q25" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R25" s="10" t="inlineStr">
         <is>
+          <t>3119</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="n"/>
+      <c r="T25" s="10" t="inlineStr">
+        <is>
           <t>에픽 버섯 스폰율 +25%</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="U25" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -2284,30 +2530,40 @@
       <c r="I26" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="10" t="inlineStr">
+      <c r="J26" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L26" s="10" t="inlineStr">
         <is>
           <t>gold_conversion</t>
         </is>
       </c>
-      <c r="K26" s="10" t="n"/>
-      <c r="L26" s="10" t="n">
+      <c r="M26" s="10" t="n"/>
+      <c r="N26" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="M26" s="10" t="n"/>
-      <c r="N26" s="10" t="n"/>
-      <c r="O26" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O26" s="10" t="n"/>
       <c r="P26" s="10" t="n"/>
-      <c r="Q26" s="10" t="n"/>
+      <c r="Q26" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R26" s="10" t="inlineStr">
         <is>
+          <t>3120</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="n"/>
+      <c r="T26" s="10" t="inlineStr">
+        <is>
           <t>점수 골드 전환율 +30%</t>
         </is>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="U26" s="10" t="inlineStr">
         <is>
           <t>흥정 기술의 상위. 누적값 기준 차이 +10%</t>
         </is>
@@ -2351,30 +2607,40 @@
       <c r="I27" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="10" t="inlineStr">
+      <c r="J27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
         <is>
           <t>colony_count</t>
         </is>
       </c>
-      <c r="K27" s="10" t="n"/>
-      <c r="L27" s="10" t="n">
+      <c r="M27" s="10" t="n"/>
+      <c r="N27" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="M27" s="10" t="n"/>
-      <c r="N27" s="10" t="n"/>
-      <c r="O27" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O27" s="10" t="n"/>
       <c r="P27" s="10" t="n"/>
-      <c r="Q27" s="10" t="n"/>
+      <c r="Q27" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R27" s="10" t="inlineStr">
         <is>
+          <t>3121</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="n"/>
+      <c r="T27" s="10" t="inlineStr">
+        <is>
           <t>군락지 수 +2 (6 → 8)</t>
         </is>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="U27" s="10" t="inlineStr">
         <is>
           <t>넓은 시야의 상위</t>
         </is>
@@ -2418,30 +2684,40 @@
       <c r="I28" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="10" t="inlineStr">
+      <c r="J28" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="L28" s="10" t="inlineStr">
         <is>
           <t>epic_yield</t>
         </is>
       </c>
-      <c r="K28" s="10" t="n"/>
-      <c r="L28" s="10" t="n">
+      <c r="M28" s="10" t="n"/>
+      <c r="N28" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="M28" s="10" t="n"/>
-      <c r="N28" s="10" t="n"/>
-      <c r="O28" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O28" s="10" t="n"/>
       <c r="P28" s="10" t="n"/>
-      <c r="Q28" s="10" t="n"/>
+      <c r="Q28" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R28" s="10" t="inlineStr">
         <is>
+          <t>3122</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="n"/>
+      <c r="T28" s="10" t="inlineStr">
+        <is>
           <t>에픽 버섯 수확량 +10%</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="U28" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -2485,30 +2761,40 @@
       <c r="I29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="10" t="inlineStr">
+      <c r="J29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="L29" s="10" t="inlineStr">
         <is>
           <t>triple_score_chance</t>
         </is>
       </c>
-      <c r="K29" s="10" t="n"/>
-      <c r="L29" s="10" t="n">
+      <c r="M29" s="10" t="n"/>
+      <c r="N29" s="10" t="n">
         <v>0.02</v>
       </c>
-      <c r="M29" s="10" t="n"/>
-      <c r="N29" s="10" t="n"/>
-      <c r="O29" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O29" s="10" t="n"/>
       <c r="P29" s="10" t="n"/>
-      <c r="Q29" s="10" t="n"/>
+      <c r="Q29" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R29" s="10" t="inlineStr">
         <is>
+          <t>3123</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="n"/>
+      <c r="T29" s="10" t="inlineStr">
+        <is>
           <t>점수 3배 확률 +7%</t>
         </is>
       </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="U29" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -2552,30 +2838,40 @@
       <c r="I30" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="10" t="inlineStr">
+      <c r="J30" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="L30" s="10" t="inlineStr">
         <is>
           <t>colony_count</t>
         </is>
       </c>
-      <c r="K30" s="10" t="n"/>
-      <c r="L30" s="10" t="n">
+      <c r="M30" s="10" t="n"/>
+      <c r="N30" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="M30" s="10" t="n"/>
-      <c r="N30" s="10" t="n"/>
-      <c r="O30" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O30" s="10" t="n"/>
       <c r="P30" s="10" t="n"/>
-      <c r="Q30" s="10" t="n"/>
+      <c r="Q30" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R30" s="10" t="inlineStr">
         <is>
+          <t>3124</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="n"/>
+      <c r="T30" s="10" t="inlineStr">
+        <is>
           <t>군락지 수 +2 (8 → 10)</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="U30" s="10" t="inlineStr">
         <is>
           <t>넓은 시야의 상위</t>
         </is>
@@ -2619,30 +2915,40 @@
       <c r="I31" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J31" s="10" t="inlineStr">
+      <c r="J31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="L31" s="10" t="inlineStr">
         <is>
           <t>unique_spawn</t>
         </is>
       </c>
-      <c r="K31" s="10" t="n"/>
-      <c r="L31" s="10" t="n">
+      <c r="M31" s="10" t="n"/>
+      <c r="N31" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="M31" s="10" t="n"/>
-      <c r="N31" s="10" t="n"/>
-      <c r="O31" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O31" s="10" t="n"/>
       <c r="P31" s="10" t="n"/>
-      <c r="Q31" s="10" t="n"/>
+      <c r="Q31" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R31" s="10" t="inlineStr">
         <is>
+          <t>3126</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="n"/>
+      <c r="T31" s="10" t="inlineStr">
+        <is>
           <t>유니크 버섯 스폰율 +5%</t>
         </is>
       </c>
-      <c r="S31" s="10" t="n"/>
+      <c r="U31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
@@ -2682,30 +2988,40 @@
       <c r="I32" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J32" s="10" t="inlineStr">
+      <c r="J32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="L32" s="10" t="inlineStr">
         <is>
           <t>epic_yield</t>
         </is>
       </c>
-      <c r="K32" s="10" t="n"/>
-      <c r="L32" s="10" t="n">
+      <c r="M32" s="10" t="n"/>
+      <c r="N32" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="M32" s="10" t="n"/>
-      <c r="N32" s="10" t="n"/>
-      <c r="O32" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O32" s="10" t="n"/>
       <c r="P32" s="10" t="n"/>
-      <c r="Q32" s="10" t="n"/>
+      <c r="Q32" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R32" s="10" t="inlineStr">
         <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="n"/>
+      <c r="T32" s="10" t="inlineStr">
+        <is>
           <t>에픽 버섯 수확량 +15%</t>
         </is>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="U32" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -2749,30 +3065,40 @@
       <c r="I33" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="10" t="inlineStr">
+      <c r="J33" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K33" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="L33" s="10" t="inlineStr">
         <is>
           <t>unique_yield</t>
         </is>
       </c>
-      <c r="K33" s="10" t="n"/>
-      <c r="L33" s="10" t="n">
+      <c r="M33" s="10" t="n"/>
+      <c r="N33" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="M33" s="10" t="n"/>
-      <c r="N33" s="10" t="n"/>
-      <c r="O33" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O33" s="10" t="n"/>
       <c r="P33" s="10" t="n"/>
-      <c r="Q33" s="10" t="n"/>
+      <c r="Q33" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R33" s="10" t="inlineStr">
         <is>
+          <t>3228</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="n"/>
+      <c r="T33" s="10" t="inlineStr">
+        <is>
           <t>유니크 버섯 수확량 +5%</t>
         </is>
       </c>
-      <c r="S33" s="10" t="n"/>
+      <c r="U33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
@@ -2812,30 +3138,40 @@
       <c r="I34" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J34" s="10" t="inlineStr">
+      <c r="J34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="L34" s="10" t="inlineStr">
         <is>
           <t>colony_respawn</t>
         </is>
       </c>
-      <c r="K34" s="10" t="n"/>
-      <c r="L34" s="10" t="n">
+      <c r="M34" s="10" t="n"/>
+      <c r="N34" s="10" t="n">
         <v>-2</v>
       </c>
-      <c r="M34" s="10" t="n"/>
-      <c r="N34" s="10" t="n"/>
-      <c r="O34" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O34" s="10" t="n"/>
       <c r="P34" s="10" t="n"/>
-      <c r="Q34" s="10" t="n"/>
+      <c r="Q34" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R34" s="10" t="inlineStr">
         <is>
+          <t>3127</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="n"/>
+      <c r="T34" s="10" t="inlineStr">
+        <is>
           <t>군락지 리스폰 −2초 (5 → 3)</t>
         </is>
       </c>
-      <c r="S34" s="10" t="n"/>
+      <c r="U34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="n">
@@ -2875,30 +3211,40 @@
       <c r="I35" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J35" s="10" t="inlineStr">
+      <c r="J35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="L35" s="10" t="inlineStr">
         <is>
           <t>golden_spawn</t>
         </is>
       </c>
-      <c r="K35" s="10" t="n"/>
-      <c r="L35" s="10" t="n">
+      <c r="M35" s="10" t="n"/>
+      <c r="N35" s="10" t="n">
         <v>0.01</v>
       </c>
-      <c r="M35" s="10" t="n"/>
-      <c r="N35" s="10" t="n"/>
-      <c r="O35" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O35" s="10" t="n"/>
       <c r="P35" s="10" t="n"/>
-      <c r="Q35" s="10" t="n"/>
+      <c r="Q35" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R35" s="10" t="inlineStr">
         <is>
+          <t>3128</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="n"/>
+      <c r="T35" s="10" t="inlineStr">
+        <is>
           <t>황금 변종 스폰율 +1%</t>
         </is>
       </c>
-      <c r="S35" s="10" t="n"/>
+      <c r="U35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
@@ -2938,30 +3284,40 @@
       <c r="I36" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J36" s="10" t="inlineStr">
+      <c r="J36" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="L36" s="10" t="inlineStr">
         <is>
           <t>unique_yield</t>
         </is>
       </c>
-      <c r="K36" s="10" t="n"/>
-      <c r="L36" s="10" t="n">
+      <c r="M36" s="10" t="n"/>
+      <c r="N36" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="M36" s="10" t="n"/>
-      <c r="N36" s="10" t="n"/>
-      <c r="O36" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O36" s="10" t="n"/>
       <c r="P36" s="10" t="n"/>
-      <c r="Q36" s="10" t="n"/>
+      <c r="Q36" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R36" s="10" t="inlineStr">
         <is>
+          <t>3130</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="n"/>
+      <c r="T36" s="10" t="inlineStr">
+        <is>
           <t>유니크 버섯 수확량 +10%</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="U36" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -3005,30 +3361,40 @@
       <c r="I37" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J37" s="10" t="inlineStr">
+      <c r="J37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="L37" s="10" t="inlineStr">
         <is>
           <t>legendary_yield</t>
         </is>
       </c>
-      <c r="K37" s="10" t="n"/>
-      <c r="L37" s="10" t="n">
+      <c r="M37" s="10" t="n"/>
+      <c r="N37" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="M37" s="10" t="n"/>
-      <c r="N37" s="10" t="n"/>
-      <c r="O37" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O37" s="10" t="n"/>
       <c r="P37" s="10" t="n"/>
-      <c r="Q37" s="10" t="n"/>
+      <c r="Q37" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R37" s="10" t="inlineStr">
         <is>
+          <t>3132</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="n"/>
+      <c r="T37" s="10" t="inlineStr">
+        <is>
           <t>보스 전용 레전더리 버섯 수확량 +3%</t>
         </is>
       </c>
-      <c r="S37" s="10" t="n"/>
+      <c r="U37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
@@ -3068,30 +3434,40 @@
       <c r="I38" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J38" s="10" t="inlineStr">
+      <c r="J38" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K38" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
         <is>
           <t>unique_spawn</t>
         </is>
       </c>
-      <c r="K38" s="10" t="n"/>
-      <c r="L38" s="10" t="n">
+      <c r="M38" s="10" t="n"/>
+      <c r="N38" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="M38" s="10" t="n"/>
-      <c r="N38" s="10" t="n"/>
-      <c r="O38" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O38" s="10" t="n"/>
       <c r="P38" s="10" t="n"/>
-      <c r="Q38" s="10" t="n"/>
+      <c r="Q38" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R38" s="10" t="inlineStr">
         <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="n"/>
+      <c r="T38" s="10" t="inlineStr">
+        <is>
           <t>유니크 버섯 스폰율 +10%</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="U38" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -3135,30 +3511,40 @@
       <c r="I39" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="10" t="inlineStr">
+      <c r="J39" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
         <is>
           <t>unique_spawn</t>
         </is>
       </c>
-      <c r="K39" s="10" t="n"/>
-      <c r="L39" s="10" t="n">
+      <c r="M39" s="10" t="n"/>
+      <c r="N39" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="M39" s="10" t="n"/>
-      <c r="N39" s="10" t="n"/>
-      <c r="O39" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O39" s="10" t="n"/>
       <c r="P39" s="10" t="n"/>
-      <c r="Q39" s="10" t="n"/>
+      <c r="Q39" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R39" s="10" t="inlineStr">
         <is>
+          <t>3134</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="n"/>
+      <c r="T39" s="10" t="inlineStr">
+        <is>
           <t>유니크 버섯 스폰율 +15%</t>
         </is>
       </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="U39" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%. 원문은 Lv.2와 같은 레어도 15</t>
         </is>
@@ -3202,30 +3588,40 @@
       <c r="I40" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="10" t="inlineStr">
+      <c r="J40" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K40" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
         <is>
           <t>golden_spawn</t>
         </is>
       </c>
-      <c r="K40" s="10" t="n"/>
-      <c r="L40" s="10" t="n">
+      <c r="M40" s="10" t="n"/>
+      <c r="N40" s="10" t="n">
         <v>0.02</v>
       </c>
-      <c r="M40" s="10" t="n"/>
-      <c r="N40" s="10" t="n"/>
-      <c r="O40" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O40" s="10" t="n"/>
       <c r="P40" s="10" t="n"/>
-      <c r="Q40" s="10" t="n"/>
+      <c r="Q40" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R40" s="10" t="inlineStr">
         <is>
+          <t>3135</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="n"/>
+      <c r="T40" s="10" t="inlineStr">
+        <is>
           <t>황금 변종 스폰율 +3%</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="U40" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -3269,30 +3665,40 @@
       <c r="I41" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J41" s="10" t="inlineStr">
+      <c r="J41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
         <is>
           <t>legendary_yield</t>
         </is>
       </c>
-      <c r="K41" s="10" t="n"/>
-      <c r="L41" s="10" t="n">
+      <c r="M41" s="10" t="n"/>
+      <c r="N41" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="M41" s="10" t="n"/>
-      <c r="N41" s="10" t="n"/>
-      <c r="O41" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O41" s="10" t="n"/>
       <c r="P41" s="10" t="n"/>
-      <c r="Q41" s="10" t="n"/>
+      <c r="Q41" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R41" s="10" t="inlineStr">
         <is>
+          <t>3340</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="n"/>
+      <c r="T41" s="10" t="inlineStr">
+        <is>
           <t>보스 전용 레전더리 버섯 수확량 +6%</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="U41" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +3%</t>
         </is>
@@ -3336,30 +3742,40 @@
       <c r="I42" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="10" t="inlineStr">
+      <c r="J42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
         <is>
           <t>gold_conversion</t>
         </is>
       </c>
-      <c r="K42" s="10" t="n"/>
-      <c r="L42" s="10" t="n">
+      <c r="M42" s="10" t="n"/>
+      <c r="N42" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="M42" s="10" t="n"/>
-      <c r="N42" s="10" t="n"/>
-      <c r="O42" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O42" s="10" t="n"/>
       <c r="P42" s="10" t="n"/>
-      <c r="Q42" s="10" t="n"/>
+      <c r="Q42" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R42" s="10" t="inlineStr">
         <is>
+          <t>3137</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="n"/>
+      <c r="T42" s="10" t="inlineStr">
+        <is>
           <t>점수 골드 전환율 +40%</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
+      <c r="U42" s="10" t="inlineStr">
         <is>
           <t>흥정 기술의 상위. 누적값 기준 차이 +10%</t>
         </is>
@@ -3403,30 +3819,40 @@
       <c r="I43" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="10" t="inlineStr">
+      <c r="J43" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K43" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="L43" s="10" t="inlineStr">
         <is>
           <t>colony_count</t>
         </is>
       </c>
-      <c r="K43" s="10" t="n"/>
-      <c r="L43" s="10" t="n">
+      <c r="M43" s="10" t="n"/>
+      <c r="N43" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="M43" s="10" t="n"/>
-      <c r="N43" s="10" t="n"/>
-      <c r="O43" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O43" s="10" t="n"/>
       <c r="P43" s="10" t="n"/>
-      <c r="Q43" s="10" t="n"/>
+      <c r="Q43" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R43" s="10" t="inlineStr">
         <is>
+          <t>3136</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="n"/>
+      <c r="T43" s="10" t="inlineStr">
+        <is>
           <t>군락지 수 +2 (10 → 12)</t>
         </is>
       </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="U43" s="10" t="inlineStr">
         <is>
           <t>넓은 시야의 상위</t>
         </is>
@@ -3470,30 +3896,40 @@
       <c r="I44" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J44" s="10" t="inlineStr">
+      <c r="J44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
         <is>
           <t>unique_yield</t>
         </is>
       </c>
-      <c r="K44" s="10" t="n"/>
-      <c r="L44" s="10" t="n">
+      <c r="M44" s="10" t="n"/>
+      <c r="N44" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="M44" s="10" t="n"/>
-      <c r="N44" s="10" t="n"/>
-      <c r="O44" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O44" s="10" t="n"/>
       <c r="P44" s="10" t="n"/>
-      <c r="Q44" s="10" t="n"/>
+      <c r="Q44" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R44" s="10" t="inlineStr">
         <is>
+          <t>3138</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="n"/>
+      <c r="T44" s="10" t="inlineStr">
+        <is>
           <t>유니크 버섯 수확량 +15%</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
+      <c r="U44" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -3537,30 +3973,40 @@
       <c r="I45" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J45" s="10" t="inlineStr">
+      <c r="J45" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="L45" s="10" t="inlineStr">
         <is>
           <t>score_rate</t>
         </is>
       </c>
-      <c r="K45" s="10" t="n"/>
-      <c r="L45" s="10" t="n">
+      <c r="M45" s="10" t="n"/>
+      <c r="N45" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="M45" s="10" t="n"/>
-      <c r="N45" s="10" t="n"/>
-      <c r="O45" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O45" s="10" t="n"/>
       <c r="P45" s="10" t="n"/>
-      <c r="Q45" s="10" t="n"/>
+      <c r="Q45" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R45" s="10" t="inlineStr">
         <is>
+          <t>3140</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="n"/>
+      <c r="T45" s="10" t="inlineStr">
+        <is>
           <t>획득 점수 +50%</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="U45" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%</t>
         </is>
@@ -3604,30 +4050,40 @@
       <c r="I46" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J46" s="10" t="inlineStr">
+      <c r="J46" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K46" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="L46" s="10" t="inlineStr">
         <is>
           <t>golden_spawn</t>
         </is>
       </c>
-      <c r="K46" s="10" t="n"/>
-      <c r="L46" s="10" t="n">
+      <c r="M46" s="10" t="n"/>
+      <c r="N46" s="10" t="n">
         <v>0.02</v>
       </c>
-      <c r="M46" s="10" t="n"/>
-      <c r="N46" s="10" t="n"/>
-      <c r="O46" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O46" s="10" t="n"/>
       <c r="P46" s="10" t="n"/>
-      <c r="Q46" s="10" t="n"/>
+      <c r="Q46" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R46" s="10" t="inlineStr">
         <is>
+          <t>3238</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="n"/>
+      <c r="T46" s="10" t="inlineStr">
+        <is>
           <t>황금 변종 스폰율 +5%</t>
         </is>
       </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="U46" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -3671,32 +4127,42 @@
       <c r="I47" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J47" s="10" t="inlineStr">
+      <c r="J47" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K47" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="L47" s="10" t="inlineStr">
         <is>
           <t>final_rush_bonus</t>
         </is>
       </c>
-      <c r="K47" s="10" t="n"/>
-      <c r="L47" s="10" t="n">
+      <c r="M47" s="10" t="n"/>
+      <c r="N47" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="M47" s="10" t="n">
+      <c r="O47" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N47" s="10" t="n"/>
-      <c r="O47" s="10" t="inlineStr">
+      <c r="P47" s="10" t="n"/>
+      <c r="Q47" s="10" t="inlineStr">
         <is>
           <t>Mycelite</t>
         </is>
       </c>
-      <c r="P47" s="10" t="n"/>
-      <c r="Q47" s="10" t="n"/>
       <c r="R47" s="10" t="inlineStr">
         <is>
+          <t>3239</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="n"/>
+      <c r="T47" s="10" t="inlineStr">
+        <is>
           <t>라운드 마지막 5초 점수·수확량 +10% / Lv</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="U47" s="10" t="inlineStr">
         <is>
           <t>param = 마지막 몇 초</t>
         </is>
@@ -3740,30 +4206,40 @@
       <c r="I48" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J48" s="10" t="inlineStr">
+      <c r="J48" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K48" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="L48" s="10" t="inlineStr">
         <is>
           <t>colony_count</t>
         </is>
       </c>
-      <c r="K48" s="10" t="n"/>
-      <c r="L48" s="10" t="n">
+      <c r="M48" s="10" t="n"/>
+      <c r="N48" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="M48" s="10" t="n"/>
-      <c r="N48" s="10" t="n"/>
-      <c r="O48" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O48" s="10" t="n"/>
       <c r="P48" s="10" t="n"/>
-      <c r="Q48" s="10" t="n"/>
+      <c r="Q48" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R48" s="10" t="inlineStr">
         <is>
+          <t>3142</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="n"/>
+      <c r="T48" s="10" t="inlineStr">
+        <is>
           <t>군락지 수 +3 (12 → 15)</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
+      <c r="U48" s="10" t="inlineStr">
         <is>
           <t>넓은 시야의 상위</t>
         </is>
@@ -3807,30 +4283,40 @@
       <c r="I49" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J49" s="10" t="inlineStr">
+      <c r="J49" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="L49" s="10" t="inlineStr">
         <is>
           <t>legendary_yield</t>
         </is>
       </c>
-      <c r="K49" s="10" t="n"/>
-      <c r="L49" s="10" t="n">
+      <c r="M49" s="10" t="n"/>
+      <c r="N49" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="M49" s="10" t="n"/>
-      <c r="N49" s="10" t="n"/>
-      <c r="O49" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O49" s="10" t="n"/>
       <c r="P49" s="10" t="n"/>
-      <c r="Q49" s="10" t="n"/>
+      <c r="Q49" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R49" s="10" t="inlineStr">
         <is>
+          <t>3141</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="n"/>
+      <c r="T49" s="10" t="inlineStr">
+        <is>
           <t>보스 전용 레전더리 버섯 수확량 +9%</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="U49" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +3%</t>
         </is>
@@ -3874,30 +4360,40 @@
       <c r="I50" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J50" s="10" t="inlineStr">
+      <c r="J50" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K50" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="L50" s="10" t="inlineStr">
         <is>
           <t>gold_conversion</t>
         </is>
       </c>
-      <c r="K50" s="10" t="n"/>
-      <c r="L50" s="10" t="n">
+      <c r="M50" s="10" t="n"/>
+      <c r="N50" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="M50" s="10" t="n"/>
-      <c r="N50" s="10" t="n"/>
-      <c r="O50" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O50" s="10" t="n"/>
       <c r="P50" s="10" t="n"/>
-      <c r="Q50" s="10" t="n"/>
+      <c r="Q50" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R50" s="10" t="inlineStr">
         <is>
+          <t>3143</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="n"/>
+      <c r="T50" s="10" t="inlineStr">
+        <is>
           <t>점수 골드 전환율 +50%</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="U50" s="10" t="inlineStr">
         <is>
           <t>흥정 기술의 상위. 누적값 기준 차이 +10%</t>
         </is>
@@ -3941,30 +4437,40 @@
       <c r="I51" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J51" s="11" t="inlineStr">
+      <c r="J51" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K51" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" s="11" t="inlineStr">
         <is>
           <t>buff_haste_duration</t>
         </is>
       </c>
-      <c r="K51" s="11" t="n"/>
-      <c r="L51" s="11" t="n">
+      <c r="M51" s="11" t="n"/>
+      <c r="N51" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="M51" s="11" t="n"/>
-      <c r="N51" s="11" t="n"/>
-      <c r="O51" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O51" s="11" t="n"/>
       <c r="P51" s="11" t="n"/>
-      <c r="Q51" s="11" t="n"/>
+      <c r="Q51" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R51" s="11" t="inlineStr">
         <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="S51" s="11" t="n"/>
+      <c r="T51" s="11" t="inlineStr">
+        <is>
           <t>가속(3초) 버프</t>
         </is>
       </c>
-      <c r="S51" s="11" t="inlineStr">
+      <c r="U51" s="11" t="inlineStr">
         <is>
           <t>value = 지속(초), 다음 노드는 +1초씩</t>
         </is>
@@ -4008,30 +4514,40 @@
       <c r="I52" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J52" s="11" t="inlineStr">
+      <c r="J52" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K52" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" s="11" t="inlineStr">
         <is>
           <t>buff_pierce_duration</t>
         </is>
       </c>
-      <c r="K52" s="11" t="n"/>
-      <c r="L52" s="11" t="n">
+      <c r="M52" s="11" t="n"/>
+      <c r="N52" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="M52" s="11" t="n"/>
-      <c r="N52" s="11" t="n"/>
-      <c r="O52" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O52" s="11" t="n"/>
       <c r="P52" s="11" t="n"/>
-      <c r="Q52" s="11" t="n"/>
+      <c r="Q52" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R52" s="11" t="inlineStr">
         <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="S52" s="11" t="n"/>
+      <c r="T52" s="11" t="inlineStr">
+        <is>
           <t>관통(3초) 버프</t>
         </is>
       </c>
-      <c r="S52" s="11" t="n"/>
+      <c r="U52" s="11" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="n">
@@ -4071,30 +4587,40 @@
       <c r="I53" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J53" s="11" t="inlineStr">
+      <c r="J53" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K53" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L53" s="11" t="inlineStr">
         <is>
           <t>buff_haste_duration</t>
         </is>
       </c>
-      <c r="K53" s="11" t="n"/>
-      <c r="L53" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="M53" s="11" t="n"/>
-      <c r="N53" s="11" t="n"/>
-      <c r="O53" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N53" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" s="11" t="n"/>
       <c r="P53" s="11" t="n"/>
-      <c r="Q53" s="11" t="n"/>
+      <c r="Q53" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R53" s="11" t="inlineStr">
         <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="S53" s="11" t="n"/>
+      <c r="T53" s="11" t="inlineStr">
+        <is>
           <t>가속(4초) 버프</t>
         </is>
       </c>
-      <c r="S53" s="11" t="n"/>
+      <c r="U53" s="11" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="n">
@@ -4134,30 +4660,40 @@
       <c r="I54" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J54" s="11" t="inlineStr">
+      <c r="J54" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K54" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L54" s="11" t="inlineStr">
         <is>
           <t>field_restoration</t>
         </is>
       </c>
-      <c r="K54" s="11" t="n"/>
-      <c r="L54" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="M54" s="11" t="n"/>
-      <c r="N54" s="11" t="n"/>
-      <c r="O54" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N54" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" s="11" t="n"/>
       <c r="P54" s="11" t="n"/>
-      <c r="Q54" s="11" t="n"/>
+      <c r="Q54" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R54" s="11" t="inlineStr">
         <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="S54" s="11" t="n"/>
+      <c r="T54" s="11" t="inlineStr">
+        <is>
           <t>필드에 그루터기 추가</t>
         </is>
       </c>
-      <c r="S54" s="11" t="inlineStr">
+      <c r="U54" s="11" t="inlineStr">
         <is>
           <t>value = 단계 (1 그루터기 / 2 꽃밭 / 3 도토리 점등)</t>
         </is>
@@ -4201,32 +4737,42 @@
       <c r="I55" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J55" s="11" t="inlineStr">
+      <c r="J55" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K55" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L55" s="11" t="inlineStr">
         <is>
           <t>poison_strike_chance</t>
         </is>
       </c>
-      <c r="K55" s="11" t="n"/>
-      <c r="L55" s="11" t="n">
+      <c r="M55" s="11" t="n"/>
+      <c r="N55" s="11" t="n">
         <v>0.03</v>
       </c>
-      <c r="M55" s="11" t="n">
+      <c r="O55" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="N55" s="11" t="n"/>
-      <c r="O55" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P55" s="11" t="n"/>
-      <c r="Q55" s="11" t="n"/>
+      <c r="Q55" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R55" s="11" t="inlineStr">
         <is>
+          <t>3203</t>
+        </is>
+      </c>
+      <c r="S55" s="11" t="n"/>
+      <c r="T55" s="11" t="inlineStr">
+        <is>
           <t>단일 버섯 획득 시 3% 확률로 다음 타격 피해 +200%</t>
         </is>
       </c>
-      <c r="S55" s="11" t="inlineStr">
+      <c r="U55" s="11" t="inlineStr">
         <is>
           <t>param = 피해 증가 (2 = +200%)</t>
         </is>
@@ -4270,32 +4816,42 @@
       <c r="I56" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J56" s="11" t="inlineStr">
+      <c r="J56" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K56" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L56" s="11" t="inlineStr">
         <is>
           <t>buff_fever_duration</t>
         </is>
       </c>
-      <c r="K56" s="11" t="n"/>
-      <c r="L56" s="11" t="n">
+      <c r="M56" s="11" t="n"/>
+      <c r="N56" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="M56" s="11" t="n">
+      <c r="O56" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="N56" s="11" t="n"/>
-      <c r="O56" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P56" s="11" t="n"/>
-      <c r="Q56" s="11" t="n"/>
+      <c r="Q56" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R56" s="11" t="inlineStr">
         <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="S56" s="11" t="n"/>
+      <c r="T56" s="11" t="inlineStr">
+        <is>
           <t>[피버] 버프 3초 · 콤보 계수 +50%</t>
         </is>
       </c>
-      <c r="S56" s="11" t="inlineStr">
+      <c r="U56" s="11" t="inlineStr">
         <is>
           <t>param = 콤보 계수 증가</t>
         </is>
@@ -4339,30 +4895,40 @@
       <c r="I57" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J57" s="11" t="inlineStr">
+      <c r="J57" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K57" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L57" s="11" t="inlineStr">
         <is>
           <t>buff_haste_duration</t>
         </is>
       </c>
-      <c r="K57" s="11" t="n"/>
-      <c r="L57" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="M57" s="11" t="n"/>
-      <c r="N57" s="11" t="n"/>
-      <c r="O57" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N57" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" s="11" t="n"/>
       <c r="P57" s="11" t="n"/>
-      <c r="Q57" s="11" t="n"/>
+      <c r="Q57" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R57" s="11" t="inlineStr">
         <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="S57" s="11" t="n"/>
+      <c r="T57" s="11" t="inlineStr">
+        <is>
           <t>가속(5초) 버프</t>
         </is>
       </c>
-      <c r="S57" s="11" t="n"/>
+      <c r="U57" s="11" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="n">
@@ -4402,32 +4968,42 @@
       <c r="I58" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J58" s="11" t="inlineStr">
+      <c r="J58" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K58" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L58" s="11" t="inlineStr">
         <is>
           <t>poison_strike_chance</t>
         </is>
       </c>
-      <c r="K58" s="11" t="n"/>
-      <c r="L58" s="11" t="n">
+      <c r="M58" s="11" t="n"/>
+      <c r="N58" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="M58" s="11" t="n">
+      <c r="O58" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="N58" s="11" t="n"/>
-      <c r="O58" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P58" s="11" t="n"/>
-      <c r="Q58" s="11" t="n"/>
+      <c r="Q58" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R58" s="11" t="inlineStr">
         <is>
+          <t>3207</t>
+        </is>
+      </c>
+      <c r="S58" s="11" t="n"/>
+      <c r="T58" s="11" t="inlineStr">
+        <is>
           <t>단일 버섯 획득 시 4% 확률로 다음 타격 피해 +200%</t>
         </is>
       </c>
-      <c r="S58" s="11" t="n"/>
+      <c r="U58" s="11" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="n">
@@ -4467,32 +5043,42 @@
       <c r="I59" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J59" s="11" t="inlineStr">
+      <c r="J59" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K59" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L59" s="11" t="inlineStr">
         <is>
           <t>chain_lightning_chance</t>
         </is>
       </c>
-      <c r="K59" s="11" t="n"/>
-      <c r="L59" s="11" t="n">
+      <c r="M59" s="11" t="n"/>
+      <c r="N59" s="11" t="n">
         <v>0.03</v>
       </c>
-      <c r="M59" s="11" t="n">
+      <c r="O59" s="11" t="n">
         <v>0.3</v>
       </c>
-      <c r="N59" s="11" t="n"/>
-      <c r="O59" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P59" s="11" t="n"/>
-      <c r="Q59" s="11" t="n"/>
+      <c r="Q59" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R59" s="11" t="inlineStr">
         <is>
+          <t>3208</t>
+        </is>
+      </c>
+      <c r="S59" s="11" t="n"/>
+      <c r="T59" s="11" t="inlineStr">
+        <is>
           <t>군락 파괴 시 3% 확률로 랜덤 군락에 번개(공격력 30%)</t>
         </is>
       </c>
-      <c r="S59" s="11" t="inlineStr">
+      <c r="U59" s="11" t="inlineStr">
         <is>
           <t>param = 번개 피해 (공격력 비율)</t>
         </is>
@@ -4536,30 +5122,40 @@
       <c r="I60" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J60" s="11" t="inlineStr">
+      <c r="J60" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L60" s="11" t="inlineStr">
         <is>
           <t>buff_homing_duration</t>
         </is>
       </c>
-      <c r="K60" s="11" t="n"/>
-      <c r="L60" s="11" t="n">
+      <c r="M60" s="11" t="n"/>
+      <c r="N60" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="M60" s="11" t="n"/>
-      <c r="N60" s="11" t="n"/>
-      <c r="O60" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O60" s="11" t="n"/>
       <c r="P60" s="11" t="n"/>
-      <c r="Q60" s="11" t="n"/>
+      <c r="Q60" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R60" s="11" t="inlineStr">
         <is>
+          <t>3107</t>
+        </is>
+      </c>
+      <c r="S60" s="11" t="n"/>
+      <c r="T60" s="11" t="inlineStr">
+        <is>
           <t>유도(3초) 버프</t>
         </is>
       </c>
-      <c r="S60" s="11" t="n"/>
+      <c r="U60" s="11" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="n">
@@ -4599,30 +5195,40 @@
       <c r="I61" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J61" s="11" t="inlineStr">
+      <c r="J61" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K61" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L61" s="11" t="inlineStr">
         <is>
           <t>buff_pierce_duration</t>
         </is>
       </c>
-      <c r="K61" s="11" t="n"/>
-      <c r="L61" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="M61" s="11" t="n"/>
-      <c r="N61" s="11" t="n"/>
-      <c r="O61" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N61" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" s="11" t="n"/>
       <c r="P61" s="11" t="n"/>
-      <c r="Q61" s="11" t="n"/>
+      <c r="Q61" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R61" s="11" t="inlineStr">
         <is>
+          <t>3310</t>
+        </is>
+      </c>
+      <c r="S61" s="11" t="n"/>
+      <c r="T61" s="11" t="inlineStr">
+        <is>
           <t>관통(4초) 버프</t>
         </is>
       </c>
-      <c r="S61" s="11" t="n"/>
+      <c r="U61" s="11" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="n">
@@ -4662,30 +5268,40 @@
       <c r="I62" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J62" s="11" t="inlineStr">
+      <c r="J62" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K62" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="L62" s="11" t="inlineStr">
         <is>
           <t>buff_pierce_duration</t>
         </is>
       </c>
-      <c r="K62" s="11" t="n"/>
-      <c r="L62" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="M62" s="11" t="n"/>
-      <c r="N62" s="11" t="n"/>
-      <c r="O62" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N62" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" s="11" t="n"/>
       <c r="P62" s="11" t="n"/>
-      <c r="Q62" s="11" t="n"/>
+      <c r="Q62" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R62" s="11" t="inlineStr">
         <is>
+          <t>3211</t>
+        </is>
+      </c>
+      <c r="S62" s="11" t="n"/>
+      <c r="T62" s="11" t="inlineStr">
+        <is>
           <t>관통(5초) 버프</t>
         </is>
       </c>
-      <c r="S62" s="11" t="inlineStr">
+      <c r="U62" s="11" t="inlineStr">
         <is>
           <t>원문은 Lv.2와 같은 레어도 7</t>
         </is>
@@ -4729,30 +5345,40 @@
       <c r="I63" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J63" s="11" t="inlineStr">
+      <c r="J63" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K63" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="L63" s="11" t="inlineStr">
         <is>
           <t>debuff_cleanse_chance</t>
         </is>
       </c>
-      <c r="K63" s="11" t="n"/>
-      <c r="L63" s="11" t="n">
+      <c r="M63" s="11" t="n"/>
+      <c r="N63" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="M63" s="11" t="n"/>
-      <c r="N63" s="11" t="n"/>
-      <c r="O63" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O63" s="11" t="n"/>
       <c r="P63" s="11" t="n"/>
-      <c r="Q63" s="11" t="n"/>
+      <c r="Q63" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R63" s="11" t="inlineStr">
         <is>
+          <t>3209</t>
+        </is>
+      </c>
+      <c r="S63" s="11" t="n"/>
+      <c r="T63" s="11" t="inlineStr">
+        <is>
           <t>군락 충돌로 디버프를 얻으면 10% 확률로 해제</t>
         </is>
       </c>
-      <c r="S63" s="11" t="n"/>
+      <c r="U63" s="11" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="n">
@@ -4792,32 +5418,42 @@
       <c r="I64" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J64" s="11" t="inlineStr">
+      <c r="J64" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K64" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L64" s="11" t="inlineStr">
         <is>
           <t>poison_strike_chance</t>
         </is>
       </c>
-      <c r="K64" s="11" t="n"/>
-      <c r="L64" s="11" t="n">
+      <c r="M64" s="11" t="n"/>
+      <c r="N64" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="M64" s="11" t="n">
+      <c r="O64" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="N64" s="11" t="n"/>
-      <c r="O64" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P64" s="11" t="n"/>
-      <c r="Q64" s="11" t="n"/>
+      <c r="Q64" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R64" s="11" t="inlineStr">
         <is>
+          <t>3213</t>
+        </is>
+      </c>
+      <c r="S64" s="11" t="n"/>
+      <c r="T64" s="11" t="inlineStr">
+        <is>
           <t>단일 버섯 획득 시 5% 확률로 다음 타격 피해 +200%</t>
         </is>
       </c>
-      <c r="S64" s="11" t="n"/>
+      <c r="U64" s="11" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="n">
@@ -4857,30 +5493,40 @@
       <c r="I65" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J65" s="11" t="inlineStr">
+      <c r="J65" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K65" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L65" s="11" t="inlineStr">
         <is>
           <t>field_restoration</t>
         </is>
       </c>
-      <c r="K65" s="11" t="n"/>
-      <c r="L65" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="M65" s="11" t="n"/>
-      <c r="N65" s="11" t="n"/>
-      <c r="O65" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N65" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" s="11" t="n"/>
       <c r="P65" s="11" t="n"/>
-      <c r="Q65" s="11" t="n"/>
+      <c r="Q65" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R65" s="11" t="inlineStr">
         <is>
+          <t>3212</t>
+        </is>
+      </c>
+      <c r="S65" s="11" t="n"/>
+      <c r="T65" s="11" t="inlineStr">
+        <is>
           <t>필드에 꽃밭 추가</t>
         </is>
       </c>
-      <c r="S65" s="11" t="n"/>
+      <c r="U65" s="11" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="n">
@@ -4920,30 +5566,40 @@
       <c r="I66" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J66" s="11" t="inlineStr">
+      <c r="J66" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K66" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="L66" s="11" t="inlineStr">
         <is>
           <t>buff_heal_duration</t>
         </is>
       </c>
-      <c r="K66" s="11" t="n"/>
-      <c r="L66" s="11" t="n">
+      <c r="M66" s="11" t="n"/>
+      <c r="N66" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="M66" s="11" t="n"/>
-      <c r="N66" s="11" t="n"/>
-      <c r="O66" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O66" s="11" t="n"/>
       <c r="P66" s="11" t="n"/>
-      <c r="Q66" s="11" t="n"/>
+      <c r="Q66" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R66" s="11" t="inlineStr">
         <is>
+          <t>3214</t>
+        </is>
+      </c>
+      <c r="S66" s="11" t="n"/>
+      <c r="T66" s="11" t="inlineStr">
+        <is>
           <t>포자 디버프 제거 + 약손(3초)</t>
         </is>
       </c>
-      <c r="S66" s="11" t="n"/>
+      <c r="U66" s="11" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="n">
@@ -4983,30 +5639,40 @@
       <c r="I67" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J67" s="11" t="inlineStr">
+      <c r="J67" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K67" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L67" s="11" t="inlineStr">
         <is>
           <t>buff_homing_duration</t>
         </is>
       </c>
-      <c r="K67" s="11" t="n"/>
-      <c r="L67" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="M67" s="11" t="n"/>
-      <c r="N67" s="11" t="n"/>
-      <c r="O67" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N67" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" s="11" t="n"/>
       <c r="P67" s="11" t="n"/>
-      <c r="Q67" s="11" t="n"/>
+      <c r="Q67" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R67" s="11" t="inlineStr">
         <is>
+          <t>3216</t>
+        </is>
+      </c>
+      <c r="S67" s="11" t="n"/>
+      <c r="T67" s="11" t="inlineStr">
+        <is>
           <t>유도(4초) 버프</t>
         </is>
       </c>
-      <c r="S67" s="11" t="n"/>
+      <c r="U67" s="11" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="n">
@@ -5046,30 +5712,40 @@
       <c r="I68" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J68" s="11" t="inlineStr">
+      <c r="J68" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K68" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L68" s="11" t="inlineStr">
         <is>
           <t>debuff_cleanse_chance</t>
         </is>
       </c>
-      <c r="K68" s="11" t="n"/>
-      <c r="L68" s="11" t="n">
+      <c r="M68" s="11" t="n"/>
+      <c r="N68" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="M68" s="11" t="n"/>
-      <c r="N68" s="11" t="n"/>
-      <c r="O68" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O68" s="11" t="n"/>
       <c r="P68" s="11" t="n"/>
-      <c r="Q68" s="11" t="n"/>
+      <c r="Q68" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R68" s="11" t="inlineStr">
         <is>
+          <t>3112</t>
+        </is>
+      </c>
+      <c r="S68" s="11" t="n"/>
+      <c r="T68" s="11" t="inlineStr">
+        <is>
           <t>군락 충돌로 디버프를 얻으면 20% 확률로 해제</t>
         </is>
       </c>
-      <c r="S68" s="11" t="n"/>
+      <c r="U68" s="11" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="n">
@@ -5109,32 +5785,42 @@
       <c r="I69" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J69" s="11" t="inlineStr">
+      <c r="J69" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K69" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="L69" s="11" t="inlineStr">
         <is>
           <t>whirlwind_chance</t>
         </is>
       </c>
-      <c r="K69" s="11" t="n"/>
-      <c r="L69" s="11" t="n">
+      <c r="M69" s="11" t="n"/>
+      <c r="N69" s="11" t="n">
         <v>0.03</v>
       </c>
-      <c r="M69" s="11" t="n">
+      <c r="O69" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="N69" s="11" t="n"/>
-      <c r="O69" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P69" s="11" t="n"/>
-      <c r="Q69" s="11" t="n"/>
+      <c r="Q69" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R69" s="11" t="inlineStr">
         <is>
+          <t>3217</t>
+        </is>
+      </c>
+      <c r="S69" s="11" t="n"/>
+      <c r="T69" s="11" t="inlineStr">
+        <is>
           <t>군락 충돌 시 3% 확률로 3초 지속 피해(공격력 5%)</t>
         </is>
       </c>
-      <c r="S69" s="11" t="inlineStr">
+      <c r="U69" s="11" t="inlineStr">
         <is>
           <t>param = 초당 피해 (공격력 비율). 지속 시간도 3/4/5초로 오르는데 칸이 하나라 계열 레벨 + 2초로 계산 필요</t>
         </is>
@@ -5178,32 +5864,42 @@
       <c r="I70" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J70" s="11" t="inlineStr">
+      <c r="J70" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K70" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="L70" s="11" t="inlineStr">
         <is>
           <t>buff_wisdom_rate</t>
         </is>
       </c>
-      <c r="K70" s="11" t="n"/>
-      <c r="L70" s="11" t="n">
+      <c r="M70" s="11" t="n"/>
+      <c r="N70" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="M70" s="11" t="n">
+      <c r="O70" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="N70" s="11" t="n"/>
-      <c r="O70" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P70" s="11" t="n"/>
-      <c r="Q70" s="11" t="n"/>
+      <c r="Q70" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R70" s="11" t="inlineStr">
         <is>
+          <t>3219</t>
+        </is>
+      </c>
+      <c r="S70" s="11" t="n"/>
+      <c r="T70" s="11" t="inlineStr">
+        <is>
           <t>[지혜] 버프 3초 · 수확기 스킬 발동률 +1%</t>
         </is>
       </c>
-      <c r="S70" s="11" t="inlineStr">
+      <c r="U70" s="11" t="inlineStr">
         <is>
           <t>param = 버프 지속(초)</t>
         </is>
@@ -5247,32 +5943,42 @@
       <c r="I71" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J71" s="11" t="inlineStr">
+      <c r="J71" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K71" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="L71" s="11" t="inlineStr">
         <is>
           <t>buff_wisdom_rate</t>
         </is>
       </c>
-      <c r="K71" s="11" t="n"/>
-      <c r="L71" s="11" t="n">
+      <c r="M71" s="11" t="n"/>
+      <c r="N71" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="M71" s="11" t="n">
+      <c r="O71" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="N71" s="11" t="n"/>
-      <c r="O71" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P71" s="11" t="n"/>
-      <c r="Q71" s="11" t="n"/>
+      <c r="Q71" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R71" s="11" t="inlineStr">
         <is>
+          <t>3220</t>
+        </is>
+      </c>
+      <c r="S71" s="11" t="n"/>
+      <c r="T71" s="11" t="inlineStr">
+        <is>
           <t>[지혜] 버프 3초 · 수확기 스킬 발동률 +2%</t>
         </is>
       </c>
-      <c r="S71" s="11" t="inlineStr">
+      <c r="U71" s="11" t="inlineStr">
         <is>
           <t>원문은 Lv.1과 같은 레어도 11</t>
         </is>
@@ -5316,32 +6022,42 @@
       <c r="I72" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J72" s="11" t="inlineStr">
+      <c r="J72" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K72" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="L72" s="11" t="inlineStr">
         <is>
           <t>buff_fever_duration</t>
         </is>
       </c>
-      <c r="K72" s="11" t="n"/>
-      <c r="L72" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M72" s="11" t="n">
+      <c r="M72" s="11" t="n"/>
+      <c r="N72" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="N72" s="11" t="n"/>
-      <c r="O72" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P72" s="11" t="n"/>
-      <c r="Q72" s="11" t="n"/>
+      <c r="Q72" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R72" s="11" t="inlineStr">
         <is>
+          <t>3116</t>
+        </is>
+      </c>
+      <c r="S72" s="11" t="n"/>
+      <c r="T72" s="11" t="inlineStr">
+        <is>
           <t>[피버] 버프 4초 · 콤보 계수 +50%</t>
         </is>
       </c>
-      <c r="S72" s="11" t="n"/>
+      <c r="U72" s="11" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="n">
@@ -5381,32 +6097,42 @@
       <c r="I73" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J73" s="11" t="inlineStr">
+      <c r="J73" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K73" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="L73" s="11" t="inlineStr">
         <is>
           <t>spore_burst_chance</t>
         </is>
       </c>
-      <c r="K73" s="11" t="n"/>
-      <c r="L73" s="11" t="n">
+      <c r="M73" s="11" t="n"/>
+      <c r="N73" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="M73" s="11" t="n">
+      <c r="O73" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="N73" s="11" t="n"/>
-      <c r="O73" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P73" s="11" t="n"/>
-      <c r="Q73" s="11" t="n"/>
+      <c r="Q73" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R73" s="11" t="inlineStr">
         <is>
+          <t>3222</t>
+        </is>
+      </c>
+      <c r="S73" s="11" t="n"/>
+      <c r="T73" s="11" t="inlineStr">
+        <is>
           <t>군락 충돌 시 1% 확률로 전체 피해(공격력 10%)</t>
         </is>
       </c>
-      <c r="S73" s="11" t="inlineStr">
+      <c r="U73" s="11" t="inlineStr">
         <is>
           <t>param = 피해 (공격력 비율)</t>
         </is>
@@ -5450,32 +6176,42 @@
       <c r="I74" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J74" s="11" t="inlineStr">
+      <c r="J74" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K74" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="L74" s="11" t="inlineStr">
         <is>
           <t>spore_burst_chance</t>
         </is>
       </c>
-      <c r="K74" s="11" t="n"/>
-      <c r="L74" s="11" t="n">
+      <c r="M74" s="11" t="n"/>
+      <c r="N74" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="M74" s="11" t="n">
+      <c r="O74" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="N74" s="11" t="n"/>
-      <c r="O74" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P74" s="11" t="n"/>
-      <c r="Q74" s="11" t="n"/>
+      <c r="Q74" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R74" s="11" t="inlineStr">
         <is>
+          <t>3326</t>
+        </is>
+      </c>
+      <c r="S74" s="11" t="n"/>
+      <c r="T74" s="11" t="inlineStr">
+        <is>
           <t>군락 충돌 시 2% 확률로 전체 피해(공격력 10%)</t>
         </is>
       </c>
-      <c r="S74" s="11" t="n"/>
+      <c r="U74" s="11" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="11" t="n">
@@ -5515,30 +6251,40 @@
       <c r="I75" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J75" s="11" t="inlineStr">
+      <c r="J75" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K75" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="L75" s="11" t="inlineStr">
         <is>
           <t>buff_homing_duration</t>
         </is>
       </c>
-      <c r="K75" s="11" t="n"/>
-      <c r="L75" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="M75" s="11" t="n"/>
-      <c r="N75" s="11" t="n"/>
-      <c r="O75" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N75" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" s="11" t="n"/>
       <c r="P75" s="11" t="n"/>
-      <c r="Q75" s="11" t="n"/>
+      <c r="Q75" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R75" s="11" t="inlineStr">
         <is>
+          <t>3329</t>
+        </is>
+      </c>
+      <c r="S75" s="11" t="n"/>
+      <c r="T75" s="11" t="inlineStr">
+        <is>
           <t>유도(5초) 버프</t>
         </is>
       </c>
-      <c r="S75" s="11" t="n"/>
+      <c r="U75" s="11" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="n">
@@ -5578,30 +6324,40 @@
       <c r="I76" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J76" s="11" t="inlineStr">
+      <c r="J76" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K76" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="L76" s="11" t="inlineStr">
         <is>
           <t>debuff_cleanse_chance</t>
         </is>
       </c>
-      <c r="K76" s="11" t="n"/>
-      <c r="L76" s="11" t="n">
+      <c r="M76" s="11" t="n"/>
+      <c r="N76" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="M76" s="11" t="n"/>
-      <c r="N76" s="11" t="n"/>
-      <c r="O76" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O76" s="11" t="n"/>
       <c r="P76" s="11" t="n"/>
-      <c r="Q76" s="11" t="n"/>
+      <c r="Q76" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R76" s="11" t="inlineStr">
         <is>
+          <t>3330</t>
+        </is>
+      </c>
+      <c r="S76" s="11" t="n"/>
+      <c r="T76" s="11" t="inlineStr">
+        <is>
           <t>군락 충돌로 디버프를 얻으면 30% 확률로 해제</t>
         </is>
       </c>
-      <c r="S76" s="11" t="n"/>
+      <c r="U76" s="11" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="n">
@@ -5641,30 +6397,40 @@
       <c r="I77" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J77" s="11" t="inlineStr">
+      <c r="J77" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="L77" s="11" t="inlineStr">
         <is>
           <t>field_restoration</t>
         </is>
       </c>
-      <c r="K77" s="11" t="n"/>
-      <c r="L77" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="M77" s="11" t="n"/>
-      <c r="N77" s="11" t="n"/>
-      <c r="O77" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N77" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O77" s="11" t="n"/>
       <c r="P77" s="11" t="n"/>
-      <c r="Q77" s="11" t="n"/>
+      <c r="Q77" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R77" s="11" t="inlineStr">
         <is>
+          <t>3125</t>
+        </is>
+      </c>
+      <c r="S77" s="11" t="n"/>
+      <c r="T77" s="11" t="inlineStr">
+        <is>
           <t>필드에 도토리 점등 추가</t>
         </is>
       </c>
-      <c r="S77" s="11" t="n"/>
+      <c r="U77" s="11" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="11" t="n">
@@ -5704,32 +6470,42 @@
       <c r="I78" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J78" s="11" t="inlineStr">
+      <c r="J78" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K78" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="L78" s="11" t="inlineStr">
         <is>
           <t>buff_split_duration</t>
         </is>
       </c>
-      <c r="K78" s="11" t="n"/>
-      <c r="L78" s="11" t="n">
+      <c r="M78" s="11" t="n"/>
+      <c r="N78" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="M78" s="11" t="n">
+      <c r="O78" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="N78" s="11" t="n"/>
-      <c r="O78" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P78" s="11" t="n"/>
-      <c r="Q78" s="11" t="n"/>
+      <c r="Q78" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R78" s="11" t="inlineStr">
         <is>
+          <t>3331</t>
+        </is>
+      </c>
+      <c r="S78" s="11" t="n"/>
+      <c r="T78" s="11" t="inlineStr">
+        <is>
           <t>10% 확률로 분열(3초) 버프</t>
         </is>
       </c>
-      <c r="S78" s="11" t="inlineStr">
+      <c r="U78" s="11" t="inlineStr">
         <is>
           <t>param = 발동 확률</t>
         </is>
@@ -5773,32 +6549,42 @@
       <c r="I79" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J79" s="11" t="inlineStr">
+      <c r="J79" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K79" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="L79" s="11" t="inlineStr">
         <is>
           <t>whirlwind_chance</t>
         </is>
       </c>
-      <c r="K79" s="11" t="n"/>
-      <c r="L79" s="11" t="n">
+      <c r="M79" s="11" t="n"/>
+      <c r="N79" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="M79" s="11" t="n">
+      <c r="O79" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="N79" s="11" t="n"/>
-      <c r="O79" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P79" s="11" t="n"/>
-      <c r="Q79" s="11" t="n"/>
+      <c r="Q79" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R79" s="11" t="inlineStr">
         <is>
+          <t>3225</t>
+        </is>
+      </c>
+      <c r="S79" s="11" t="n"/>
+      <c r="T79" s="11" t="inlineStr">
+        <is>
           <t>군락 충돌 시 4% 확률로 4초 지속 피해(공격력 5%)</t>
         </is>
       </c>
-      <c r="S79" s="11" t="n"/>
+      <c r="U79" s="11" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="n">
@@ -5838,32 +6624,42 @@
       <c r="I80" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J80" s="11" t="inlineStr">
+      <c r="J80" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K80" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="L80" s="11" t="inlineStr">
         <is>
           <t>buff_wisdom_rate</t>
         </is>
       </c>
-      <c r="K80" s="11" t="n"/>
-      <c r="L80" s="11" t="n">
+      <c r="M80" s="11" t="n"/>
+      <c r="N80" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="M80" s="11" t="n">
+      <c r="O80" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="N80" s="11" t="n"/>
-      <c r="O80" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P80" s="11" t="n"/>
-      <c r="Q80" s="11" t="n"/>
+      <c r="Q80" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R80" s="11" t="inlineStr">
         <is>
+          <t>3229</t>
+        </is>
+      </c>
+      <c r="S80" s="11" t="n"/>
+      <c r="T80" s="11" t="inlineStr">
+        <is>
           <t>[지혜] 버프 3초 · 수확기 스킬 발동률 +3%</t>
         </is>
       </c>
-      <c r="S80" s="11" t="n"/>
+      <c r="U80" s="11" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="11" t="n">
@@ -5903,30 +6699,40 @@
       <c r="I81" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J81" s="11" t="inlineStr">
+      <c r="J81" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K81" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="L81" s="11" t="inlineStr">
         <is>
           <t>buff_heal_duration</t>
         </is>
       </c>
-      <c r="K81" s="11" t="n"/>
-      <c r="L81" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="M81" s="11" t="n"/>
-      <c r="N81" s="11" t="n"/>
-      <c r="O81" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N81" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" s="11" t="n"/>
       <c r="P81" s="11" t="n"/>
-      <c r="Q81" s="11" t="n"/>
+      <c r="Q81" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R81" s="11" t="inlineStr">
         <is>
+          <t>3129</t>
+        </is>
+      </c>
+      <c r="S81" s="11" t="n"/>
+      <c r="T81" s="11" t="inlineStr">
+        <is>
           <t>포자 디버프 제거 + 약손(4초)</t>
         </is>
       </c>
-      <c r="S81" s="11" t="n"/>
+      <c r="U81" s="11" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="n">
@@ -5966,32 +6772,42 @@
       <c r="I82" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J82" s="11" t="inlineStr">
+      <c r="J82" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K82" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="L82" s="11" t="inlineStr">
         <is>
           <t>chain_lightning_chance</t>
         </is>
       </c>
-      <c r="K82" s="11" t="n"/>
-      <c r="L82" s="11" t="n">
+      <c r="M82" s="11" t="n"/>
+      <c r="N82" s="11" t="n">
         <v>0.02</v>
       </c>
-      <c r="M82" s="11" t="n">
+      <c r="O82" s="11" t="n">
         <v>0.3</v>
       </c>
-      <c r="N82" s="11" t="n"/>
-      <c r="O82" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P82" s="11" t="n"/>
-      <c r="Q82" s="11" t="n"/>
+      <c r="Q82" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R82" s="11" t="inlineStr">
         <is>
+          <t>3230</t>
+        </is>
+      </c>
+      <c r="S82" s="11" t="n"/>
+      <c r="T82" s="11" t="inlineStr">
+        <is>
           <t>군락 파괴 시 5% 확률로 랜덤 군락에 번개(공격력 30%)</t>
         </is>
       </c>
-      <c r="S82" s="11" t="inlineStr">
+      <c r="U82" s="11" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -6035,30 +6851,40 @@
       <c r="I83" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J83" s="11" t="inlineStr">
+      <c r="J83" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K83" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="L83" s="11" t="inlineStr">
         <is>
           <t>buff_heal_duration</t>
         </is>
       </c>
-      <c r="K83" s="11" t="n"/>
-      <c r="L83" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="M83" s="11" t="n"/>
-      <c r="N83" s="11" t="n"/>
-      <c r="O83" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N83" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O83" s="11" t="n"/>
       <c r="P83" s="11" t="n"/>
-      <c r="Q83" s="11" t="n"/>
+      <c r="Q83" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R83" s="11" t="inlineStr">
         <is>
+          <t>3232</t>
+        </is>
+      </c>
+      <c r="S83" s="11" t="n"/>
+      <c r="T83" s="11" t="inlineStr">
+        <is>
           <t>포자 디버프 제거 + 약손(5초)</t>
         </is>
       </c>
-      <c r="S83" s="11" t="n"/>
+      <c r="U83" s="11" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="11" t="n">
@@ -6098,32 +6924,42 @@
       <c r="I84" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J84" s="11" t="inlineStr">
+      <c r="J84" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K84" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="L84" s="11" t="inlineStr">
         <is>
           <t>chain_lightning_chance</t>
         </is>
       </c>
-      <c r="K84" s="11" t="n"/>
-      <c r="L84" s="11" t="n">
+      <c r="M84" s="11" t="n"/>
+      <c r="N84" s="11" t="n">
         <v>0.02</v>
       </c>
-      <c r="M84" s="11" t="n">
+      <c r="O84" s="11" t="n">
         <v>0.3</v>
       </c>
-      <c r="N84" s="11" t="n"/>
-      <c r="O84" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P84" s="11" t="n"/>
-      <c r="Q84" s="11" t="n"/>
+      <c r="Q84" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R84" s="11" t="inlineStr">
         <is>
+          <t>3233</t>
+        </is>
+      </c>
+      <c r="S84" s="11" t="n"/>
+      <c r="T84" s="11" t="inlineStr">
+        <is>
           <t>군락 파괴 시 7% 확률로 랜덤 위치에 번개(공격력 30%)</t>
         </is>
       </c>
-      <c r="S84" s="11" t="inlineStr">
+      <c r="U84" s="11" t="inlineStr">
         <is>
           <t>확인 필요: 원문 Lv.3만 "랜덤 위치", Lv.1·2는 "랜덤 군락"</t>
         </is>
@@ -6167,30 +7003,40 @@
       <c r="I85" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="J85" s="11" t="inlineStr">
+      <c r="J85" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K85" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="L85" s="11" t="inlineStr">
         <is>
           <t>opening_buff_chance</t>
         </is>
       </c>
-      <c r="K85" s="11" t="n"/>
-      <c r="L85" s="11" t="n">
+      <c r="M85" s="11" t="n"/>
+      <c r="N85" s="11" t="n">
         <v>0.02</v>
       </c>
-      <c r="M85" s="11" t="n"/>
-      <c r="N85" s="11" t="n"/>
-      <c r="O85" s="11" t="inlineStr">
+      <c r="O85" s="11" t="n"/>
+      <c r="P85" s="11" t="n"/>
+      <c r="Q85" s="11" t="inlineStr">
         <is>
           <t>Mycelite</t>
         </is>
       </c>
-      <c r="P85" s="11" t="n"/>
-      <c r="Q85" s="11" t="n"/>
       <c r="R85" s="11" t="inlineStr">
         <is>
+          <t>3234</t>
+        </is>
+      </c>
+      <c r="S85" s="11" t="n"/>
+      <c r="T85" s="11" t="inlineStr">
+        <is>
           <t>게임 시작 시 보유 버프 스킬 즉시 발동 확률 +2% / Lv</t>
         </is>
       </c>
-      <c r="S85" s="11" t="n"/>
+      <c r="U85" s="11" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="11" t="n">
@@ -6230,32 +7076,42 @@
       <c r="I86" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J86" s="11" t="inlineStr">
+      <c r="J86" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K86" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="L86" s="11" t="inlineStr">
         <is>
           <t>buff_split_duration</t>
         </is>
       </c>
-      <c r="K86" s="11" t="n"/>
-      <c r="L86" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M86" s="11" t="n">
+      <c r="M86" s="11" t="n"/>
+      <c r="N86" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O86" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="N86" s="11" t="n"/>
-      <c r="O86" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P86" s="11" t="n"/>
-      <c r="Q86" s="11" t="n"/>
+      <c r="Q86" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R86" s="11" t="inlineStr">
         <is>
+          <t>3235</t>
+        </is>
+      </c>
+      <c r="S86" s="11" t="n"/>
+      <c r="T86" s="11" t="inlineStr">
+        <is>
           <t>10% 확률로 분열(4초) 버프</t>
         </is>
       </c>
-      <c r="S86" s="11" t="n"/>
+      <c r="U86" s="11" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="n">
@@ -6295,32 +7151,42 @@
       <c r="I87" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J87" s="11" t="inlineStr">
+      <c r="J87" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K87" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="L87" s="11" t="inlineStr">
         <is>
           <t>buff_split_duration</t>
         </is>
       </c>
-      <c r="K87" s="11" t="n"/>
-      <c r="L87" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M87" s="11" t="n">
+      <c r="M87" s="11" t="n"/>
+      <c r="N87" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="N87" s="11" t="n"/>
-      <c r="O87" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P87" s="11" t="n"/>
-      <c r="Q87" s="11" t="n"/>
+      <c r="Q87" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R87" s="11" t="inlineStr">
         <is>
+          <t>3236</t>
+        </is>
+      </c>
+      <c r="S87" s="11" t="n"/>
+      <c r="T87" s="11" t="inlineStr">
+        <is>
           <t>10% 확률로 분열(5초) 버프</t>
         </is>
       </c>
-      <c r="S87" s="11" t="inlineStr">
+      <c r="U87" s="11" t="inlineStr">
         <is>
           <t>원문은 Lv.2와 같은 레어도 16</t>
         </is>
@@ -6364,32 +7230,42 @@
       <c r="I88" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J88" s="11" t="inlineStr">
+      <c r="J88" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K88" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="L88" s="11" t="inlineStr">
         <is>
           <t>spore_burst_chance</t>
         </is>
       </c>
-      <c r="K88" s="11" t="n"/>
-      <c r="L88" s="11" t="n">
+      <c r="M88" s="11" t="n"/>
+      <c r="N88" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="M88" s="11" t="n">
+      <c r="O88" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="N88" s="11" t="n"/>
-      <c r="O88" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P88" s="11" t="n"/>
-      <c r="Q88" s="11" t="n"/>
+      <c r="Q88" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R88" s="11" t="inlineStr">
         <is>
+          <t>3345</t>
+        </is>
+      </c>
+      <c r="S88" s="11" t="n"/>
+      <c r="T88" s="11" t="inlineStr">
+        <is>
           <t>군락 충돌 시 3% 확률로 전체 피해(공격력 10%)</t>
         </is>
       </c>
-      <c r="S88" s="11" t="n"/>
+      <c r="U88" s="11" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="11" t="n">
@@ -6429,32 +7305,42 @@
       <c r="I89" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J89" s="11" t="inlineStr">
+      <c r="J89" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K89" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="L89" s="11" t="inlineStr">
         <is>
           <t>whirlwind_chance</t>
         </is>
       </c>
-      <c r="K89" s="11" t="n"/>
-      <c r="L89" s="11" t="n">
+      <c r="M89" s="11" t="n"/>
+      <c r="N89" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="M89" s="11" t="n">
+      <c r="O89" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="N89" s="11" t="n"/>
-      <c r="O89" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P89" s="11" t="n"/>
-      <c r="Q89" s="11" t="n"/>
+      <c r="Q89" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R89" s="11" t="inlineStr">
         <is>
+          <t>3139</t>
+        </is>
+      </c>
+      <c r="S89" s="11" t="n"/>
+      <c r="T89" s="11" t="inlineStr">
+        <is>
           <t>군락 충돌 시 5% 확률로 5초 지속 피해(공격력 5%)</t>
         </is>
       </c>
-      <c r="S89" s="11" t="n"/>
+      <c r="U89" s="11" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="n">
@@ -6494,32 +7380,42 @@
       <c r="I90" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J90" s="11" t="inlineStr">
+      <c r="J90" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K90" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="L90" s="11" t="inlineStr">
         <is>
           <t>buff_fever_duration</t>
         </is>
       </c>
-      <c r="K90" s="11" t="n"/>
-      <c r="L90" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M90" s="11" t="n">
+      <c r="M90" s="11" t="n"/>
+      <c r="N90" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O90" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="N90" s="11" t="n"/>
-      <c r="O90" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P90" s="11" t="n"/>
-      <c r="Q90" s="11" t="n"/>
+      <c r="Q90" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R90" s="11" t="inlineStr">
         <is>
+          <t>3237</t>
+        </is>
+      </c>
+      <c r="S90" s="11" t="n"/>
+      <c r="T90" s="11" t="inlineStr">
+        <is>
           <t>[피버] 버프 5초 · 콤보 계수 +50%</t>
         </is>
       </c>
-      <c r="S90" s="11" t="n"/>
+      <c r="U90" s="11" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="12" t="n">
@@ -6559,30 +7455,40 @@
       <c r="I91" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J91" s="12" t="inlineStr">
+      <c r="J91" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" s="12" t="inlineStr">
         <is>
           <t>harvester_damage</t>
         </is>
       </c>
-      <c r="K91" s="12" t="n"/>
-      <c r="L91" s="12" t="n">
+      <c r="M91" s="12" t="n"/>
+      <c r="N91" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="M91" s="12" t="n"/>
-      <c r="N91" s="12" t="n"/>
-      <c r="O91" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O91" s="12" t="n"/>
       <c r="P91" s="12" t="n"/>
-      <c r="Q91" s="12" t="n"/>
+      <c r="Q91" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R91" s="12" t="inlineStr">
         <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="S91" s="12" t="n"/>
+      <c r="T91" s="12" t="inlineStr">
+        <is>
           <t>공격력 +2 (1 → 3)</t>
         </is>
       </c>
-      <c r="S91" s="12" t="n"/>
+      <c r="U91" s="12" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="12" t="n">
@@ -6622,30 +7528,40 @@
       <c r="I92" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J92" s="12" t="inlineStr">
+      <c r="J92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" s="12" t="inlineStr">
         <is>
           <t>combo_rate</t>
         </is>
       </c>
-      <c r="K92" s="12" t="n"/>
-      <c r="L92" s="12" t="n">
+      <c r="M92" s="12" t="n"/>
+      <c r="N92" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="M92" s="12" t="n"/>
-      <c r="N92" s="12" t="n"/>
-      <c r="O92" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O92" s="12" t="n"/>
       <c r="P92" s="12" t="n"/>
-      <c r="Q92" s="12" t="n"/>
+      <c r="Q92" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R92" s="12" t="inlineStr">
         <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="S92" s="12" t="n"/>
+      <c r="T92" s="12" t="inlineStr">
+        <is>
           <t>콤보 계수 +20%</t>
         </is>
       </c>
-      <c r="S92" s="12" t="n"/>
+      <c r="U92" s="12" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="12" t="n">
@@ -6685,30 +7601,40 @@
       <c r="I93" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J93" s="12" t="inlineStr">
+      <c r="J93" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L93" s="12" t="inlineStr">
         <is>
           <t>harvester_speed</t>
         </is>
       </c>
-      <c r="K93" s="12" t="n"/>
-      <c r="L93" s="12" t="n">
+      <c r="M93" s="12" t="n"/>
+      <c r="N93" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="M93" s="12" t="n"/>
-      <c r="N93" s="12" t="n"/>
-      <c r="O93" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O93" s="12" t="n"/>
       <c r="P93" s="12" t="n"/>
-      <c r="Q93" s="12" t="n"/>
+      <c r="Q93" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R93" s="12" t="inlineStr">
         <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="S93" s="12" t="n"/>
+      <c r="T93" s="12" t="inlineStr">
+        <is>
           <t>수확기 속도 +10%</t>
         </is>
       </c>
-      <c r="S93" s="12" t="n"/>
+      <c r="U93" s="12" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="n">
@@ -6748,30 +7674,40 @@
       <c r="I94" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J94" s="12" t="inlineStr">
+      <c r="J94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L94" s="12" t="inlineStr">
         <is>
           <t>crit_chance</t>
         </is>
       </c>
-      <c r="K94" s="12" t="n"/>
-      <c r="L94" s="12" t="n">
+      <c r="M94" s="12" t="n"/>
+      <c r="N94" s="12" t="n">
         <v>0.02</v>
       </c>
-      <c r="M94" s="12" t="n"/>
-      <c r="N94" s="12" t="n"/>
-      <c r="O94" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O94" s="12" t="n"/>
       <c r="P94" s="12" t="n"/>
-      <c r="Q94" s="12" t="n"/>
+      <c r="Q94" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R94" s="12" t="inlineStr">
         <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="S94" s="12" t="n"/>
+      <c r="T94" s="12" t="inlineStr">
+        <is>
           <t>치명타 확률 2%</t>
         </is>
       </c>
-      <c r="S94" s="12" t="n"/>
+      <c r="U94" s="12" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="12" t="n">
@@ -6811,30 +7747,40 @@
       <c r="I95" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J95" s="12" t="inlineStr">
+      <c r="J95" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L95" s="12" t="inlineStr">
         <is>
           <t>bar_length</t>
         </is>
       </c>
-      <c r="K95" s="12" t="n"/>
-      <c r="L95" s="12" t="n">
+      <c r="M95" s="12" t="n"/>
+      <c r="N95" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="M95" s="12" t="n"/>
-      <c r="N95" s="12" t="n"/>
-      <c r="O95" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O95" s="12" t="n"/>
       <c r="P95" s="12" t="n"/>
-      <c r="Q95" s="12" t="n"/>
+      <c r="Q95" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R95" s="12" t="inlineStr">
         <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="S95" s="12" t="n"/>
+      <c r="T95" s="12" t="inlineStr">
+        <is>
           <t>바 길이 +20%</t>
         </is>
       </c>
-      <c r="S95" s="12" t="n"/>
+      <c r="U95" s="12" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="12" t="n">
@@ -6874,30 +7820,40 @@
       <c r="I96" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J96" s="12" t="inlineStr">
+      <c r="J96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L96" s="12" t="inlineStr">
         <is>
           <t>harvester_damage</t>
         </is>
       </c>
-      <c r="K96" s="12" t="n"/>
-      <c r="L96" s="12" t="n">
+      <c r="M96" s="12" t="n"/>
+      <c r="N96" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="M96" s="12" t="n"/>
-      <c r="N96" s="12" t="n"/>
-      <c r="O96" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O96" s="12" t="n"/>
       <c r="P96" s="12" t="n"/>
-      <c r="Q96" s="12" t="n"/>
+      <c r="Q96" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R96" s="12" t="inlineStr">
         <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="S96" s="12" t="n"/>
+      <c r="T96" s="12" t="inlineStr">
+        <is>
           <t>공격력 +2 (3 → 5)</t>
         </is>
       </c>
-      <c r="S96" s="12" t="n"/>
+      <c r="U96" s="12" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="12" t="n">
@@ -6937,30 +7893,40 @@
       <c r="I97" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J97" s="12" t="inlineStr">
+      <c r="J97" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L97" s="12" t="inlineStr">
         <is>
           <t>harvester_size</t>
         </is>
       </c>
-      <c r="K97" s="12" t="n"/>
-      <c r="L97" s="12" t="n">
+      <c r="M97" s="12" t="n"/>
+      <c r="N97" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="M97" s="12" t="n"/>
-      <c r="N97" s="12" t="n"/>
-      <c r="O97" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O97" s="12" t="n"/>
       <c r="P97" s="12" t="n"/>
-      <c r="Q97" s="12" t="n"/>
+      <c r="Q97" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R97" s="12" t="inlineStr">
         <is>
+          <t>3305</t>
+        </is>
+      </c>
+      <c r="S97" s="12" t="n"/>
+      <c r="T97" s="12" t="inlineStr">
+        <is>
           <t>수확기 크기 +10%</t>
         </is>
       </c>
-      <c r="S97" s="12" t="n"/>
+      <c r="U97" s="12" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="12" t="n">
@@ -7000,30 +7966,40 @@
       <c r="I98" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J98" s="12" t="inlineStr">
+      <c r="J98" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K98" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L98" s="12" t="inlineStr">
         <is>
           <t>harvester_size</t>
         </is>
       </c>
-      <c r="K98" s="12" t="n"/>
-      <c r="L98" s="12" t="n">
+      <c r="M98" s="12" t="n"/>
+      <c r="N98" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="M98" s="12" t="n"/>
-      <c r="N98" s="12" t="n"/>
-      <c r="O98" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O98" s="12" t="n"/>
       <c r="P98" s="12" t="n"/>
-      <c r="Q98" s="12" t="n"/>
+      <c r="Q98" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R98" s="12" t="inlineStr">
         <is>
+          <t>3307</t>
+        </is>
+      </c>
+      <c r="S98" s="12" t="n"/>
+      <c r="T98" s="12" t="inlineStr">
+        <is>
           <t>수확기 크기 +20%</t>
         </is>
       </c>
-      <c r="S98" s="12" t="inlineStr">
+      <c r="U98" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%. 원문은 Lv.1과 같은 레어도 5</t>
         </is>
@@ -7067,30 +8043,40 @@
       <c r="I99" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J99" s="12" t="inlineStr">
+      <c r="J99" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K99" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L99" s="12" t="inlineStr">
         <is>
           <t>harvester_damage</t>
         </is>
       </c>
-      <c r="K99" s="12" t="n"/>
-      <c r="L99" s="12" t="n">
+      <c r="M99" s="12" t="n"/>
+      <c r="N99" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="M99" s="12" t="n"/>
-      <c r="N99" s="12" t="n"/>
-      <c r="O99" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O99" s="12" t="n"/>
       <c r="P99" s="12" t="n"/>
-      <c r="Q99" s="12" t="n"/>
+      <c r="Q99" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R99" s="12" t="inlineStr">
         <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="S99" s="12" t="n"/>
+      <c r="T99" s="12" t="inlineStr">
+        <is>
           <t>공격력 +2 (5 → 7)</t>
         </is>
       </c>
-      <c r="S99" s="12" t="inlineStr">
+      <c r="U99" s="12" t="inlineStr">
         <is>
           <t>확인 필요: 원문은 "+3 (5 → 7)", 화살표 기준 +2로 넣음</t>
         </is>
@@ -7134,30 +8120,40 @@
       <c r="I100" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J100" s="12" t="inlineStr">
+      <c r="J100" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K100" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L100" s="12" t="inlineStr">
         <is>
           <t>bar_length</t>
         </is>
       </c>
-      <c r="K100" s="12" t="n"/>
-      <c r="L100" s="12" t="n">
+      <c r="M100" s="12" t="n"/>
+      <c r="N100" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="M100" s="12" t="n"/>
-      <c r="N100" s="12" t="n"/>
-      <c r="O100" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O100" s="12" t="n"/>
       <c r="P100" s="12" t="n"/>
-      <c r="Q100" s="12" t="n"/>
+      <c r="Q100" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R100" s="12" t="inlineStr">
         <is>
+          <t>3106</t>
+        </is>
+      </c>
+      <c r="S100" s="12" t="n"/>
+      <c r="T100" s="12" t="inlineStr">
+        <is>
           <t>바 길이 +30%</t>
         </is>
       </c>
-      <c r="S100" s="12" t="inlineStr">
+      <c r="U100" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%</t>
         </is>
@@ -7201,30 +8197,40 @@
       <c r="I101" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J101" s="12" t="inlineStr">
+      <c r="J101" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K101" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L101" s="12" t="inlineStr">
         <is>
           <t>harvester_size</t>
         </is>
       </c>
-      <c r="K101" s="12" t="n"/>
-      <c r="L101" s="12" t="n">
+      <c r="M101" s="12" t="n"/>
+      <c r="N101" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="M101" s="12" t="n"/>
-      <c r="N101" s="12" t="n"/>
-      <c r="O101" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O101" s="12" t="n"/>
       <c r="P101" s="12" t="n"/>
-      <c r="Q101" s="12" t="n"/>
+      <c r="Q101" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R101" s="12" t="inlineStr">
         <is>
+          <t>3308</t>
+        </is>
+      </c>
+      <c r="S101" s="12" t="n"/>
+      <c r="T101" s="12" t="inlineStr">
+        <is>
           <t>수확기 크기 +30%</t>
         </is>
       </c>
-      <c r="S101" s="12" t="inlineStr">
+      <c r="U101" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%</t>
         </is>
@@ -7268,30 +8274,40 @@
       <c r="I102" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J102" s="12" t="inlineStr">
+      <c r="J102" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K102" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L102" s="12" t="inlineStr">
         <is>
           <t>harvester_speed</t>
         </is>
       </c>
-      <c r="K102" s="12" t="n"/>
-      <c r="L102" s="12" t="n">
+      <c r="M102" s="12" t="n"/>
+      <c r="N102" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="M102" s="12" t="n"/>
-      <c r="N102" s="12" t="n"/>
-      <c r="O102" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O102" s="12" t="n"/>
       <c r="P102" s="12" t="n"/>
-      <c r="Q102" s="12" t="n"/>
+      <c r="Q102" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R102" s="12" t="inlineStr">
         <is>
+          <t>3309</t>
+        </is>
+      </c>
+      <c r="S102" s="12" t="n"/>
+      <c r="T102" s="12" t="inlineStr">
+        <is>
           <t>수확기 속도 +20%</t>
         </is>
       </c>
-      <c r="S102" s="12" t="inlineStr">
+      <c r="U102" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%</t>
         </is>
@@ -7335,30 +8351,40 @@
       <c r="I103" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J103" s="12" t="inlineStr">
+      <c r="J103" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K103" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L103" s="12" t="inlineStr">
         <is>
           <t>crit_chance</t>
         </is>
       </c>
-      <c r="K103" s="12" t="n"/>
-      <c r="L103" s="12" t="n">
+      <c r="M103" s="12" t="n"/>
+      <c r="N103" s="12" t="n">
         <v>0.02</v>
       </c>
-      <c r="M103" s="12" t="n"/>
-      <c r="N103" s="12" t="n"/>
-      <c r="O103" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O103" s="12" t="n"/>
       <c r="P103" s="12" t="n"/>
-      <c r="Q103" s="12" t="n"/>
+      <c r="Q103" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R103" s="12" t="inlineStr">
         <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="S103" s="12" t="n"/>
+      <c r="T103" s="12" t="inlineStr">
+        <is>
           <t>치명타 확률 4%</t>
         </is>
       </c>
-      <c r="S103" s="12" t="inlineStr">
+      <c r="U103" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -7402,30 +8428,40 @@
       <c r="I104" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J104" s="12" t="inlineStr">
+      <c r="J104" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K104" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L104" s="12" t="inlineStr">
         <is>
           <t>orbit_harvester_count</t>
         </is>
       </c>
-      <c r="K104" s="12" t="n"/>
-      <c r="L104" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="M104" s="12" t="n"/>
-      <c r="N104" s="12" t="n"/>
-      <c r="O104" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N104" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O104" s="12" t="n"/>
       <c r="P104" s="12" t="n"/>
-      <c r="Q104" s="12" t="n"/>
+      <c r="Q104" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R104" s="12" t="inlineStr">
         <is>
+          <t>3313</t>
+        </is>
+      </c>
+      <c r="S104" s="12" t="n"/>
+      <c r="T104" s="12" t="inlineStr">
+        <is>
           <t>회전 꼬마 수확기 +1 (0 → 1)</t>
         </is>
       </c>
-      <c r="S104" s="12" t="n"/>
+      <c r="U104" s="12" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="12" t="n">
@@ -7465,30 +8501,40 @@
       <c r="I105" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J105" s="12" t="inlineStr">
+      <c r="J105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L105" s="12" t="inlineStr">
         <is>
           <t>bar_length</t>
         </is>
       </c>
-      <c r="K105" s="12" t="n"/>
-      <c r="L105" s="12" t="n">
+      <c r="M105" s="12" t="n"/>
+      <c r="N105" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="M105" s="12" t="n"/>
-      <c r="N105" s="12" t="n"/>
-      <c r="O105" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O105" s="12" t="n"/>
       <c r="P105" s="12" t="n"/>
-      <c r="Q105" s="12" t="n"/>
+      <c r="Q105" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R105" s="12" t="inlineStr">
         <is>
+          <t>3109</t>
+        </is>
+      </c>
+      <c r="S105" s="12" t="n"/>
+      <c r="T105" s="12" t="inlineStr">
+        <is>
           <t>바 길이 +50%</t>
         </is>
       </c>
-      <c r="S105" s="12" t="inlineStr">
+      <c r="U105" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +20%</t>
         </is>
@@ -7532,30 +8578,40 @@
       <c r="I106" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J106" s="12" t="inlineStr">
+      <c r="J106" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K106" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L106" s="12" t="inlineStr">
         <is>
           <t>boss_damage</t>
         </is>
       </c>
-      <c r="K106" s="12" t="n"/>
-      <c r="L106" s="12" t="n">
+      <c r="M106" s="12" t="n"/>
+      <c r="N106" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="M106" s="12" t="n"/>
-      <c r="N106" s="12" t="n"/>
-      <c r="O106" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O106" s="12" t="n"/>
       <c r="P106" s="12" t="n"/>
-      <c r="Q106" s="12" t="n"/>
+      <c r="Q106" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R106" s="12" t="inlineStr">
         <is>
+          <t>3314</t>
+        </is>
+      </c>
+      <c r="S106" s="12" t="n"/>
+      <c r="T106" s="12" t="inlineStr">
+        <is>
           <t>보스 피해 +20%</t>
         </is>
       </c>
-      <c r="S106" s="12" t="n"/>
+      <c r="U106" s="12" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="12" t="n">
@@ -7595,30 +8651,40 @@
       <c r="I107" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J107" s="12" t="inlineStr">
+      <c r="J107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L107" s="12" t="inlineStr">
         <is>
           <t>combo_rate</t>
         </is>
       </c>
-      <c r="K107" s="12" t="n"/>
-      <c r="L107" s="12" t="n">
+      <c r="M107" s="12" t="n"/>
+      <c r="N107" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="M107" s="12" t="n"/>
-      <c r="N107" s="12" t="n"/>
-      <c r="O107" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O107" s="12" t="n"/>
       <c r="P107" s="12" t="n"/>
-      <c r="Q107" s="12" t="n"/>
+      <c r="Q107" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R107" s="12" t="inlineStr">
         <is>
+          <t>3315</t>
+        </is>
+      </c>
+      <c r="S107" s="12" t="n"/>
+      <c r="T107" s="12" t="inlineStr">
+        <is>
           <t>콤보 계수 +40%</t>
         </is>
       </c>
-      <c r="S107" s="12" t="inlineStr">
+      <c r="U107" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +20%</t>
         </is>
@@ -7662,30 +8728,40 @@
       <c r="I108" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J108" s="12" t="inlineStr">
+      <c r="J108" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K108" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L108" s="12" t="inlineStr">
         <is>
           <t>round_time</t>
         </is>
       </c>
-      <c r="K108" s="12" t="n"/>
-      <c r="L108" s="12" t="n">
+      <c r="M108" s="12" t="n"/>
+      <c r="N108" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="M108" s="12" t="n"/>
-      <c r="N108" s="12" t="n"/>
-      <c r="O108" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O108" s="12" t="n"/>
       <c r="P108" s="12" t="n"/>
-      <c r="Q108" s="12" t="n"/>
+      <c r="Q108" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R108" s="12" t="inlineStr">
         <is>
+          <t>3316</t>
+        </is>
+      </c>
+      <c r="S108" s="12" t="n"/>
+      <c r="T108" s="12" t="inlineStr">
+        <is>
           <t>지속 시간 +3초 (15 → 18)</t>
         </is>
       </c>
-      <c r="S108" s="12" t="inlineStr">
+      <c r="U108" s="12" t="inlineStr">
         <is>
           <t>확인 필요: 원문은 "+2초 (15 → 18)", 화살표 기준 +3으로 넣음</t>
         </is>
@@ -7729,30 +8805,40 @@
       <c r="I109" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J109" s="12" t="inlineStr">
+      <c r="J109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L109" s="12" t="inlineStr">
         <is>
           <t>crit_chance</t>
         </is>
       </c>
-      <c r="K109" s="12" t="n"/>
-      <c r="L109" s="12" t="n">
+      <c r="M109" s="12" t="n"/>
+      <c r="N109" s="12" t="n">
         <v>0.02</v>
       </c>
-      <c r="M109" s="12" t="n"/>
-      <c r="N109" s="12" t="n"/>
-      <c r="O109" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O109" s="12" t="n"/>
       <c r="P109" s="12" t="n"/>
-      <c r="Q109" s="12" t="n"/>
+      <c r="Q109" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R109" s="12" t="inlineStr">
         <is>
+          <t>3317</t>
+        </is>
+      </c>
+      <c r="S109" s="12" t="n"/>
+      <c r="T109" s="12" t="inlineStr">
+        <is>
           <t>치명타 확률 6%</t>
         </is>
       </c>
-      <c r="S109" s="12" t="n"/>
+      <c r="U109" s="12" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="12" t="n">
@@ -7792,30 +8878,40 @@
       <c r="I110" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J110" s="12" t="inlineStr">
+      <c r="J110" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K110" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L110" s="12" t="inlineStr">
         <is>
           <t>harvester_damage</t>
         </is>
       </c>
-      <c r="K110" s="12" t="n"/>
-      <c r="L110" s="12" t="n">
+      <c r="M110" s="12" t="n"/>
+      <c r="N110" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="M110" s="12" t="n"/>
-      <c r="N110" s="12" t="n"/>
-      <c r="O110" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O110" s="12" t="n"/>
       <c r="P110" s="12" t="n"/>
-      <c r="Q110" s="12" t="n"/>
+      <c r="Q110" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R110" s="12" t="inlineStr">
         <is>
+          <t>3318</t>
+        </is>
+      </c>
+      <c r="S110" s="12" t="n"/>
+      <c r="T110" s="12" t="inlineStr">
+        <is>
           <t>공격력 +3 (7 → 10)</t>
         </is>
       </c>
-      <c r="S110" s="12" t="n"/>
+      <c r="U110" s="12" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="12" t="n">
@@ -7855,30 +8951,40 @@
       <c r="I111" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J111" s="12" t="inlineStr">
+      <c r="J111" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K111" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L111" s="12" t="inlineStr">
         <is>
           <t>boss_damage</t>
         </is>
       </c>
-      <c r="K111" s="12" t="n"/>
-      <c r="L111" s="12" t="n">
+      <c r="M111" s="12" t="n"/>
+      <c r="N111" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="M111" s="12" t="n"/>
-      <c r="N111" s="12" t="n"/>
-      <c r="O111" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O111" s="12" t="n"/>
       <c r="P111" s="12" t="n"/>
-      <c r="Q111" s="12" t="n"/>
+      <c r="Q111" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R111" s="12" t="inlineStr">
         <is>
+          <t>3320</t>
+        </is>
+      </c>
+      <c r="S111" s="12" t="n"/>
+      <c r="T111" s="12" t="inlineStr">
+        <is>
           <t>보스 피해 +40%</t>
         </is>
       </c>
-      <c r="S111" s="12" t="n"/>
+      <c r="U111" s="12" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="12" t="n">
@@ -7918,32 +9024,42 @@
       <c r="I112" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J112" s="12" t="inlineStr">
+      <c r="J112" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L112" s="12" t="inlineStr">
         <is>
           <t>clone_bar_duration</t>
         </is>
       </c>
-      <c r="K112" s="12" t="n"/>
-      <c r="L112" s="12" t="n">
+      <c r="M112" s="12" t="n"/>
+      <c r="N112" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="M112" s="12" t="n">
+      <c r="O112" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="N112" s="12" t="n"/>
-      <c r="O112" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P112" s="12" t="n"/>
-      <c r="Q112" s="12" t="n"/>
+      <c r="Q112" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R112" s="12" t="inlineStr">
         <is>
+          <t>3115</t>
+        </is>
+      </c>
+      <c r="S112" s="12" t="n"/>
+      <c r="T112" s="12" t="inlineStr">
+        <is>
           <t>10% 확률로 3초 분신 바</t>
         </is>
       </c>
-      <c r="S112" s="12" t="inlineStr">
+      <c r="U112" s="12" t="inlineStr">
         <is>
           <t>param = 발동 확률</t>
         </is>
@@ -7987,30 +9103,40 @@
       <c r="I113" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J113" s="12" t="inlineStr">
+      <c r="J113" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K113" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L113" s="12" t="inlineStr">
         <is>
           <t>round_time</t>
         </is>
       </c>
-      <c r="K113" s="12" t="n"/>
-      <c r="L113" s="12" t="n">
+      <c r="M113" s="12" t="n"/>
+      <c r="N113" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="M113" s="12" t="n"/>
-      <c r="N113" s="12" t="n"/>
-      <c r="O113" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O113" s="12" t="n"/>
       <c r="P113" s="12" t="n"/>
-      <c r="Q113" s="12" t="n"/>
+      <c r="Q113" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R113" s="12" t="inlineStr">
         <is>
+          <t>3321</t>
+        </is>
+      </c>
+      <c r="S113" s="12" t="n"/>
+      <c r="T113" s="12" t="inlineStr">
+        <is>
           <t>지속 시간 +3초 (18 → 21)</t>
         </is>
       </c>
-      <c r="S113" s="12" t="n"/>
+      <c r="U113" s="12" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="12" t="n">
@@ -8050,30 +9176,40 @@
       <c r="I114" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J114" s="12" t="inlineStr">
+      <c r="J114" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K114" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L114" s="12" t="inlineStr">
         <is>
           <t>harvester_speed</t>
         </is>
       </c>
-      <c r="K114" s="12" t="n"/>
-      <c r="L114" s="12" t="n">
+      <c r="M114" s="12" t="n"/>
+      <c r="N114" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="M114" s="12" t="n"/>
-      <c r="N114" s="12" t="n"/>
-      <c r="O114" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O114" s="12" t="n"/>
       <c r="P114" s="12" t="n"/>
-      <c r="Q114" s="12" t="n"/>
+      <c r="Q114" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R114" s="12" t="inlineStr">
         <is>
+          <t>3323</t>
+        </is>
+      </c>
+      <c r="S114" s="12" t="n"/>
+      <c r="T114" s="12" t="inlineStr">
+        <is>
           <t>수확기 속도 +30%</t>
         </is>
       </c>
-      <c r="S114" s="12" t="n"/>
+      <c r="U114" s="12" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="12" t="n">
@@ -8113,30 +9249,40 @@
       <c r="I115" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J115" s="12" t="inlineStr">
+      <c r="J115" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K115" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L115" s="12" t="inlineStr">
         <is>
           <t>combo_rate</t>
         </is>
       </c>
-      <c r="K115" s="12" t="n"/>
-      <c r="L115" s="12" t="n">
+      <c r="M115" s="12" t="n"/>
+      <c r="N115" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="M115" s="12" t="n"/>
-      <c r="N115" s="12" t="n"/>
-      <c r="O115" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O115" s="12" t="n"/>
       <c r="P115" s="12" t="n"/>
-      <c r="Q115" s="12" t="n"/>
+      <c r="Q115" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R115" s="12" t="inlineStr">
         <is>
+          <t>3221</t>
+        </is>
+      </c>
+      <c r="S115" s="12" t="n"/>
+      <c r="T115" s="12" t="inlineStr">
+        <is>
           <t>콤보 계수 +60%</t>
         </is>
       </c>
-      <c r="S115" s="12" t="n"/>
+      <c r="U115" s="12" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="12" t="n">
@@ -8176,30 +9322,40 @@
       <c r="I116" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J116" s="12" t="inlineStr">
+      <c r="J116" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K116" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L116" s="12" t="inlineStr">
         <is>
           <t>orbit_harvester_count</t>
         </is>
       </c>
-      <c r="K116" s="12" t="n"/>
-      <c r="L116" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="M116" s="12" t="n"/>
-      <c r="N116" s="12" t="n"/>
-      <c r="O116" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N116" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O116" s="12" t="n"/>
       <c r="P116" s="12" t="n"/>
-      <c r="Q116" s="12" t="n"/>
+      <c r="Q116" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R116" s="12" t="inlineStr">
         <is>
+          <t>3223</t>
+        </is>
+      </c>
+      <c r="S116" s="12" t="n"/>
+      <c r="T116" s="12" t="inlineStr">
+        <is>
           <t>회전 꼬마 수확기 +1 (1 → 2)</t>
         </is>
       </c>
-      <c r="S116" s="12" t="n"/>
+      <c r="U116" s="12" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="12" t="n">
@@ -8239,30 +9395,40 @@
       <c r="I117" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J117" s="12" t="inlineStr">
+      <c r="J117" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K117" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L117" s="12" t="inlineStr">
         <is>
           <t>orbit_harvester_damage</t>
         </is>
       </c>
-      <c r="K117" s="12" t="n"/>
-      <c r="L117" s="12" t="n">
+      <c r="M117" s="12" t="n"/>
+      <c r="N117" s="12" t="n">
         <v>0.05</v>
       </c>
-      <c r="M117" s="12" t="n"/>
-      <c r="N117" s="12" t="n"/>
-      <c r="O117" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O117" s="12" t="n"/>
       <c r="P117" s="12" t="n"/>
-      <c r="Q117" s="12" t="n"/>
+      <c r="Q117" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R117" s="12" t="inlineStr">
         <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="S117" s="12" t="n"/>
+      <c r="T117" s="12" t="inlineStr">
+        <is>
           <t>회전 꼬마 수확기 공격력 5%</t>
         </is>
       </c>
-      <c r="S117" s="12" t="n"/>
+      <c r="U117" s="12" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="12" t="n">
@@ -8302,30 +9468,40 @@
       <c r="I118" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J118" s="12" t="inlineStr">
+      <c r="J118" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K118" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L118" s="12" t="inlineStr">
         <is>
           <t>boss_damage</t>
         </is>
       </c>
-      <c r="K118" s="12" t="n"/>
-      <c r="L118" s="12" t="n">
+      <c r="M118" s="12" t="n"/>
+      <c r="N118" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="M118" s="12" t="n"/>
-      <c r="N118" s="12" t="n"/>
-      <c r="O118" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O118" s="12" t="n"/>
       <c r="P118" s="12" t="n"/>
-      <c r="Q118" s="12" t="n"/>
+      <c r="Q118" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R118" s="12" t="inlineStr">
         <is>
+          <t>3325</t>
+        </is>
+      </c>
+      <c r="S118" s="12" t="n"/>
+      <c r="T118" s="12" t="inlineStr">
+        <is>
           <t>보스 피해 +60%</t>
         </is>
       </c>
-      <c r="S118" s="12" t="n"/>
+      <c r="U118" s="12" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="12" t="n">
@@ -8365,32 +9541,42 @@
       <c r="I119" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J119" s="12" t="inlineStr">
+      <c r="J119" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K119" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L119" s="12" t="inlineStr">
         <is>
           <t>clone_bar_duration</t>
         </is>
       </c>
-      <c r="K119" s="12" t="n"/>
-      <c r="L119" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M119" s="12" t="n">
+      <c r="M119" s="12" t="n"/>
+      <c r="N119" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O119" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="N119" s="12" t="n"/>
-      <c r="O119" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P119" s="12" t="n"/>
-      <c r="Q119" s="12" t="n"/>
+      <c r="Q119" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R119" s="12" t="inlineStr">
         <is>
+          <t>3327</t>
+        </is>
+      </c>
+      <c r="S119" s="12" t="n"/>
+      <c r="T119" s="12" t="inlineStr">
+        <is>
           <t>10% 확률로 4초 분신 바</t>
         </is>
       </c>
-      <c r="S119" s="12" t="n"/>
+      <c r="U119" s="12" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="12" t="n">
@@ -8430,30 +9616,40 @@
       <c r="I120" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J120" s="12" t="inlineStr">
+      <c r="J120" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K120" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L120" s="12" t="inlineStr">
         <is>
           <t>combo_rate</t>
         </is>
       </c>
-      <c r="K120" s="12" t="n"/>
-      <c r="L120" s="12" t="n">
+      <c r="M120" s="12" t="n"/>
+      <c r="N120" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="M120" s="12" t="n"/>
-      <c r="N120" s="12" t="n"/>
-      <c r="O120" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O120" s="12" t="n"/>
       <c r="P120" s="12" t="n"/>
-      <c r="Q120" s="12" t="n"/>
+      <c r="Q120" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R120" s="12" t="inlineStr">
         <is>
+          <t>3328</t>
+        </is>
+      </c>
+      <c r="S120" s="12" t="n"/>
+      <c r="T120" s="12" t="inlineStr">
+        <is>
           <t>콤보 계수 +80%</t>
         </is>
       </c>
-      <c r="S120" s="12" t="n"/>
+      <c r="U120" s="12" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="12" t="n">
@@ -8493,30 +9689,40 @@
       <c r="I121" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J121" s="12" t="inlineStr">
+      <c r="J121" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K121" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L121" s="12" t="inlineStr">
         <is>
           <t>crit_damage</t>
         </is>
       </c>
-      <c r="K121" s="12" t="n"/>
-      <c r="L121" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="M121" s="12" t="n"/>
-      <c r="N121" s="12" t="n"/>
-      <c r="O121" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N121" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O121" s="12" t="n"/>
       <c r="P121" s="12" t="n"/>
-      <c r="Q121" s="12" t="n"/>
+      <c r="Q121" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R121" s="12" t="inlineStr">
         <is>
+          <t>3224</t>
+        </is>
+      </c>
+      <c r="S121" s="12" t="n"/>
+      <c r="T121" s="12" t="inlineStr">
+        <is>
           <t>치명타 피해 100%</t>
         </is>
       </c>
-      <c r="S121" s="12" t="n"/>
+      <c r="U121" s="12" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="12" t="n">
@@ -8556,30 +9762,40 @@
       <c r="I122" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J122" s="12" t="inlineStr">
+      <c r="J122" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K122" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L122" s="12" t="inlineStr">
         <is>
           <t>crit_chance</t>
         </is>
       </c>
-      <c r="K122" s="12" t="n"/>
-      <c r="L122" s="12" t="n">
+      <c r="M122" s="12" t="n"/>
+      <c r="N122" s="12" t="n">
         <v>0.02</v>
       </c>
-      <c r="M122" s="12" t="n"/>
-      <c r="N122" s="12" t="n"/>
-      <c r="O122" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O122" s="12" t="n"/>
       <c r="P122" s="12" t="n"/>
-      <c r="Q122" s="12" t="n"/>
+      <c r="Q122" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R122" s="12" t="inlineStr">
         <is>
+          <t>3226</t>
+        </is>
+      </c>
+      <c r="S122" s="12" t="n"/>
+      <c r="T122" s="12" t="inlineStr">
+        <is>
           <t>치명타 확률 8%</t>
         </is>
       </c>
-      <c r="S122" s="12" t="n"/>
+      <c r="U122" s="12" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="12" t="n">
@@ -8619,30 +9835,40 @@
       <c r="I123" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J123" s="12" t="inlineStr">
+      <c r="J123" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K123" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L123" s="12" t="inlineStr">
         <is>
           <t>round_time</t>
         </is>
       </c>
-      <c r="K123" s="12" t="n"/>
-      <c r="L123" s="12" t="n">
+      <c r="M123" s="12" t="n"/>
+      <c r="N123" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="M123" s="12" t="n"/>
-      <c r="N123" s="12" t="n"/>
-      <c r="O123" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O123" s="12" t="n"/>
       <c r="P123" s="12" t="n"/>
-      <c r="Q123" s="12" t="n"/>
+      <c r="Q123" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R123" s="12" t="inlineStr">
         <is>
+          <t>3332</t>
+        </is>
+      </c>
+      <c r="S123" s="12" t="n"/>
+      <c r="T123" s="12" t="inlineStr">
+        <is>
           <t>지속 시간 +3초 (21 → 24)</t>
         </is>
       </c>
-      <c r="S123" s="12" t="n"/>
+      <c r="U123" s="12" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="12" t="n">
@@ -8682,30 +9908,40 @@
       <c r="I124" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J124" s="12" t="inlineStr">
+      <c r="J124" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K124" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L124" s="12" t="inlineStr">
         <is>
           <t>round_time</t>
         </is>
       </c>
-      <c r="K124" s="12" t="n"/>
-      <c r="L124" s="12" t="n">
+      <c r="M124" s="12" t="n"/>
+      <c r="N124" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="M124" s="12" t="n"/>
-      <c r="N124" s="12" t="n"/>
-      <c r="O124" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O124" s="12" t="n"/>
       <c r="P124" s="12" t="n"/>
-      <c r="Q124" s="12" t="n"/>
+      <c r="Q124" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R124" s="12" t="inlineStr">
         <is>
+          <t>3333</t>
+        </is>
+      </c>
+      <c r="S124" s="12" t="n"/>
+      <c r="T124" s="12" t="inlineStr">
+        <is>
           <t>지속 시간 +3초 (24 → 27)</t>
         </is>
       </c>
-      <c r="S124" s="12" t="inlineStr">
+      <c r="U124" s="12" t="inlineStr">
         <is>
           <t>원문은 Lv.3과 같은 레어도 14</t>
         </is>
@@ -8749,30 +9985,40 @@
       <c r="I125" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J125" s="12" t="inlineStr">
+      <c r="J125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L125" s="12" t="inlineStr">
         <is>
           <t>boss_damage</t>
         </is>
       </c>
-      <c r="K125" s="12" t="n"/>
-      <c r="L125" s="12" t="n">
+      <c r="M125" s="12" t="n"/>
+      <c r="N125" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="M125" s="12" t="n"/>
-      <c r="N125" s="12" t="n"/>
-      <c r="O125" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O125" s="12" t="n"/>
       <c r="P125" s="12" t="n"/>
-      <c r="Q125" s="12" t="n"/>
+      <c r="Q125" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R125" s="12" t="inlineStr">
         <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="S125" s="12" t="n"/>
+      <c r="T125" s="12" t="inlineStr">
+        <is>
           <t>보스 피해 +80%</t>
         </is>
       </c>
-      <c r="S125" s="12" t="n"/>
+      <c r="U125" s="12" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="12" t="n">
@@ -8812,30 +10058,40 @@
       <c r="I126" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J126" s="12" t="inlineStr">
+      <c r="J126" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K126" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L126" s="12" t="inlineStr">
         <is>
           <t>combo_rate</t>
         </is>
       </c>
-      <c r="K126" s="12" t="n"/>
-      <c r="L126" s="12" t="n">
+      <c r="M126" s="12" t="n"/>
+      <c r="N126" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="M126" s="12" t="n"/>
-      <c r="N126" s="12" t="n"/>
-      <c r="O126" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O126" s="12" t="n"/>
       <c r="P126" s="12" t="n"/>
-      <c r="Q126" s="12" t="n"/>
+      <c r="Q126" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R126" s="12" t="inlineStr">
         <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="S126" s="12" t="n"/>
+      <c r="T126" s="12" t="inlineStr">
+        <is>
           <t>콤보 계수 +100%</t>
         </is>
       </c>
-      <c r="S126" s="12" t="n"/>
+      <c r="U126" s="12" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="12" t="n">
@@ -8875,30 +10131,40 @@
       <c r="I127" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J127" s="12" t="inlineStr">
+      <c r="J127" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K127" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L127" s="12" t="inlineStr">
         <is>
           <t>orbit_harvester_damage</t>
         </is>
       </c>
-      <c r="K127" s="12" t="n"/>
-      <c r="L127" s="12" t="n">
+      <c r="M127" s="12" t="n"/>
+      <c r="N127" s="12" t="n">
         <v>0.05</v>
       </c>
-      <c r="M127" s="12" t="n"/>
-      <c r="N127" s="12" t="n"/>
-      <c r="O127" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O127" s="12" t="n"/>
       <c r="P127" s="12" t="n"/>
-      <c r="Q127" s="12" t="n"/>
+      <c r="Q127" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R127" s="12" t="inlineStr">
         <is>
+          <t>3334</t>
+        </is>
+      </c>
+      <c r="S127" s="12" t="n"/>
+      <c r="T127" s="12" t="inlineStr">
+        <is>
           <t>회전 꼬마 수확기 공격력 10%</t>
         </is>
       </c>
-      <c r="S127" s="12" t="n"/>
+      <c r="U127" s="12" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="12" t="n">
@@ -8938,30 +10204,40 @@
       <c r="I128" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J128" s="12" t="inlineStr">
+      <c r="J128" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L128" s="12" t="inlineStr">
         <is>
           <t>harvester_damage</t>
         </is>
       </c>
-      <c r="K128" s="12" t="n"/>
-      <c r="L128" s="12" t="n">
+      <c r="M128" s="12" t="n"/>
+      <c r="N128" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="M128" s="12" t="n"/>
-      <c r="N128" s="12" t="n"/>
-      <c r="O128" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O128" s="12" t="n"/>
       <c r="P128" s="12" t="n"/>
-      <c r="Q128" s="12" t="n"/>
+      <c r="Q128" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R128" s="12" t="inlineStr">
         <is>
+          <t>3335</t>
+        </is>
+      </c>
+      <c r="S128" s="12" t="n"/>
+      <c r="T128" s="12" t="inlineStr">
+        <is>
           <t>공격력 +5 (10 → 15)</t>
         </is>
       </c>
-      <c r="S128" s="12" t="n"/>
+      <c r="U128" s="12" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="12" t="n">
@@ -9001,30 +10277,40 @@
       <c r="I129" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="J129" s="12" t="inlineStr">
+      <c r="J129" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K129" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="L129" s="12" t="inlineStr">
         <is>
           <t>harvester_slot</t>
         </is>
       </c>
-      <c r="K129" s="12" t="n"/>
-      <c r="L129" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="M129" s="12" t="n"/>
-      <c r="N129" s="12" t="n"/>
-      <c r="O129" s="12" t="inlineStr">
+      <c r="N129" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" s="12" t="n"/>
+      <c r="P129" s="12" t="n"/>
+      <c r="Q129" s="12" t="inlineStr">
         <is>
           <t>Mycelite</t>
         </is>
       </c>
-      <c r="P129" s="12" t="n"/>
-      <c r="Q129" s="12" t="n"/>
       <c r="R129" s="12" t="inlineStr">
         <is>
+          <t>3337</t>
+        </is>
+      </c>
+      <c r="S129" s="12" t="n"/>
+      <c r="T129" s="12" t="inlineStr">
+        <is>
           <t>수확기 개수 +1 / Lv (최대 5개 장착)</t>
         </is>
       </c>
-      <c r="S129" s="12" t="n"/>
+      <c r="U129" s="12" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="12" t="n">
@@ -9064,30 +10350,40 @@
       <c r="I130" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J130" s="12" t="inlineStr">
+      <c r="J130" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="L130" s="12" t="inlineStr">
         <is>
           <t>boss_damage</t>
         </is>
       </c>
-      <c r="K130" s="12" t="n"/>
-      <c r="L130" s="12" t="n">
+      <c r="M130" s="12" t="n"/>
+      <c r="N130" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="M130" s="12" t="n"/>
-      <c r="N130" s="12" t="n"/>
-      <c r="O130" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O130" s="12" t="n"/>
       <c r="P130" s="12" t="n"/>
-      <c r="Q130" s="12" t="n"/>
+      <c r="Q130" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R130" s="12" t="inlineStr">
         <is>
+          <t>3338</t>
+        </is>
+      </c>
+      <c r="S130" s="12" t="n"/>
+      <c r="T130" s="12" t="inlineStr">
+        <is>
           <t>보스 피해 +100%</t>
         </is>
       </c>
-      <c r="S130" s="12" t="n"/>
+      <c r="U130" s="12" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="12" t="n">
@@ -9127,32 +10423,42 @@
       <c r="I131" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J131" s="12" t="inlineStr">
+      <c r="J131" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K131" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="L131" s="12" t="inlineStr">
         <is>
           <t>clone_bar_duration</t>
         </is>
       </c>
-      <c r="K131" s="12" t="n"/>
-      <c r="L131" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M131" s="12" t="n">
+      <c r="M131" s="12" t="n"/>
+      <c r="N131" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O131" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="N131" s="12" t="n"/>
-      <c r="O131" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="P131" s="12" t="n"/>
-      <c r="Q131" s="12" t="n"/>
+      <c r="Q131" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R131" s="12" t="inlineStr">
         <is>
+          <t>3133</t>
+        </is>
+      </c>
+      <c r="S131" s="12" t="n"/>
+      <c r="T131" s="12" t="inlineStr">
+        <is>
           <t>10% 확률로 5초 분신 바</t>
         </is>
       </c>
-      <c r="S131" s="12" t="n"/>
+      <c r="U131" s="12" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="12" t="n">
@@ -9192,30 +10498,40 @@
       <c r="I132" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J132" s="12" t="inlineStr">
+      <c r="J132" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K132" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L132" s="12" t="inlineStr">
         <is>
           <t>crit_chance</t>
         </is>
       </c>
-      <c r="K132" s="12" t="n"/>
-      <c r="L132" s="12" t="n">
+      <c r="M132" s="12" t="n"/>
+      <c r="N132" s="12" t="n">
         <v>0.02</v>
       </c>
-      <c r="M132" s="12" t="n"/>
-      <c r="N132" s="12" t="n"/>
-      <c r="O132" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O132" s="12" t="n"/>
       <c r="P132" s="12" t="n"/>
-      <c r="Q132" s="12" t="n"/>
+      <c r="Q132" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R132" s="12" t="inlineStr">
         <is>
+          <t>3341</t>
+        </is>
+      </c>
+      <c r="S132" s="12" t="n"/>
+      <c r="T132" s="12" t="inlineStr">
+        <is>
           <t>치명타 확률 10%</t>
         </is>
       </c>
-      <c r="S132" s="12" t="n"/>
+      <c r="U132" s="12" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="12" t="n">
@@ -9255,30 +10571,40 @@
       <c r="I133" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J133" s="12" t="inlineStr">
+      <c r="J133" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K133" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L133" s="12" t="inlineStr">
         <is>
           <t>clone_bar_count</t>
         </is>
       </c>
-      <c r="K133" s="12" t="n"/>
-      <c r="L133" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="M133" s="12" t="n"/>
-      <c r="N133" s="12" t="n"/>
-      <c r="O133" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N133" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O133" s="12" t="n"/>
       <c r="P133" s="12" t="n"/>
-      <c r="Q133" s="12" t="n"/>
+      <c r="Q133" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R133" s="12" t="inlineStr">
         <is>
+          <t>3339</t>
+        </is>
+      </c>
+      <c r="S133" s="12" t="n"/>
+      <c r="T133" s="12" t="inlineStr">
+        <is>
           <t>분신 바 +1 (1 → 2)</t>
         </is>
       </c>
-      <c r="S133" s="12" t="n"/>
+      <c r="U133" s="12" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="12" t="n">
@@ -9318,30 +10644,40 @@
       <c r="I134" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J134" s="12" t="inlineStr">
+      <c r="J134" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K134" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="L134" s="12" t="inlineStr">
         <is>
           <t>orbit_harvester_count</t>
         </is>
       </c>
-      <c r="K134" s="12" t="n"/>
-      <c r="L134" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="M134" s="12" t="n"/>
-      <c r="N134" s="12" t="n"/>
-      <c r="O134" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="N134" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O134" s="12" t="n"/>
       <c r="P134" s="12" t="n"/>
-      <c r="Q134" s="12" t="n"/>
+      <c r="Q134" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R134" s="12" t="inlineStr">
         <is>
+          <t>3342</t>
+        </is>
+      </c>
+      <c r="S134" s="12" t="n"/>
+      <c r="T134" s="12" t="inlineStr">
+        <is>
           <t>회전 꼬마 수확기 +1 (2 → 3)</t>
         </is>
       </c>
-      <c r="S134" s="12" t="n"/>
+      <c r="U134" s="12" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="12" t="n">
@@ -9381,30 +10717,40 @@
       <c r="I135" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J135" s="12" t="inlineStr">
+      <c r="J135" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K135" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="L135" s="12" t="inlineStr">
         <is>
           <t>orbit_harvester_damage</t>
         </is>
       </c>
-      <c r="K135" s="12" t="n"/>
-      <c r="L135" s="12" t="n">
+      <c r="M135" s="12" t="n"/>
+      <c r="N135" s="12" t="n">
         <v>0.05</v>
       </c>
-      <c r="M135" s="12" t="n"/>
-      <c r="N135" s="12" t="n"/>
-      <c r="O135" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O135" s="12" t="n"/>
       <c r="P135" s="12" t="n"/>
-      <c r="Q135" s="12" t="n"/>
+      <c r="Q135" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R135" s="12" t="inlineStr">
         <is>
+          <t>3343</t>
+        </is>
+      </c>
+      <c r="S135" s="12" t="n"/>
+      <c r="T135" s="12" t="inlineStr">
+        <is>
           <t>회전 꼬마 수확기 공격력 15%</t>
         </is>
       </c>
-      <c r="S135" s="12" t="n"/>
+      <c r="U135" s="12" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="12" t="n">
@@ -9444,30 +10790,40 @@
       <c r="I136" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J136" s="12" t="inlineStr">
+      <c r="J136" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K136" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="L136" s="12" t="inlineStr">
         <is>
           <t>crit_damage</t>
         </is>
       </c>
-      <c r="K136" s="12" t="n"/>
-      <c r="L136" s="12" t="n">
+      <c r="M136" s="12" t="n"/>
+      <c r="N136" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="M136" s="12" t="n"/>
-      <c r="N136" s="12" t="n"/>
-      <c r="O136" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O136" s="12" t="n"/>
       <c r="P136" s="12" t="n"/>
-      <c r="Q136" s="12" t="n"/>
+      <c r="Q136" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R136" s="12" t="inlineStr">
         <is>
+          <t>3344</t>
+        </is>
+      </c>
+      <c r="S136" s="12" t="n"/>
+      <c r="T136" s="12" t="inlineStr">
+        <is>
           <t>치명타 피해 120%</t>
         </is>
       </c>
-      <c r="S136" s="12" t="inlineStr">
+      <c r="U136" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +20%</t>
         </is>
@@ -9511,30 +10867,40 @@
       <c r="I137" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J137" s="12" t="inlineStr">
+      <c r="J137" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K137" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="L137" s="12" t="inlineStr">
         <is>
           <t>crit_damage</t>
         </is>
       </c>
-      <c r="K137" s="12" t="n"/>
-      <c r="L137" s="12" t="n">
+      <c r="M137" s="12" t="n"/>
+      <c r="N137" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="M137" s="12" t="n"/>
-      <c r="N137" s="12" t="n"/>
-      <c r="O137" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O137" s="12" t="n"/>
       <c r="P137" s="12" t="n"/>
-      <c r="Q137" s="12" t="n"/>
+      <c r="Q137" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R137" s="12" t="inlineStr">
         <is>
+          <t>3346</t>
+        </is>
+      </c>
+      <c r="S137" s="12" t="n"/>
+      <c r="T137" s="12" t="inlineStr">
+        <is>
           <t>치명타 피해 150%</t>
         </is>
       </c>
-      <c r="S137" s="12" t="inlineStr">
+      <c r="U137" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +30%</t>
         </is>
@@ -9578,30 +10944,40 @@
       <c r="I138" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J138" s="12" t="inlineStr">
+      <c r="J138" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="L138" s="12" t="inlineStr">
         <is>
           <t>round_time</t>
         </is>
       </c>
-      <c r="K138" s="12" t="n"/>
-      <c r="L138" s="12" t="n">
+      <c r="M138" s="12" t="n"/>
+      <c r="N138" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="M138" s="12" t="n"/>
-      <c r="N138" s="12" t="n"/>
-      <c r="O138" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
+      <c r="O138" s="12" t="n"/>
       <c r="P138" s="12" t="n"/>
-      <c r="Q138" s="12" t="n"/>
+      <c r="Q138" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="R138" s="12" t="inlineStr">
         <is>
+          <t>3347</t>
+        </is>
+      </c>
+      <c r="S138" s="12" t="n"/>
+      <c r="T138" s="12" t="inlineStr">
+        <is>
           <t>지속 시간 +3초 (27 → 30)</t>
         </is>
       </c>
-      <c r="S138" s="12" t="n"/>
+      <c r="U138" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/Data/Tables/Skill.xlsx
+++ b/Assets/Data/Tables/Skill.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U138"/>
+  <dimension ref="A1:V138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="11" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="48" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
     <col width="52" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -621,20 +621,25 @@
       </c>
       <c r="R1" s="5" t="inlineStr">
         <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="S1" s="5" t="inlineStr">
+        <is>
           <t>requires</t>
         </is>
       </c>
-      <c r="S1" s="5" t="inlineStr">
+      <c r="T1" s="5" t="inlineStr">
         <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="T1" s="5" t="inlineStr">
+      <c r="U1" s="5" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="U1" s="6" t="inlineStr">
+      <c r="V1" s="6" t="inlineStr">
         <is>
           <t>#memo</t>
         </is>
@@ -728,20 +733,25 @@
       </c>
       <c r="R2" s="7" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
           <t>int[]</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
+      <c r="T2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="T2" s="7" t="inlineStr">
+      <c r="U2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="U2" s="7" t="n"/>
+      <c r="V2" s="7" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
@@ -831,20 +841,25 @@
       </c>
       <c r="R3" s="8" t="inlineStr">
         <is>
-          <t>선행 스킬 index (쉼표 구분, 트리 연결 미정)</t>
+          <t>연결 노드 index. 트리에 선으로 그리고, 1레벨 이상 배우면 열린다</t>
         </is>
       </c>
       <c r="S3" s="8" t="inlineStr">
         <is>
+          <t>이전 레벨 노드 index (쉼표 구분). 최대 레벨까지 배워야 열린다</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
           <t>아이콘 경로 (Resources 기준)</t>
         </is>
       </c>
-      <c r="T3" s="8" t="inlineStr">
+      <c r="U3" s="8" t="inlineStr">
         <is>
           <t>인게임 설명</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
+      <c r="V3" s="8" t="inlineStr">
         <is>
           <t>기획 메모 (게임에서 읽지 않음)</t>
         </is>
@@ -914,12 +929,13 @@
       </c>
       <c r="R4" s="9" t="n"/>
       <c r="S4" s="9" t="n"/>
-      <c r="T4" s="9" t="inlineStr">
+      <c r="T4" s="9" t="n"/>
+      <c r="U4" s="9" t="inlineStr">
         <is>
           <t>공격력 +2 (3초) 버프 / Lv</t>
         </is>
       </c>
-      <c r="U4" s="9" t="inlineStr">
+      <c r="V4" s="9" t="inlineStr">
         <is>
           <t>첫 레벨업은 골드, 이후 균사석 — currency 한 칸이라 가격 구조 정해지면 열 추가 필요. param = 버프 지속(초)</t>
         </is>
@@ -985,18 +1001,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R5" s="10" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
+      <c r="R5" s="10" t="n">
+        <v>3001</v>
       </c>
       <c r="S5" s="10" t="n"/>
-      <c r="T5" s="10" t="inlineStr">
+      <c r="T5" s="10" t="n"/>
+      <c r="U5" s="10" t="inlineStr">
         <is>
           <t>획득 점수 +10% / Lv</t>
         </is>
       </c>
-      <c r="U5" s="10" t="n"/>
+      <c r="V5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="n">
@@ -1058,18 +1073,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R6" s="10" t="inlineStr">
-        <is>
-          <t>3101</t>
-        </is>
+      <c r="R6" s="10" t="n">
+        <v>3101</v>
       </c>
       <c r="S6" s="10" t="n"/>
-      <c r="T6" s="10" t="inlineStr">
+      <c r="T6" s="10" t="n"/>
+      <c r="U6" s="10" t="inlineStr">
         <is>
           <t>점수 골드 전환율 +10%</t>
         </is>
       </c>
-      <c r="U6" s="10" t="n"/>
+      <c r="V6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="n">
@@ -1131,18 +1145,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R7" s="10" t="inlineStr">
-        <is>
-          <t>3102</t>
-        </is>
+      <c r="R7" s="10" t="n">
+        <v>3101</v>
       </c>
       <c r="S7" s="10" t="n"/>
-      <c r="T7" s="10" t="inlineStr">
+      <c r="T7" s="10" t="n"/>
+      <c r="U7" s="10" t="inlineStr">
         <is>
           <t>군락지 수 +1 (3 → 4)</t>
         </is>
       </c>
-      <c r="U7" s="10" t="n"/>
+      <c r="V7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="n">
@@ -1204,18 +1217,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R8" s="10" t="inlineStr">
-        <is>
-          <t>3103</t>
-        </is>
+      <c r="R8" s="10" t="n">
+        <v>3103</v>
       </c>
       <c r="S8" s="10" t="n"/>
-      <c r="T8" s="10" t="inlineStr">
+      <c r="T8" s="10" t="n"/>
+      <c r="U8" s="10" t="inlineStr">
         <is>
           <t>군락지 주변 단일 버섯 +1 (3 → 4)</t>
         </is>
       </c>
-      <c r="U8" s="10" t="n"/>
+      <c r="V8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="n">
@@ -1256,7 +1268,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K9" s="10" t="n">
         <v>4</v>
@@ -1277,18 +1289,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R9" s="10" t="inlineStr">
-        <is>
-          <t>3306</t>
-        </is>
+      <c r="R9" s="10" t="n">
+        <v>3102</v>
       </c>
       <c r="S9" s="10" t="n"/>
-      <c r="T9" s="10" t="inlineStr">
+      <c r="T9" s="10" t="n"/>
+      <c r="U9" s="10" t="inlineStr">
         <is>
           <t>일반 버섯 수확량 +5%</t>
         </is>
       </c>
-      <c r="U9" s="10" t="n"/>
+      <c r="V9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n">
@@ -1329,10 +1340,10 @@
         <v>3</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K10" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
@@ -1352,18 +1363,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R10" s="10" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
+      <c r="R10" s="10" t="n">
+        <v>3103</v>
       </c>
       <c r="S10" s="10" t="n"/>
-      <c r="T10" s="10" t="inlineStr">
+      <c r="T10" s="10" t="n"/>
+      <c r="U10" s="10" t="inlineStr">
         <is>
           <t>에픽 버섯 스폰율 +10% / +15% / +20%</t>
         </is>
       </c>
-      <c r="U10" s="10" t="inlineStr">
+      <c r="V10" s="10" t="inlineStr">
         <is>
           <t>Lv.1 10, Lv.2 15, Lv.3 20 → base 5% + 5%/Lv</t>
         </is>
@@ -1408,7 +1418,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" s="10" t="n">
         <v>5</v>
@@ -1429,18 +1439,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R11" s="10" t="inlineStr">
+      <c r="R11" s="10" t="n">
+        <v>3102</v>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>3105</t>
         </is>
       </c>
-      <c r="S11" s="10" t="n"/>
-      <c r="T11" s="10" t="inlineStr">
+      <c r="T11" s="10" t="n"/>
+      <c r="U11" s="10" t="inlineStr">
         <is>
           <t>일반 버섯 수확량 +10%</t>
         </is>
       </c>
-      <c r="U11" s="10" t="inlineStr">
+      <c r="V11" s="10" t="inlineStr">
         <is>
           <t>원문 % = 누적값으로 보고 차이(+5%)만 더함</t>
         </is>
@@ -1485,10 +1498,10 @@
         <v>1</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
@@ -1506,18 +1519,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R12" s="10" t="inlineStr">
-        <is>
-          <t>3311</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="n"/>
-      <c r="T12" s="10" t="inlineStr">
+      <c r="R12" s="10" t="n">
+        <v>3105</v>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="T12" s="10" t="n"/>
+      <c r="U12" s="10" t="inlineStr">
         <is>
           <t>점수 골드 전환율 +15%</t>
         </is>
       </c>
-      <c r="U12" s="10" t="inlineStr">
+      <c r="V12" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -1562,7 +1578,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="10" t="n">
         <v>7</v>
@@ -1583,18 +1599,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R13" s="10" t="inlineStr">
-        <is>
-          <t>3210</t>
-        </is>
+      <c r="R13" s="10" t="n">
+        <v>3104</v>
       </c>
       <c r="S13" s="10" t="n"/>
-      <c r="T13" s="10" t="inlineStr">
+      <c r="T13" s="10" t="n"/>
+      <c r="U13" s="10" t="inlineStr">
         <is>
           <t>군락지 리스폰 −1초 (7 → 6)</t>
         </is>
       </c>
-      <c r="U13" s="10" t="n"/>
+      <c r="V13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n">
@@ -1635,10 +1650,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
@@ -1656,18 +1671,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R14" s="10" t="inlineStr">
+      <c r="R14" s="10" t="n">
+        <v>3107</v>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>3108</t>
         </is>
       </c>
-      <c r="S14" s="10" t="n"/>
-      <c r="T14" s="10" t="inlineStr">
+      <c r="T14" s="10" t="n"/>
+      <c r="U14" s="10" t="inlineStr">
         <is>
           <t>점수 골드 전환율 +20%</t>
         </is>
       </c>
-      <c r="U14" s="10" t="inlineStr">
+      <c r="V14" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -1712,7 +1730,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" s="10" t="n">
         <v>9</v>
@@ -1733,18 +1751,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R15" s="10" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="n"/>
-      <c r="T15" s="10" t="inlineStr">
+      <c r="R15" s="10" t="n">
+        <v>3106</v>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>3109</t>
+        </is>
+      </c>
+      <c r="T15" s="10" t="n"/>
+      <c r="U15" s="10" t="inlineStr">
         <is>
           <t>군락지 리스폰 −1초 (6 → 5)</t>
         </is>
       </c>
-      <c r="U15" s="10" t="n"/>
+      <c r="V15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
@@ -1785,7 +1806,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K16" s="10" t="n">
         <v>9</v>
@@ -1806,18 +1827,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R16" s="10" t="inlineStr">
-        <is>
-          <t>3215</t>
-        </is>
+      <c r="R16" s="10" t="n">
+        <v>3108</v>
       </c>
       <c r="S16" s="10" t="n"/>
-      <c r="T16" s="10" t="inlineStr">
+      <c r="T16" s="10" t="n"/>
+      <c r="U16" s="10" t="inlineStr">
         <is>
           <t>점수 3배 확률 +3%</t>
         </is>
       </c>
-      <c r="U16" s="10" t="n"/>
+      <c r="V16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n">
@@ -1879,18 +1899,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R17" s="10" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="n"/>
-      <c r="T17" s="10" t="inlineStr">
+      <c r="R17" s="10" t="n">
+        <v>3109</v>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="T17" s="10" t="n"/>
+      <c r="U17" s="10" t="inlineStr">
         <is>
           <t>군락지 수 +1 (4 → 5)</t>
         </is>
       </c>
-      <c r="U17" s="10" t="n"/>
+      <c r="V17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
@@ -1931,7 +1954,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" s="10" t="n">
         <v>11</v>
@@ -1952,18 +1975,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R18" s="10" t="inlineStr">
-        <is>
-          <t>3113</t>
-        </is>
+      <c r="R18" s="10" t="n">
+        <v>3110</v>
       </c>
       <c r="S18" s="10" t="n"/>
-      <c r="T18" s="10" t="inlineStr">
+      <c r="T18" s="10" t="n"/>
+      <c r="U18" s="10" t="inlineStr">
         <is>
           <t>에픽 버섯 수확량 +5%</t>
         </is>
       </c>
-      <c r="U18" s="10" t="n"/>
+      <c r="V18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n">
@@ -2025,18 +2047,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R19" s="10" t="inlineStr">
-        <is>
-          <t>3319</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="n"/>
-      <c r="T19" s="10" t="inlineStr">
+      <c r="R19" s="10" t="n">
+        <v>3109</v>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="T19" s="10" t="n"/>
+      <c r="U19" s="10" t="inlineStr">
         <is>
           <t>군락지 주변 단일 버섯 +1 (4 → 5)</t>
         </is>
       </c>
-      <c r="U19" s="10" t="n"/>
+      <c r="V19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
@@ -2077,7 +2102,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K20" s="10" t="n">
         <v>11</v>
@@ -2098,18 +2123,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R20" s="10" t="inlineStr">
-        <is>
-          <t>3218</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="n"/>
-      <c r="T20" s="10" t="inlineStr">
+      <c r="R20" s="10" t="n">
+        <v>3108</v>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>3107</t>
+        </is>
+      </c>
+      <c r="T20" s="10" t="n"/>
+      <c r="U20" s="10" t="inlineStr">
         <is>
           <t>일반 버섯 수확량 +15%</t>
         </is>
       </c>
-      <c r="U20" s="10" t="inlineStr">
+      <c r="V20" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -2154,7 +2182,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" s="10" t="n">
         <v>12</v>
@@ -2175,18 +2203,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R21" s="10" t="inlineStr">
-        <is>
-          <t>3114</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="n"/>
-      <c r="T21" s="10" t="inlineStr">
+      <c r="R21" s="10" t="n">
+        <v>3111</v>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>3113</t>
+        </is>
+      </c>
+      <c r="T21" s="10" t="n"/>
+      <c r="U21" s="10" t="inlineStr">
         <is>
           <t>군락지 수 +1 (5 → 6)</t>
         </is>
       </c>
-      <c r="U21" s="10" t="n"/>
+      <c r="V21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
@@ -2227,7 +2258,7 @@
         <v>1</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="10" t="n">
         <v>13</v>
@@ -2248,18 +2279,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R22" s="10" t="inlineStr">
-        <is>
-          <t>3117</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="n"/>
-      <c r="T22" s="10" t="inlineStr">
+      <c r="R22" s="10" t="n">
+        <v>3110</v>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>3112</t>
+        </is>
+      </c>
+      <c r="T22" s="10" t="n"/>
+      <c r="U22" s="10" t="inlineStr">
         <is>
           <t>점수 3배 확률 +5%</t>
         </is>
       </c>
-      <c r="U22" s="10" t="inlineStr">
+      <c r="V22" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -2304,7 +2338,7 @@
         <v>1</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K23" s="10" t="n">
         <v>13</v>
@@ -2325,18 +2359,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R23" s="10" t="inlineStr">
-        <is>
-          <t>3322</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="n"/>
-      <c r="T23" s="10" t="inlineStr">
+      <c r="R23" s="10" t="n">
+        <v>3111</v>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>3115</t>
+        </is>
+      </c>
+      <c r="T23" s="10" t="n"/>
+      <c r="U23" s="10" t="inlineStr">
         <is>
           <t>군락지 주변 단일 버섯 +1 (5 → 6)</t>
         </is>
       </c>
-      <c r="U23" s="10" t="n"/>
+      <c r="V23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
@@ -2377,10 +2414,10 @@
         <v>1</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K24" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
@@ -2398,18 +2435,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R24" s="10" t="inlineStr">
-        <is>
-          <t>3118</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="n"/>
-      <c r="T24" s="10" t="inlineStr">
+      <c r="R24" s="10" t="n">
+        <v>3114</v>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="T24" s="10" t="n"/>
+      <c r="U24" s="10" t="inlineStr">
         <is>
           <t>획득 점수 +40%</t>
         </is>
       </c>
-      <c r="U24" s="10" t="inlineStr">
+      <c r="V24" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%</t>
         </is>
@@ -2454,10 +2494,10 @@
         <v>1</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K25" s="10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
@@ -2475,18 +2515,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R25" s="10" t="inlineStr">
-        <is>
-          <t>3119</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="n"/>
-      <c r="T25" s="10" t="inlineStr">
+      <c r="R25" s="10" t="n">
+        <v>3113</v>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>3106</t>
+        </is>
+      </c>
+      <c r="T25" s="10" t="n"/>
+      <c r="U25" s="10" t="inlineStr">
         <is>
           <t>에픽 버섯 스폰율 +25%</t>
         </is>
       </c>
-      <c r="U25" s="10" t="inlineStr">
+      <c r="V25" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -2531,10 +2574,10 @@
         <v>1</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K26" s="10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
@@ -2552,18 +2595,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R26" s="10" t="inlineStr">
-        <is>
-          <t>3120</t>
-        </is>
+      <c r="R26" s="10" t="n">
+        <v>3112</v>
       </c>
       <c r="S26" s="10" t="n"/>
-      <c r="T26" s="10" t="inlineStr">
+      <c r="T26" s="10" t="n"/>
+      <c r="U26" s="10" t="inlineStr">
         <is>
           <t>점수 골드 전환율 +30%</t>
         </is>
       </c>
-      <c r="U26" s="10" t="inlineStr">
+      <c r="V26" s="10" t="inlineStr">
         <is>
           <t>흥정 기술의 상위. 누적값 기준 차이 +10%</t>
         </is>
@@ -2608,10 +2650,10 @@
         <v>1</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27" s="10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
@@ -2629,18 +2671,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R27" s="10" t="inlineStr">
-        <is>
-          <t>3121</t>
-        </is>
+      <c r="R27" s="10" t="n">
+        <v>3117</v>
       </c>
       <c r="S27" s="10" t="n"/>
-      <c r="T27" s="10" t="inlineStr">
+      <c r="T27" s="10" t="n"/>
+      <c r="U27" s="10" t="inlineStr">
         <is>
           <t>군락지 수 +2 (6 → 8)</t>
         </is>
       </c>
-      <c r="U27" s="10" t="inlineStr">
+      <c r="V27" s="10" t="inlineStr">
         <is>
           <t>넓은 시야의 상위</t>
         </is>
@@ -2685,7 +2726,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K28" s="10" t="n">
         <v>16</v>
@@ -2706,18 +2747,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R28" s="10" t="inlineStr">
-        <is>
-          <t>3122</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="n"/>
-      <c r="T28" s="10" t="inlineStr">
+      <c r="R28" s="10" t="n">
+        <v>3116</v>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>3114</t>
+        </is>
+      </c>
+      <c r="T28" s="10" t="n"/>
+      <c r="U28" s="10" t="inlineStr">
         <is>
           <t>에픽 버섯 수확량 +10%</t>
         </is>
       </c>
-      <c r="U28" s="10" t="inlineStr">
+      <c r="V28" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -2762,10 +2806,10 @@
         <v>1</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
@@ -2783,18 +2827,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R29" s="10" t="inlineStr">
-        <is>
-          <t>3123</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="n"/>
-      <c r="T29" s="10" t="inlineStr">
+      <c r="R29" s="10" t="n">
+        <v>3122</v>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>3118</t>
+        </is>
+      </c>
+      <c r="T29" s="10" t="n"/>
+      <c r="U29" s="10" t="inlineStr">
         <is>
           <t>점수 3배 확률 +7%</t>
         </is>
       </c>
-      <c r="U29" s="10" t="inlineStr">
+      <c r="V29" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -2839,10 +2886,10 @@
         <v>1</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
@@ -2860,18 +2907,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R30" s="10" t="inlineStr">
-        <is>
-          <t>3124</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="n"/>
-      <c r="T30" s="10" t="inlineStr">
+      <c r="R30" s="10" t="n">
+        <v>3115</v>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>3123</t>
+        </is>
+      </c>
+      <c r="T30" s="10" t="n"/>
+      <c r="U30" s="10" t="inlineStr">
         <is>
           <t>군락지 수 +2 (8 → 10)</t>
         </is>
       </c>
-      <c r="U30" s="10" t="inlineStr">
+      <c r="V30" s="10" t="inlineStr">
         <is>
           <t>넓은 시야의 상위</t>
         </is>
@@ -2919,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
@@ -2937,18 +2987,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R31" s="10" t="inlineStr">
-        <is>
-          <t>3126</t>
-        </is>
+      <c r="R31" s="10" t="n">
+        <v>3121</v>
       </c>
       <c r="S31" s="10" t="n"/>
-      <c r="T31" s="10" t="inlineStr">
+      <c r="T31" s="10" t="n"/>
+      <c r="U31" s="10" t="inlineStr">
         <is>
           <t>유니크 버섯 스폰율 +5%</t>
         </is>
       </c>
-      <c r="U31" s="10" t="n"/>
+      <c r="V31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
@@ -2989,10 +3038,10 @@
         <v>1</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
@@ -3010,18 +3059,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R32" s="10" t="inlineStr">
-        <is>
-          <t>3227</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="n"/>
-      <c r="T32" s="10" t="inlineStr">
+      <c r="R32" s="10" t="n">
+        <v>3122</v>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>3124</t>
+        </is>
+      </c>
+      <c r="T32" s="10" t="n"/>
+      <c r="U32" s="10" t="inlineStr">
         <is>
           <t>에픽 버섯 수확량 +15%</t>
         </is>
       </c>
-      <c r="U32" s="10" t="inlineStr">
+      <c r="V32" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -3066,7 +3118,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K33" s="10" t="n">
         <v>18</v>
@@ -3087,18 +3139,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R33" s="10" t="inlineStr">
-        <is>
-          <t>3228</t>
-        </is>
+      <c r="R33" s="10" t="n">
+        <v>3118</v>
       </c>
       <c r="S33" s="10" t="n"/>
-      <c r="T33" s="10" t="inlineStr">
+      <c r="T33" s="10" t="n"/>
+      <c r="U33" s="10" t="inlineStr">
         <is>
           <t>유니크 버섯 수확량 +5%</t>
         </is>
       </c>
-      <c r="U33" s="10" t="n"/>
+      <c r="V33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
@@ -3139,7 +3190,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K34" s="10" t="n">
         <v>19</v>
@@ -3160,18 +3211,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R34" s="10" t="inlineStr">
-        <is>
-          <t>3127</t>
-        </is>
-      </c>
-      <c r="S34" s="10" t="n"/>
-      <c r="T34" s="10" t="inlineStr">
+      <c r="R34" s="10" t="n">
+        <v>3119</v>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
+      </c>
+      <c r="T34" s="10" t="n"/>
+      <c r="U34" s="10" t="inlineStr">
         <is>
           <t>군락지 리스폰 −2초 (5 → 3)</t>
         </is>
       </c>
-      <c r="U34" s="10" t="n"/>
+      <c r="V34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="n">
@@ -3212,10 +3266,10 @@
         <v>1</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L35" s="10" t="inlineStr">
         <is>
@@ -3233,18 +3287,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R35" s="10" t="inlineStr">
-        <is>
-          <t>3128</t>
-        </is>
+      <c r="R35" s="10" t="n">
+        <v>3121</v>
       </c>
       <c r="S35" s="10" t="n"/>
-      <c r="T35" s="10" t="inlineStr">
+      <c r="T35" s="10" t="n"/>
+      <c r="U35" s="10" t="inlineStr">
         <is>
           <t>황금 변종 스폰율 +1%</t>
         </is>
       </c>
-      <c r="U35" s="10" t="n"/>
+      <c r="V35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
@@ -3285,7 +3338,7 @@
         <v>1</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K36" s="10" t="n">
         <v>20</v>
@@ -3306,18 +3359,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R36" s="10" t="inlineStr">
-        <is>
-          <t>3130</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="n"/>
-      <c r="T36" s="10" t="inlineStr">
+      <c r="R36" s="10" t="n">
+        <v>3124</v>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>3129</t>
+        </is>
+      </c>
+      <c r="T36" s="10" t="n"/>
+      <c r="U36" s="10" t="inlineStr">
         <is>
           <t>유니크 버섯 수확량 +10%</t>
         </is>
       </c>
-      <c r="U36" s="10" t="inlineStr">
+      <c r="V36" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -3362,10 +3418,10 @@
         <v>1</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L37" s="10" t="inlineStr">
         <is>
@@ -3383,18 +3439,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R37" s="10" t="inlineStr">
-        <is>
-          <t>3132</t>
-        </is>
+      <c r="R37" s="10" t="n">
+        <v>3129</v>
       </c>
       <c r="S37" s="10" t="n"/>
-      <c r="T37" s="10" t="inlineStr">
+      <c r="T37" s="10" t="n"/>
+      <c r="U37" s="10" t="inlineStr">
         <is>
           <t>보스 전용 레전더리 버섯 수확량 +3%</t>
         </is>
       </c>
-      <c r="U37" s="10" t="n"/>
+      <c r="V37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
@@ -3435,7 +3490,7 @@
         <v>1</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K38" s="10" t="n">
         <v>21</v>
@@ -3456,18 +3511,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R38" s="10" t="inlineStr">
-        <is>
-          <t>3336</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="n"/>
-      <c r="T38" s="10" t="inlineStr">
+      <c r="R38" s="10" t="n">
+        <v>3126</v>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>3127</t>
+        </is>
+      </c>
+      <c r="T38" s="10" t="n"/>
+      <c r="U38" s="10" t="inlineStr">
         <is>
           <t>유니크 버섯 스폰율 +10%</t>
         </is>
       </c>
-      <c r="U38" s="10" t="inlineStr">
+      <c r="V38" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -3512,7 +3570,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K39" s="10" t="n">
         <v>22</v>
@@ -3533,18 +3591,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R39" s="10" t="inlineStr">
+      <c r="R39" s="10" t="n">
+        <v>3130</v>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>3134</t>
         </is>
       </c>
-      <c r="S39" s="10" t="n"/>
-      <c r="T39" s="10" t="inlineStr">
+      <c r="T39" s="10" t="n"/>
+      <c r="U39" s="10" t="inlineStr">
         <is>
           <t>유니크 버섯 스폰율 +15%</t>
         </is>
       </c>
-      <c r="U39" s="10" t="inlineStr">
+      <c r="V39" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%. 원문은 Lv.2와 같은 레어도 15</t>
         </is>
@@ -3589,7 +3650,7 @@
         <v>1</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K40" s="10" t="n">
         <v>23</v>
@@ -3610,18 +3671,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R40" s="10" t="inlineStr">
-        <is>
-          <t>3135</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="n"/>
-      <c r="T40" s="10" t="inlineStr">
+      <c r="R40" s="10" t="n">
+        <v>3130</v>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="T40" s="10" t="n"/>
+      <c r="U40" s="10" t="inlineStr">
         <is>
           <t>황금 변종 스폰율 +3%</t>
         </is>
       </c>
-      <c r="U40" s="10" t="inlineStr">
+      <c r="V40" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -3666,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K41" s="10" t="n">
         <v>23</v>
@@ -3687,18 +3751,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R41" s="10" t="inlineStr">
-        <is>
-          <t>3340</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="n"/>
-      <c r="T41" s="10" t="inlineStr">
+      <c r="R41" s="10" t="n">
+        <v>3129</v>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>3133</t>
+        </is>
+      </c>
+      <c r="T41" s="10" t="n"/>
+      <c r="U41" s="10" t="inlineStr">
         <is>
           <t>보스 전용 레전더리 버섯 수확량 +6%</t>
         </is>
       </c>
-      <c r="U41" s="10" t="inlineStr">
+      <c r="V41" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +3%</t>
         </is>
@@ -3743,10 +3810,10 @@
         <v>1</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L42" s="10" t="inlineStr">
         <is>
@@ -3764,18 +3831,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R42" s="10" t="inlineStr">
-        <is>
-          <t>3137</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="n"/>
-      <c r="T42" s="10" t="inlineStr">
+      <c r="R42" s="10" t="n">
+        <v>3125</v>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>3122</t>
+        </is>
+      </c>
+      <c r="T42" s="10" t="n"/>
+      <c r="U42" s="10" t="inlineStr">
         <is>
           <t>점수 골드 전환율 +40%</t>
         </is>
       </c>
-      <c r="U42" s="10" t="inlineStr">
+      <c r="V42" s="10" t="inlineStr">
         <is>
           <t>흥정 기술의 상위. 누적값 기준 차이 +10%</t>
         </is>
@@ -3820,10 +3890,10 @@
         <v>1</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L43" s="10" t="inlineStr">
         <is>
@@ -3841,18 +3911,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R43" s="10" t="inlineStr">
-        <is>
-          <t>3136</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="n"/>
-      <c r="T43" s="10" t="inlineStr">
+      <c r="R43" s="10" t="n">
+        <v>3127</v>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>3126</t>
+        </is>
+      </c>
+      <c r="T43" s="10" t="n"/>
+      <c r="U43" s="10" t="inlineStr">
         <is>
           <t>군락지 수 +2 (10 → 12)</t>
         </is>
       </c>
-      <c r="U43" s="10" t="inlineStr">
+      <c r="V43" s="10" t="inlineStr">
         <is>
           <t>넓은 시야의 상위</t>
         </is>
@@ -3897,10 +3970,10 @@
         <v>1</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K44" s="10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L44" s="10" t="inlineStr">
         <is>
@@ -3918,18 +3991,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R44" s="10" t="inlineStr">
-        <is>
-          <t>3138</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="n"/>
-      <c r="T44" s="10" t="inlineStr">
+      <c r="R44" s="10" t="n">
+        <v>3133</v>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>3132</t>
+        </is>
+      </c>
+      <c r="T44" s="10" t="n"/>
+      <c r="U44" s="10" t="inlineStr">
         <is>
           <t>유니크 버섯 수확량 +15%</t>
         </is>
       </c>
-      <c r="U44" s="10" t="inlineStr">
+      <c r="V44" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -3974,7 +4050,7 @@
         <v>1</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" s="10" t="n">
         <v>26</v>
@@ -3995,18 +4071,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R45" s="10" t="inlineStr">
-        <is>
-          <t>3140</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="n"/>
-      <c r="T45" s="10" t="inlineStr">
+      <c r="R45" s="10" t="n">
+        <v>3128</v>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>3120</t>
+        </is>
+      </c>
+      <c r="T45" s="10" t="n"/>
+      <c r="U45" s="10" t="inlineStr">
         <is>
           <t>획득 점수 +50%</t>
         </is>
       </c>
-      <c r="U45" s="10" t="inlineStr">
+      <c r="V45" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%</t>
         </is>
@@ -4072,18 +4151,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R46" s="10" t="inlineStr">
-        <is>
-          <t>3238</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="n"/>
-      <c r="T46" s="10" t="inlineStr">
+      <c r="R46" s="10" t="n">
+        <v>3135</v>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>3136</t>
+        </is>
+      </c>
+      <c r="T46" s="10" t="n"/>
+      <c r="U46" s="10" t="inlineStr">
         <is>
           <t>황금 변종 스폰율 +5%</t>
         </is>
       </c>
-      <c r="U46" s="10" t="inlineStr">
+      <c r="V46" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -4128,10 +4210,10 @@
         <v>5</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K47" s="10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L47" s="10" t="inlineStr">
         <is>
@@ -4151,18 +4233,17 @@
           <t>Mycelite</t>
         </is>
       </c>
-      <c r="R47" s="10" t="inlineStr">
-        <is>
-          <t>3239</t>
-        </is>
+      <c r="R47" s="10" t="n">
+        <v>3145</v>
       </c>
       <c r="S47" s="10" t="n"/>
-      <c r="T47" s="10" t="inlineStr">
+      <c r="T47" s="10" t="n"/>
+      <c r="U47" s="10" t="inlineStr">
         <is>
           <t>라운드 마지막 5초 점수·수확량 +10% / Lv</t>
         </is>
       </c>
-      <c r="U47" s="10" t="inlineStr">
+      <c r="V47" s="10" t="inlineStr">
         <is>
           <t>param = 마지막 몇 초</t>
         </is>
@@ -4207,7 +4288,7 @@
         <v>1</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K48" s="10" t="n">
         <v>27</v>
@@ -4228,18 +4309,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R48" s="10" t="inlineStr">
-        <is>
-          <t>3142</t>
-        </is>
+      <c r="R48" s="10" t="n">
+        <v>3142</v>
       </c>
       <c r="S48" s="10" t="n"/>
-      <c r="T48" s="10" t="inlineStr">
+      <c r="T48" s="10" t="n"/>
+      <c r="U48" s="10" t="inlineStr">
         <is>
           <t>군락지 수 +3 (12 → 15)</t>
         </is>
       </c>
-      <c r="U48" s="10" t="inlineStr">
+      <c r="V48" s="10" t="inlineStr">
         <is>
           <t>넓은 시야의 상위</t>
         </is>
@@ -4284,7 +4364,7 @@
         <v>1</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K49" s="10" t="n">
         <v>27</v>
@@ -4305,18 +4385,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R49" s="10" t="inlineStr">
-        <is>
-          <t>3141</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="n"/>
-      <c r="T49" s="10" t="inlineStr">
+      <c r="R49" s="10" t="n">
+        <v>3140</v>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>3137</t>
+        </is>
+      </c>
+      <c r="T49" s="10" t="n"/>
+      <c r="U49" s="10" t="inlineStr">
         <is>
           <t>보스 전용 레전더리 버섯 수확량 +9%</t>
         </is>
       </c>
-      <c r="U49" s="10" t="inlineStr">
+      <c r="V49" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +3%</t>
         </is>
@@ -4361,7 +4444,7 @@
         <v>1</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K50" s="10" t="n">
         <v>27</v>
@@ -4382,18 +4465,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R50" s="10" t="inlineStr">
-        <is>
-          <t>3143</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="n"/>
-      <c r="T50" s="10" t="inlineStr">
+      <c r="R50" s="10" t="n">
+        <v>3137</v>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>3138</t>
+        </is>
+      </c>
+      <c r="T50" s="10" t="n"/>
+      <c r="U50" s="10" t="inlineStr">
         <is>
           <t>점수 골드 전환율 +50%</t>
         </is>
       </c>
-      <c r="U50" s="10" t="inlineStr">
+      <c r="V50" s="10" t="inlineStr">
         <is>
           <t>흥정 기술의 상위. 누적값 기준 차이 +10%</t>
         </is>
@@ -4459,18 +4545,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R51" s="11" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
+      <c r="R51" s="11" t="n">
+        <v>3001</v>
       </c>
       <c r="S51" s="11" t="n"/>
-      <c r="T51" s="11" t="inlineStr">
+      <c r="T51" s="11" t="n"/>
+      <c r="U51" s="11" t="inlineStr">
         <is>
           <t>가속(3초) 버프</t>
         </is>
       </c>
-      <c r="U51" s="11" t="inlineStr">
+      <c r="V51" s="11" t="inlineStr">
         <is>
           <t>value = 지속(초), 다음 노드는 +1초씩</t>
         </is>
@@ -4515,10 +4600,10 @@
         <v>1</v>
       </c>
       <c r="J52" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L52" s="11" t="inlineStr">
         <is>
@@ -4536,18 +4621,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R52" s="11" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
+      <c r="R52" s="11" t="n">
+        <v>3201</v>
       </c>
       <c r="S52" s="11" t="n"/>
-      <c r="T52" s="11" t="inlineStr">
+      <c r="T52" s="11" t="n"/>
+      <c r="U52" s="11" t="inlineStr">
         <is>
           <t>관통(3초) 버프</t>
         </is>
       </c>
-      <c r="U52" s="11" t="n"/>
+      <c r="V52" s="11" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="n">
@@ -4591,7 +4675,7 @@
         <v>3</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
@@ -4609,18 +4693,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R53" s="11" t="inlineStr">
+      <c r="R53" s="11" t="n">
+        <v>3202</v>
+      </c>
+      <c r="S53" s="11" t="inlineStr">
         <is>
           <t>3201</t>
         </is>
       </c>
-      <c r="S53" s="11" t="n"/>
-      <c r="T53" s="11" t="inlineStr">
+      <c r="T53" s="11" t="n"/>
+      <c r="U53" s="11" t="inlineStr">
         <is>
           <t>가속(4초) 버프</t>
         </is>
       </c>
-      <c r="U53" s="11" t="n"/>
+      <c r="V53" s="11" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="n">
@@ -4682,18 +4769,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R54" s="11" t="inlineStr">
-        <is>
-          <t>3202</t>
-        </is>
+      <c r="R54" s="11" t="n">
+        <v>3201</v>
       </c>
       <c r="S54" s="11" t="n"/>
-      <c r="T54" s="11" t="inlineStr">
+      <c r="T54" s="11" t="n"/>
+      <c r="U54" s="11" t="inlineStr">
         <is>
           <t>필드에 그루터기 추가</t>
         </is>
       </c>
-      <c r="U54" s="11" t="inlineStr">
+      <c r="V54" s="11" t="inlineStr">
         <is>
           <t>value = 단계 (1 그루터기 / 2 꽃밭 / 3 도토리 점등)</t>
         </is>
@@ -4738,7 +4824,7 @@
         <v>1</v>
       </c>
       <c r="J55" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K55" s="11" t="n">
         <v>3</v>
@@ -4761,18 +4847,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R55" s="11" t="inlineStr">
-        <is>
-          <t>3203</t>
-        </is>
+      <c r="R55" s="11" t="n">
+        <v>3204</v>
       </c>
       <c r="S55" s="11" t="n"/>
-      <c r="T55" s="11" t="inlineStr">
+      <c r="T55" s="11" t="n"/>
+      <c r="U55" s="11" t="inlineStr">
         <is>
           <t>단일 버섯 획득 시 3% 확률로 다음 타격 피해 +200%</t>
         </is>
       </c>
-      <c r="U55" s="11" t="inlineStr">
+      <c r="V55" s="11" t="inlineStr">
         <is>
           <t>param = 피해 증가 (2 = +200%)</t>
         </is>
@@ -4820,7 +4905,7 @@
         <v>4</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L56" s="11" t="inlineStr">
         <is>
@@ -4840,18 +4925,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R56" s="11" t="inlineStr">
-        <is>
-          <t>3204</t>
-        </is>
+      <c r="R56" s="11" t="n">
+        <v>3202</v>
       </c>
       <c r="S56" s="11" t="n"/>
-      <c r="T56" s="11" t="inlineStr">
+      <c r="T56" s="11" t="n"/>
+      <c r="U56" s="11" t="inlineStr">
         <is>
           <t>[피버] 버프 3초 · 콤보 계수 +50%</t>
         </is>
       </c>
-      <c r="U56" s="11" t="inlineStr">
+      <c r="V56" s="11" t="inlineStr">
         <is>
           <t>param = 콤보 계수 증가</t>
         </is>
@@ -4899,7 +4983,7 @@
         <v>3</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
@@ -4917,18 +5001,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R57" s="11" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
-      </c>
-      <c r="S57" s="11" t="n"/>
-      <c r="T57" s="11" t="inlineStr">
+      <c r="R57" s="11" t="n">
+        <v>3202</v>
+      </c>
+      <c r="S57" s="11" t="inlineStr">
+        <is>
+          <t>3203</t>
+        </is>
+      </c>
+      <c r="T57" s="11" t="n"/>
+      <c r="U57" s="11" t="inlineStr">
         <is>
           <t>가속(5초) 버프</t>
         </is>
       </c>
-      <c r="U57" s="11" t="n"/>
+      <c r="V57" s="11" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="n">
@@ -4969,7 +5056,7 @@
         <v>1</v>
       </c>
       <c r="J58" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K58" s="11" t="n">
         <v>5</v>
@@ -4992,18 +5079,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R58" s="11" t="inlineStr">
-        <is>
-          <t>3207</t>
-        </is>
-      </c>
-      <c r="S58" s="11" t="n"/>
-      <c r="T58" s="11" t="inlineStr">
+      <c r="R58" s="11" t="n">
+        <v>3204</v>
+      </c>
+      <c r="S58" s="11" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="T58" s="11" t="n"/>
+      <c r="U58" s="11" t="inlineStr">
         <is>
           <t>단일 버섯 획득 시 4% 확률로 다음 타격 피해 +200%</t>
         </is>
       </c>
-      <c r="U58" s="11" t="n"/>
+      <c r="V58" s="11" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="n">
@@ -5067,18 +5157,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R59" s="11" t="inlineStr">
-        <is>
-          <t>3208</t>
-        </is>
+      <c r="R59" s="11" t="n">
+        <v>3205</v>
       </c>
       <c r="S59" s="11" t="n"/>
-      <c r="T59" s="11" t="inlineStr">
+      <c r="T59" s="11" t="n"/>
+      <c r="U59" s="11" t="inlineStr">
         <is>
           <t>군락 파괴 시 3% 확률로 랜덤 군락에 번개(공격력 30%)</t>
         </is>
       </c>
-      <c r="U59" s="11" t="inlineStr">
+      <c r="V59" s="11" t="inlineStr">
         <is>
           <t>param = 번개 피해 (공격력 비율)</t>
         </is>
@@ -5123,10 +5212,10 @@
         <v>1</v>
       </c>
       <c r="J60" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L60" s="11" t="inlineStr">
         <is>
@@ -5144,18 +5233,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R60" s="11" t="inlineStr">
-        <is>
-          <t>3107</t>
-        </is>
+      <c r="R60" s="11" t="n">
+        <v>3211</v>
       </c>
       <c r="S60" s="11" t="n"/>
-      <c r="T60" s="11" t="inlineStr">
+      <c r="T60" s="11" t="n"/>
+      <c r="U60" s="11" t="inlineStr">
         <is>
           <t>유도(3초) 버프</t>
         </is>
       </c>
-      <c r="U60" s="11" t="n"/>
+      <c r="V60" s="11" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="n">
@@ -5217,18 +5305,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R61" s="11" t="inlineStr">
-        <is>
-          <t>3310</t>
-        </is>
-      </c>
-      <c r="S61" s="11" t="n"/>
-      <c r="T61" s="11" t="inlineStr">
+      <c r="R61" s="11" t="n">
+        <v>3206</v>
+      </c>
+      <c r="S61" s="11" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="T61" s="11" t="n"/>
+      <c r="U61" s="11" t="inlineStr">
         <is>
           <t>관통(4초) 버프</t>
         </is>
       </c>
-      <c r="U61" s="11" t="n"/>
+      <c r="V61" s="11" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="n">
@@ -5269,7 +5360,7 @@
         <v>1</v>
       </c>
       <c r="J62" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K62" s="11" t="n">
         <v>7</v>
@@ -5290,18 +5381,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R62" s="11" t="inlineStr">
+      <c r="R62" s="11" t="n">
+        <v>3207</v>
+      </c>
+      <c r="S62" s="11" t="inlineStr">
         <is>
           <t>3211</t>
         </is>
       </c>
-      <c r="S62" s="11" t="n"/>
-      <c r="T62" s="11" t="inlineStr">
+      <c r="T62" s="11" t="n"/>
+      <c r="U62" s="11" t="inlineStr">
         <is>
           <t>관통(5초) 버프</t>
         </is>
       </c>
-      <c r="U62" s="11" t="inlineStr">
+      <c r="V62" s="11" t="inlineStr">
         <is>
           <t>원문은 Lv.2와 같은 레어도 7</t>
         </is>
@@ -5367,18 +5461,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R63" s="11" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
+      <c r="R63" s="11" t="n">
+        <v>3209</v>
       </c>
       <c r="S63" s="11" t="n"/>
-      <c r="T63" s="11" t="inlineStr">
+      <c r="T63" s="11" t="n"/>
+      <c r="U63" s="11" t="inlineStr">
         <is>
           <t>군락 충돌로 디버프를 얻으면 10% 확률로 해제</t>
         </is>
       </c>
-      <c r="U63" s="11" t="n"/>
+      <c r="V63" s="11" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="n">
@@ -5419,10 +5512,10 @@
         <v>1</v>
       </c>
       <c r="J64" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L64" s="11" t="inlineStr">
         <is>
@@ -5442,18 +5535,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R64" s="11" t="inlineStr">
-        <is>
-          <t>3213</t>
-        </is>
-      </c>
-      <c r="S64" s="11" t="n"/>
-      <c r="T64" s="11" t="inlineStr">
+      <c r="R64" s="11" t="n">
+        <v>3215</v>
+      </c>
+      <c r="S64" s="11" t="inlineStr">
+        <is>
+          <t>3208</t>
+        </is>
+      </c>
+      <c r="T64" s="11" t="n"/>
+      <c r="U64" s="11" t="inlineStr">
         <is>
           <t>단일 버섯 획득 시 5% 확률로 다음 타격 피해 +200%</t>
         </is>
       </c>
-      <c r="U64" s="11" t="n"/>
+      <c r="V64" s="11" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="n">
@@ -5515,18 +5611,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R65" s="11" t="inlineStr">
-        <is>
-          <t>3212</t>
-        </is>
-      </c>
-      <c r="S65" s="11" t="n"/>
-      <c r="T65" s="11" t="inlineStr">
+      <c r="R65" s="11" t="n">
+        <v>3208</v>
+      </c>
+      <c r="S65" s="11" t="inlineStr">
+        <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="T65" s="11" t="n"/>
+      <c r="U65" s="11" t="inlineStr">
         <is>
           <t>필드에 꽃밭 추가</t>
         </is>
       </c>
-      <c r="U65" s="11" t="n"/>
+      <c r="V65" s="11" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="n">
@@ -5567,10 +5666,10 @@
         <v>1</v>
       </c>
       <c r="J66" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L66" s="11" t="inlineStr">
         <is>
@@ -5588,18 +5687,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R66" s="11" t="inlineStr">
-        <is>
-          <t>3214</t>
-        </is>
+      <c r="R66" s="11" t="n">
+        <v>3212</v>
       </c>
       <c r="S66" s="11" t="n"/>
-      <c r="T66" s="11" t="inlineStr">
+      <c r="T66" s="11" t="n"/>
+      <c r="U66" s="11" t="inlineStr">
         <is>
           <t>포자 디버프 제거 + 약손(3초)</t>
         </is>
       </c>
-      <c r="U66" s="11" t="n"/>
+      <c r="V66" s="11" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="n">
@@ -5640,7 +5738,7 @@
         <v>1</v>
       </c>
       <c r="J67" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K67" s="11" t="n">
         <v>10</v>
@@ -5661,18 +5759,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R67" s="11" t="inlineStr">
-        <is>
-          <t>3216</t>
-        </is>
-      </c>
-      <c r="S67" s="11" t="n"/>
-      <c r="T67" s="11" t="inlineStr">
+      <c r="R67" s="11" t="n">
+        <v>3211</v>
+      </c>
+      <c r="S67" s="11" t="inlineStr">
+        <is>
+          <t>3210</t>
+        </is>
+      </c>
+      <c r="T67" s="11" t="n"/>
+      <c r="U67" s="11" t="inlineStr">
         <is>
           <t>유도(4초) 버프</t>
         </is>
       </c>
-      <c r="U67" s="11" t="n"/>
+      <c r="V67" s="11" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="n">
@@ -5713,7 +5814,7 @@
         <v>1</v>
       </c>
       <c r="J68" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K68" s="11" t="n">
         <v>10</v>
@@ -5734,18 +5835,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R68" s="11" t="inlineStr">
-        <is>
-          <t>3112</t>
-        </is>
-      </c>
-      <c r="S68" s="11" t="n"/>
-      <c r="T68" s="11" t="inlineStr">
+      <c r="R68" s="11" t="n">
+        <v>3209</v>
+      </c>
+      <c r="S68" s="11" t="inlineStr">
+        <is>
+          <t>3213</t>
+        </is>
+      </c>
+      <c r="T68" s="11" t="n"/>
+      <c r="U68" s="11" t="inlineStr">
         <is>
           <t>군락 충돌로 디버프를 얻으면 20% 확률로 해제</t>
         </is>
       </c>
-      <c r="U68" s="11" t="n"/>
+      <c r="V68" s="11" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="n">
@@ -5786,7 +5890,7 @@
         <v>1</v>
       </c>
       <c r="J69" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K69" s="11" t="n">
         <v>11</v>
@@ -5809,18 +5913,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R69" s="11" t="inlineStr">
-        <is>
-          <t>3217</t>
-        </is>
+      <c r="R69" s="11" t="n">
+        <v>3214</v>
       </c>
       <c r="S69" s="11" t="n"/>
-      <c r="T69" s="11" t="inlineStr">
+      <c r="T69" s="11" t="n"/>
+      <c r="U69" s="11" t="inlineStr">
         <is>
           <t>군락 충돌 시 3% 확률로 3초 지속 피해(공격력 5%)</t>
         </is>
       </c>
-      <c r="U69" s="11" t="inlineStr">
+      <c r="V69" s="11" t="inlineStr">
         <is>
           <t>param = 초당 피해 (공격력 비율). 지속 시간도 3/4/5초로 오르는데 칸이 하나라 계열 레벨 + 2초로 계산 필요</t>
         </is>
@@ -5888,18 +5991,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R70" s="11" t="inlineStr">
-        <is>
-          <t>3219</t>
-        </is>
+      <c r="R70" s="11" t="n">
+        <v>3211</v>
       </c>
       <c r="S70" s="11" t="n"/>
-      <c r="T70" s="11" t="inlineStr">
+      <c r="T70" s="11" t="n"/>
+      <c r="U70" s="11" t="inlineStr">
         <is>
           <t>[지혜] 버프 3초 · 수확기 스킬 발동률 +1%</t>
         </is>
       </c>
-      <c r="U70" s="11" t="inlineStr">
+      <c r="V70" s="11" t="inlineStr">
         <is>
           <t>param = 버프 지속(초)</t>
         </is>
@@ -5944,7 +6046,7 @@
         <v>1</v>
       </c>
       <c r="J71" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K71" s="11" t="n">
         <v>13</v>
@@ -5967,18 +6069,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R71" s="11" t="inlineStr">
+      <c r="R71" s="11" t="n">
+        <v>3217</v>
+      </c>
+      <c r="S71" s="11" t="inlineStr">
         <is>
           <t>3220</t>
         </is>
       </c>
-      <c r="S71" s="11" t="n"/>
-      <c r="T71" s="11" t="inlineStr">
+      <c r="T71" s="11" t="n"/>
+      <c r="U71" s="11" t="inlineStr">
         <is>
           <t>[지혜] 버프 3초 · 수확기 스킬 발동률 +2%</t>
         </is>
       </c>
-      <c r="U71" s="11" t="inlineStr">
+      <c r="V71" s="11" t="inlineStr">
         <is>
           <t>원문은 Lv.1과 같은 레어도 11</t>
         </is>
@@ -6026,7 +6131,7 @@
         <v>4</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L72" s="11" t="inlineStr">
         <is>
@@ -6046,18 +6151,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R72" s="11" t="inlineStr">
-        <is>
-          <t>3116</t>
-        </is>
-      </c>
-      <c r="S72" s="11" t="n"/>
-      <c r="T72" s="11" t="inlineStr">
+      <c r="R72" s="11" t="n">
+        <v>3221</v>
+      </c>
+      <c r="S72" s="11" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
+      </c>
+      <c r="T72" s="11" t="n"/>
+      <c r="U72" s="11" t="inlineStr">
         <is>
           <t>[피버] 버프 4초 · 콤보 계수 +50%</t>
         </is>
       </c>
-      <c r="U72" s="11" t="n"/>
+      <c r="V72" s="11" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="n">
@@ -6101,7 +6209,7 @@
         <v>4</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
@@ -6121,18 +6229,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R73" s="11" t="inlineStr">
-        <is>
-          <t>3222</t>
-        </is>
+      <c r="R73" s="11" t="n">
+        <v>3215</v>
       </c>
       <c r="S73" s="11" t="n"/>
-      <c r="T73" s="11" t="inlineStr">
+      <c r="T73" s="11" t="n"/>
+      <c r="U73" s="11" t="inlineStr">
         <is>
           <t>군락 충돌 시 1% 확률로 전체 피해(공격력 10%)</t>
         </is>
       </c>
-      <c r="U73" s="11" t="inlineStr">
+      <c r="V73" s="11" t="inlineStr">
         <is>
           <t>param = 피해 (공격력 비율)</t>
         </is>
@@ -6200,18 +6307,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R74" s="11" t="inlineStr">
-        <is>
-          <t>3326</t>
-        </is>
-      </c>
-      <c r="S74" s="11" t="n"/>
-      <c r="T74" s="11" t="inlineStr">
+      <c r="R74" s="11" t="n">
+        <v>3213</v>
+      </c>
+      <c r="S74" s="11" t="inlineStr">
+        <is>
+          <t>3223</t>
+        </is>
+      </c>
+      <c r="T74" s="11" t="n"/>
+      <c r="U74" s="11" t="inlineStr">
         <is>
           <t>군락 충돌 시 2% 확률로 전체 피해(공격력 10%)</t>
         </is>
       </c>
-      <c r="U74" s="11" t="n"/>
+      <c r="V74" s="11" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="11" t="n">
@@ -6252,7 +6362,7 @@
         <v>1</v>
       </c>
       <c r="J75" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K75" s="11" t="n">
         <v>17</v>
@@ -6273,18 +6383,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R75" s="11" t="inlineStr">
-        <is>
-          <t>3329</t>
-        </is>
-      </c>
-      <c r="S75" s="11" t="n"/>
-      <c r="T75" s="11" t="inlineStr">
+      <c r="R75" s="11" t="n">
+        <v>3221</v>
+      </c>
+      <c r="S75" s="11" t="inlineStr">
+        <is>
+          <t>3217</t>
+        </is>
+      </c>
+      <c r="T75" s="11" t="n"/>
+      <c r="U75" s="11" t="inlineStr">
         <is>
           <t>유도(5초) 버프</t>
         </is>
       </c>
-      <c r="U75" s="11" t="n"/>
+      <c r="V75" s="11" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="n">
@@ -6325,7 +6438,7 @@
         <v>1</v>
       </c>
       <c r="J76" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K76" s="11" t="n">
         <v>17</v>
@@ -6346,18 +6459,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R76" s="11" t="inlineStr">
-        <is>
-          <t>3330</t>
-        </is>
-      </c>
-      <c r="S76" s="11" t="n"/>
-      <c r="T76" s="11" t="inlineStr">
+      <c r="R76" s="11" t="n">
+        <v>3224</v>
+      </c>
+      <c r="S76" s="11" t="inlineStr">
+        <is>
+          <t>3218</t>
+        </is>
+      </c>
+      <c r="T76" s="11" t="n"/>
+      <c r="U76" s="11" t="inlineStr">
         <is>
           <t>군락 충돌로 디버프를 얻으면 30% 확률로 해제</t>
         </is>
       </c>
-      <c r="U76" s="11" t="n"/>
+      <c r="V76" s="11" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="n">
@@ -6398,10 +6514,10 @@
         <v>1</v>
       </c>
       <c r="J77" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
@@ -6419,18 +6535,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R77" s="11" t="inlineStr">
-        <is>
-          <t>3125</t>
-        </is>
-      </c>
-      <c r="S77" s="11" t="n"/>
-      <c r="T77" s="11" t="inlineStr">
+      <c r="R77" s="11" t="n">
+        <v>3223</v>
+      </c>
+      <c r="S77" s="11" t="inlineStr">
+        <is>
+          <t>3215</t>
+        </is>
+      </c>
+      <c r="T77" s="11" t="n"/>
+      <c r="U77" s="11" t="inlineStr">
         <is>
           <t>필드에 도토리 점등 추가</t>
         </is>
       </c>
-      <c r="U77" s="11" t="n"/>
+      <c r="V77" s="11" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="11" t="n">
@@ -6474,7 +6593,7 @@
         <v>4</v>
       </c>
       <c r="K78" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L78" s="11" t="inlineStr">
         <is>
@@ -6494,18 +6613,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R78" s="11" t="inlineStr">
-        <is>
-          <t>3331</t>
-        </is>
+      <c r="R78" s="11" t="n">
+        <v>3221</v>
       </c>
       <c r="S78" s="11" t="n"/>
-      <c r="T78" s="11" t="inlineStr">
+      <c r="T78" s="11" t="n"/>
+      <c r="U78" s="11" t="inlineStr">
         <is>
           <t>10% 확률로 분열(3초) 버프</t>
         </is>
       </c>
-      <c r="U78" s="11" t="inlineStr">
+      <c r="V78" s="11" t="inlineStr">
         <is>
           <t>param = 발동 확률</t>
         </is>
@@ -6550,10 +6668,10 @@
         <v>1</v>
       </c>
       <c r="J79" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
@@ -6573,18 +6691,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R79" s="11" t="inlineStr">
-        <is>
-          <t>3225</t>
-        </is>
-      </c>
-      <c r="S79" s="11" t="n"/>
-      <c r="T79" s="11" t="inlineStr">
+      <c r="R79" s="11" t="n">
+        <v>3227</v>
+      </c>
+      <c r="S79" s="11" t="inlineStr">
+        <is>
+          <t>3219</t>
+        </is>
+      </c>
+      <c r="T79" s="11" t="n"/>
+      <c r="U79" s="11" t="inlineStr">
         <is>
           <t>군락 충돌 시 4% 확률로 4초 지속 피해(공격력 5%)</t>
         </is>
       </c>
-      <c r="U79" s="11" t="n"/>
+      <c r="V79" s="11" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="n">
@@ -6625,10 +6746,10 @@
         <v>1</v>
       </c>
       <c r="J80" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K80" s="11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L80" s="11" t="inlineStr">
         <is>
@@ -6648,18 +6769,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R80" s="11" t="inlineStr">
-        <is>
-          <t>3229</t>
-        </is>
-      </c>
-      <c r="S80" s="11" t="n"/>
-      <c r="T80" s="11" t="inlineStr">
+      <c r="R80" s="11" t="n">
+        <v>3231</v>
+      </c>
+      <c r="S80" s="11" t="inlineStr">
+        <is>
+          <t>3221</t>
+        </is>
+      </c>
+      <c r="T80" s="11" t="n"/>
+      <c r="U80" s="11" t="inlineStr">
         <is>
           <t>[지혜] 버프 3초 · 수확기 스킬 발동률 +3%</t>
         </is>
       </c>
-      <c r="U80" s="11" t="n"/>
+      <c r="V80" s="11" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="11" t="n">
@@ -6700,7 +6824,7 @@
         <v>1</v>
       </c>
       <c r="J81" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K81" s="11" t="n">
         <v>19</v>
@@ -6721,18 +6845,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R81" s="11" t="inlineStr">
-        <is>
-          <t>3129</t>
-        </is>
-      </c>
-      <c r="S81" s="11" t="n"/>
-      <c r="T81" s="11" t="inlineStr">
+      <c r="R81" s="11" t="n">
+        <v>3220</v>
+      </c>
+      <c r="S81" s="11" t="inlineStr">
+        <is>
+          <t>3216</t>
+        </is>
+      </c>
+      <c r="T81" s="11" t="n"/>
+      <c r="U81" s="11" t="inlineStr">
         <is>
           <t>포자 디버프 제거 + 약손(4초)</t>
         </is>
       </c>
-      <c r="U81" s="11" t="n"/>
+      <c r="V81" s="11" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="n">
@@ -6773,10 +6900,10 @@
         <v>1</v>
       </c>
       <c r="J82" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K82" s="11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L82" s="11" t="inlineStr">
         <is>
@@ -6796,18 +6923,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R82" s="11" t="inlineStr">
-        <is>
-          <t>3230</t>
-        </is>
-      </c>
-      <c r="S82" s="11" t="n"/>
-      <c r="T82" s="11" t="inlineStr">
+      <c r="R82" s="11" t="n">
+        <v>3229</v>
+      </c>
+      <c r="S82" s="11" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
+      </c>
+      <c r="T82" s="11" t="n"/>
+      <c r="U82" s="11" t="inlineStr">
         <is>
           <t>군락 파괴 시 5% 확률로 랜덤 군락에 번개(공격력 30%)</t>
         </is>
       </c>
-      <c r="U82" s="11" t="inlineStr">
+      <c r="V82" s="11" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -6852,7 +6982,7 @@
         <v>1</v>
       </c>
       <c r="J83" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K83" s="11" t="n">
         <v>21</v>
@@ -6873,18 +7003,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R83" s="11" t="inlineStr">
-        <is>
-          <t>3232</t>
-        </is>
-      </c>
-      <c r="S83" s="11" t="n"/>
-      <c r="T83" s="11" t="inlineStr">
+      <c r="R83" s="11" t="n">
+        <v>3228</v>
+      </c>
+      <c r="S83" s="11" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="T83" s="11" t="n"/>
+      <c r="U83" s="11" t="inlineStr">
         <is>
           <t>포자 디버프 제거 + 약손(5초)</t>
         </is>
       </c>
-      <c r="U83" s="11" t="n"/>
+      <c r="V83" s="11" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="11" t="n">
@@ -6925,10 +7058,10 @@
         <v>1</v>
       </c>
       <c r="J84" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K84" s="11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L84" s="11" t="inlineStr">
         <is>
@@ -6948,18 +7081,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R84" s="11" t="inlineStr">
-        <is>
-          <t>3233</t>
-        </is>
-      </c>
-      <c r="S84" s="11" t="n"/>
-      <c r="T84" s="11" t="inlineStr">
+      <c r="R84" s="11" t="n">
+        <v>3226</v>
+      </c>
+      <c r="S84" s="11" t="inlineStr">
+        <is>
+          <t>3232</t>
+        </is>
+      </c>
+      <c r="T84" s="11" t="n"/>
+      <c r="U84" s="11" t="inlineStr">
         <is>
           <t>군락 파괴 시 7% 확률로 랜덤 위치에 번개(공격력 30%)</t>
         </is>
       </c>
-      <c r="U84" s="11" t="inlineStr">
+      <c r="V84" s="11" t="inlineStr">
         <is>
           <t>확인 필요: 원문 Lv.3만 "랜덤 위치", Lv.1·2는 "랜덤 군락"</t>
         </is>
@@ -7004,10 +7140,10 @@
         <v>5</v>
       </c>
       <c r="J85" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
@@ -7025,18 +7161,17 @@
           <t>Mycelite</t>
         </is>
       </c>
-      <c r="R85" s="11" t="inlineStr">
-        <is>
-          <t>3234</t>
-        </is>
+      <c r="R85" s="11" t="n">
+        <v>3230</v>
       </c>
       <c r="S85" s="11" t="n"/>
-      <c r="T85" s="11" t="inlineStr">
+      <c r="T85" s="11" t="n"/>
+      <c r="U85" s="11" t="inlineStr">
         <is>
           <t>게임 시작 시 보유 버프 스킬 즉시 발동 확률 +2% / Lv</t>
         </is>
       </c>
-      <c r="U85" s="11" t="n"/>
+      <c r="V85" s="11" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="11" t="n">
@@ -7077,10 +7212,10 @@
         <v>1</v>
       </c>
       <c r="J86" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K86" s="11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L86" s="11" t="inlineStr">
         <is>
@@ -7100,18 +7235,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R86" s="11" t="inlineStr">
-        <is>
-          <t>3235</t>
-        </is>
-      </c>
-      <c r="S86" s="11" t="n"/>
-      <c r="T86" s="11" t="inlineStr">
+      <c r="R86" s="11" t="n">
+        <v>3225</v>
+      </c>
+      <c r="S86" s="11" t="inlineStr">
+        <is>
+          <t>3228</t>
+        </is>
+      </c>
+      <c r="T86" s="11" t="n"/>
+      <c r="U86" s="11" t="inlineStr">
         <is>
           <t>10% 확률로 분열(4초) 버프</t>
         </is>
       </c>
-      <c r="U86" s="11" t="n"/>
+      <c r="V86" s="11" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="n">
@@ -7152,10 +7290,10 @@
         <v>1</v>
       </c>
       <c r="J87" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
@@ -7175,18 +7313,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R87" s="11" t="inlineStr">
+      <c r="R87" s="11" t="n">
+        <v>3231</v>
+      </c>
+      <c r="S87" s="11" t="inlineStr">
         <is>
           <t>3236</t>
         </is>
       </c>
-      <c r="S87" s="11" t="n"/>
-      <c r="T87" s="11" t="inlineStr">
+      <c r="T87" s="11" t="n"/>
+      <c r="U87" s="11" t="inlineStr">
         <is>
           <t>10% 확률로 분열(5초) 버프</t>
         </is>
       </c>
-      <c r="U87" s="11" t="inlineStr">
+      <c r="V87" s="11" t="inlineStr">
         <is>
           <t>원문은 Lv.2와 같은 레어도 16</t>
         </is>
@@ -7231,10 +7372,10 @@
         <v>1</v>
       </c>
       <c r="J88" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K88" s="11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L88" s="11" t="inlineStr">
         <is>
@@ -7254,18 +7395,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R88" s="11" t="inlineStr">
-        <is>
-          <t>3345</t>
-        </is>
-      </c>
-      <c r="S88" s="11" t="n"/>
-      <c r="T88" s="11" t="inlineStr">
+      <c r="R88" s="11" t="n">
+        <v>3227</v>
+      </c>
+      <c r="S88" s="11" t="inlineStr">
+        <is>
+          <t>3224</t>
+        </is>
+      </c>
+      <c r="T88" s="11" t="n"/>
+      <c r="U88" s="11" t="inlineStr">
         <is>
           <t>군락 충돌 시 3% 확률로 전체 피해(공격력 10%)</t>
         </is>
       </c>
-      <c r="U88" s="11" t="n"/>
+      <c r="V88" s="11" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="11" t="n">
@@ -7306,10 +7450,10 @@
         <v>1</v>
       </c>
       <c r="J89" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
@@ -7329,18 +7473,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R89" s="11" t="inlineStr">
-        <is>
-          <t>3139</t>
-        </is>
-      </c>
-      <c r="S89" s="11" t="n"/>
-      <c r="T89" s="11" t="inlineStr">
+      <c r="R89" s="11" t="n">
+        <v>3232</v>
+      </c>
+      <c r="S89" s="11" t="inlineStr">
+        <is>
+          <t>3229</t>
+        </is>
+      </c>
+      <c r="T89" s="11" t="n"/>
+      <c r="U89" s="11" t="inlineStr">
         <is>
           <t>군락 충돌 시 5% 확률로 5초 지속 피해(공격력 5%)</t>
         </is>
       </c>
-      <c r="U89" s="11" t="n"/>
+      <c r="V89" s="11" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="n">
@@ -7381,7 +7528,7 @@
         <v>1</v>
       </c>
       <c r="J90" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K90" s="11" t="n">
         <v>26</v>
@@ -7404,18 +7551,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R90" s="11" t="inlineStr">
-        <is>
-          <t>3237</t>
-        </is>
-      </c>
-      <c r="S90" s="11" t="n"/>
-      <c r="T90" s="11" t="inlineStr">
+      <c r="R90" s="11" t="n">
+        <v>3236</v>
+      </c>
+      <c r="S90" s="11" t="inlineStr">
+        <is>
+          <t>3222</t>
+        </is>
+      </c>
+      <c r="T90" s="11" t="n"/>
+      <c r="U90" s="11" t="inlineStr">
         <is>
           <t>[피버] 버프 5초 · 콤보 계수 +50%</t>
         </is>
       </c>
-      <c r="U90" s="11" t="n"/>
+      <c r="V90" s="11" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="12" t="n">
@@ -7477,18 +7627,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R91" s="12" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
+      <c r="R91" s="12" t="n">
+        <v>3001</v>
       </c>
       <c r="S91" s="12" t="n"/>
-      <c r="T91" s="12" t="inlineStr">
+      <c r="T91" s="12" t="n"/>
+      <c r="U91" s="12" t="inlineStr">
         <is>
           <t>공격력 +2 (1 → 3)</t>
         </is>
       </c>
-      <c r="U91" s="12" t="n"/>
+      <c r="V91" s="12" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="12" t="n">
@@ -7532,7 +7681,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L92" s="12" t="inlineStr">
         <is>
@@ -7550,18 +7699,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R92" s="12" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
+      <c r="R92" s="12" t="n">
+        <v>3303</v>
       </c>
       <c r="S92" s="12" t="n"/>
-      <c r="T92" s="12" t="inlineStr">
+      <c r="T92" s="12" t="n"/>
+      <c r="U92" s="12" t="inlineStr">
         <is>
           <t>콤보 계수 +20%</t>
         </is>
       </c>
-      <c r="U92" s="12" t="n"/>
+      <c r="V92" s="12" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="12" t="n">
@@ -7602,7 +7750,7 @@
         <v>1</v>
       </c>
       <c r="J93" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K93" s="12" t="n">
         <v>2</v>
@@ -7623,18 +7771,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R93" s="12" t="inlineStr">
-        <is>
-          <t>3301</t>
-        </is>
+      <c r="R93" s="12" t="n">
+        <v>3301</v>
       </c>
       <c r="S93" s="12" t="n"/>
-      <c r="T93" s="12" t="inlineStr">
+      <c r="T93" s="12" t="n"/>
+      <c r="U93" s="12" t="inlineStr">
         <is>
           <t>수확기 속도 +10%</t>
         </is>
       </c>
-      <c r="U93" s="12" t="n"/>
+      <c r="V93" s="12" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="n">
@@ -7675,7 +7822,7 @@
         <v>1</v>
       </c>
       <c r="J94" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" s="12" t="n">
         <v>2</v>
@@ -7696,18 +7843,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R94" s="12" t="inlineStr">
-        <is>
-          <t>3302</t>
-        </is>
+      <c r="R94" s="12" t="n">
+        <v>3301</v>
       </c>
       <c r="S94" s="12" t="n"/>
-      <c r="T94" s="12" t="inlineStr">
+      <c r="T94" s="12" t="n"/>
+      <c r="U94" s="12" t="inlineStr">
         <is>
           <t>치명타 확률 2%</t>
         </is>
       </c>
-      <c r="U94" s="12" t="n"/>
+      <c r="V94" s="12" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="12" t="n">
@@ -7748,10 +7894,10 @@
         <v>1</v>
       </c>
       <c r="J95" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
@@ -7769,18 +7915,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R95" s="12" t="inlineStr">
-        <is>
-          <t>3303</t>
-        </is>
+      <c r="R95" s="12" t="n">
+        <v>3302</v>
       </c>
       <c r="S95" s="12" t="n"/>
-      <c r="T95" s="12" t="inlineStr">
+      <c r="T95" s="12" t="n"/>
+      <c r="U95" s="12" t="inlineStr">
         <is>
           <t>바 길이 +20%</t>
         </is>
       </c>
-      <c r="U95" s="12" t="n"/>
+      <c r="V95" s="12" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="12" t="n">
@@ -7821,7 +7966,7 @@
         <v>1</v>
       </c>
       <c r="J96" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K96" s="12" t="n">
         <v>3</v>
@@ -7842,18 +7987,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R96" s="12" t="inlineStr">
-        <is>
-          <t>3304</t>
-        </is>
-      </c>
-      <c r="S96" s="12" t="n"/>
-      <c r="T96" s="12" t="inlineStr">
+      <c r="R96" s="12" t="n">
+        <v>3304</v>
+      </c>
+      <c r="S96" s="12" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="T96" s="12" t="n"/>
+      <c r="U96" s="12" t="inlineStr">
         <is>
           <t>공격력 +2 (3 → 5)</t>
         </is>
       </c>
-      <c r="U96" s="12" t="n"/>
+      <c r="V96" s="12" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="12" t="n">
@@ -7915,18 +8063,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R97" s="12" t="inlineStr">
-        <is>
-          <t>3305</t>
-        </is>
+      <c r="R97" s="12" t="n">
+        <v>3303</v>
       </c>
       <c r="S97" s="12" t="n"/>
-      <c r="T97" s="12" t="inlineStr">
+      <c r="T97" s="12" t="n"/>
+      <c r="U97" s="12" t="inlineStr">
         <is>
           <t>수확기 크기 +10%</t>
         </is>
       </c>
-      <c r="U97" s="12" t="n"/>
+      <c r="V97" s="12" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="12" t="n">
@@ -7967,7 +8114,7 @@
         <v>1</v>
       </c>
       <c r="J98" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K98" s="12" t="n">
         <v>5</v>
@@ -7988,18 +8135,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R98" s="12" t="inlineStr">
+      <c r="R98" s="12" t="n">
+        <v>3303</v>
+      </c>
+      <c r="S98" s="12" t="inlineStr">
         <is>
           <t>3307</t>
         </is>
       </c>
-      <c r="S98" s="12" t="n"/>
-      <c r="T98" s="12" t="inlineStr">
+      <c r="T98" s="12" t="n"/>
+      <c r="U98" s="12" t="inlineStr">
         <is>
           <t>수확기 크기 +20%</t>
         </is>
       </c>
-      <c r="U98" s="12" t="inlineStr">
+      <c r="V98" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%. 원문은 Lv.1과 같은 레어도 5</t>
         </is>
@@ -8044,10 +8194,10 @@
         <v>1</v>
       </c>
       <c r="J99" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
@@ -8065,18 +8215,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R99" s="12" t="inlineStr">
-        <is>
-          <t>3104</t>
-        </is>
-      </c>
-      <c r="S99" s="12" t="n"/>
-      <c r="T99" s="12" t="inlineStr">
+      <c r="R99" s="12" t="n">
+        <v>3304</v>
+      </c>
+      <c r="S99" s="12" t="inlineStr">
+        <is>
+          <t>3306</t>
+        </is>
+      </c>
+      <c r="T99" s="12" t="n"/>
+      <c r="U99" s="12" t="inlineStr">
         <is>
           <t>공격력 +2 (5 → 7)</t>
         </is>
       </c>
-      <c r="U99" s="12" t="inlineStr">
+      <c r="V99" s="12" t="inlineStr">
         <is>
           <t>확인 필요: 원문은 "+3 (5 → 7)", 화살표 기준 +2로 넣음</t>
         </is>
@@ -8121,10 +8274,10 @@
         <v>1</v>
       </c>
       <c r="J100" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K100" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L100" s="12" t="inlineStr">
         <is>
@@ -8142,18 +8295,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R100" s="12" t="inlineStr">
-        <is>
-          <t>3106</t>
-        </is>
-      </c>
-      <c r="S100" s="12" t="n"/>
-      <c r="T100" s="12" t="inlineStr">
+      <c r="R100" s="12" t="n">
+        <v>3308</v>
+      </c>
+      <c r="S100" s="12" t="inlineStr">
+        <is>
+          <t>3305</t>
+        </is>
+      </c>
+      <c r="T100" s="12" t="n"/>
+      <c r="U100" s="12" t="inlineStr">
         <is>
           <t>바 길이 +30%</t>
         </is>
       </c>
-      <c r="U100" s="12" t="inlineStr">
+      <c r="V100" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%</t>
         </is>
@@ -8198,10 +8354,10 @@
         <v>1</v>
       </c>
       <c r="J101" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
@@ -8219,18 +8375,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R101" s="12" t="inlineStr">
+      <c r="R101" s="12" t="n">
+        <v>3312</v>
+      </c>
+      <c r="S101" s="12" t="inlineStr">
         <is>
           <t>3308</t>
         </is>
       </c>
-      <c r="S101" s="12" t="n"/>
-      <c r="T101" s="12" t="inlineStr">
+      <c r="T101" s="12" t="n"/>
+      <c r="U101" s="12" t="inlineStr">
         <is>
           <t>수확기 크기 +30%</t>
         </is>
       </c>
-      <c r="U101" s="12" t="inlineStr">
+      <c r="V101" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%</t>
         </is>
@@ -8296,18 +8455,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R102" s="12" t="inlineStr">
-        <is>
-          <t>3309</t>
-        </is>
-      </c>
-      <c r="S102" s="12" t="n"/>
-      <c r="T102" s="12" t="inlineStr">
+      <c r="R102" s="12" t="n">
+        <v>3307</v>
+      </c>
+      <c r="S102" s="12" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="T102" s="12" t="n"/>
+      <c r="U102" s="12" t="inlineStr">
         <is>
           <t>수확기 속도 +20%</t>
         </is>
       </c>
-      <c r="U102" s="12" t="inlineStr">
+      <c r="V102" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%</t>
         </is>
@@ -8352,10 +8514,10 @@
         <v>1</v>
       </c>
       <c r="J103" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
@@ -8373,18 +8535,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R103" s="12" t="inlineStr">
-        <is>
-          <t>3312</t>
-        </is>
-      </c>
-      <c r="S103" s="12" t="n"/>
-      <c r="T103" s="12" t="inlineStr">
+      <c r="R103" s="12" t="n">
+        <v>3309</v>
+      </c>
+      <c r="S103" s="12" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="T103" s="12" t="n"/>
+      <c r="U103" s="12" t="inlineStr">
         <is>
           <t>치명타 확률 4%</t>
         </is>
       </c>
-      <c r="U103" s="12" t="inlineStr">
+      <c r="V103" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -8429,10 +8594,10 @@
         <v>1</v>
       </c>
       <c r="J104" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K104" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L104" s="12" t="inlineStr">
         <is>
@@ -8450,18 +8615,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R104" s="12" t="inlineStr">
-        <is>
-          <t>3313</t>
-        </is>
+      <c r="R104" s="12" t="n">
+        <v>3313</v>
       </c>
       <c r="S104" s="12" t="n"/>
-      <c r="T104" s="12" t="inlineStr">
+      <c r="T104" s="12" t="n"/>
+      <c r="U104" s="12" t="inlineStr">
         <is>
           <t>회전 꼬마 수확기 +1 (0 → 1)</t>
         </is>
       </c>
-      <c r="U104" s="12" t="n"/>
+      <c r="V104" s="12" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="12" t="n">
@@ -8502,10 +8666,10 @@
         <v>1</v>
       </c>
       <c r="J105" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
@@ -8523,18 +8687,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R105" s="12" t="inlineStr">
-        <is>
-          <t>3109</t>
-        </is>
-      </c>
-      <c r="S105" s="12" t="n"/>
-      <c r="T105" s="12" t="inlineStr">
+      <c r="R105" s="12" t="n">
+        <v>3312</v>
+      </c>
+      <c r="S105" s="12" t="inlineStr">
+        <is>
+          <t>3310</t>
+        </is>
+      </c>
+      <c r="T105" s="12" t="n"/>
+      <c r="U105" s="12" t="inlineStr">
         <is>
           <t>바 길이 +50%</t>
         </is>
       </c>
-      <c r="U105" s="12" t="inlineStr">
+      <c r="V105" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +20%</t>
         </is>
@@ -8579,7 +8746,7 @@
         <v>1</v>
       </c>
       <c r="J106" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K106" s="12" t="n">
         <v>9</v>
@@ -8600,18 +8767,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R106" s="12" t="inlineStr">
-        <is>
-          <t>3314</t>
-        </is>
+      <c r="R106" s="12" t="n">
+        <v>3313</v>
       </c>
       <c r="S106" s="12" t="n"/>
-      <c r="T106" s="12" t="inlineStr">
+      <c r="T106" s="12" t="n"/>
+      <c r="U106" s="12" t="inlineStr">
         <is>
           <t>보스 피해 +20%</t>
         </is>
       </c>
-      <c r="U106" s="12" t="n"/>
+      <c r="V106" s="12" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="12" t="n">
@@ -8655,7 +8821,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
@@ -8673,18 +8839,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R107" s="12" t="inlineStr">
-        <is>
-          <t>3315</t>
-        </is>
-      </c>
-      <c r="S107" s="12" t="n"/>
-      <c r="T107" s="12" t="inlineStr">
+      <c r="R107" s="12" t="n">
+        <v>3310</v>
+      </c>
+      <c r="S107" s="12" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="T107" s="12" t="n"/>
+      <c r="U107" s="12" t="inlineStr">
         <is>
           <t>콤보 계수 +40%</t>
         </is>
       </c>
-      <c r="U107" s="12" t="inlineStr">
+      <c r="V107" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +20%</t>
         </is>
@@ -8729,10 +8898,10 @@
         <v>1</v>
       </c>
       <c r="J108" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K108" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L108" s="12" t="inlineStr">
         <is>
@@ -8750,18 +8919,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R108" s="12" t="inlineStr">
-        <is>
-          <t>3316</t>
-        </is>
+      <c r="R108" s="12" t="n">
+        <v>3310</v>
       </c>
       <c r="S108" s="12" t="n"/>
-      <c r="T108" s="12" t="inlineStr">
+      <c r="T108" s="12" t="n"/>
+      <c r="U108" s="12" t="inlineStr">
         <is>
           <t>지속 시간 +3초 (15 → 18)</t>
         </is>
       </c>
-      <c r="U108" s="12" t="inlineStr">
+      <c r="V108" s="12" t="inlineStr">
         <is>
           <t>확인 필요: 원문은 "+2초 (15 → 18)", 화살표 기준 +3으로 넣음</t>
         </is>
@@ -8806,10 +8974,10 @@
         <v>1</v>
       </c>
       <c r="J109" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
@@ -8827,18 +8995,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R109" s="12" t="inlineStr">
-        <is>
-          <t>3317</t>
-        </is>
-      </c>
-      <c r="S109" s="12" t="n"/>
-      <c r="T109" s="12" t="inlineStr">
+      <c r="R109" s="12" t="n">
+        <v>3306</v>
+      </c>
+      <c r="S109" s="12" t="inlineStr">
+        <is>
+          <t>3313</t>
+        </is>
+      </c>
+      <c r="T109" s="12" t="n"/>
+      <c r="U109" s="12" t="inlineStr">
         <is>
           <t>치명타 확률 6%</t>
         </is>
       </c>
-      <c r="U109" s="12" t="n"/>
+      <c r="V109" s="12" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="12" t="n">
@@ -8879,10 +9050,10 @@
         <v>1</v>
       </c>
       <c r="J110" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K110" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L110" s="12" t="inlineStr">
         <is>
@@ -8900,18 +9071,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R110" s="12" t="inlineStr">
-        <is>
-          <t>3318</t>
-        </is>
-      </c>
-      <c r="S110" s="12" t="n"/>
-      <c r="T110" s="12" t="inlineStr">
+      <c r="R110" s="12" t="n">
+        <v>3314</v>
+      </c>
+      <c r="S110" s="12" t="inlineStr">
+        <is>
+          <t>3309</t>
+        </is>
+      </c>
+      <c r="T110" s="12" t="n"/>
+      <c r="U110" s="12" t="inlineStr">
         <is>
           <t>공격력 +3 (7 → 10)</t>
         </is>
       </c>
-      <c r="U110" s="12" t="n"/>
+      <c r="V110" s="12" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="12" t="n">
@@ -8952,10 +9126,10 @@
         <v>1</v>
       </c>
       <c r="J111" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
@@ -8973,18 +9147,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R111" s="12" t="inlineStr">
-        <is>
-          <t>3320</t>
-        </is>
-      </c>
-      <c r="S111" s="12" t="n"/>
-      <c r="T111" s="12" t="inlineStr">
+      <c r="R111" s="12" t="n">
+        <v>3313</v>
+      </c>
+      <c r="S111" s="12" t="inlineStr">
+        <is>
+          <t>3316</t>
+        </is>
+      </c>
+      <c r="T111" s="12" t="n"/>
+      <c r="U111" s="12" t="inlineStr">
         <is>
           <t>보스 피해 +40%</t>
         </is>
       </c>
-      <c r="U111" s="12" t="n"/>
+      <c r="V111" s="12" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="12" t="n">
@@ -9028,7 +9205,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L112" s="12" t="inlineStr">
         <is>
@@ -9048,18 +9225,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R112" s="12" t="inlineStr">
-        <is>
-          <t>3115</t>
-        </is>
+      <c r="R112" s="12" t="n">
+        <v>3324</v>
       </c>
       <c r="S112" s="12" t="n"/>
-      <c r="T112" s="12" t="inlineStr">
+      <c r="T112" s="12" t="n"/>
+      <c r="U112" s="12" t="inlineStr">
         <is>
           <t>10% 확률로 3초 분신 바</t>
         </is>
       </c>
-      <c r="U112" s="12" t="inlineStr">
+      <c r="V112" s="12" t="inlineStr">
         <is>
           <t>param = 발동 확률</t>
         </is>
@@ -9104,7 +9280,7 @@
         <v>1</v>
       </c>
       <c r="J113" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K113" s="12" t="n">
         <v>13</v>
@@ -9125,18 +9301,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R113" s="12" t="inlineStr">
-        <is>
-          <t>3321</t>
-        </is>
-      </c>
-      <c r="S113" s="12" t="n"/>
-      <c r="T113" s="12" t="inlineStr">
+      <c r="R113" s="12" t="n">
+        <v>3317</v>
+      </c>
+      <c r="S113" s="12" t="inlineStr">
+        <is>
+          <t>3318</t>
+        </is>
+      </c>
+      <c r="T113" s="12" t="n"/>
+      <c r="U113" s="12" t="inlineStr">
         <is>
           <t>지속 시간 +3초 (18 → 21)</t>
         </is>
       </c>
-      <c r="U113" s="12" t="n"/>
+      <c r="V113" s="12" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="12" t="n">
@@ -9177,7 +9356,7 @@
         <v>1</v>
       </c>
       <c r="J114" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K114" s="12" t="n">
         <v>14</v>
@@ -9198,18 +9377,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R114" s="12" t="inlineStr">
-        <is>
-          <t>3323</t>
-        </is>
-      </c>
-      <c r="S114" s="12" t="n"/>
-      <c r="T114" s="12" t="inlineStr">
+      <c r="R114" s="12" t="n">
+        <v>3315</v>
+      </c>
+      <c r="S114" s="12" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="T114" s="12" t="n"/>
+      <c r="U114" s="12" t="inlineStr">
         <is>
           <t>수확기 속도 +30%</t>
         </is>
       </c>
-      <c r="U114" s="12" t="n"/>
+      <c r="V114" s="12" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="12" t="n">
@@ -9250,10 +9432,10 @@
         <v>1</v>
       </c>
       <c r="J115" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
@@ -9271,18 +9453,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R115" s="12" t="inlineStr">
-        <is>
-          <t>3221</t>
-        </is>
-      </c>
-      <c r="S115" s="12" t="n"/>
-      <c r="T115" s="12" t="inlineStr">
+      <c r="R115" s="12" t="n">
+        <v>3318</v>
+      </c>
+      <c r="S115" s="12" t="inlineStr">
+        <is>
+          <t>3317</t>
+        </is>
+      </c>
+      <c r="T115" s="12" t="n"/>
+      <c r="U115" s="12" t="inlineStr">
         <is>
           <t>콤보 계수 +60%</t>
         </is>
       </c>
-      <c r="U115" s="12" t="n"/>
+      <c r="V115" s="12" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="12" t="n">
@@ -9323,10 +9508,10 @@
         <v>1</v>
       </c>
       <c r="J116" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K116" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L116" s="12" t="inlineStr">
         <is>
@@ -9344,18 +9529,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R116" s="12" t="inlineStr">
-        <is>
-          <t>3223</t>
-        </is>
-      </c>
-      <c r="S116" s="12" t="n"/>
-      <c r="T116" s="12" t="inlineStr">
+      <c r="R116" s="12" t="n">
+        <v>3319</v>
+      </c>
+      <c r="S116" s="12" t="inlineStr">
+        <is>
+          <t>3314</t>
+        </is>
+      </c>
+      <c r="T116" s="12" t="n"/>
+      <c r="U116" s="12" t="inlineStr">
         <is>
           <t>회전 꼬마 수확기 +1 (1 → 2)</t>
         </is>
       </c>
-      <c r="U116" s="12" t="n"/>
+      <c r="V116" s="12" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="12" t="n">
@@ -9396,10 +9584,10 @@
         <v>1</v>
       </c>
       <c r="J117" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
@@ -9417,18 +9605,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R117" s="12" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
+      <c r="R117" s="12" t="n">
+        <v>3319</v>
       </c>
       <c r="S117" s="12" t="n"/>
-      <c r="T117" s="12" t="inlineStr">
+      <c r="T117" s="12" t="n"/>
+      <c r="U117" s="12" t="inlineStr">
         <is>
           <t>회전 꼬마 수확기 공격력 5%</t>
         </is>
       </c>
-      <c r="U117" s="12" t="n"/>
+      <c r="V117" s="12" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="12" t="n">
@@ -9469,10 +9656,10 @@
         <v>1</v>
       </c>
       <c r="J118" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K118" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L118" s="12" t="inlineStr">
         <is>
@@ -9490,18 +9677,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R118" s="12" t="inlineStr">
-        <is>
-          <t>3325</t>
-        </is>
-      </c>
-      <c r="S118" s="12" t="n"/>
-      <c r="T118" s="12" t="inlineStr">
+      <c r="R118" s="12" t="n">
+        <v>3331</v>
+      </c>
+      <c r="S118" s="12" t="inlineStr">
+        <is>
+          <t>3321</t>
+        </is>
+      </c>
+      <c r="T118" s="12" t="n"/>
+      <c r="U118" s="12" t="inlineStr">
         <is>
           <t>보스 피해 +60%</t>
         </is>
       </c>
-      <c r="U118" s="12" t="n"/>
+      <c r="V118" s="12" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="12" t="n">
@@ -9542,10 +9732,10 @@
         <v>1</v>
       </c>
       <c r="J119" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
@@ -9565,18 +9755,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R119" s="12" t="inlineStr">
-        <is>
-          <t>3327</t>
-        </is>
-      </c>
-      <c r="S119" s="12" t="n"/>
-      <c r="T119" s="12" t="inlineStr">
+      <c r="R119" s="12" t="n">
+        <v>3324</v>
+      </c>
+      <c r="S119" s="12" t="inlineStr">
+        <is>
+          <t>3322</t>
+        </is>
+      </c>
+      <c r="T119" s="12" t="n"/>
+      <c r="U119" s="12" t="inlineStr">
         <is>
           <t>10% 확률로 4초 분신 바</t>
         </is>
       </c>
-      <c r="U119" s="12" t="n"/>
+      <c r="V119" s="12" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="12" t="n">
@@ -9617,10 +9810,10 @@
         <v>1</v>
       </c>
       <c r="J120" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K120" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L120" s="12" t="inlineStr">
         <is>
@@ -9638,18 +9831,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R120" s="12" t="inlineStr">
-        <is>
-          <t>3328</t>
-        </is>
-      </c>
-      <c r="S120" s="12" t="n"/>
-      <c r="T120" s="12" t="inlineStr">
+      <c r="R120" s="12" t="n">
+        <v>3323</v>
+      </c>
+      <c r="S120" s="12" t="inlineStr">
+        <is>
+          <t>3325</t>
+        </is>
+      </c>
+      <c r="T120" s="12" t="n"/>
+      <c r="U120" s="12" t="inlineStr">
         <is>
           <t>콤보 계수 +80%</t>
         </is>
       </c>
-      <c r="U120" s="12" t="n"/>
+      <c r="V120" s="12" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="12" t="n">
@@ -9690,7 +9886,7 @@
         <v>1</v>
       </c>
       <c r="J121" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K121" s="12" t="n">
         <v>16</v>
@@ -9711,18 +9907,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R121" s="12" t="inlineStr">
-        <is>
-          <t>3224</t>
-        </is>
+      <c r="R121" s="12" t="n">
+        <v>3321</v>
       </c>
       <c r="S121" s="12" t="n"/>
-      <c r="T121" s="12" t="inlineStr">
+      <c r="T121" s="12" t="n"/>
+      <c r="U121" s="12" t="inlineStr">
         <is>
           <t>치명타 피해 100%</t>
         </is>
       </c>
-      <c r="U121" s="12" t="n"/>
+      <c r="V121" s="12" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="12" t="n">
@@ -9763,10 +9958,10 @@
         <v>1</v>
       </c>
       <c r="J122" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K122" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L122" s="12" t="inlineStr">
         <is>
@@ -9784,18 +9979,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R122" s="12" t="inlineStr">
-        <is>
-          <t>3226</t>
-        </is>
-      </c>
-      <c r="S122" s="12" t="n"/>
-      <c r="T122" s="12" t="inlineStr">
+      <c r="R122" s="12" t="n">
+        <v>3331</v>
+      </c>
+      <c r="S122" s="12" t="inlineStr">
+        <is>
+          <t>3319</t>
+        </is>
+      </c>
+      <c r="T122" s="12" t="n"/>
+      <c r="U122" s="12" t="inlineStr">
         <is>
           <t>치명타 확률 8%</t>
         </is>
       </c>
-      <c r="U122" s="12" t="n"/>
+      <c r="V122" s="12" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="12" t="n">
@@ -9836,7 +10034,7 @@
         <v>1</v>
       </c>
       <c r="J123" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K123" s="12" t="n">
         <v>19</v>
@@ -9857,18 +10055,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R123" s="12" t="inlineStr">
-        <is>
-          <t>3332</t>
-        </is>
-      </c>
-      <c r="S123" s="12" t="n"/>
-      <c r="T123" s="12" t="inlineStr">
+      <c r="R123" s="12" t="n">
+        <v>3325</v>
+      </c>
+      <c r="S123" s="12" t="inlineStr">
+        <is>
+          <t>3323</t>
+        </is>
+      </c>
+      <c r="T123" s="12" t="n"/>
+      <c r="U123" s="12" t="inlineStr">
         <is>
           <t>지속 시간 +3초 (21 → 24)</t>
         </is>
       </c>
-      <c r="U123" s="12" t="n"/>
+      <c r="V123" s="12" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="12" t="n">
@@ -9909,7 +10110,7 @@
         <v>1</v>
       </c>
       <c r="J124" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K124" s="12" t="n">
         <v>20</v>
@@ -9930,18 +10131,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R124" s="12" t="inlineStr">
+      <c r="R124" s="12" t="n">
+        <v>3325</v>
+      </c>
+      <c r="S124" s="12" t="inlineStr">
         <is>
           <t>3333</t>
         </is>
       </c>
-      <c r="S124" s="12" t="n"/>
-      <c r="T124" s="12" t="inlineStr">
+      <c r="T124" s="12" t="n"/>
+      <c r="U124" s="12" t="inlineStr">
         <is>
           <t>지속 시간 +3초 (24 → 27)</t>
         </is>
       </c>
-      <c r="U124" s="12" t="inlineStr">
+      <c r="V124" s="12" t="inlineStr">
         <is>
           <t>원문은 Lv.3과 같은 레어도 14</t>
         </is>
@@ -9986,10 +10190,10 @@
         <v>1</v>
       </c>
       <c r="J125" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
@@ -10007,18 +10211,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R125" s="12" t="inlineStr">
-        <is>
-          <t>3131</t>
-        </is>
-      </c>
-      <c r="S125" s="12" t="n"/>
-      <c r="T125" s="12" t="inlineStr">
+      <c r="R125" s="12" t="n">
+        <v>3327</v>
+      </c>
+      <c r="S125" s="12" t="inlineStr">
+        <is>
+          <t>3328</t>
+        </is>
+      </c>
+      <c r="T125" s="12" t="n"/>
+      <c r="U125" s="12" t="inlineStr">
         <is>
           <t>보스 피해 +80%</t>
         </is>
       </c>
-      <c r="U125" s="12" t="n"/>
+      <c r="V125" s="12" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="12" t="n">
@@ -10059,10 +10266,10 @@
         <v>1</v>
       </c>
       <c r="J126" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K126" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L126" s="12" t="inlineStr">
         <is>
@@ -10080,18 +10287,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R126" s="12" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="S126" s="12" t="n"/>
-      <c r="T126" s="12" t="inlineStr">
+      <c r="R126" s="12" t="n">
+        <v>3329</v>
+      </c>
+      <c r="S126" s="12" t="inlineStr">
+        <is>
+          <t>3330</t>
+        </is>
+      </c>
+      <c r="T126" s="12" t="n"/>
+      <c r="U126" s="12" t="inlineStr">
         <is>
           <t>콤보 계수 +100%</t>
         </is>
       </c>
-      <c r="U126" s="12" t="n"/>
+      <c r="V126" s="12" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="12" t="n">
@@ -10132,7 +10342,7 @@
         <v>1</v>
       </c>
       <c r="J127" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K127" s="12" t="n">
         <v>21</v>
@@ -10153,18 +10363,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R127" s="12" t="inlineStr">
-        <is>
-          <t>3334</t>
-        </is>
-      </c>
-      <c r="S127" s="12" t="n"/>
-      <c r="T127" s="12" t="inlineStr">
+      <c r="R127" s="12" t="n">
+        <v>3328</v>
+      </c>
+      <c r="S127" s="12" t="inlineStr">
+        <is>
+          <t>3327</t>
+        </is>
+      </c>
+      <c r="T127" s="12" t="n"/>
+      <c r="U127" s="12" t="inlineStr">
         <is>
           <t>회전 꼬마 수확기 공격력 10%</t>
         </is>
       </c>
-      <c r="U127" s="12" t="n"/>
+      <c r="V127" s="12" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="12" t="n">
@@ -10205,10 +10418,10 @@
         <v>1</v>
       </c>
       <c r="J128" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K128" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L128" s="12" t="inlineStr">
         <is>
@@ -10226,18 +10439,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R128" s="12" t="inlineStr">
-        <is>
-          <t>3335</t>
-        </is>
-      </c>
-      <c r="S128" s="12" t="n"/>
-      <c r="T128" s="12" t="inlineStr">
+      <c r="R128" s="12" t="n">
+        <v>3326</v>
+      </c>
+      <c r="S128" s="12" t="inlineStr">
+        <is>
+          <t>3320</t>
+        </is>
+      </c>
+      <c r="T128" s="12" t="n"/>
+      <c r="U128" s="12" t="inlineStr">
         <is>
           <t>공격력 +5 (10 → 15)</t>
         </is>
       </c>
-      <c r="U128" s="12" t="n"/>
+      <c r="V128" s="12" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="12" t="n">
@@ -10278,10 +10494,10 @@
         <v>4</v>
       </c>
       <c r="J129" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
@@ -10299,18 +10515,17 @@
           <t>Mycelite</t>
         </is>
       </c>
-      <c r="R129" s="12" t="inlineStr">
-        <is>
-          <t>3337</t>
-        </is>
+      <c r="R129" s="12" t="n">
+        <v>3341</v>
       </c>
       <c r="S129" s="12" t="n"/>
-      <c r="T129" s="12" t="inlineStr">
+      <c r="T129" s="12" t="n"/>
+      <c r="U129" s="12" t="inlineStr">
         <is>
           <t>수확기 개수 +1 / Lv (최대 5개 장착)</t>
         </is>
       </c>
-      <c r="U129" s="12" t="n"/>
+      <c r="V129" s="12" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="12" t="n">
@@ -10351,10 +10566,10 @@
         <v>1</v>
       </c>
       <c r="J130" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L130" s="12" t="inlineStr">
         <is>
@@ -10372,18 +10587,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R130" s="12" t="inlineStr">
-        <is>
-          <t>3338</t>
-        </is>
-      </c>
-      <c r="S130" s="12" t="n"/>
-      <c r="T130" s="12" t="inlineStr">
+      <c r="R130" s="12" t="n">
+        <v>3337</v>
+      </c>
+      <c r="S130" s="12" t="inlineStr">
+        <is>
+          <t>3335</t>
+        </is>
+      </c>
+      <c r="T130" s="12" t="n"/>
+      <c r="U130" s="12" t="inlineStr">
         <is>
           <t>보스 피해 +100%</t>
         </is>
       </c>
-      <c r="U130" s="12" t="n"/>
+      <c r="V130" s="12" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="12" t="n">
@@ -10424,10 +10642,10 @@
         <v>1</v>
       </c>
       <c r="J131" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
@@ -10447,18 +10665,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R131" s="12" t="inlineStr">
-        <is>
-          <t>3133</t>
-        </is>
-      </c>
-      <c r="S131" s="12" t="n"/>
-      <c r="T131" s="12" t="inlineStr">
+      <c r="R131" s="12" t="n">
+        <v>3334</v>
+      </c>
+      <c r="S131" s="12" t="inlineStr">
+        <is>
+          <t>3329</t>
+        </is>
+      </c>
+      <c r="T131" s="12" t="n"/>
+      <c r="U131" s="12" t="inlineStr">
         <is>
           <t>10% 확률로 5초 분신 바</t>
         </is>
       </c>
-      <c r="U131" s="12" t="n"/>
+      <c r="V131" s="12" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="12" t="n">
@@ -10499,10 +10720,10 @@
         <v>1</v>
       </c>
       <c r="J132" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K132" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L132" s="12" t="inlineStr">
         <is>
@@ -10520,18 +10741,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R132" s="12" t="inlineStr">
-        <is>
-          <t>3341</t>
-        </is>
-      </c>
-      <c r="S132" s="12" t="n"/>
-      <c r="T132" s="12" t="inlineStr">
+      <c r="R132" s="12" t="n">
+        <v>3331</v>
+      </c>
+      <c r="S132" s="12" t="inlineStr">
+        <is>
+          <t>3332</t>
+        </is>
+      </c>
+      <c r="T132" s="12" t="n"/>
+      <c r="U132" s="12" t="inlineStr">
         <is>
           <t>치명타 확률 10%</t>
         </is>
       </c>
-      <c r="U132" s="12" t="n"/>
+      <c r="V132" s="12" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="12" t="n">
@@ -10572,10 +10796,10 @@
         <v>1</v>
       </c>
       <c r="J133" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
@@ -10593,18 +10817,17 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R133" s="12" t="inlineStr">
-        <is>
-          <t>3339</t>
-        </is>
+      <c r="R133" s="12" t="n">
+        <v>3333</v>
       </c>
       <c r="S133" s="12" t="n"/>
-      <c r="T133" s="12" t="inlineStr">
+      <c r="T133" s="12" t="n"/>
+      <c r="U133" s="12" t="inlineStr">
         <is>
           <t>분신 바 +1 (1 → 2)</t>
         </is>
       </c>
-      <c r="U133" s="12" t="n"/>
+      <c r="V133" s="12" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="12" t="n">
@@ -10645,10 +10868,10 @@
         <v>1</v>
       </c>
       <c r="J134" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K134" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L134" s="12" t="inlineStr">
         <is>
@@ -10666,18 +10889,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R134" s="12" t="inlineStr">
-        <is>
-          <t>3342</t>
-        </is>
-      </c>
-      <c r="S134" s="12" t="n"/>
-      <c r="T134" s="12" t="inlineStr">
+      <c r="R134" s="12" t="n">
+        <v>3335</v>
+      </c>
+      <c r="S134" s="12" t="inlineStr">
+        <is>
+          <t>3326</t>
+        </is>
+      </c>
+      <c r="T134" s="12" t="n"/>
+      <c r="U134" s="12" t="inlineStr">
         <is>
           <t>회전 꼬마 수확기 +1 (2 → 3)</t>
         </is>
       </c>
-      <c r="U134" s="12" t="n"/>
+      <c r="V134" s="12" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="12" t="n">
@@ -10718,10 +10944,10 @@
         <v>1</v>
       </c>
       <c r="J135" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K135" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
@@ -10739,18 +10965,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R135" s="12" t="inlineStr">
-        <is>
-          <t>3343</t>
-        </is>
-      </c>
-      <c r="S135" s="12" t="n"/>
-      <c r="T135" s="12" t="inlineStr">
+      <c r="R135" s="12" t="n">
+        <v>3335</v>
+      </c>
+      <c r="S135" s="12" t="inlineStr">
+        <is>
+          <t>3337</t>
+        </is>
+      </c>
+      <c r="T135" s="12" t="n"/>
+      <c r="U135" s="12" t="inlineStr">
         <is>
           <t>회전 꼬마 수확기 공격력 15%</t>
         </is>
       </c>
-      <c r="U135" s="12" t="n"/>
+      <c r="V135" s="12" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="12" t="n">
@@ -10791,10 +11020,10 @@
         <v>1</v>
       </c>
       <c r="J136" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K136" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L136" s="12" t="inlineStr">
         <is>
@@ -10812,18 +11041,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R136" s="12" t="inlineStr">
-        <is>
-          <t>3344</t>
-        </is>
-      </c>
-      <c r="S136" s="12" t="n"/>
-      <c r="T136" s="12" t="inlineStr">
+      <c r="R136" s="12" t="n">
+        <v>3337</v>
+      </c>
+      <c r="S136" s="12" t="inlineStr">
+        <is>
+          <t>3331</t>
+        </is>
+      </c>
+      <c r="T136" s="12" t="n"/>
+      <c r="U136" s="12" t="inlineStr">
         <is>
           <t>치명타 피해 120%</t>
         </is>
       </c>
-      <c r="U136" s="12" t="inlineStr">
+      <c r="V136" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +20%</t>
         </is>
@@ -10871,7 +11103,7 @@
         <v>1</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
@@ -10889,18 +11121,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R137" s="12" t="inlineStr">
+      <c r="R137" s="12" t="n">
+        <v>3342</v>
+      </c>
+      <c r="S137" s="12" t="inlineStr">
         <is>
           <t>3346</t>
         </is>
       </c>
-      <c r="S137" s="12" t="n"/>
-      <c r="T137" s="12" t="inlineStr">
+      <c r="T137" s="12" t="n"/>
+      <c r="U137" s="12" t="inlineStr">
         <is>
           <t>치명타 피해 150%</t>
         </is>
       </c>
-      <c r="U137" s="12" t="inlineStr">
+      <c r="V137" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +30%</t>
         </is>
@@ -10945,7 +11180,7 @@
         <v>1</v>
       </c>
       <c r="J138" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K138" s="12" t="n">
         <v>27</v>
@@ -10966,18 +11201,21 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="R138" s="12" t="inlineStr">
-        <is>
-          <t>3347</t>
-        </is>
-      </c>
-      <c r="S138" s="12" t="n"/>
-      <c r="T138" s="12" t="inlineStr">
+      <c r="R138" s="12" t="n">
+        <v>3343</v>
+      </c>
+      <c r="S138" s="12" t="inlineStr">
+        <is>
+          <t>3334</t>
+        </is>
+      </c>
+      <c r="T138" s="12" t="n"/>
+      <c r="U138" s="12" t="inlineStr">
         <is>
           <t>지속 시간 +3초 (27 → 30)</t>
         </is>
       </c>
-      <c r="U138" s="12" t="n"/>
+      <c r="V138" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/Data/Tables/Skill.xlsx
+++ b/Assets/Data/Tables/Skill.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
-          <t>세로 줄 (0~4, 왼쪽부터). 시작 노드는 2</t>
+          <t>세로 줄 (0부터, 왼쪽부터). 칸 수 제한 없음, 화면보다 넓으면 가로로 스크롤</t>
         </is>
       </c>
       <c r="K3" s="8" t="inlineStr">
@@ -904,7 +904,7 @@
         <v>10</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>3</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K5" s="10" t="n">
         <v>1</v>
@@ -1052,10 +1052,10 @@
         <v>1</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K6" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L6" s="10" t="inlineStr">
         <is>
@@ -1124,10 +1124,10 @@
         <v>1</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="K7" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
@@ -1196,10 +1196,10 @@
         <v>1</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="K8" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L8" s="10" t="inlineStr">
         <is>
@@ -1268,10 +1268,10 @@
         <v>1</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K9" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L9" s="10" t="inlineStr">
         <is>
@@ -1340,10 +1340,10 @@
         <v>3</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="K10" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
@@ -1418,10 +1418,10 @@
         <v>1</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K11" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
@@ -1498,10 +1498,10 @@
         <v>1</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
         <v>1</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
@@ -1650,10 +1650,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
@@ -1730,10 +1730,10 @@
         <v>1</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K15" s="10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
         <v>1</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K16" s="10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
@@ -1878,10 +1878,10 @@
         <v>1</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K17" s="10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
@@ -1954,10 +1954,10 @@
         <v>1</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K18" s="10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         <v>1</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K19" s="10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
@@ -2102,10 +2102,10 @@
         <v>1</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K20" s="10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
@@ -2182,10 +2182,10 @@
         <v>1</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K21" s="10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
@@ -2258,10 +2258,10 @@
         <v>1</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K22" s="10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
@@ -2338,10 +2338,10 @@
         <v>1</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K23" s="10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
         <v>1</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K24" s="10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
@@ -2494,10 +2494,10 @@
         <v>1</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="K25" s="10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
@@ -2574,10 +2574,10 @@
         <v>1</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K26" s="10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
@@ -2650,10 +2650,10 @@
         <v>1</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K27" s="10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
@@ -2726,10 +2726,10 @@
         <v>1</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L28" s="10" t="inlineStr">
         <is>
@@ -2806,10 +2806,10 @@
         <v>1</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
@@ -2886,10 +2886,10 @@
         <v>1</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
         <v>1</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
@@ -3038,10 +3038,10 @@
         <v>1</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
@@ -3118,10 +3118,10 @@
         <v>1</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K33" s="10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L33" s="10" t="inlineStr">
         <is>
@@ -3190,10 +3190,10 @@
         <v>1</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K34" s="10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L34" s="10" t="inlineStr">
         <is>
@@ -3266,10 +3266,10 @@
         <v>1</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L35" s="10" t="inlineStr">
         <is>
@@ -3338,10 +3338,10 @@
         <v>1</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L36" s="10" t="inlineStr">
         <is>
@@ -3418,10 +3418,10 @@
         <v>1</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L37" s="10" t="inlineStr">
         <is>
@@ -3490,10 +3490,10 @@
         <v>1</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K38" s="10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L38" s="10" t="inlineStr">
         <is>
@@ -3570,10 +3570,10 @@
         <v>1</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L39" s="10" t="inlineStr">
         <is>
@@ -3650,10 +3650,10 @@
         <v>1</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L40" s="10" t="inlineStr">
         <is>
@@ -3730,10 +3730,10 @@
         <v>1</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L41" s="10" t="inlineStr">
         <is>
@@ -3810,10 +3810,10 @@
         <v>1</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L42" s="10" t="inlineStr">
         <is>
@@ -3890,10 +3890,10 @@
         <v>1</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L43" s="10" t="inlineStr">
         <is>
@@ -3970,10 +3970,10 @@
         <v>1</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K44" s="10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L44" s="10" t="inlineStr">
         <is>
@@ -4050,10 +4050,10 @@
         <v>1</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K45" s="10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L45" s="10" t="inlineStr">
         <is>
@@ -4130,10 +4130,10 @@
         <v>1</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K46" s="10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L46" s="10" t="inlineStr">
         <is>
@@ -4210,10 +4210,10 @@
         <v>5</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K47" s="10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L47" s="10" t="inlineStr">
         <is>
@@ -4288,10 +4288,10 @@
         <v>1</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L48" s="10" t="inlineStr">
         <is>
@@ -4364,10 +4364,10 @@
         <v>1</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L49" s="10" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>1</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L50" s="10" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>1</v>
       </c>
       <c r="J51" s="11" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K51" s="11" t="n">
         <v>1</v>
@@ -4600,7 +4600,7 @@
         <v>1</v>
       </c>
       <c r="J52" s="11" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="K52" s="11" t="n">
         <v>2</v>
@@ -4672,7 +4672,7 @@
         <v>1</v>
       </c>
       <c r="J53" s="11" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="K53" s="11" t="n">
         <v>3</v>
@@ -4748,10 +4748,10 @@
         <v>1</v>
       </c>
       <c r="J54" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="K54" s="11" t="n">
         <v>4</v>
-      </c>
-      <c r="K54" s="11" t="n">
-        <v>2</v>
       </c>
       <c r="L54" s="11" t="inlineStr">
         <is>
@@ -4824,10 +4824,10 @@
         <v>1</v>
       </c>
       <c r="J55" s="11" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
@@ -4902,10 +4902,10 @@
         <v>1</v>
       </c>
       <c r="J56" s="11" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L56" s="11" t="inlineStr">
         <is>
@@ -4980,10 +4980,10 @@
         <v>1</v>
       </c>
       <c r="J57" s="11" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
@@ -5056,10 +5056,10 @@
         <v>1</v>
       </c>
       <c r="J58" s="11" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L58" s="11" t="inlineStr">
         <is>
@@ -5134,10 +5134,10 @@
         <v>1</v>
       </c>
       <c r="J59" s="11" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
@@ -5212,10 +5212,10 @@
         <v>1</v>
       </c>
       <c r="J60" s="11" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L60" s="11" t="inlineStr">
         <is>
@@ -5284,10 +5284,10 @@
         <v>1</v>
       </c>
       <c r="J61" s="11" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
@@ -5360,10 +5360,10 @@
         <v>1</v>
       </c>
       <c r="J62" s="11" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L62" s="11" t="inlineStr">
         <is>
@@ -5440,10 +5440,10 @@
         <v>1</v>
       </c>
       <c r="J63" s="11" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
@@ -5512,10 +5512,10 @@
         <v>1</v>
       </c>
       <c r="J64" s="11" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L64" s="11" t="inlineStr">
         <is>
@@ -5590,10 +5590,10 @@
         <v>1</v>
       </c>
       <c r="J65" s="11" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
@@ -5666,10 +5666,10 @@
         <v>1</v>
       </c>
       <c r="J66" s="11" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L66" s="11" t="inlineStr">
         <is>
@@ -5738,10 +5738,10 @@
         <v>1</v>
       </c>
       <c r="J67" s="11" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
@@ -5814,10 +5814,10 @@
         <v>1</v>
       </c>
       <c r="J68" s="11" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L68" s="11" t="inlineStr">
         <is>
@@ -5890,10 +5890,10 @@
         <v>1</v>
       </c>
       <c r="J69" s="11" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
@@ -5968,10 +5968,10 @@
         <v>1</v>
       </c>
       <c r="J70" s="11" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L70" s="11" t="inlineStr">
         <is>
@@ -6046,10 +6046,10 @@
         <v>1</v>
       </c>
       <c r="J71" s="11" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
@@ -6128,10 +6128,10 @@
         <v>1</v>
       </c>
       <c r="J72" s="11" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L72" s="11" t="inlineStr">
         <is>
@@ -6206,10 +6206,10 @@
         <v>1</v>
       </c>
       <c r="J73" s="11" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
@@ -6284,10 +6284,10 @@
         <v>1</v>
       </c>
       <c r="J74" s="11" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L74" s="11" t="inlineStr">
         <is>
@@ -6362,10 +6362,10 @@
         <v>1</v>
       </c>
       <c r="J75" s="11" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
@@ -6438,10 +6438,10 @@
         <v>1</v>
       </c>
       <c r="J76" s="11" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="K76" s="11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L76" s="11" t="inlineStr">
         <is>
@@ -6514,10 +6514,10 @@
         <v>1</v>
       </c>
       <c r="J77" s="11" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
@@ -6590,10 +6590,10 @@
         <v>1</v>
       </c>
       <c r="J78" s="11" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="K78" s="11" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L78" s="11" t="inlineStr">
         <is>
@@ -6668,10 +6668,10 @@
         <v>1</v>
       </c>
       <c r="J79" s="11" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
@@ -6746,10 +6746,10 @@
         <v>1</v>
       </c>
       <c r="J80" s="11" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="K80" s="11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L80" s="11" t="inlineStr">
         <is>
@@ -6824,10 +6824,10 @@
         <v>1</v>
       </c>
       <c r="J81" s="11" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
@@ -6900,10 +6900,10 @@
         <v>1</v>
       </c>
       <c r="J82" s="11" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="K82" s="11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L82" s="11" t="inlineStr">
         <is>
@@ -6982,10 +6982,10 @@
         <v>1</v>
       </c>
       <c r="J83" s="11" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
@@ -7058,10 +7058,10 @@
         <v>1</v>
       </c>
       <c r="J84" s="11" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="K84" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L84" s="11" t="inlineStr">
         <is>
@@ -7140,10 +7140,10 @@
         <v>5</v>
       </c>
       <c r="J85" s="11" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
@@ -7212,10 +7212,10 @@
         <v>1</v>
       </c>
       <c r="J86" s="11" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="K86" s="11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L86" s="11" t="inlineStr">
         <is>
@@ -7290,10 +7290,10 @@
         <v>1</v>
       </c>
       <c r="J87" s="11" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
@@ -7372,10 +7372,10 @@
         <v>1</v>
       </c>
       <c r="J88" s="11" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="K88" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L88" s="11" t="inlineStr">
         <is>
@@ -7450,10 +7450,10 @@
         <v>1</v>
       </c>
       <c r="J89" s="11" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
@@ -7528,10 +7528,10 @@
         <v>1</v>
       </c>
       <c r="J90" s="11" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="K90" s="11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L90" s="11" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>1</v>
       </c>
       <c r="J91" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K91" s="12" t="n">
         <v>1</v>
@@ -7750,7 +7750,7 @@
         <v>1</v>
       </c>
       <c r="J93" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K93" s="12" t="n">
         <v>2</v>
@@ -7822,10 +7822,10 @@
         <v>1</v>
       </c>
       <c r="J94" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K94" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L94" s="12" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>0</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
@@ -7966,10 +7966,10 @@
         <v>1</v>
       </c>
       <c r="J96" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K96" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L96" s="12" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>1</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L97" s="12" t="inlineStr">
         <is>
@@ -8114,10 +8114,10 @@
         <v>1</v>
       </c>
       <c r="J98" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K98" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L98" s="12" t="inlineStr">
         <is>
@@ -8194,10 +8194,10 @@
         <v>1</v>
       </c>
       <c r="J99" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
@@ -8274,10 +8274,10 @@
         <v>1</v>
       </c>
       <c r="J100" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K100" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L100" s="12" t="inlineStr">
         <is>
@@ -8354,10 +8354,10 @@
         <v>1</v>
       </c>
       <c r="J101" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
@@ -8434,10 +8434,10 @@
         <v>1</v>
       </c>
       <c r="J102" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K102" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L102" s="12" t="inlineStr">
         <is>
@@ -8514,10 +8514,10 @@
         <v>1</v>
       </c>
       <c r="J103" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
@@ -8594,10 +8594,10 @@
         <v>1</v>
       </c>
       <c r="J104" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K104" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L104" s="12" t="inlineStr">
         <is>
@@ -8666,10 +8666,10 @@
         <v>1</v>
       </c>
       <c r="J105" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
@@ -8746,10 +8746,10 @@
         <v>1</v>
       </c>
       <c r="J106" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K106" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L106" s="12" t="inlineStr">
         <is>
@@ -8818,10 +8818,10 @@
         <v>1</v>
       </c>
       <c r="J107" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
@@ -8898,10 +8898,10 @@
         <v>1</v>
       </c>
       <c r="J108" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K108" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L108" s="12" t="inlineStr">
         <is>
@@ -8974,10 +8974,10 @@
         <v>1</v>
       </c>
       <c r="J109" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
@@ -9050,10 +9050,10 @@
         <v>1</v>
       </c>
       <c r="J110" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K110" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L110" s="12" t="inlineStr">
         <is>
@@ -9126,10 +9126,10 @@
         <v>1</v>
       </c>
       <c r="J111" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
@@ -9202,10 +9202,10 @@
         <v>1</v>
       </c>
       <c r="J112" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K112" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L112" s="12" t="inlineStr">
         <is>
@@ -9280,10 +9280,10 @@
         <v>1</v>
       </c>
       <c r="J113" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
@@ -9356,10 +9356,10 @@
         <v>1</v>
       </c>
       <c r="J114" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K114" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L114" s="12" t="inlineStr">
         <is>
@@ -9432,10 +9432,10 @@
         <v>1</v>
       </c>
       <c r="J115" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
@@ -9508,10 +9508,10 @@
         <v>1</v>
       </c>
       <c r="J116" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K116" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L116" s="12" t="inlineStr">
         <is>
@@ -9584,10 +9584,10 @@
         <v>1</v>
       </c>
       <c r="J117" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
@@ -9656,10 +9656,10 @@
         <v>1</v>
       </c>
       <c r="J118" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K118" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L118" s="12" t="inlineStr">
         <is>
@@ -9732,10 +9732,10 @@
         <v>1</v>
       </c>
       <c r="J119" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
@@ -9810,10 +9810,10 @@
         <v>1</v>
       </c>
       <c r="J120" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K120" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L120" s="12" t="inlineStr">
         <is>
@@ -9886,10 +9886,10 @@
         <v>1</v>
       </c>
       <c r="J121" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
@@ -9958,10 +9958,10 @@
         <v>1</v>
       </c>
       <c r="J122" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K122" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L122" s="12" t="inlineStr">
         <is>
@@ -10034,10 +10034,10 @@
         <v>1</v>
       </c>
       <c r="J123" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
@@ -10110,10 +10110,10 @@
         <v>1</v>
       </c>
       <c r="J124" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K124" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L124" s="12" t="inlineStr">
         <is>
@@ -10190,10 +10190,10 @@
         <v>1</v>
       </c>
       <c r="J125" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
@@ -10266,10 +10266,10 @@
         <v>1</v>
       </c>
       <c r="J126" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K126" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L126" s="12" t="inlineStr">
         <is>
@@ -10342,10 +10342,10 @@
         <v>1</v>
       </c>
       <c r="J127" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
@@ -10418,10 +10418,10 @@
         <v>1</v>
       </c>
       <c r="J128" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K128" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L128" s="12" t="inlineStr">
         <is>
@@ -10494,10 +10494,10 @@
         <v>4</v>
       </c>
       <c r="J129" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>1</v>
       </c>
       <c r="J130" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K130" s="12" t="n">
         <v>25</v>
@@ -10642,10 +10642,10 @@
         <v>1</v>
       </c>
       <c r="J131" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>1</v>
       </c>
       <c r="J132" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K132" s="12" t="n">
         <v>25</v>
@@ -10796,10 +10796,10 @@
         <v>1</v>
       </c>
       <c r="J133" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>1</v>
       </c>
       <c r="J134" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K134" s="12" t="n">
         <v>25</v>
@@ -10944,7 +10944,7 @@
         <v>1</v>
       </c>
       <c r="J135" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K135" s="12" t="n">
         <v>25</v>
@@ -11020,10 +11020,10 @@
         <v>1</v>
       </c>
       <c r="J136" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K136" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L136" s="12" t="inlineStr">
         <is>
@@ -11100,10 +11100,10 @@
         <v>1</v>
       </c>
       <c r="J137" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
@@ -11180,10 +11180,10 @@
         <v>1</v>
       </c>
       <c r="J138" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K138" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L138" s="12" t="inlineStr">
         <is>

--- a/Assets/Data/Tables/Skill.xlsx
+++ b/Assets/Data/Tables/Skill.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V138"/>
+  <dimension ref="A1:Y138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -529,8 +529,9 @@
     <col width="11" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="52" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -621,25 +622,40 @@
       </c>
       <c r="R1" s="5" t="inlineStr">
         <is>
+          <t>levelPrice</t>
+        </is>
+      </c>
+      <c r="S1" s="5" t="inlineStr">
+        <is>
+          <t>levelCurrency</t>
+        </is>
+      </c>
+      <c r="T1" s="5" t="inlineStr">
+        <is>
+          <t>priceGrowth</t>
+        </is>
+      </c>
+      <c r="U1" s="5" t="inlineStr">
+        <is>
           <t>link</t>
         </is>
       </c>
-      <c r="S1" s="5" t="inlineStr">
+      <c r="V1" s="5" t="inlineStr">
         <is>
           <t>requires</t>
         </is>
       </c>
-      <c r="T1" s="5" t="inlineStr">
+      <c r="W1" s="5" t="inlineStr">
         <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="U1" s="5" t="inlineStr">
+      <c r="X1" s="5" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="V1" s="6" t="inlineStr">
+      <c r="Y1" s="6" t="inlineStr">
         <is>
           <t>#memo</t>
         </is>
@@ -733,25 +749,40 @@
       </c>
       <c r="R2" s="7" t="inlineStr">
         <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="T2" s="7" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
+      <c r="V2" s="7" t="inlineStr">
         <is>
           <t>int[]</t>
         </is>
       </c>
-      <c r="T2" s="7" t="inlineStr">
+      <c r="W2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="U2" s="7" t="inlineStr">
+      <c r="X2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="V2" s="7" t="n"/>
+      <c r="Y2" s="7" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
@@ -831,35 +862,50 @@
       </c>
       <c r="P3" s="8" t="inlineStr">
         <is>
-          <t>해금 가격 (미정)</t>
+          <t>첫 레벨 가격</t>
         </is>
       </c>
       <c r="Q3" s="8" t="inlineStr">
         <is>
-          <t>해금 재화 (Gold / Mycelite)</t>
+          <t>첫 레벨 재화 (Gold / Mycelite)</t>
         </is>
       </c>
       <c r="R3" s="8" t="inlineStr">
         <is>
+          <t>2레벨부터의 첫 가격. 비우면 unlockPrice × priceGrowth^(레벨-1)을 같은 재화로</t>
+        </is>
+      </c>
+      <c r="S3" s="8" t="inlineStr">
+        <is>
+          <t>2레벨부터의 재화 (levelPrice가 있을 때만)</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>레벨마다 가격 배율 (비우면 1). 노드 안 마지막/첫 ≤ ×4</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
           <t>연결 노드 index. 트리에 선으로 그리고, 1레벨 이상 배우면 열린다</t>
         </is>
       </c>
-      <c r="S3" s="8" t="inlineStr">
+      <c r="V3" s="8" t="inlineStr">
         <is>
           <t>이전 레벨 노드 index (쉼표 구분). 최대 레벨까지 배워야 열린다</t>
         </is>
       </c>
-      <c r="T3" s="8" t="inlineStr">
+      <c r="W3" s="8" t="inlineStr">
         <is>
           <t>아이콘 경로 (Resources 기준)</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
+      <c r="X3" s="8" t="inlineStr">
         <is>
           <t>인게임 설명</t>
         </is>
       </c>
-      <c r="V3" s="8" t="inlineStr">
+      <c r="Y3" s="8" t="inlineStr">
         <is>
           <t>기획 메모 (게임에서 읽지 않음)</t>
         </is>
@@ -921,21 +967,34 @@
       <c r="O4" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="P4" s="9" t="n"/>
+      <c r="P4" s="9" t="n">
+        <v>45</v>
+      </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R4" s="9" t="n"/>
-      <c r="S4" s="9" t="n"/>
-      <c r="T4" s="9" t="n"/>
-      <c r="U4" s="9" t="inlineStr">
+      <c r="R4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="9" t="inlineStr">
+        <is>
+          <t>Mycelite</t>
+        </is>
+      </c>
+      <c r="T4" s="9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="U4" s="9" t="n"/>
+      <c r="V4" s="9" t="n"/>
+      <c r="W4" s="9" t="n"/>
+      <c r="X4" s="9" t="inlineStr">
         <is>
           <t>공격력 +2 (3초) 버프 / Lv</t>
         </is>
       </c>
-      <c r="V4" s="9" t="inlineStr">
+      <c r="Y4" s="9" t="inlineStr">
         <is>
           <t>첫 레벨업은 골드, 이후 균사석 — currency 한 칸이라 가격 구조 정해지면 열 추가 필요. param = 버프 지속(초)</t>
         </is>
@@ -995,23 +1054,36 @@
         <v>0.1</v>
       </c>
       <c r="O5" s="10" t="n"/>
-      <c r="P5" s="10" t="n"/>
+      <c r="P5" s="10" t="n">
+        <v>55</v>
+      </c>
       <c r="Q5" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
       <c r="R5" s="10" t="n">
+        <v>114</v>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="T5" s="10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="U5" s="10" t="n">
         <v>3001</v>
       </c>
-      <c r="S5" s="10" t="n"/>
-      <c r="T5" s="10" t="n"/>
-      <c r="U5" s="10" t="inlineStr">
+      <c r="V5" s="10" t="n"/>
+      <c r="W5" s="10" t="n"/>
+      <c r="X5" s="10" t="inlineStr">
         <is>
           <t>획득 점수 +10% / Lv</t>
         </is>
       </c>
-      <c r="V5" s="10" t="n"/>
+      <c r="Y5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="n">
@@ -1067,23 +1139,28 @@
         <v>0.1</v>
       </c>
       <c r="O6" s="10" t="n"/>
-      <c r="P6" s="10" t="n"/>
+      <c r="P6" s="10" t="n">
+        <v>280</v>
+      </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R6" s="10" t="n">
-        <v>3101</v>
-      </c>
+      <c r="R6" s="10" t="n"/>
       <c r="S6" s="10" t="n"/>
       <c r="T6" s="10" t="n"/>
-      <c r="U6" s="10" t="inlineStr">
+      <c r="U6" s="10" t="n">
+        <v>3101</v>
+      </c>
+      <c r="V6" s="10" t="n"/>
+      <c r="W6" s="10" t="n"/>
+      <c r="X6" s="10" t="inlineStr">
         <is>
           <t>점수 골드 전환율 +10%</t>
         </is>
       </c>
-      <c r="V6" s="10" t="n"/>
+      <c r="Y6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="n">
@@ -1139,23 +1216,28 @@
         <v>1</v>
       </c>
       <c r="O7" s="10" t="n"/>
-      <c r="P7" s="10" t="n"/>
+      <c r="P7" s="10" t="n">
+        <v>450</v>
+      </c>
       <c r="Q7" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R7" s="10" t="n">
-        <v>3101</v>
-      </c>
+      <c r="R7" s="10" t="n"/>
       <c r="S7" s="10" t="n"/>
       <c r="T7" s="10" t="n"/>
-      <c r="U7" s="10" t="inlineStr">
+      <c r="U7" s="10" t="n">
+        <v>3101</v>
+      </c>
+      <c r="V7" s="10" t="n"/>
+      <c r="W7" s="10" t="n"/>
+      <c r="X7" s="10" t="inlineStr">
         <is>
           <t>군락지 수 +1 (3 → 4)</t>
         </is>
       </c>
-      <c r="V7" s="10" t="n"/>
+      <c r="Y7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="n">
@@ -1211,23 +1293,28 @@
         <v>1</v>
       </c>
       <c r="O8" s="10" t="n"/>
-      <c r="P8" s="10" t="n"/>
+      <c r="P8" s="10" t="n">
+        <v>1400</v>
+      </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R8" s="10" t="n">
-        <v>3103</v>
-      </c>
+      <c r="R8" s="10" t="n"/>
       <c r="S8" s="10" t="n"/>
       <c r="T8" s="10" t="n"/>
-      <c r="U8" s="10" t="inlineStr">
+      <c r="U8" s="10" t="n">
+        <v>3103</v>
+      </c>
+      <c r="V8" s="10" t="n"/>
+      <c r="W8" s="10" t="n"/>
+      <c r="X8" s="10" t="inlineStr">
         <is>
           <t>군락지 주변 단일 버섯 +1 (3 → 4)</t>
         </is>
       </c>
-      <c r="V8" s="10" t="n"/>
+      <c r="Y8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="n">
@@ -1283,23 +1370,28 @@
         <v>0.05</v>
       </c>
       <c r="O9" s="10" t="n"/>
-      <c r="P9" s="10" t="n"/>
+      <c r="P9" s="10" t="n">
+        <v>1100</v>
+      </c>
       <c r="Q9" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R9" s="10" t="n">
-        <v>3102</v>
-      </c>
+      <c r="R9" s="10" t="n"/>
       <c r="S9" s="10" t="n"/>
       <c r="T9" s="10" t="n"/>
-      <c r="U9" s="10" t="inlineStr">
+      <c r="U9" s="10" t="n">
+        <v>3102</v>
+      </c>
+      <c r="V9" s="10" t="n"/>
+      <c r="W9" s="10" t="n"/>
+      <c r="X9" s="10" t="inlineStr">
         <is>
           <t>일반 버섯 수확량 +5%</t>
         </is>
       </c>
-      <c r="V9" s="10" t="n"/>
+      <c r="Y9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n">
@@ -1357,23 +1449,30 @@
         <v>0.05</v>
       </c>
       <c r="O10" s="10" t="n"/>
-      <c r="P10" s="10" t="n"/>
+      <c r="P10" s="10" t="n">
+        <v>2100</v>
+      </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R10" s="10" t="n">
+      <c r="R10" s="10" t="n"/>
+      <c r="S10" s="10" t="n"/>
+      <c r="T10" s="10" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="U10" s="10" t="n">
         <v>3103</v>
       </c>
-      <c r="S10" s="10" t="n"/>
-      <c r="T10" s="10" t="n"/>
-      <c r="U10" s="10" t="inlineStr">
+      <c r="V10" s="10" t="n"/>
+      <c r="W10" s="10" t="n"/>
+      <c r="X10" s="10" t="inlineStr">
         <is>
           <t>에픽 버섯 스폰율 +10% / +15% / +20%</t>
         </is>
       </c>
-      <c r="V10" s="10" t="inlineStr">
+      <c r="Y10" s="10" t="inlineStr">
         <is>
           <t>Lv.1 10, Lv.2 15, Lv.3 20 → base 5% + 5%/Lv</t>
         </is>
@@ -1433,27 +1532,32 @@
         <v>0.05</v>
       </c>
       <c r="O11" s="10" t="n"/>
-      <c r="P11" s="10" t="n"/>
+      <c r="P11" s="10" t="n">
+        <v>1800</v>
+      </c>
       <c r="Q11" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R11" s="10" t="n">
+      <c r="R11" s="10" t="n"/>
+      <c r="S11" s="10" t="n"/>
+      <c r="T11" s="10" t="n"/>
+      <c r="U11" s="10" t="n">
         <v>3102</v>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="V11" s="10" t="inlineStr">
         <is>
           <t>3105</t>
         </is>
       </c>
-      <c r="T11" s="10" t="n"/>
-      <c r="U11" s="10" t="inlineStr">
+      <c r="W11" s="10" t="n"/>
+      <c r="X11" s="10" t="inlineStr">
         <is>
           <t>일반 버섯 수확량 +10%</t>
         </is>
       </c>
-      <c r="V11" s="10" t="inlineStr">
+      <c r="Y11" s="10" t="inlineStr">
         <is>
           <t>원문 % = 누적값으로 보고 차이(+5%)만 더함</t>
         </is>
@@ -1513,27 +1617,32 @@
         <v>0.05</v>
       </c>
       <c r="O12" s="10" t="n"/>
-      <c r="P12" s="10" t="n"/>
+      <c r="P12" s="10" t="n">
+        <v>9800</v>
+      </c>
       <c r="Q12" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R12" s="10" t="n">
+      <c r="R12" s="10" t="n"/>
+      <c r="S12" s="10" t="n"/>
+      <c r="T12" s="10" t="n"/>
+      <c r="U12" s="10" t="n">
         <v>3105</v>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="V12" s="10" t="inlineStr">
         <is>
           <t>3102</t>
         </is>
       </c>
-      <c r="T12" s="10" t="n"/>
-      <c r="U12" s="10" t="inlineStr">
+      <c r="W12" s="10" t="n"/>
+      <c r="X12" s="10" t="inlineStr">
         <is>
           <t>점수 골드 전환율 +15%</t>
         </is>
       </c>
-      <c r="V12" s="10" t="inlineStr">
+      <c r="Y12" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -1593,23 +1702,28 @@
         <v>-1</v>
       </c>
       <c r="O13" s="10" t="n"/>
-      <c r="P13" s="10" t="n"/>
+      <c r="P13" s="10" t="n">
+        <v>9800</v>
+      </c>
       <c r="Q13" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R13" s="10" t="n">
-        <v>3104</v>
-      </c>
+      <c r="R13" s="10" t="n"/>
       <c r="S13" s="10" t="n"/>
       <c r="T13" s="10" t="n"/>
-      <c r="U13" s="10" t="inlineStr">
+      <c r="U13" s="10" t="n">
+        <v>3104</v>
+      </c>
+      <c r="V13" s="10" t="n"/>
+      <c r="W13" s="10" t="n"/>
+      <c r="X13" s="10" t="inlineStr">
         <is>
           <t>군락지 리스폰 −1초 (7 → 6)</t>
         </is>
       </c>
-      <c r="V13" s="10" t="n"/>
+      <c r="Y13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n">
@@ -1665,27 +1779,32 @@
         <v>0.05</v>
       </c>
       <c r="O14" s="10" t="n"/>
-      <c r="P14" s="10" t="n"/>
+      <c r="P14" s="10" t="n">
+        <v>21000</v>
+      </c>
       <c r="Q14" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R14" s="10" t="n">
+      <c r="R14" s="10" t="n"/>
+      <c r="S14" s="10" t="n"/>
+      <c r="T14" s="10" t="n"/>
+      <c r="U14" s="10" t="n">
         <v>3107</v>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="V14" s="10" t="inlineStr">
         <is>
           <t>3108</t>
         </is>
       </c>
-      <c r="T14" s="10" t="n"/>
-      <c r="U14" s="10" t="inlineStr">
+      <c r="W14" s="10" t="n"/>
+      <c r="X14" s="10" t="inlineStr">
         <is>
           <t>점수 골드 전환율 +20%</t>
         </is>
       </c>
-      <c r="V14" s="10" t="inlineStr">
+      <c r="Y14" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -1745,27 +1864,32 @@
         <v>-1</v>
       </c>
       <c r="O15" s="10" t="n"/>
-      <c r="P15" s="10" t="n"/>
+      <c r="P15" s="10" t="n">
+        <v>36000</v>
+      </c>
       <c r="Q15" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R15" s="10" t="n">
+      <c r="R15" s="10" t="n"/>
+      <c r="S15" s="10" t="n"/>
+      <c r="T15" s="10" t="n"/>
+      <c r="U15" s="10" t="n">
         <v>3106</v>
       </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="V15" s="10" t="inlineStr">
         <is>
           <t>3109</t>
         </is>
       </c>
-      <c r="T15" s="10" t="n"/>
-      <c r="U15" s="10" t="inlineStr">
+      <c r="W15" s="10" t="n"/>
+      <c r="X15" s="10" t="inlineStr">
         <is>
           <t>군락지 리스폰 −1초 (6 → 5)</t>
         </is>
       </c>
-      <c r="V15" s="10" t="n"/>
+      <c r="Y15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
@@ -1821,23 +1945,28 @@
         <v>0.03</v>
       </c>
       <c r="O16" s="10" t="n"/>
-      <c r="P16" s="10" t="n"/>
+      <c r="P16" s="10" t="n">
+        <v>17000</v>
+      </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R16" s="10" t="n">
-        <v>3108</v>
-      </c>
+      <c r="R16" s="10" t="n"/>
       <c r="S16" s="10" t="n"/>
       <c r="T16" s="10" t="n"/>
-      <c r="U16" s="10" t="inlineStr">
+      <c r="U16" s="10" t="n">
+        <v>3108</v>
+      </c>
+      <c r="V16" s="10" t="n"/>
+      <c r="W16" s="10" t="n"/>
+      <c r="X16" s="10" t="inlineStr">
         <is>
           <t>점수 3배 확률 +3%</t>
         </is>
       </c>
-      <c r="V16" s="10" t="n"/>
+      <c r="Y16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n">
@@ -1893,27 +2022,32 @@
         <v>1</v>
       </c>
       <c r="O17" s="10" t="n"/>
-      <c r="P17" s="10" t="n"/>
+      <c r="P17" s="10" t="n">
+        <v>36000</v>
+      </c>
       <c r="Q17" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R17" s="10" t="n">
+      <c r="R17" s="10" t="n"/>
+      <c r="S17" s="10" t="n"/>
+      <c r="T17" s="10" t="n"/>
+      <c r="U17" s="10" t="n">
         <v>3109</v>
       </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="V17" s="10" t="inlineStr">
         <is>
           <t>3103</t>
         </is>
       </c>
-      <c r="T17" s="10" t="n"/>
-      <c r="U17" s="10" t="inlineStr">
+      <c r="W17" s="10" t="n"/>
+      <c r="X17" s="10" t="inlineStr">
         <is>
           <t>군락지 수 +1 (4 → 5)</t>
         </is>
       </c>
-      <c r="V17" s="10" t="n"/>
+      <c r="Y17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
@@ -1969,23 +2103,28 @@
         <v>0.05</v>
       </c>
       <c r="O18" s="10" t="n"/>
-      <c r="P18" s="10" t="n"/>
+      <c r="P18" s="10" t="n">
+        <v>100000</v>
+      </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R18" s="10" t="n">
-        <v>3110</v>
-      </c>
+      <c r="R18" s="10" t="n"/>
       <c r="S18" s="10" t="n"/>
       <c r="T18" s="10" t="n"/>
-      <c r="U18" s="10" t="inlineStr">
+      <c r="U18" s="10" t="n">
+        <v>3110</v>
+      </c>
+      <c r="V18" s="10" t="n"/>
+      <c r="W18" s="10" t="n"/>
+      <c r="X18" s="10" t="inlineStr">
         <is>
           <t>에픽 버섯 수확량 +5%</t>
         </is>
       </c>
-      <c r="V18" s="10" t="n"/>
+      <c r="Y18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n">
@@ -2041,27 +2180,32 @@
         <v>1</v>
       </c>
       <c r="O19" s="10" t="n"/>
-      <c r="P19" s="10" t="n"/>
+      <c r="P19" s="10" t="n">
+        <v>150000</v>
+      </c>
       <c r="Q19" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R19" s="10" t="n">
+      <c r="R19" s="10" t="n"/>
+      <c r="S19" s="10" t="n"/>
+      <c r="T19" s="10" t="n"/>
+      <c r="U19" s="10" t="n">
         <v>3109</v>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="V19" s="10" t="inlineStr">
         <is>
           <t>3104</t>
         </is>
       </c>
-      <c r="T19" s="10" t="n"/>
-      <c r="U19" s="10" t="inlineStr">
+      <c r="W19" s="10" t="n"/>
+      <c r="X19" s="10" t="inlineStr">
         <is>
           <t>군락지 주변 단일 버섯 +1 (4 → 5)</t>
         </is>
       </c>
-      <c r="V19" s="10" t="n"/>
+      <c r="Y19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
@@ -2117,27 +2261,32 @@
         <v>0.05</v>
       </c>
       <c r="O20" s="10" t="n"/>
-      <c r="P20" s="10" t="n"/>
+      <c r="P20" s="10" t="n">
+        <v>100000</v>
+      </c>
       <c r="Q20" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R20" s="10" t="n">
+      <c r="R20" s="10" t="n"/>
+      <c r="S20" s="10" t="n"/>
+      <c r="T20" s="10" t="n"/>
+      <c r="U20" s="10" t="n">
         <v>3108</v>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="V20" s="10" t="inlineStr">
         <is>
           <t>3107</t>
         </is>
       </c>
-      <c r="T20" s="10" t="n"/>
-      <c r="U20" s="10" t="inlineStr">
+      <c r="W20" s="10" t="n"/>
+      <c r="X20" s="10" t="inlineStr">
         <is>
           <t>일반 버섯 수확량 +15%</t>
         </is>
       </c>
-      <c r="V20" s="10" t="inlineStr">
+      <c r="Y20" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -2197,27 +2346,32 @@
         <v>1</v>
       </c>
       <c r="O21" s="10" t="n"/>
-      <c r="P21" s="10" t="n"/>
+      <c r="P21" s="10" t="n">
+        <v>150000</v>
+      </c>
       <c r="Q21" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R21" s="10" t="n">
+      <c r="R21" s="10" t="n"/>
+      <c r="S21" s="10" t="n"/>
+      <c r="T21" s="10" t="n"/>
+      <c r="U21" s="10" t="n">
         <v>3111</v>
       </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="V21" s="10" t="inlineStr">
         <is>
           <t>3113</t>
         </is>
       </c>
-      <c r="T21" s="10" t="n"/>
-      <c r="U21" s="10" t="inlineStr">
+      <c r="W21" s="10" t="n"/>
+      <c r="X21" s="10" t="inlineStr">
         <is>
           <t>군락지 수 +1 (5 → 6)</t>
         </is>
       </c>
-      <c r="V21" s="10" t="n"/>
+      <c r="Y21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
@@ -2273,27 +2427,32 @@
         <v>0.02</v>
       </c>
       <c r="O22" s="10" t="n"/>
-      <c r="P22" s="10" t="n"/>
+      <c r="P22" s="10" t="n">
+        <v>380000</v>
+      </c>
       <c r="Q22" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R22" s="10" t="n">
+      <c r="R22" s="10" t="n"/>
+      <c r="S22" s="10" t="n"/>
+      <c r="T22" s="10" t="n"/>
+      <c r="U22" s="10" t="n">
         <v>3110</v>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="V22" s="10" t="inlineStr">
         <is>
           <t>3112</t>
         </is>
       </c>
-      <c r="T22" s="10" t="n"/>
-      <c r="U22" s="10" t="inlineStr">
+      <c r="W22" s="10" t="n"/>
+      <c r="X22" s="10" t="inlineStr">
         <is>
           <t>점수 3배 확률 +5%</t>
         </is>
       </c>
-      <c r="V22" s="10" t="inlineStr">
+      <c r="Y22" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -2353,27 +2512,32 @@
         <v>1</v>
       </c>
       <c r="O23" s="10" t="n"/>
-      <c r="P23" s="10" t="n"/>
+      <c r="P23" s="10" t="n">
+        <v>390000</v>
+      </c>
       <c r="Q23" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R23" s="10" t="n">
+      <c r="R23" s="10" t="n"/>
+      <c r="S23" s="10" t="n"/>
+      <c r="T23" s="10" t="n"/>
+      <c r="U23" s="10" t="n">
         <v>3111</v>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="V23" s="10" t="inlineStr">
         <is>
           <t>3115</t>
         </is>
       </c>
-      <c r="T23" s="10" t="n"/>
-      <c r="U23" s="10" t="inlineStr">
+      <c r="W23" s="10" t="n"/>
+      <c r="X23" s="10" t="inlineStr">
         <is>
           <t>군락지 주변 단일 버섯 +1 (5 → 6)</t>
         </is>
       </c>
-      <c r="V23" s="10" t="n"/>
+      <c r="Y23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
@@ -2429,27 +2593,32 @@
         <v>0.1</v>
       </c>
       <c r="O24" s="10" t="n"/>
-      <c r="P24" s="10" t="n"/>
+      <c r="P24" s="10" t="n">
+        <v>1100000</v>
+      </c>
       <c r="Q24" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R24" s="10" t="n">
+      <c r="R24" s="10" t="n"/>
+      <c r="S24" s="10" t="n"/>
+      <c r="T24" s="10" t="n"/>
+      <c r="U24" s="10" t="n">
         <v>3114</v>
       </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="V24" s="10" t="inlineStr">
         <is>
           <t>3101</t>
         </is>
       </c>
-      <c r="T24" s="10" t="n"/>
-      <c r="U24" s="10" t="inlineStr">
+      <c r="W24" s="10" t="n"/>
+      <c r="X24" s="10" t="inlineStr">
         <is>
           <t>획득 점수 +40%</t>
         </is>
       </c>
-      <c r="V24" s="10" t="inlineStr">
+      <c r="Y24" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%</t>
         </is>
@@ -2509,27 +2678,32 @@
         <v>0.05</v>
       </c>
       <c r="O25" s="10" t="n"/>
-      <c r="P25" s="10" t="n"/>
+      <c r="P25" s="10" t="n">
+        <v>1100000</v>
+      </c>
       <c r="Q25" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R25" s="10" t="n">
+      <c r="R25" s="10" t="n"/>
+      <c r="S25" s="10" t="n"/>
+      <c r="T25" s="10" t="n"/>
+      <c r="U25" s="10" t="n">
         <v>3113</v>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="V25" s="10" t="inlineStr">
         <is>
           <t>3106</t>
         </is>
       </c>
-      <c r="T25" s="10" t="n"/>
-      <c r="U25" s="10" t="inlineStr">
+      <c r="W25" s="10" t="n"/>
+      <c r="X25" s="10" t="inlineStr">
         <is>
           <t>에픽 버섯 스폰율 +25%</t>
         </is>
       </c>
-      <c r="V25" s="10" t="inlineStr">
+      <c r="Y25" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -2589,23 +2763,28 @@
         <v>0.1</v>
       </c>
       <c r="O26" s="10" t="n"/>
-      <c r="P26" s="10" t="n"/>
+      <c r="P26" s="10" t="n">
+        <v>1100000</v>
+      </c>
       <c r="Q26" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R26" s="10" t="n">
-        <v>3112</v>
-      </c>
+      <c r="R26" s="10" t="n"/>
       <c r="S26" s="10" t="n"/>
       <c r="T26" s="10" t="n"/>
-      <c r="U26" s="10" t="inlineStr">
+      <c r="U26" s="10" t="n">
+        <v>3112</v>
+      </c>
+      <c r="V26" s="10" t="n"/>
+      <c r="W26" s="10" t="n"/>
+      <c r="X26" s="10" t="inlineStr">
         <is>
           <t>점수 골드 전환율 +30%</t>
         </is>
       </c>
-      <c r="V26" s="10" t="inlineStr">
+      <c r="Y26" s="10" t="inlineStr">
         <is>
           <t>흥정 기술의 상위. 누적값 기준 차이 +10%</t>
         </is>
@@ -2665,23 +2844,28 @@
         <v>2</v>
       </c>
       <c r="O27" s="10" t="n"/>
-      <c r="P27" s="10" t="n"/>
+      <c r="P27" s="10" t="n">
+        <v>1500000</v>
+      </c>
       <c r="Q27" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R27" s="10" t="n">
-        <v>3117</v>
-      </c>
+      <c r="R27" s="10" t="n"/>
       <c r="S27" s="10" t="n"/>
       <c r="T27" s="10" t="n"/>
-      <c r="U27" s="10" t="inlineStr">
+      <c r="U27" s="10" t="n">
+        <v>3117</v>
+      </c>
+      <c r="V27" s="10" t="n"/>
+      <c r="W27" s="10" t="n"/>
+      <c r="X27" s="10" t="inlineStr">
         <is>
           <t>군락지 수 +2 (6 → 8)</t>
         </is>
       </c>
-      <c r="V27" s="10" t="inlineStr">
+      <c r="Y27" s="10" t="inlineStr">
         <is>
           <t>넓은 시야의 상위</t>
         </is>
@@ -2741,27 +2925,32 @@
         <v>0.05</v>
       </c>
       <c r="O28" s="10" t="n"/>
-      <c r="P28" s="10" t="n"/>
+      <c r="P28" s="10" t="n">
+        <v>2500000</v>
+      </c>
       <c r="Q28" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R28" s="10" t="n">
+      <c r="R28" s="10" t="n"/>
+      <c r="S28" s="10" t="n"/>
+      <c r="T28" s="10" t="n"/>
+      <c r="U28" s="10" t="n">
         <v>3116</v>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="V28" s="10" t="inlineStr">
         <is>
           <t>3114</t>
         </is>
       </c>
-      <c r="T28" s="10" t="n"/>
-      <c r="U28" s="10" t="inlineStr">
+      <c r="W28" s="10" t="n"/>
+      <c r="X28" s="10" t="inlineStr">
         <is>
           <t>에픽 버섯 수확량 +10%</t>
         </is>
       </c>
-      <c r="V28" s="10" t="inlineStr">
+      <c r="Y28" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -2821,27 +3010,32 @@
         <v>0.02</v>
       </c>
       <c r="O29" s="10" t="n"/>
-      <c r="P29" s="10" t="n"/>
+      <c r="P29" s="10" t="n">
+        <v>2300000</v>
+      </c>
       <c r="Q29" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R29" s="10" t="n">
+      <c r="R29" s="10" t="n"/>
+      <c r="S29" s="10" t="n"/>
+      <c r="T29" s="10" t="n"/>
+      <c r="U29" s="10" t="n">
         <v>3122</v>
       </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="V29" s="10" t="inlineStr">
         <is>
           <t>3118</t>
         </is>
       </c>
-      <c r="T29" s="10" t="n"/>
-      <c r="U29" s="10" t="inlineStr">
+      <c r="W29" s="10" t="n"/>
+      <c r="X29" s="10" t="inlineStr">
         <is>
           <t>점수 3배 확률 +7%</t>
         </is>
       </c>
-      <c r="V29" s="10" t="inlineStr">
+      <c r="Y29" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -2901,27 +3095,32 @@
         <v>2</v>
       </c>
       <c r="O30" s="10" t="n"/>
-      <c r="P30" s="10" t="n"/>
+      <c r="P30" s="10" t="n">
+        <v>3300000</v>
+      </c>
       <c r="Q30" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R30" s="10" t="n">
+      <c r="R30" s="10" t="n"/>
+      <c r="S30" s="10" t="n"/>
+      <c r="T30" s="10" t="n"/>
+      <c r="U30" s="10" t="n">
         <v>3115</v>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="V30" s="10" t="inlineStr">
         <is>
           <t>3123</t>
         </is>
       </c>
-      <c r="T30" s="10" t="n"/>
-      <c r="U30" s="10" t="inlineStr">
+      <c r="W30" s="10" t="n"/>
+      <c r="X30" s="10" t="inlineStr">
         <is>
           <t>군락지 수 +2 (8 → 10)</t>
         </is>
       </c>
-      <c r="V30" s="10" t="inlineStr">
+      <c r="Y30" s="10" t="inlineStr">
         <is>
           <t>넓은 시야의 상위</t>
         </is>
@@ -2981,23 +3180,28 @@
         <v>0.05</v>
       </c>
       <c r="O31" s="10" t="n"/>
-      <c r="P31" s="10" t="n"/>
+      <c r="P31" s="10" t="n">
+        <v>2500000</v>
+      </c>
       <c r="Q31" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R31" s="10" t="n">
-        <v>3121</v>
-      </c>
+      <c r="R31" s="10" t="n"/>
       <c r="S31" s="10" t="n"/>
       <c r="T31" s="10" t="n"/>
-      <c r="U31" s="10" t="inlineStr">
+      <c r="U31" s="10" t="n">
+        <v>3121</v>
+      </c>
+      <c r="V31" s="10" t="n"/>
+      <c r="W31" s="10" t="n"/>
+      <c r="X31" s="10" t="inlineStr">
         <is>
           <t>유니크 버섯 스폰율 +5%</t>
         </is>
       </c>
-      <c r="V31" s="10" t="n"/>
+      <c r="Y31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
@@ -3053,27 +3257,32 @@
         <v>0.05</v>
       </c>
       <c r="O32" s="10" t="n"/>
-      <c r="P32" s="10" t="n"/>
+      <c r="P32" s="10" t="n">
+        <v>9700000</v>
+      </c>
       <c r="Q32" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R32" s="10" t="n">
+      <c r="R32" s="10" t="n"/>
+      <c r="S32" s="10" t="n"/>
+      <c r="T32" s="10" t="n"/>
+      <c r="U32" s="10" t="n">
         <v>3122</v>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="V32" s="10" t="inlineStr">
         <is>
           <t>3124</t>
         </is>
       </c>
-      <c r="T32" s="10" t="n"/>
-      <c r="U32" s="10" t="inlineStr">
+      <c r="W32" s="10" t="n"/>
+      <c r="X32" s="10" t="inlineStr">
         <is>
           <t>에픽 버섯 수확량 +15%</t>
         </is>
       </c>
-      <c r="V32" s="10" t="inlineStr">
+      <c r="Y32" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -3133,23 +3342,28 @@
         <v>0.05</v>
       </c>
       <c r="O33" s="10" t="n"/>
-      <c r="P33" s="10" t="n"/>
+      <c r="P33" s="10" t="n">
+        <v>9700000</v>
+      </c>
       <c r="Q33" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R33" s="10" t="n">
-        <v>3118</v>
-      </c>
+      <c r="R33" s="10" t="n"/>
       <c r="S33" s="10" t="n"/>
       <c r="T33" s="10" t="n"/>
-      <c r="U33" s="10" t="inlineStr">
+      <c r="U33" s="10" t="n">
+        <v>3118</v>
+      </c>
+      <c r="V33" s="10" t="n"/>
+      <c r="W33" s="10" t="n"/>
+      <c r="X33" s="10" t="inlineStr">
         <is>
           <t>유니크 버섯 수확량 +5%</t>
         </is>
       </c>
-      <c r="V33" s="10" t="n"/>
+      <c r="Y33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
@@ -3205,27 +3419,32 @@
         <v>-2</v>
       </c>
       <c r="O34" s="10" t="n"/>
-      <c r="P34" s="10" t="n"/>
+      <c r="P34" s="10" t="n">
+        <v>11000000</v>
+      </c>
       <c r="Q34" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R34" s="10" t="n">
+      <c r="R34" s="10" t="n"/>
+      <c r="S34" s="10" t="n"/>
+      <c r="T34" s="10" t="n"/>
+      <c r="U34" s="10" t="n">
         <v>3119</v>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="V34" s="10" t="inlineStr">
         <is>
           <t>3111</t>
         </is>
       </c>
-      <c r="T34" s="10" t="n"/>
-      <c r="U34" s="10" t="inlineStr">
+      <c r="W34" s="10" t="n"/>
+      <c r="X34" s="10" t="inlineStr">
         <is>
           <t>군락지 리스폰 −2초 (5 → 3)</t>
         </is>
       </c>
-      <c r="V34" s="10" t="n"/>
+      <c r="Y34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="n">
@@ -3281,23 +3500,28 @@
         <v>0.01</v>
       </c>
       <c r="O35" s="10" t="n"/>
-      <c r="P35" s="10" t="n"/>
+      <c r="P35" s="10" t="n">
+        <v>11000000</v>
+      </c>
       <c r="Q35" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R35" s="10" t="n">
-        <v>3121</v>
-      </c>
+      <c r="R35" s="10" t="n"/>
       <c r="S35" s="10" t="n"/>
       <c r="T35" s="10" t="n"/>
-      <c r="U35" s="10" t="inlineStr">
+      <c r="U35" s="10" t="n">
+        <v>3121</v>
+      </c>
+      <c r="V35" s="10" t="n"/>
+      <c r="W35" s="10" t="n"/>
+      <c r="X35" s="10" t="inlineStr">
         <is>
           <t>황금 변종 스폰율 +1%</t>
         </is>
       </c>
-      <c r="V35" s="10" t="n"/>
+      <c r="Y35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
@@ -3353,27 +3577,32 @@
         <v>0.05</v>
       </c>
       <c r="O36" s="10" t="n"/>
-      <c r="P36" s="10" t="n"/>
+      <c r="P36" s="10" t="n">
+        <v>16000000</v>
+      </c>
       <c r="Q36" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R36" s="10" t="n">
+      <c r="R36" s="10" t="n"/>
+      <c r="S36" s="10" t="n"/>
+      <c r="T36" s="10" t="n"/>
+      <c r="U36" s="10" t="n">
         <v>3124</v>
       </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="V36" s="10" t="inlineStr">
         <is>
           <t>3129</t>
         </is>
       </c>
-      <c r="T36" s="10" t="n"/>
-      <c r="U36" s="10" t="inlineStr">
+      <c r="W36" s="10" t="n"/>
+      <c r="X36" s="10" t="inlineStr">
         <is>
           <t>유니크 버섯 수확량 +10%</t>
         </is>
       </c>
-      <c r="V36" s="10" t="inlineStr">
+      <c r="Y36" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -3433,23 +3662,28 @@
         <v>0.03</v>
       </c>
       <c r="O37" s="10" t="n"/>
-      <c r="P37" s="10" t="n"/>
+      <c r="P37" s="10" t="n">
+        <v>17000000</v>
+      </c>
       <c r="Q37" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R37" s="10" t="n">
-        <v>3129</v>
-      </c>
+      <c r="R37" s="10" t="n"/>
       <c r="S37" s="10" t="n"/>
       <c r="T37" s="10" t="n"/>
-      <c r="U37" s="10" t="inlineStr">
+      <c r="U37" s="10" t="n">
+        <v>3129</v>
+      </c>
+      <c r="V37" s="10" t="n"/>
+      <c r="W37" s="10" t="n"/>
+      <c r="X37" s="10" t="inlineStr">
         <is>
           <t>보스 전용 레전더리 버섯 수확량 +3%</t>
         </is>
       </c>
-      <c r="V37" s="10" t="n"/>
+      <c r="Y37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
@@ -3505,27 +3739,32 @@
         <v>0.05</v>
       </c>
       <c r="O38" s="10" t="n"/>
-      <c r="P38" s="10" t="n"/>
+      <c r="P38" s="10" t="n">
+        <v>17000000</v>
+      </c>
       <c r="Q38" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R38" s="10" t="n">
+      <c r="R38" s="10" t="n"/>
+      <c r="S38" s="10" t="n"/>
+      <c r="T38" s="10" t="n"/>
+      <c r="U38" s="10" t="n">
         <v>3126</v>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="V38" s="10" t="inlineStr">
         <is>
           <t>3127</t>
         </is>
       </c>
-      <c r="T38" s="10" t="n"/>
-      <c r="U38" s="10" t="inlineStr">
+      <c r="W38" s="10" t="n"/>
+      <c r="X38" s="10" t="inlineStr">
         <is>
           <t>유니크 버섯 스폰율 +10%</t>
         </is>
       </c>
-      <c r="V38" s="10" t="inlineStr">
+      <c r="Y38" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -3585,27 +3824,32 @@
         <v>0.05</v>
       </c>
       <c r="O39" s="10" t="n"/>
-      <c r="P39" s="10" t="n"/>
+      <c r="P39" s="10" t="n">
+        <v>19000000</v>
+      </c>
       <c r="Q39" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R39" s="10" t="n">
+      <c r="R39" s="10" t="n"/>
+      <c r="S39" s="10" t="n"/>
+      <c r="T39" s="10" t="n"/>
+      <c r="U39" s="10" t="n">
         <v>3130</v>
       </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="V39" s="10" t="inlineStr">
         <is>
           <t>3134</t>
         </is>
       </c>
-      <c r="T39" s="10" t="n"/>
-      <c r="U39" s="10" t="inlineStr">
+      <c r="W39" s="10" t="n"/>
+      <c r="X39" s="10" t="inlineStr">
         <is>
           <t>유니크 버섯 스폰율 +15%</t>
         </is>
       </c>
-      <c r="V39" s="10" t="inlineStr">
+      <c r="Y39" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%. 원문은 Lv.2와 같은 레어도 15</t>
         </is>
@@ -3665,27 +3909,32 @@
         <v>0.02</v>
       </c>
       <c r="O40" s="10" t="n"/>
-      <c r="P40" s="10" t="n"/>
+      <c r="P40" s="10" t="n">
+        <v>25000000</v>
+      </c>
       <c r="Q40" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R40" s="10" t="n">
+      <c r="R40" s="10" t="n"/>
+      <c r="S40" s="10" t="n"/>
+      <c r="T40" s="10" t="n"/>
+      <c r="U40" s="10" t="n">
         <v>3130</v>
       </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="V40" s="10" t="inlineStr">
         <is>
           <t>3131</t>
         </is>
       </c>
-      <c r="T40" s="10" t="n"/>
-      <c r="U40" s="10" t="inlineStr">
+      <c r="W40" s="10" t="n"/>
+      <c r="X40" s="10" t="inlineStr">
         <is>
           <t>황금 변종 스폰율 +3%</t>
         </is>
       </c>
-      <c r="V40" s="10" t="inlineStr">
+      <c r="Y40" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -3745,27 +3994,32 @@
         <v>0.03</v>
       </c>
       <c r="O41" s="10" t="n"/>
-      <c r="P41" s="10" t="n"/>
+      <c r="P41" s="10" t="n">
+        <v>23000000</v>
+      </c>
       <c r="Q41" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R41" s="10" t="n">
+      <c r="R41" s="10" t="n"/>
+      <c r="S41" s="10" t="n"/>
+      <c r="T41" s="10" t="n"/>
+      <c r="U41" s="10" t="n">
         <v>3129</v>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="V41" s="10" t="inlineStr">
         <is>
           <t>3133</t>
         </is>
       </c>
-      <c r="T41" s="10" t="n"/>
-      <c r="U41" s="10" t="inlineStr">
+      <c r="W41" s="10" t="n"/>
+      <c r="X41" s="10" t="inlineStr">
         <is>
           <t>보스 전용 레전더리 버섯 수확량 +6%</t>
         </is>
       </c>
-      <c r="V41" s="10" t="inlineStr">
+      <c r="Y41" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +3%</t>
         </is>
@@ -3825,27 +4079,32 @@
         <v>0.1</v>
       </c>
       <c r="O42" s="10" t="n"/>
-      <c r="P42" s="10" t="n"/>
+      <c r="P42" s="10" t="n">
+        <v>23000000</v>
+      </c>
       <c r="Q42" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R42" s="10" t="n">
+      <c r="R42" s="10" t="n"/>
+      <c r="S42" s="10" t="n"/>
+      <c r="T42" s="10" t="n"/>
+      <c r="U42" s="10" t="n">
         <v>3125</v>
       </c>
-      <c r="S42" s="10" t="inlineStr">
+      <c r="V42" s="10" t="inlineStr">
         <is>
           <t>3122</t>
         </is>
       </c>
-      <c r="T42" s="10" t="n"/>
-      <c r="U42" s="10" t="inlineStr">
+      <c r="W42" s="10" t="n"/>
+      <c r="X42" s="10" t="inlineStr">
         <is>
           <t>점수 골드 전환율 +40%</t>
         </is>
       </c>
-      <c r="V42" s="10" t="inlineStr">
+      <c r="Y42" s="10" t="inlineStr">
         <is>
           <t>흥정 기술의 상위. 누적값 기준 차이 +10%</t>
         </is>
@@ -3905,27 +4164,32 @@
         <v>2</v>
       </c>
       <c r="O43" s="10" t="n"/>
-      <c r="P43" s="10" t="n"/>
+      <c r="P43" s="10" t="n">
+        <v>25000000</v>
+      </c>
       <c r="Q43" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R43" s="10" t="n">
+      <c r="R43" s="10" t="n"/>
+      <c r="S43" s="10" t="n"/>
+      <c r="T43" s="10" t="n"/>
+      <c r="U43" s="10" t="n">
         <v>3127</v>
       </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="V43" s="10" t="inlineStr">
         <is>
           <t>3126</t>
         </is>
       </c>
-      <c r="T43" s="10" t="n"/>
-      <c r="U43" s="10" t="inlineStr">
+      <c r="W43" s="10" t="n"/>
+      <c r="X43" s="10" t="inlineStr">
         <is>
           <t>군락지 수 +2 (10 → 12)</t>
         </is>
       </c>
-      <c r="V43" s="10" t="inlineStr">
+      <c r="Y43" s="10" t="inlineStr">
         <is>
           <t>넓은 시야의 상위</t>
         </is>
@@ -3985,27 +4249,32 @@
         <v>0.05</v>
       </c>
       <c r="O44" s="10" t="n"/>
-      <c r="P44" s="10" t="n"/>
+      <c r="P44" s="10" t="n">
+        <v>37000000</v>
+      </c>
       <c r="Q44" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R44" s="10" t="n">
+      <c r="R44" s="10" t="n"/>
+      <c r="S44" s="10" t="n"/>
+      <c r="T44" s="10" t="n"/>
+      <c r="U44" s="10" t="n">
         <v>3133</v>
       </c>
-      <c r="S44" s="10" t="inlineStr">
+      <c r="V44" s="10" t="inlineStr">
         <is>
           <t>3132</t>
         </is>
       </c>
-      <c r="T44" s="10" t="n"/>
-      <c r="U44" s="10" t="inlineStr">
+      <c r="W44" s="10" t="n"/>
+      <c r="X44" s="10" t="inlineStr">
         <is>
           <t>유니크 버섯 수확량 +15%</t>
         </is>
       </c>
-      <c r="V44" s="10" t="inlineStr">
+      <c r="Y44" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -4065,27 +4334,32 @@
         <v>0.1</v>
       </c>
       <c r="O45" s="10" t="n"/>
-      <c r="P45" s="10" t="n"/>
+      <c r="P45" s="10" t="n">
+        <v>35000000</v>
+      </c>
       <c r="Q45" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R45" s="10" t="n">
+      <c r="R45" s="10" t="n"/>
+      <c r="S45" s="10" t="n"/>
+      <c r="T45" s="10" t="n"/>
+      <c r="U45" s="10" t="n">
         <v>3128</v>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="V45" s="10" t="inlineStr">
         <is>
           <t>3120</t>
         </is>
       </c>
-      <c r="T45" s="10" t="n"/>
-      <c r="U45" s="10" t="inlineStr">
+      <c r="W45" s="10" t="n"/>
+      <c r="X45" s="10" t="inlineStr">
         <is>
           <t>획득 점수 +50%</t>
         </is>
       </c>
-      <c r="V45" s="10" t="inlineStr">
+      <c r="Y45" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%</t>
         </is>
@@ -4145,27 +4419,32 @@
         <v>0.02</v>
       </c>
       <c r="O46" s="10" t="n"/>
-      <c r="P46" s="10" t="n"/>
+      <c r="P46" s="10" t="n">
+        <v>37000000</v>
+      </c>
       <c r="Q46" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R46" s="10" t="n">
+      <c r="R46" s="10" t="n"/>
+      <c r="S46" s="10" t="n"/>
+      <c r="T46" s="10" t="n"/>
+      <c r="U46" s="10" t="n">
         <v>3135</v>
       </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="V46" s="10" t="inlineStr">
         <is>
           <t>3136</t>
         </is>
       </c>
-      <c r="T46" s="10" t="n"/>
-      <c r="U46" s="10" t="inlineStr">
+      <c r="W46" s="10" t="n"/>
+      <c r="X46" s="10" t="inlineStr">
         <is>
           <t>황금 변종 스폰율 +5%</t>
         </is>
       </c>
-      <c r="V46" s="10" t="inlineStr">
+      <c r="Y46" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -4227,23 +4506,30 @@
       <c r="O47" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="P47" s="10" t="n"/>
+      <c r="P47" s="10" t="n">
+        <v>3</v>
+      </c>
       <c r="Q47" s="10" t="inlineStr">
         <is>
           <t>Mycelite</t>
         </is>
       </c>
-      <c r="R47" s="10" t="n">
+      <c r="R47" s="10" t="n"/>
+      <c r="S47" s="10" t="n"/>
+      <c r="T47" s="10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U47" s="10" t="n">
         <v>3145</v>
       </c>
-      <c r="S47" s="10" t="n"/>
-      <c r="T47" s="10" t="n"/>
-      <c r="U47" s="10" t="inlineStr">
+      <c r="V47" s="10" t="n"/>
+      <c r="W47" s="10" t="n"/>
+      <c r="X47" s="10" t="inlineStr">
         <is>
           <t>라운드 마지막 5초 점수·수확량 +10% / Lv</t>
         </is>
       </c>
-      <c r="V47" s="10" t="inlineStr">
+      <c r="Y47" s="10" t="inlineStr">
         <is>
           <t>param = 마지막 몇 초</t>
         </is>
@@ -4303,23 +4589,28 @@
         <v>3</v>
       </c>
       <c r="O48" s="10" t="n"/>
-      <c r="P48" s="10" t="n"/>
+      <c r="P48" s="10" t="n">
+        <v>51000000</v>
+      </c>
       <c r="Q48" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R48" s="10" t="n">
-        <v>3142</v>
-      </c>
+      <c r="R48" s="10" t="n"/>
       <c r="S48" s="10" t="n"/>
       <c r="T48" s="10" t="n"/>
-      <c r="U48" s="10" t="inlineStr">
+      <c r="U48" s="10" t="n">
+        <v>3142</v>
+      </c>
+      <c r="V48" s="10" t="n"/>
+      <c r="W48" s="10" t="n"/>
+      <c r="X48" s="10" t="inlineStr">
         <is>
           <t>군락지 수 +3 (12 → 15)</t>
         </is>
       </c>
-      <c r="V48" s="10" t="inlineStr">
+      <c r="Y48" s="10" t="inlineStr">
         <is>
           <t>넓은 시야의 상위</t>
         </is>
@@ -4379,27 +4670,32 @@
         <v>0.03</v>
       </c>
       <c r="O49" s="10" t="n"/>
-      <c r="P49" s="10" t="n"/>
+      <c r="P49" s="10" t="n">
+        <v>47000000</v>
+      </c>
       <c r="Q49" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R49" s="10" t="n">
+      <c r="R49" s="10" t="n"/>
+      <c r="S49" s="10" t="n"/>
+      <c r="T49" s="10" t="n"/>
+      <c r="U49" s="10" t="n">
         <v>3140</v>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="V49" s="10" t="inlineStr">
         <is>
           <t>3137</t>
         </is>
       </c>
-      <c r="T49" s="10" t="n"/>
-      <c r="U49" s="10" t="inlineStr">
+      <c r="W49" s="10" t="n"/>
+      <c r="X49" s="10" t="inlineStr">
         <is>
           <t>보스 전용 레전더리 버섯 수확량 +9%</t>
         </is>
       </c>
-      <c r="V49" s="10" t="inlineStr">
+      <c r="Y49" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +3%</t>
         </is>
@@ -4459,27 +4755,32 @@
         <v>0.1</v>
       </c>
       <c r="O50" s="10" t="n"/>
-      <c r="P50" s="10" t="n"/>
+      <c r="P50" s="10" t="n">
+        <v>65000000</v>
+      </c>
       <c r="Q50" s="10" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R50" s="10" t="n">
+      <c r="R50" s="10" t="n"/>
+      <c r="S50" s="10" t="n"/>
+      <c r="T50" s="10" t="n"/>
+      <c r="U50" s="10" t="n">
         <v>3137</v>
       </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="V50" s="10" t="inlineStr">
         <is>
           <t>3138</t>
         </is>
       </c>
-      <c r="T50" s="10" t="n"/>
-      <c r="U50" s="10" t="inlineStr">
+      <c r="W50" s="10" t="n"/>
+      <c r="X50" s="10" t="inlineStr">
         <is>
           <t>점수 골드 전환율 +50%</t>
         </is>
       </c>
-      <c r="V50" s="10" t="inlineStr">
+      <c r="Y50" s="10" t="inlineStr">
         <is>
           <t>흥정 기술의 상위. 누적값 기준 차이 +10%</t>
         </is>
@@ -4539,23 +4840,28 @@
         <v>3</v>
       </c>
       <c r="O51" s="11" t="n"/>
-      <c r="P51" s="11" t="n"/>
+      <c r="P51" s="11" t="n">
+        <v>170</v>
+      </c>
       <c r="Q51" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R51" s="11" t="n">
-        <v>3001</v>
-      </c>
+      <c r="R51" s="11" t="n"/>
       <c r="S51" s="11" t="n"/>
       <c r="T51" s="11" t="n"/>
-      <c r="U51" s="11" t="inlineStr">
+      <c r="U51" s="11" t="n">
+        <v>3001</v>
+      </c>
+      <c r="V51" s="11" t="n"/>
+      <c r="W51" s="11" t="n"/>
+      <c r="X51" s="11" t="inlineStr">
         <is>
           <t>가속(3초) 버프</t>
         </is>
       </c>
-      <c r="V51" s="11" t="inlineStr">
+      <c r="Y51" s="11" t="inlineStr">
         <is>
           <t>value = 지속(초), 다음 노드는 +1초씩</t>
         </is>
@@ -4615,23 +4921,28 @@
         <v>3</v>
       </c>
       <c r="O52" s="11" t="n"/>
-      <c r="P52" s="11" t="n"/>
+      <c r="P52" s="11" t="n">
+        <v>170</v>
+      </c>
       <c r="Q52" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R52" s="11" t="n">
-        <v>3201</v>
-      </c>
+      <c r="R52" s="11" t="n"/>
       <c r="S52" s="11" t="n"/>
       <c r="T52" s="11" t="n"/>
-      <c r="U52" s="11" t="inlineStr">
+      <c r="U52" s="11" t="n">
+        <v>3201</v>
+      </c>
+      <c r="V52" s="11" t="n"/>
+      <c r="W52" s="11" t="n"/>
+      <c r="X52" s="11" t="inlineStr">
         <is>
           <t>관통(3초) 버프</t>
         </is>
       </c>
-      <c r="V52" s="11" t="n"/>
+      <c r="Y52" s="11" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="n">
@@ -4687,27 +4998,32 @@
         <v>1</v>
       </c>
       <c r="O53" s="11" t="n"/>
-      <c r="P53" s="11" t="n"/>
+      <c r="P53" s="11" t="n">
+        <v>240</v>
+      </c>
       <c r="Q53" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R53" s="11" t="n">
+      <c r="R53" s="11" t="n"/>
+      <c r="S53" s="11" t="n"/>
+      <c r="T53" s="11" t="n"/>
+      <c r="U53" s="11" t="n">
         <v>3202</v>
       </c>
-      <c r="S53" s="11" t="inlineStr">
+      <c r="V53" s="11" t="inlineStr">
         <is>
           <t>3201</t>
         </is>
       </c>
-      <c r="T53" s="11" t="n"/>
-      <c r="U53" s="11" t="inlineStr">
+      <c r="W53" s="11" t="n"/>
+      <c r="X53" s="11" t="inlineStr">
         <is>
           <t>가속(4초) 버프</t>
         </is>
       </c>
-      <c r="V53" s="11" t="n"/>
+      <c r="Y53" s="11" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="n">
@@ -4763,23 +5079,28 @@
         <v>1</v>
       </c>
       <c r="O54" s="11" t="n"/>
-      <c r="P54" s="11" t="n"/>
+      <c r="P54" s="11" t="n">
+        <v>240</v>
+      </c>
       <c r="Q54" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R54" s="11" t="n">
-        <v>3201</v>
-      </c>
+      <c r="R54" s="11" t="n"/>
       <c r="S54" s="11" t="n"/>
       <c r="T54" s="11" t="n"/>
-      <c r="U54" s="11" t="inlineStr">
+      <c r="U54" s="11" t="n">
+        <v>3201</v>
+      </c>
+      <c r="V54" s="11" t="n"/>
+      <c r="W54" s="11" t="n"/>
+      <c r="X54" s="11" t="inlineStr">
         <is>
           <t>필드에 그루터기 추가</t>
         </is>
       </c>
-      <c r="V54" s="11" t="inlineStr">
+      <c r="Y54" s="11" t="inlineStr">
         <is>
           <t>value = 단계 (1 그루터기 / 2 꽃밭 / 3 도토리 점등)</t>
         </is>
@@ -4841,23 +5162,28 @@
       <c r="O55" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="P55" s="11" t="n"/>
+      <c r="P55" s="11" t="n">
+        <v>910</v>
+      </c>
       <c r="Q55" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R55" s="11" t="n">
-        <v>3204</v>
-      </c>
+      <c r="R55" s="11" t="n"/>
       <c r="S55" s="11" t="n"/>
       <c r="T55" s="11" t="n"/>
-      <c r="U55" s="11" t="inlineStr">
+      <c r="U55" s="11" t="n">
+        <v>3204</v>
+      </c>
+      <c r="V55" s="11" t="n"/>
+      <c r="W55" s="11" t="n"/>
+      <c r="X55" s="11" t="inlineStr">
         <is>
           <t>단일 버섯 획득 시 3% 확률로 다음 타격 피해 +200%</t>
         </is>
       </c>
-      <c r="V55" s="11" t="inlineStr">
+      <c r="Y55" s="11" t="inlineStr">
         <is>
           <t>param = 피해 증가 (2 = +200%)</t>
         </is>
@@ -4919,23 +5245,28 @@
       <c r="O56" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="P56" s="11" t="n"/>
+      <c r="P56" s="11" t="n">
+        <v>1400</v>
+      </c>
       <c r="Q56" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R56" s="11" t="n">
-        <v>3202</v>
-      </c>
+      <c r="R56" s="11" t="n"/>
       <c r="S56" s="11" t="n"/>
       <c r="T56" s="11" t="n"/>
-      <c r="U56" s="11" t="inlineStr">
+      <c r="U56" s="11" t="n">
+        <v>3202</v>
+      </c>
+      <c r="V56" s="11" t="n"/>
+      <c r="W56" s="11" t="n"/>
+      <c r="X56" s="11" t="inlineStr">
         <is>
           <t>[피버] 버프 3초 · 콤보 계수 +50%</t>
         </is>
       </c>
-      <c r="V56" s="11" t="inlineStr">
+      <c r="Y56" s="11" t="inlineStr">
         <is>
           <t>param = 콤보 계수 증가</t>
         </is>
@@ -4995,27 +5326,32 @@
         <v>1</v>
       </c>
       <c r="O57" s="11" t="n"/>
-      <c r="P57" s="11" t="n"/>
+      <c r="P57" s="11" t="n">
+        <v>1400</v>
+      </c>
       <c r="Q57" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R57" s="11" t="n">
+      <c r="R57" s="11" t="n"/>
+      <c r="S57" s="11" t="n"/>
+      <c r="T57" s="11" t="n"/>
+      <c r="U57" s="11" t="n">
         <v>3202</v>
       </c>
-      <c r="S57" s="11" t="inlineStr">
+      <c r="V57" s="11" t="inlineStr">
         <is>
           <t>3203</t>
         </is>
       </c>
-      <c r="T57" s="11" t="n"/>
-      <c r="U57" s="11" t="inlineStr">
+      <c r="W57" s="11" t="n"/>
+      <c r="X57" s="11" t="inlineStr">
         <is>
           <t>가속(5초) 버프</t>
         </is>
       </c>
-      <c r="V57" s="11" t="n"/>
+      <c r="Y57" s="11" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="n">
@@ -5073,27 +5409,32 @@
       <c r="O58" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="P58" s="11" t="n"/>
+      <c r="P58" s="11" t="n">
+        <v>3200</v>
+      </c>
       <c r="Q58" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R58" s="11" t="n">
+      <c r="R58" s="11" t="n"/>
+      <c r="S58" s="11" t="n"/>
+      <c r="T58" s="11" t="n"/>
+      <c r="U58" s="11" t="n">
         <v>3204</v>
       </c>
-      <c r="S58" s="11" t="inlineStr">
+      <c r="V58" s="11" t="inlineStr">
         <is>
           <t>3205</t>
         </is>
       </c>
-      <c r="T58" s="11" t="n"/>
-      <c r="U58" s="11" t="inlineStr">
+      <c r="W58" s="11" t="n"/>
+      <c r="X58" s="11" t="inlineStr">
         <is>
           <t>단일 버섯 획득 시 4% 확률로 다음 타격 피해 +200%</t>
         </is>
       </c>
-      <c r="V58" s="11" t="n"/>
+      <c r="Y58" s="11" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="n">
@@ -5151,23 +5492,28 @@
       <c r="O59" s="11" t="n">
         <v>0.3</v>
       </c>
-      <c r="P59" s="11" t="n"/>
+      <c r="P59" s="11" t="n">
+        <v>8400</v>
+      </c>
       <c r="Q59" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R59" s="11" t="n">
-        <v>3205</v>
-      </c>
+      <c r="R59" s="11" t="n"/>
       <c r="S59" s="11" t="n"/>
       <c r="T59" s="11" t="n"/>
-      <c r="U59" s="11" t="inlineStr">
+      <c r="U59" s="11" t="n">
+        <v>3205</v>
+      </c>
+      <c r="V59" s="11" t="n"/>
+      <c r="W59" s="11" t="n"/>
+      <c r="X59" s="11" t="inlineStr">
         <is>
           <t>군락 파괴 시 3% 확률로 랜덤 군락에 번개(공격력 30%)</t>
         </is>
       </c>
-      <c r="V59" s="11" t="inlineStr">
+      <c r="Y59" s="11" t="inlineStr">
         <is>
           <t>param = 번개 피해 (공격력 비율)</t>
         </is>
@@ -5227,23 +5573,28 @@
         <v>3</v>
       </c>
       <c r="O60" s="11" t="n"/>
-      <c r="P60" s="11" t="n"/>
+      <c r="P60" s="11" t="n">
+        <v>5800</v>
+      </c>
       <c r="Q60" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R60" s="11" t="n">
-        <v>3211</v>
-      </c>
+      <c r="R60" s="11" t="n"/>
       <c r="S60" s="11" t="n"/>
       <c r="T60" s="11" t="n"/>
-      <c r="U60" s="11" t="inlineStr">
+      <c r="U60" s="11" t="n">
+        <v>3211</v>
+      </c>
+      <c r="V60" s="11" t="n"/>
+      <c r="W60" s="11" t="n"/>
+      <c r="X60" s="11" t="inlineStr">
         <is>
           <t>유도(3초) 버프</t>
         </is>
       </c>
-      <c r="V60" s="11" t="n"/>
+      <c r="Y60" s="11" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="n">
@@ -5299,27 +5650,32 @@
         <v>1</v>
       </c>
       <c r="O61" s="11" t="n"/>
-      <c r="P61" s="11" t="n"/>
+      <c r="P61" s="11" t="n">
+        <v>5800</v>
+      </c>
       <c r="Q61" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R61" s="11" t="n">
+      <c r="R61" s="11" t="n"/>
+      <c r="S61" s="11" t="n"/>
+      <c r="T61" s="11" t="n"/>
+      <c r="U61" s="11" t="n">
         <v>3206</v>
       </c>
-      <c r="S61" s="11" t="inlineStr">
+      <c r="V61" s="11" t="inlineStr">
         <is>
           <t>3202</t>
         </is>
       </c>
-      <c r="T61" s="11" t="n"/>
-      <c r="U61" s="11" t="inlineStr">
+      <c r="W61" s="11" t="n"/>
+      <c r="X61" s="11" t="inlineStr">
         <is>
           <t>관통(4초) 버프</t>
         </is>
       </c>
-      <c r="V61" s="11" t="n"/>
+      <c r="Y61" s="11" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="n">
@@ -5375,27 +5731,32 @@
         <v>1</v>
       </c>
       <c r="O62" s="11" t="n"/>
-      <c r="P62" s="11" t="n"/>
+      <c r="P62" s="11" t="n">
+        <v>8400</v>
+      </c>
       <c r="Q62" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R62" s="11" t="n">
+      <c r="R62" s="11" t="n"/>
+      <c r="S62" s="11" t="n"/>
+      <c r="T62" s="11" t="n"/>
+      <c r="U62" s="11" t="n">
         <v>3207</v>
       </c>
-      <c r="S62" s="11" t="inlineStr">
+      <c r="V62" s="11" t="inlineStr">
         <is>
           <t>3211</t>
         </is>
       </c>
-      <c r="T62" s="11" t="n"/>
-      <c r="U62" s="11" t="inlineStr">
+      <c r="W62" s="11" t="n"/>
+      <c r="X62" s="11" t="inlineStr">
         <is>
           <t>관통(5초) 버프</t>
         </is>
       </c>
-      <c r="V62" s="11" t="inlineStr">
+      <c r="Y62" s="11" t="inlineStr">
         <is>
           <t>원문은 Lv.2와 같은 레어도 7</t>
         </is>
@@ -5455,23 +5816,28 @@
         <v>0.1</v>
       </c>
       <c r="O63" s="11" t="n"/>
-      <c r="P63" s="11" t="n"/>
+      <c r="P63" s="11" t="n">
+        <v>16000</v>
+      </c>
       <c r="Q63" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R63" s="11" t="n">
-        <v>3209</v>
-      </c>
+      <c r="R63" s="11" t="n"/>
       <c r="S63" s="11" t="n"/>
       <c r="T63" s="11" t="n"/>
-      <c r="U63" s="11" t="inlineStr">
+      <c r="U63" s="11" t="n">
+        <v>3209</v>
+      </c>
+      <c r="V63" s="11" t="n"/>
+      <c r="W63" s="11" t="n"/>
+      <c r="X63" s="11" t="inlineStr">
         <is>
           <t>군락 충돌로 디버프를 얻으면 10% 확률로 해제</t>
         </is>
       </c>
-      <c r="V63" s="11" t="n"/>
+      <c r="Y63" s="11" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="n">
@@ -5529,27 +5895,32 @@
       <c r="O64" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="P64" s="11" t="n"/>
+      <c r="P64" s="11" t="n">
+        <v>17000</v>
+      </c>
       <c r="Q64" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R64" s="11" t="n">
+      <c r="R64" s="11" t="n"/>
+      <c r="S64" s="11" t="n"/>
+      <c r="T64" s="11" t="n"/>
+      <c r="U64" s="11" t="n">
         <v>3215</v>
       </c>
-      <c r="S64" s="11" t="inlineStr">
+      <c r="V64" s="11" t="inlineStr">
         <is>
           <t>3208</t>
         </is>
       </c>
-      <c r="T64" s="11" t="n"/>
-      <c r="U64" s="11" t="inlineStr">
+      <c r="W64" s="11" t="n"/>
+      <c r="X64" s="11" t="inlineStr">
         <is>
           <t>단일 버섯 획득 시 5% 확률로 다음 타격 피해 +200%</t>
         </is>
       </c>
-      <c r="V64" s="11" t="n"/>
+      <c r="Y64" s="11" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="n">
@@ -5605,27 +5976,32 @@
         <v>1</v>
       </c>
       <c r="O65" s="11" t="n"/>
-      <c r="P65" s="11" t="n"/>
+      <c r="P65" s="11" t="n">
+        <v>10000</v>
+      </c>
       <c r="Q65" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R65" s="11" t="n">
+      <c r="R65" s="11" t="n"/>
+      <c r="S65" s="11" t="n"/>
+      <c r="T65" s="11" t="n"/>
+      <c r="U65" s="11" t="n">
         <v>3208</v>
       </c>
-      <c r="S65" s="11" t="inlineStr">
+      <c r="V65" s="11" t="inlineStr">
         <is>
           <t>3204</t>
         </is>
       </c>
-      <c r="T65" s="11" t="n"/>
-      <c r="U65" s="11" t="inlineStr">
+      <c r="W65" s="11" t="n"/>
+      <c r="X65" s="11" t="inlineStr">
         <is>
           <t>필드에 꽃밭 추가</t>
         </is>
       </c>
-      <c r="V65" s="11" t="n"/>
+      <c r="Y65" s="11" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="n">
@@ -5681,23 +6057,28 @@
         <v>3</v>
       </c>
       <c r="O66" s="11" t="n"/>
-      <c r="P66" s="11" t="n"/>
+      <c r="P66" s="11" t="n">
+        <v>82000</v>
+      </c>
       <c r="Q66" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R66" s="11" t="n">
-        <v>3212</v>
-      </c>
+      <c r="R66" s="11" t="n"/>
       <c r="S66" s="11" t="n"/>
       <c r="T66" s="11" t="n"/>
-      <c r="U66" s="11" t="inlineStr">
+      <c r="U66" s="11" t="n">
+        <v>3212</v>
+      </c>
+      <c r="V66" s="11" t="n"/>
+      <c r="W66" s="11" t="n"/>
+      <c r="X66" s="11" t="inlineStr">
         <is>
           <t>포자 디버프 제거 + 약손(3초)</t>
         </is>
       </c>
-      <c r="V66" s="11" t="n"/>
+      <c r="Y66" s="11" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="n">
@@ -5753,27 +6134,32 @@
         <v>1</v>
       </c>
       <c r="O67" s="11" t="n"/>
-      <c r="P67" s="11" t="n"/>
+      <c r="P67" s="11" t="n">
+        <v>82000</v>
+      </c>
       <c r="Q67" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R67" s="11" t="n">
+      <c r="R67" s="11" t="n"/>
+      <c r="S67" s="11" t="n"/>
+      <c r="T67" s="11" t="n"/>
+      <c r="U67" s="11" t="n">
         <v>3211</v>
       </c>
-      <c r="S67" s="11" t="inlineStr">
+      <c r="V67" s="11" t="inlineStr">
         <is>
           <t>3210</t>
         </is>
       </c>
-      <c r="T67" s="11" t="n"/>
-      <c r="U67" s="11" t="inlineStr">
+      <c r="W67" s="11" t="n"/>
+      <c r="X67" s="11" t="inlineStr">
         <is>
           <t>유도(4초) 버프</t>
         </is>
       </c>
-      <c r="V67" s="11" t="n"/>
+      <c r="Y67" s="11" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="n">
@@ -5829,27 +6215,32 @@
         <v>0.1</v>
       </c>
       <c r="O68" s="11" t="n"/>
-      <c r="P68" s="11" t="n"/>
+      <c r="P68" s="11" t="n">
+        <v>45000</v>
+      </c>
       <c r="Q68" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R68" s="11" t="n">
+      <c r="R68" s="11" t="n"/>
+      <c r="S68" s="11" t="n"/>
+      <c r="T68" s="11" t="n"/>
+      <c r="U68" s="11" t="n">
         <v>3209</v>
       </c>
-      <c r="S68" s="11" t="inlineStr">
+      <c r="V68" s="11" t="inlineStr">
         <is>
           <t>3213</t>
         </is>
       </c>
-      <c r="T68" s="11" t="n"/>
-      <c r="U68" s="11" t="inlineStr">
+      <c r="W68" s="11" t="n"/>
+      <c r="X68" s="11" t="inlineStr">
         <is>
           <t>군락 충돌로 디버프를 얻으면 20% 확률로 해제</t>
         </is>
       </c>
-      <c r="V68" s="11" t="n"/>
+      <c r="Y68" s="11" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="n">
@@ -5907,23 +6298,28 @@
       <c r="O69" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="P69" s="11" t="n"/>
+      <c r="P69" s="11" t="n">
+        <v>310000</v>
+      </c>
       <c r="Q69" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R69" s="11" t="n">
-        <v>3214</v>
-      </c>
+      <c r="R69" s="11" t="n"/>
       <c r="S69" s="11" t="n"/>
       <c r="T69" s="11" t="n"/>
-      <c r="U69" s="11" t="inlineStr">
+      <c r="U69" s="11" t="n">
+        <v>3214</v>
+      </c>
+      <c r="V69" s="11" t="n"/>
+      <c r="W69" s="11" t="n"/>
+      <c r="X69" s="11" t="inlineStr">
         <is>
           <t>군락 충돌 시 3% 확률로 3초 지속 피해(공격력 5%)</t>
         </is>
       </c>
-      <c r="V69" s="11" t="inlineStr">
+      <c r="Y69" s="11" t="inlineStr">
         <is>
           <t>param = 초당 피해 (공격력 비율). 지속 시간도 3/4/5초로 오르는데 칸이 하나라 계열 레벨 + 2초로 계산 필요</t>
         </is>
@@ -5985,23 +6381,28 @@
       <c r="O70" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="P70" s="11" t="n"/>
+      <c r="P70" s="11" t="n">
+        <v>1000000</v>
+      </c>
       <c r="Q70" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R70" s="11" t="n">
-        <v>3211</v>
-      </c>
+      <c r="R70" s="11" t="n"/>
       <c r="S70" s="11" t="n"/>
       <c r="T70" s="11" t="n"/>
-      <c r="U70" s="11" t="inlineStr">
+      <c r="U70" s="11" t="n">
+        <v>3211</v>
+      </c>
+      <c r="V70" s="11" t="n"/>
+      <c r="W70" s="11" t="n"/>
+      <c r="X70" s="11" t="inlineStr">
         <is>
           <t>[지혜] 버프 3초 · 수확기 스킬 발동률 +1%</t>
         </is>
       </c>
-      <c r="V70" s="11" t="inlineStr">
+      <c r="Y70" s="11" t="inlineStr">
         <is>
           <t>param = 버프 지속(초)</t>
         </is>
@@ -6063,27 +6464,32 @@
       <c r="O71" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="P71" s="11" t="n"/>
+      <c r="P71" s="11" t="n">
+        <v>1100000</v>
+      </c>
       <c r="Q71" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R71" s="11" t="n">
+      <c r="R71" s="11" t="n"/>
+      <c r="S71" s="11" t="n"/>
+      <c r="T71" s="11" t="n"/>
+      <c r="U71" s="11" t="n">
         <v>3217</v>
       </c>
-      <c r="S71" s="11" t="inlineStr">
+      <c r="V71" s="11" t="inlineStr">
         <is>
           <t>3220</t>
         </is>
       </c>
-      <c r="T71" s="11" t="n"/>
-      <c r="U71" s="11" t="inlineStr">
+      <c r="W71" s="11" t="n"/>
+      <c r="X71" s="11" t="inlineStr">
         <is>
           <t>[지혜] 버프 3초 · 수확기 스킬 발동률 +2%</t>
         </is>
       </c>
-      <c r="V71" s="11" t="inlineStr">
+      <c r="Y71" s="11" t="inlineStr">
         <is>
           <t>원문은 Lv.1과 같은 레어도 11</t>
         </is>
@@ -6145,27 +6551,32 @@
       <c r="O72" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="P72" s="11" t="n"/>
+      <c r="P72" s="11" t="n">
+        <v>1100000</v>
+      </c>
       <c r="Q72" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R72" s="11" t="n">
+      <c r="R72" s="11" t="n"/>
+      <c r="S72" s="11" t="n"/>
+      <c r="T72" s="11" t="n"/>
+      <c r="U72" s="11" t="n">
         <v>3221</v>
       </c>
-      <c r="S72" s="11" t="inlineStr">
+      <c r="V72" s="11" t="inlineStr">
         <is>
           <t>3206</t>
         </is>
       </c>
-      <c r="T72" s="11" t="n"/>
-      <c r="U72" s="11" t="inlineStr">
+      <c r="W72" s="11" t="n"/>
+      <c r="X72" s="11" t="inlineStr">
         <is>
           <t>[피버] 버프 4초 · 콤보 계수 +50%</t>
         </is>
       </c>
-      <c r="V72" s="11" t="n"/>
+      <c r="Y72" s="11" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="n">
@@ -6223,23 +6634,28 @@
       <c r="O73" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="P73" s="11" t="n"/>
+      <c r="P73" s="11" t="n">
+        <v>1100000</v>
+      </c>
       <c r="Q73" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R73" s="11" t="n">
-        <v>3215</v>
-      </c>
+      <c r="R73" s="11" t="n"/>
       <c r="S73" s="11" t="n"/>
       <c r="T73" s="11" t="n"/>
-      <c r="U73" s="11" t="inlineStr">
+      <c r="U73" s="11" t="n">
+        <v>3215</v>
+      </c>
+      <c r="V73" s="11" t="n"/>
+      <c r="W73" s="11" t="n"/>
+      <c r="X73" s="11" t="inlineStr">
         <is>
           <t>군락 충돌 시 1% 확률로 전체 피해(공격력 10%)</t>
         </is>
       </c>
-      <c r="V73" s="11" t="inlineStr">
+      <c r="Y73" s="11" t="inlineStr">
         <is>
           <t>param = 피해 (공격력 비율)</t>
         </is>
@@ -6301,27 +6717,32 @@
       <c r="O74" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="P74" s="11" t="n"/>
+      <c r="P74" s="11" t="n">
+        <v>1900000</v>
+      </c>
       <c r="Q74" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R74" s="11" t="n">
+      <c r="R74" s="11" t="n"/>
+      <c r="S74" s="11" t="n"/>
+      <c r="T74" s="11" t="n"/>
+      <c r="U74" s="11" t="n">
         <v>3213</v>
       </c>
-      <c r="S74" s="11" t="inlineStr">
+      <c r="V74" s="11" t="inlineStr">
         <is>
           <t>3223</t>
         </is>
       </c>
-      <c r="T74" s="11" t="n"/>
-      <c r="U74" s="11" t="inlineStr">
+      <c r="W74" s="11" t="n"/>
+      <c r="X74" s="11" t="inlineStr">
         <is>
           <t>군락 충돌 시 2% 확률로 전체 피해(공격력 10%)</t>
         </is>
       </c>
-      <c r="V74" s="11" t="n"/>
+      <c r="Y74" s="11" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="11" t="n">
@@ -6377,27 +6798,32 @@
         <v>1</v>
       </c>
       <c r="O75" s="11" t="n"/>
-      <c r="P75" s="11" t="n"/>
+      <c r="P75" s="11" t="n">
+        <v>3700000</v>
+      </c>
       <c r="Q75" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R75" s="11" t="n">
+      <c r="R75" s="11" t="n"/>
+      <c r="S75" s="11" t="n"/>
+      <c r="T75" s="11" t="n"/>
+      <c r="U75" s="11" t="n">
         <v>3221</v>
       </c>
-      <c r="S75" s="11" t="inlineStr">
+      <c r="V75" s="11" t="inlineStr">
         <is>
           <t>3217</t>
         </is>
       </c>
-      <c r="T75" s="11" t="n"/>
-      <c r="U75" s="11" t="inlineStr">
+      <c r="W75" s="11" t="n"/>
+      <c r="X75" s="11" t="inlineStr">
         <is>
           <t>유도(5초) 버프</t>
         </is>
       </c>
-      <c r="V75" s="11" t="n"/>
+      <c r="Y75" s="11" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="n">
@@ -6453,27 +6879,32 @@
         <v>0.1</v>
       </c>
       <c r="O76" s="11" t="n"/>
-      <c r="P76" s="11" t="n"/>
+      <c r="P76" s="11" t="n">
+        <v>3500000</v>
+      </c>
       <c r="Q76" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R76" s="11" t="n">
+      <c r="R76" s="11" t="n"/>
+      <c r="S76" s="11" t="n"/>
+      <c r="T76" s="11" t="n"/>
+      <c r="U76" s="11" t="n">
         <v>3224</v>
       </c>
-      <c r="S76" s="11" t="inlineStr">
+      <c r="V76" s="11" t="inlineStr">
         <is>
           <t>3218</t>
         </is>
       </c>
-      <c r="T76" s="11" t="n"/>
-      <c r="U76" s="11" t="inlineStr">
+      <c r="W76" s="11" t="n"/>
+      <c r="X76" s="11" t="inlineStr">
         <is>
           <t>군락 충돌로 디버프를 얻으면 30% 확률로 해제</t>
         </is>
       </c>
-      <c r="V76" s="11" t="n"/>
+      <c r="Y76" s="11" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="n">
@@ -6529,27 +6960,32 @@
         <v>1</v>
       </c>
       <c r="O77" s="11" t="n"/>
-      <c r="P77" s="11" t="n"/>
+      <c r="P77" s="11" t="n">
+        <v>3300000</v>
+      </c>
       <c r="Q77" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R77" s="11" t="n">
+      <c r="R77" s="11" t="n"/>
+      <c r="S77" s="11" t="n"/>
+      <c r="T77" s="11" t="n"/>
+      <c r="U77" s="11" t="n">
         <v>3223</v>
       </c>
-      <c r="S77" s="11" t="inlineStr">
+      <c r="V77" s="11" t="inlineStr">
         <is>
           <t>3215</t>
         </is>
       </c>
-      <c r="T77" s="11" t="n"/>
-      <c r="U77" s="11" t="inlineStr">
+      <c r="W77" s="11" t="n"/>
+      <c r="X77" s="11" t="inlineStr">
         <is>
           <t>필드에 도토리 점등 추가</t>
         </is>
       </c>
-      <c r="V77" s="11" t="n"/>
+      <c r="Y77" s="11" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="11" t="n">
@@ -6607,23 +7043,28 @@
       <c r="O78" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="P78" s="11" t="n"/>
+      <c r="P78" s="11" t="n">
+        <v>5400000</v>
+      </c>
       <c r="Q78" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R78" s="11" t="n">
-        <v>3221</v>
-      </c>
+      <c r="R78" s="11" t="n"/>
       <c r="S78" s="11" t="n"/>
       <c r="T78" s="11" t="n"/>
-      <c r="U78" s="11" t="inlineStr">
+      <c r="U78" s="11" t="n">
+        <v>3221</v>
+      </c>
+      <c r="V78" s="11" t="n"/>
+      <c r="W78" s="11" t="n"/>
+      <c r="X78" s="11" t="inlineStr">
         <is>
           <t>10% 확률로 분열(3초) 버프</t>
         </is>
       </c>
-      <c r="V78" s="11" t="inlineStr">
+      <c r="Y78" s="11" t="inlineStr">
         <is>
           <t>param = 발동 확률</t>
         </is>
@@ -6685,27 +7126,32 @@
       <c r="O79" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="P79" s="11" t="n"/>
+      <c r="P79" s="11" t="n">
+        <v>5600000</v>
+      </c>
       <c r="Q79" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R79" s="11" t="n">
+      <c r="R79" s="11" t="n"/>
+      <c r="S79" s="11" t="n"/>
+      <c r="T79" s="11" t="n"/>
+      <c r="U79" s="11" t="n">
         <v>3227</v>
       </c>
-      <c r="S79" s="11" t="inlineStr">
+      <c r="V79" s="11" t="inlineStr">
         <is>
           <t>3219</t>
         </is>
       </c>
-      <c r="T79" s="11" t="n"/>
-      <c r="U79" s="11" t="inlineStr">
+      <c r="W79" s="11" t="n"/>
+      <c r="X79" s="11" t="inlineStr">
         <is>
           <t>군락 충돌 시 4% 확률로 4초 지속 피해(공격력 5%)</t>
         </is>
       </c>
-      <c r="V79" s="11" t="n"/>
+      <c r="Y79" s="11" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="n">
@@ -6763,27 +7209,32 @@
       <c r="O80" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="P80" s="11" t="n"/>
+      <c r="P80" s="11" t="n">
+        <v>14000000</v>
+      </c>
       <c r="Q80" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R80" s="11" t="n">
+      <c r="R80" s="11" t="n"/>
+      <c r="S80" s="11" t="n"/>
+      <c r="T80" s="11" t="n"/>
+      <c r="U80" s="11" t="n">
         <v>3231</v>
       </c>
-      <c r="S80" s="11" t="inlineStr">
+      <c r="V80" s="11" t="inlineStr">
         <is>
           <t>3221</t>
         </is>
       </c>
-      <c r="T80" s="11" t="n"/>
-      <c r="U80" s="11" t="inlineStr">
+      <c r="W80" s="11" t="n"/>
+      <c r="X80" s="11" t="inlineStr">
         <is>
           <t>[지혜] 버프 3초 · 수확기 스킬 발동률 +3%</t>
         </is>
       </c>
-      <c r="V80" s="11" t="n"/>
+      <c r="Y80" s="11" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="11" t="n">
@@ -6839,27 +7290,32 @@
         <v>1</v>
       </c>
       <c r="O81" s="11" t="n"/>
-      <c r="P81" s="11" t="n"/>
+      <c r="P81" s="11" t="n">
+        <v>14000000</v>
+      </c>
       <c r="Q81" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R81" s="11" t="n">
+      <c r="R81" s="11" t="n"/>
+      <c r="S81" s="11" t="n"/>
+      <c r="T81" s="11" t="n"/>
+      <c r="U81" s="11" t="n">
         <v>3220</v>
       </c>
-      <c r="S81" s="11" t="inlineStr">
+      <c r="V81" s="11" t="inlineStr">
         <is>
           <t>3216</t>
         </is>
       </c>
-      <c r="T81" s="11" t="n"/>
-      <c r="U81" s="11" t="inlineStr">
+      <c r="W81" s="11" t="n"/>
+      <c r="X81" s="11" t="inlineStr">
         <is>
           <t>포자 디버프 제거 + 약손(4초)</t>
         </is>
       </c>
-      <c r="V81" s="11" t="n"/>
+      <c r="Y81" s="11" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="n">
@@ -6917,27 +7373,32 @@
       <c r="O82" s="11" t="n">
         <v>0.3</v>
       </c>
-      <c r="P82" s="11" t="n"/>
+      <c r="P82" s="11" t="n">
+        <v>23000000</v>
+      </c>
       <c r="Q82" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R82" s="11" t="n">
+      <c r="R82" s="11" t="n"/>
+      <c r="S82" s="11" t="n"/>
+      <c r="T82" s="11" t="n"/>
+      <c r="U82" s="11" t="n">
         <v>3229</v>
       </c>
-      <c r="S82" s="11" t="inlineStr">
+      <c r="V82" s="11" t="inlineStr">
         <is>
           <t>3209</t>
         </is>
       </c>
-      <c r="T82" s="11" t="n"/>
-      <c r="U82" s="11" t="inlineStr">
+      <c r="W82" s="11" t="n"/>
+      <c r="X82" s="11" t="inlineStr">
         <is>
           <t>군락 파괴 시 5% 확률로 랜덤 군락에 번개(공격력 30%)</t>
         </is>
       </c>
-      <c r="V82" s="11" t="inlineStr">
+      <c r="Y82" s="11" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -6997,27 +7458,32 @@
         <v>1</v>
       </c>
       <c r="O83" s="11" t="n"/>
-      <c r="P83" s="11" t="n"/>
+      <c r="P83" s="11" t="n">
+        <v>23000000</v>
+      </c>
       <c r="Q83" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R83" s="11" t="n">
+      <c r="R83" s="11" t="n"/>
+      <c r="S83" s="11" t="n"/>
+      <c r="T83" s="11" t="n"/>
+      <c r="U83" s="11" t="n">
         <v>3228</v>
       </c>
-      <c r="S83" s="11" t="inlineStr">
+      <c r="V83" s="11" t="inlineStr">
         <is>
           <t>3231</t>
         </is>
       </c>
-      <c r="T83" s="11" t="n"/>
-      <c r="U83" s="11" t="inlineStr">
+      <c r="W83" s="11" t="n"/>
+      <c r="X83" s="11" t="inlineStr">
         <is>
           <t>포자 디버프 제거 + 약손(5초)</t>
         </is>
       </c>
-      <c r="V83" s="11" t="n"/>
+      <c r="Y83" s="11" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="11" t="n">
@@ -7075,27 +7541,32 @@
       <c r="O84" s="11" t="n">
         <v>0.3</v>
       </c>
-      <c r="P84" s="11" t="n"/>
+      <c r="P84" s="11" t="n">
+        <v>35000000</v>
+      </c>
       <c r="Q84" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R84" s="11" t="n">
+      <c r="R84" s="11" t="n"/>
+      <c r="S84" s="11" t="n"/>
+      <c r="T84" s="11" t="n"/>
+      <c r="U84" s="11" t="n">
         <v>3226</v>
       </c>
-      <c r="S84" s="11" t="inlineStr">
+      <c r="V84" s="11" t="inlineStr">
         <is>
           <t>3232</t>
         </is>
       </c>
-      <c r="T84" s="11" t="n"/>
-      <c r="U84" s="11" t="inlineStr">
+      <c r="W84" s="11" t="n"/>
+      <c r="X84" s="11" t="inlineStr">
         <is>
           <t>군락 파괴 시 7% 확률로 랜덤 위치에 번개(공격력 30%)</t>
         </is>
       </c>
-      <c r="V84" s="11" t="inlineStr">
+      <c r="Y84" s="11" t="inlineStr">
         <is>
           <t>확인 필요: 원문 Lv.3만 "랜덤 위치", Lv.1·2는 "랜덤 군락"</t>
         </is>
@@ -7155,23 +7626,30 @@
         <v>0.02</v>
       </c>
       <c r="O85" s="11" t="n"/>
-      <c r="P85" s="11" t="n"/>
+      <c r="P85" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="Q85" s="11" t="inlineStr">
         <is>
           <t>Mycelite</t>
         </is>
       </c>
-      <c r="R85" s="11" t="n">
+      <c r="R85" s="11" t="n"/>
+      <c r="S85" s="11" t="n"/>
+      <c r="T85" s="11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U85" s="11" t="n">
         <v>3230</v>
       </c>
-      <c r="S85" s="11" t="n"/>
-      <c r="T85" s="11" t="n"/>
-      <c r="U85" s="11" t="inlineStr">
+      <c r="V85" s="11" t="n"/>
+      <c r="W85" s="11" t="n"/>
+      <c r="X85" s="11" t="inlineStr">
         <is>
           <t>게임 시작 시 보유 버프 스킬 즉시 발동 확률 +2% / Lv</t>
         </is>
       </c>
-      <c r="V85" s="11" t="n"/>
+      <c r="Y85" s="11" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="11" t="n">
@@ -7229,27 +7707,32 @@
       <c r="O86" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="P86" s="11" t="n"/>
+      <c r="P86" s="11" t="n">
+        <v>35000000</v>
+      </c>
       <c r="Q86" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R86" s="11" t="n">
+      <c r="R86" s="11" t="n"/>
+      <c r="S86" s="11" t="n"/>
+      <c r="T86" s="11" t="n"/>
+      <c r="U86" s="11" t="n">
         <v>3225</v>
       </c>
-      <c r="S86" s="11" t="inlineStr">
+      <c r="V86" s="11" t="inlineStr">
         <is>
           <t>3228</t>
         </is>
       </c>
-      <c r="T86" s="11" t="n"/>
-      <c r="U86" s="11" t="inlineStr">
+      <c r="W86" s="11" t="n"/>
+      <c r="X86" s="11" t="inlineStr">
         <is>
           <t>10% 확률로 분열(4초) 버프</t>
         </is>
       </c>
-      <c r="V86" s="11" t="n"/>
+      <c r="Y86" s="11" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="n">
@@ -7307,27 +7790,32 @@
       <c r="O87" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="P87" s="11" t="n"/>
+      <c r="P87" s="11" t="n">
+        <v>35000000</v>
+      </c>
       <c r="Q87" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R87" s="11" t="n">
+      <c r="R87" s="11" t="n"/>
+      <c r="S87" s="11" t="n"/>
+      <c r="T87" s="11" t="n"/>
+      <c r="U87" s="11" t="n">
         <v>3231</v>
       </c>
-      <c r="S87" s="11" t="inlineStr">
+      <c r="V87" s="11" t="inlineStr">
         <is>
           <t>3236</t>
         </is>
       </c>
-      <c r="T87" s="11" t="n"/>
-      <c r="U87" s="11" t="inlineStr">
+      <c r="W87" s="11" t="n"/>
+      <c r="X87" s="11" t="inlineStr">
         <is>
           <t>10% 확률로 분열(5초) 버프</t>
         </is>
       </c>
-      <c r="V87" s="11" t="inlineStr">
+      <c r="Y87" s="11" t="inlineStr">
         <is>
           <t>원문은 Lv.2와 같은 레어도 16</t>
         </is>
@@ -7389,27 +7877,32 @@
       <c r="O88" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="P88" s="11" t="n"/>
+      <c r="P88" s="11" t="n">
+        <v>35000000</v>
+      </c>
       <c r="Q88" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R88" s="11" t="n">
+      <c r="R88" s="11" t="n"/>
+      <c r="S88" s="11" t="n"/>
+      <c r="T88" s="11" t="n"/>
+      <c r="U88" s="11" t="n">
         <v>3227</v>
       </c>
-      <c r="S88" s="11" t="inlineStr">
+      <c r="V88" s="11" t="inlineStr">
         <is>
           <t>3224</t>
         </is>
       </c>
-      <c r="T88" s="11" t="n"/>
-      <c r="U88" s="11" t="inlineStr">
+      <c r="W88" s="11" t="n"/>
+      <c r="X88" s="11" t="inlineStr">
         <is>
           <t>군락 충돌 시 3% 확률로 전체 피해(공격력 10%)</t>
         </is>
       </c>
-      <c r="V88" s="11" t="n"/>
+      <c r="Y88" s="11" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="11" t="n">
@@ -7467,27 +7960,32 @@
       <c r="O89" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="P89" s="11" t="n"/>
+      <c r="P89" s="11" t="n">
+        <v>35000000</v>
+      </c>
       <c r="Q89" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R89" s="11" t="n">
+      <c r="R89" s="11" t="n"/>
+      <c r="S89" s="11" t="n"/>
+      <c r="T89" s="11" t="n"/>
+      <c r="U89" s="11" t="n">
         <v>3232</v>
       </c>
-      <c r="S89" s="11" t="inlineStr">
+      <c r="V89" s="11" t="inlineStr">
         <is>
           <t>3229</t>
         </is>
       </c>
-      <c r="T89" s="11" t="n"/>
-      <c r="U89" s="11" t="inlineStr">
+      <c r="W89" s="11" t="n"/>
+      <c r="X89" s="11" t="inlineStr">
         <is>
           <t>군락 충돌 시 5% 확률로 5초 지속 피해(공격력 5%)</t>
         </is>
       </c>
-      <c r="V89" s="11" t="n"/>
+      <c r="Y89" s="11" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="n">
@@ -7545,27 +8043,32 @@
       <c r="O90" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="P90" s="11" t="n"/>
+      <c r="P90" s="11" t="n">
+        <v>65000000</v>
+      </c>
       <c r="Q90" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R90" s="11" t="n">
+      <c r="R90" s="11" t="n"/>
+      <c r="S90" s="11" t="n"/>
+      <c r="T90" s="11" t="n"/>
+      <c r="U90" s="11" t="n">
         <v>3236</v>
       </c>
-      <c r="S90" s="11" t="inlineStr">
+      <c r="V90" s="11" t="inlineStr">
         <is>
           <t>3222</t>
         </is>
       </c>
-      <c r="T90" s="11" t="n"/>
-      <c r="U90" s="11" t="inlineStr">
+      <c r="W90" s="11" t="n"/>
+      <c r="X90" s="11" t="inlineStr">
         <is>
           <t>[피버] 버프 5초 · 콤보 계수 +50%</t>
         </is>
       </c>
-      <c r="V90" s="11" t="n"/>
+      <c r="Y90" s="11" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="12" t="n">
@@ -7621,23 +8124,28 @@
         <v>2</v>
       </c>
       <c r="O91" s="12" t="n"/>
-      <c r="P91" s="12" t="n"/>
+      <c r="P91" s="12" t="n">
+        <v>130</v>
+      </c>
       <c r="Q91" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R91" s="12" t="n">
-        <v>3001</v>
-      </c>
+      <c r="R91" s="12" t="n"/>
       <c r="S91" s="12" t="n"/>
       <c r="T91" s="12" t="n"/>
-      <c r="U91" s="12" t="inlineStr">
+      <c r="U91" s="12" t="n">
+        <v>3001</v>
+      </c>
+      <c r="V91" s="12" t="n"/>
+      <c r="W91" s="12" t="n"/>
+      <c r="X91" s="12" t="inlineStr">
         <is>
           <t>공격력 +2 (1 → 3)</t>
         </is>
       </c>
-      <c r="V91" s="12" t="n"/>
+      <c r="Y91" s="12" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="12" t="n">
@@ -7693,23 +8201,28 @@
         <v>0.2</v>
       </c>
       <c r="O92" s="12" t="n"/>
-      <c r="P92" s="12" t="n"/>
+      <c r="P92" s="12" t="n">
+        <v>240</v>
+      </c>
       <c r="Q92" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R92" s="12" t="n">
-        <v>3303</v>
-      </c>
+      <c r="R92" s="12" t="n"/>
       <c r="S92" s="12" t="n"/>
       <c r="T92" s="12" t="n"/>
-      <c r="U92" s="12" t="inlineStr">
+      <c r="U92" s="12" t="n">
+        <v>3303</v>
+      </c>
+      <c r="V92" s="12" t="n"/>
+      <c r="W92" s="12" t="n"/>
+      <c r="X92" s="12" t="inlineStr">
         <is>
           <t>콤보 계수 +20%</t>
         </is>
       </c>
-      <c r="V92" s="12" t="n"/>
+      <c r="Y92" s="12" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="12" t="n">
@@ -7765,23 +8278,28 @@
         <v>0.1</v>
       </c>
       <c r="O93" s="12" t="n"/>
-      <c r="P93" s="12" t="n"/>
+      <c r="P93" s="12" t="n">
+        <v>170</v>
+      </c>
       <c r="Q93" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R93" s="12" t="n">
-        <v>3301</v>
-      </c>
+      <c r="R93" s="12" t="n"/>
       <c r="S93" s="12" t="n"/>
       <c r="T93" s="12" t="n"/>
-      <c r="U93" s="12" t="inlineStr">
+      <c r="U93" s="12" t="n">
+        <v>3301</v>
+      </c>
+      <c r="V93" s="12" t="n"/>
+      <c r="W93" s="12" t="n"/>
+      <c r="X93" s="12" t="inlineStr">
         <is>
           <t>수확기 속도 +10%</t>
         </is>
       </c>
-      <c r="V93" s="12" t="n"/>
+      <c r="Y93" s="12" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="n">
@@ -7837,23 +8355,28 @@
         <v>0.02</v>
       </c>
       <c r="O94" s="12" t="n"/>
-      <c r="P94" s="12" t="n"/>
+      <c r="P94" s="12" t="n">
+        <v>240</v>
+      </c>
       <c r="Q94" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R94" s="12" t="n">
-        <v>3301</v>
-      </c>
+      <c r="R94" s="12" t="n"/>
       <c r="S94" s="12" t="n"/>
       <c r="T94" s="12" t="n"/>
-      <c r="U94" s="12" t="inlineStr">
+      <c r="U94" s="12" t="n">
+        <v>3301</v>
+      </c>
+      <c r="V94" s="12" t="n"/>
+      <c r="W94" s="12" t="n"/>
+      <c r="X94" s="12" t="inlineStr">
         <is>
           <t>치명타 확률 2%</t>
         </is>
       </c>
-      <c r="V94" s="12" t="n"/>
+      <c r="Y94" s="12" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="12" t="n">
@@ -7909,23 +8432,28 @@
         <v>0.2</v>
       </c>
       <c r="O95" s="12" t="n"/>
-      <c r="P95" s="12" t="n"/>
+      <c r="P95" s="12" t="n">
+        <v>800</v>
+      </c>
       <c r="Q95" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R95" s="12" t="n">
-        <v>3302</v>
-      </c>
+      <c r="R95" s="12" t="n"/>
       <c r="S95" s="12" t="n"/>
       <c r="T95" s="12" t="n"/>
-      <c r="U95" s="12" t="inlineStr">
+      <c r="U95" s="12" t="n">
+        <v>3302</v>
+      </c>
+      <c r="V95" s="12" t="n"/>
+      <c r="W95" s="12" t="n"/>
+      <c r="X95" s="12" t="inlineStr">
         <is>
           <t>바 길이 +20%</t>
         </is>
       </c>
-      <c r="V95" s="12" t="n"/>
+      <c r="Y95" s="12" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="12" t="n">
@@ -7981,27 +8509,32 @@
         <v>2</v>
       </c>
       <c r="O96" s="12" t="n"/>
-      <c r="P96" s="12" t="n"/>
+      <c r="P96" s="12" t="n">
+        <v>800</v>
+      </c>
       <c r="Q96" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R96" s="12" t="n">
+      <c r="R96" s="12" t="n"/>
+      <c r="S96" s="12" t="n"/>
+      <c r="T96" s="12" t="n"/>
+      <c r="U96" s="12" t="n">
         <v>3304</v>
       </c>
-      <c r="S96" s="12" t="inlineStr">
+      <c r="V96" s="12" t="inlineStr">
         <is>
           <t>3301</t>
         </is>
       </c>
-      <c r="T96" s="12" t="n"/>
-      <c r="U96" s="12" t="inlineStr">
+      <c r="W96" s="12" t="n"/>
+      <c r="X96" s="12" t="inlineStr">
         <is>
           <t>공격력 +2 (3 → 5)</t>
         </is>
       </c>
-      <c r="V96" s="12" t="n"/>
+      <c r="Y96" s="12" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="12" t="n">
@@ -8057,23 +8590,28 @@
         <v>0.1</v>
       </c>
       <c r="O97" s="12" t="n"/>
-      <c r="P97" s="12" t="n"/>
+      <c r="P97" s="12" t="n">
+        <v>1400</v>
+      </c>
       <c r="Q97" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R97" s="12" t="n">
-        <v>3303</v>
-      </c>
+      <c r="R97" s="12" t="n"/>
       <c r="S97" s="12" t="n"/>
       <c r="T97" s="12" t="n"/>
-      <c r="U97" s="12" t="inlineStr">
+      <c r="U97" s="12" t="n">
+        <v>3303</v>
+      </c>
+      <c r="V97" s="12" t="n"/>
+      <c r="W97" s="12" t="n"/>
+      <c r="X97" s="12" t="inlineStr">
         <is>
           <t>수확기 크기 +10%</t>
         </is>
       </c>
-      <c r="V97" s="12" t="n"/>
+      <c r="Y97" s="12" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="12" t="n">
@@ -8129,27 +8667,32 @@
         <v>0.1</v>
       </c>
       <c r="O98" s="12" t="n"/>
-      <c r="P98" s="12" t="n"/>
+      <c r="P98" s="12" t="n">
+        <v>1400</v>
+      </c>
       <c r="Q98" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R98" s="12" t="n">
+      <c r="R98" s="12" t="n"/>
+      <c r="S98" s="12" t="n"/>
+      <c r="T98" s="12" t="n"/>
+      <c r="U98" s="12" t="n">
         <v>3303</v>
       </c>
-      <c r="S98" s="12" t="inlineStr">
+      <c r="V98" s="12" t="inlineStr">
         <is>
           <t>3307</t>
         </is>
       </c>
-      <c r="T98" s="12" t="n"/>
-      <c r="U98" s="12" t="inlineStr">
+      <c r="W98" s="12" t="n"/>
+      <c r="X98" s="12" t="inlineStr">
         <is>
           <t>수확기 크기 +20%</t>
         </is>
       </c>
-      <c r="V98" s="12" t="inlineStr">
+      <c r="Y98" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%. 원문은 Lv.1과 같은 레어도 5</t>
         </is>
@@ -8209,27 +8752,32 @@
         <v>2</v>
       </c>
       <c r="O99" s="12" t="n"/>
-      <c r="P99" s="12" t="n"/>
+      <c r="P99" s="12" t="n">
+        <v>3200</v>
+      </c>
       <c r="Q99" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R99" s="12" t="n">
+      <c r="R99" s="12" t="n"/>
+      <c r="S99" s="12" t="n"/>
+      <c r="T99" s="12" t="n"/>
+      <c r="U99" s="12" t="n">
         <v>3304</v>
       </c>
-      <c r="S99" s="12" t="inlineStr">
+      <c r="V99" s="12" t="inlineStr">
         <is>
           <t>3306</t>
         </is>
       </c>
-      <c r="T99" s="12" t="n"/>
-      <c r="U99" s="12" t="inlineStr">
+      <c r="W99" s="12" t="n"/>
+      <c r="X99" s="12" t="inlineStr">
         <is>
           <t>공격력 +2 (5 → 7)</t>
         </is>
       </c>
-      <c r="V99" s="12" t="inlineStr">
+      <c r="Y99" s="12" t="inlineStr">
         <is>
           <t>확인 필요: 원문은 "+3 (5 → 7)", 화살표 기준 +2로 넣음</t>
         </is>
@@ -8289,27 +8837,32 @@
         <v>0.1</v>
       </c>
       <c r="O100" s="12" t="n"/>
-      <c r="P100" s="12" t="n"/>
+      <c r="P100" s="12" t="n">
+        <v>4500</v>
+      </c>
       <c r="Q100" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R100" s="12" t="n">
+      <c r="R100" s="12" t="n"/>
+      <c r="S100" s="12" t="n"/>
+      <c r="T100" s="12" t="n"/>
+      <c r="U100" s="12" t="n">
         <v>3308</v>
       </c>
-      <c r="S100" s="12" t="inlineStr">
+      <c r="V100" s="12" t="inlineStr">
         <is>
           <t>3305</t>
         </is>
       </c>
-      <c r="T100" s="12" t="n"/>
-      <c r="U100" s="12" t="inlineStr">
+      <c r="W100" s="12" t="n"/>
+      <c r="X100" s="12" t="inlineStr">
         <is>
           <t>바 길이 +30%</t>
         </is>
       </c>
-      <c r="V100" s="12" t="inlineStr">
+      <c r="Y100" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%</t>
         </is>
@@ -8369,27 +8922,32 @@
         <v>0.1</v>
       </c>
       <c r="O101" s="12" t="n"/>
-      <c r="P101" s="12" t="n"/>
+      <c r="P101" s="12" t="n">
+        <v>4300</v>
+      </c>
       <c r="Q101" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R101" s="12" t="n">
+      <c r="R101" s="12" t="n"/>
+      <c r="S101" s="12" t="n"/>
+      <c r="T101" s="12" t="n"/>
+      <c r="U101" s="12" t="n">
         <v>3312</v>
       </c>
-      <c r="S101" s="12" t="inlineStr">
+      <c r="V101" s="12" t="inlineStr">
         <is>
           <t>3308</t>
         </is>
       </c>
-      <c r="T101" s="12" t="n"/>
-      <c r="U101" s="12" t="inlineStr">
+      <c r="W101" s="12" t="n"/>
+      <c r="X101" s="12" t="inlineStr">
         <is>
           <t>수확기 크기 +30%</t>
         </is>
       </c>
-      <c r="V101" s="12" t="inlineStr">
+      <c r="Y101" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%</t>
         </is>
@@ -8449,27 +9007,32 @@
         <v>0.1</v>
       </c>
       <c r="O102" s="12" t="n"/>
-      <c r="P102" s="12" t="n"/>
+      <c r="P102" s="12" t="n">
+        <v>4300</v>
+      </c>
       <c r="Q102" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R102" s="12" t="n">
+      <c r="R102" s="12" t="n"/>
+      <c r="S102" s="12" t="n"/>
+      <c r="T102" s="12" t="n"/>
+      <c r="U102" s="12" t="n">
         <v>3307</v>
       </c>
-      <c r="S102" s="12" t="inlineStr">
+      <c r="V102" s="12" t="inlineStr">
         <is>
           <t>3303</t>
         </is>
       </c>
-      <c r="T102" s="12" t="n"/>
-      <c r="U102" s="12" t="inlineStr">
+      <c r="W102" s="12" t="n"/>
+      <c r="X102" s="12" t="inlineStr">
         <is>
           <t>수확기 속도 +20%</t>
         </is>
       </c>
-      <c r="V102" s="12" t="inlineStr">
+      <c r="Y102" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%</t>
         </is>
@@ -8529,27 +9092,32 @@
         <v>0.02</v>
       </c>
       <c r="O103" s="12" t="n"/>
-      <c r="P103" s="12" t="n"/>
+      <c r="P103" s="12" t="n">
+        <v>10000</v>
+      </c>
       <c r="Q103" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R103" s="12" t="n">
+      <c r="R103" s="12" t="n"/>
+      <c r="S103" s="12" t="n"/>
+      <c r="T103" s="12" t="n"/>
+      <c r="U103" s="12" t="n">
         <v>3309</v>
       </c>
-      <c r="S103" s="12" t="inlineStr">
+      <c r="V103" s="12" t="inlineStr">
         <is>
           <t>3304</t>
         </is>
       </c>
-      <c r="T103" s="12" t="n"/>
-      <c r="U103" s="12" t="inlineStr">
+      <c r="W103" s="12" t="n"/>
+      <c r="X103" s="12" t="inlineStr">
         <is>
           <t>치명타 확률 4%</t>
         </is>
       </c>
-      <c r="V103" s="12" t="inlineStr">
+      <c r="Y103" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -8609,23 +9177,28 @@
         <v>1</v>
       </c>
       <c r="O104" s="12" t="n"/>
-      <c r="P104" s="12" t="n"/>
+      <c r="P104" s="12" t="n">
+        <v>16000</v>
+      </c>
       <c r="Q104" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R104" s="12" t="n">
-        <v>3313</v>
-      </c>
+      <c r="R104" s="12" t="n"/>
       <c r="S104" s="12" t="n"/>
       <c r="T104" s="12" t="n"/>
-      <c r="U104" s="12" t="inlineStr">
+      <c r="U104" s="12" t="n">
+        <v>3313</v>
+      </c>
+      <c r="V104" s="12" t="n"/>
+      <c r="W104" s="12" t="n"/>
+      <c r="X104" s="12" t="inlineStr">
         <is>
           <t>회전 꼬마 수확기 +1 (0 → 1)</t>
         </is>
       </c>
-      <c r="V104" s="12" t="n"/>
+      <c r="Y104" s="12" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="12" t="n">
@@ -8681,27 +9254,32 @@
         <v>0.2</v>
       </c>
       <c r="O105" s="12" t="n"/>
-      <c r="P105" s="12" t="n"/>
+      <c r="P105" s="12" t="n">
+        <v>53000</v>
+      </c>
       <c r="Q105" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R105" s="12" t="n">
+      <c r="R105" s="12" t="n"/>
+      <c r="S105" s="12" t="n"/>
+      <c r="T105" s="12" t="n"/>
+      <c r="U105" s="12" t="n">
         <v>3312</v>
       </c>
-      <c r="S105" s="12" t="inlineStr">
+      <c r="V105" s="12" t="inlineStr">
         <is>
           <t>3310</t>
         </is>
       </c>
-      <c r="T105" s="12" t="n"/>
-      <c r="U105" s="12" t="inlineStr">
+      <c r="W105" s="12" t="n"/>
+      <c r="X105" s="12" t="inlineStr">
         <is>
           <t>바 길이 +50%</t>
         </is>
       </c>
-      <c r="V105" s="12" t="inlineStr">
+      <c r="Y105" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +20%</t>
         </is>
@@ -8761,23 +9339,28 @@
         <v>0.2</v>
       </c>
       <c r="O106" s="12" t="n"/>
-      <c r="P106" s="12" t="n"/>
+      <c r="P106" s="12" t="n">
+        <v>37000</v>
+      </c>
       <c r="Q106" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R106" s="12" t="n">
-        <v>3313</v>
-      </c>
+      <c r="R106" s="12" t="n"/>
       <c r="S106" s="12" t="n"/>
       <c r="T106" s="12" t="n"/>
-      <c r="U106" s="12" t="inlineStr">
+      <c r="U106" s="12" t="n">
+        <v>3313</v>
+      </c>
+      <c r="V106" s="12" t="n"/>
+      <c r="W106" s="12" t="n"/>
+      <c r="X106" s="12" t="inlineStr">
         <is>
           <t>보스 피해 +20%</t>
         </is>
       </c>
-      <c r="V106" s="12" t="n"/>
+      <c r="Y106" s="12" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="12" t="n">
@@ -8833,27 +9416,32 @@
         <v>0.2</v>
       </c>
       <c r="O107" s="12" t="n"/>
-      <c r="P107" s="12" t="n"/>
+      <c r="P107" s="12" t="n">
+        <v>53000</v>
+      </c>
       <c r="Q107" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R107" s="12" t="n">
+      <c r="R107" s="12" t="n"/>
+      <c r="S107" s="12" t="n"/>
+      <c r="T107" s="12" t="n"/>
+      <c r="U107" s="12" t="n">
         <v>3310</v>
       </c>
-      <c r="S107" s="12" t="inlineStr">
+      <c r="V107" s="12" t="inlineStr">
         <is>
           <t>3302</t>
         </is>
       </c>
-      <c r="T107" s="12" t="n"/>
-      <c r="U107" s="12" t="inlineStr">
+      <c r="W107" s="12" t="n"/>
+      <c r="X107" s="12" t="inlineStr">
         <is>
           <t>콤보 계수 +40%</t>
         </is>
       </c>
-      <c r="V107" s="12" t="inlineStr">
+      <c r="Y107" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +20%</t>
         </is>
@@ -8913,23 +9501,28 @@
         <v>3</v>
       </c>
       <c r="O108" s="12" t="n"/>
-      <c r="P108" s="12" t="n"/>
+      <c r="P108" s="12" t="n">
+        <v>21000</v>
+      </c>
       <c r="Q108" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R108" s="12" t="n">
-        <v>3310</v>
-      </c>
+      <c r="R108" s="12" t="n"/>
       <c r="S108" s="12" t="n"/>
       <c r="T108" s="12" t="n"/>
-      <c r="U108" s="12" t="inlineStr">
+      <c r="U108" s="12" t="n">
+        <v>3310</v>
+      </c>
+      <c r="V108" s="12" t="n"/>
+      <c r="W108" s="12" t="n"/>
+      <c r="X108" s="12" t="inlineStr">
         <is>
           <t>지속 시간 +3초 (15 → 18)</t>
         </is>
       </c>
-      <c r="V108" s="12" t="inlineStr">
+      <c r="Y108" s="12" t="inlineStr">
         <is>
           <t>확인 필요: 원문은 "+2초 (15 → 18)", 화살표 기준 +3으로 넣음</t>
         </is>
@@ -8989,27 +9582,32 @@
         <v>0.02</v>
       </c>
       <c r="O109" s="12" t="n"/>
-      <c r="P109" s="12" t="n"/>
+      <c r="P109" s="12" t="n">
+        <v>180000</v>
+      </c>
       <c r="Q109" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R109" s="12" t="n">
+      <c r="R109" s="12" t="n"/>
+      <c r="S109" s="12" t="n"/>
+      <c r="T109" s="12" t="n"/>
+      <c r="U109" s="12" t="n">
         <v>3306</v>
       </c>
-      <c r="S109" s="12" t="inlineStr">
+      <c r="V109" s="12" t="inlineStr">
         <is>
           <t>3313</t>
         </is>
       </c>
-      <c r="T109" s="12" t="n"/>
-      <c r="U109" s="12" t="inlineStr">
+      <c r="W109" s="12" t="n"/>
+      <c r="X109" s="12" t="inlineStr">
         <is>
           <t>치명타 확률 6%</t>
         </is>
       </c>
-      <c r="V109" s="12" t="n"/>
+      <c r="Y109" s="12" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="12" t="n">
@@ -9065,27 +9663,32 @@
         <v>3</v>
       </c>
       <c r="O110" s="12" t="n"/>
-      <c r="P110" s="12" t="n"/>
+      <c r="P110" s="12" t="n">
+        <v>180000</v>
+      </c>
       <c r="Q110" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R110" s="12" t="n">
+      <c r="R110" s="12" t="n"/>
+      <c r="S110" s="12" t="n"/>
+      <c r="T110" s="12" t="n"/>
+      <c r="U110" s="12" t="n">
         <v>3314</v>
       </c>
-      <c r="S110" s="12" t="inlineStr">
+      <c r="V110" s="12" t="inlineStr">
         <is>
           <t>3309</t>
         </is>
       </c>
-      <c r="T110" s="12" t="n"/>
-      <c r="U110" s="12" t="inlineStr">
+      <c r="W110" s="12" t="n"/>
+      <c r="X110" s="12" t="inlineStr">
         <is>
           <t>공격력 +3 (7 → 10)</t>
         </is>
       </c>
-      <c r="V110" s="12" t="n"/>
+      <c r="Y110" s="12" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="12" t="n">
@@ -9141,27 +9744,32 @@
         <v>0.2</v>
       </c>
       <c r="O111" s="12" t="n"/>
-      <c r="P111" s="12" t="n"/>
+      <c r="P111" s="12" t="n">
+        <v>560000</v>
+      </c>
       <c r="Q111" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R111" s="12" t="n">
+      <c r="R111" s="12" t="n"/>
+      <c r="S111" s="12" t="n"/>
+      <c r="T111" s="12" t="n"/>
+      <c r="U111" s="12" t="n">
         <v>3313</v>
       </c>
-      <c r="S111" s="12" t="inlineStr">
+      <c r="V111" s="12" t="inlineStr">
         <is>
           <t>3316</t>
         </is>
       </c>
-      <c r="T111" s="12" t="n"/>
-      <c r="U111" s="12" t="inlineStr">
+      <c r="W111" s="12" t="n"/>
+      <c r="X111" s="12" t="inlineStr">
         <is>
           <t>보스 피해 +40%</t>
         </is>
       </c>
-      <c r="V111" s="12" t="n"/>
+      <c r="Y111" s="12" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="12" t="n">
@@ -9219,23 +9827,28 @@
       <c r="O112" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="P112" s="12" t="n"/>
+      <c r="P112" s="12" t="n">
+        <v>1000000</v>
+      </c>
       <c r="Q112" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R112" s="12" t="n">
-        <v>3324</v>
-      </c>
+      <c r="R112" s="12" t="n"/>
       <c r="S112" s="12" t="n"/>
       <c r="T112" s="12" t="n"/>
-      <c r="U112" s="12" t="inlineStr">
+      <c r="U112" s="12" t="n">
+        <v>3324</v>
+      </c>
+      <c r="V112" s="12" t="n"/>
+      <c r="W112" s="12" t="n"/>
+      <c r="X112" s="12" t="inlineStr">
         <is>
           <t>10% 확률로 3초 분신 바</t>
         </is>
       </c>
-      <c r="V112" s="12" t="inlineStr">
+      <c r="Y112" s="12" t="inlineStr">
         <is>
           <t>param = 발동 확률</t>
         </is>
@@ -9295,27 +9908,32 @@
         <v>3</v>
       </c>
       <c r="O113" s="12" t="n"/>
-      <c r="P113" s="12" t="n"/>
+      <c r="P113" s="12" t="n">
+        <v>390000</v>
+      </c>
       <c r="Q113" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R113" s="12" t="n">
+      <c r="R113" s="12" t="n"/>
+      <c r="S113" s="12" t="n"/>
+      <c r="T113" s="12" t="n"/>
+      <c r="U113" s="12" t="n">
         <v>3317</v>
       </c>
-      <c r="S113" s="12" t="inlineStr">
+      <c r="V113" s="12" t="inlineStr">
         <is>
           <t>3318</t>
         </is>
       </c>
-      <c r="T113" s="12" t="n"/>
-      <c r="U113" s="12" t="inlineStr">
+      <c r="W113" s="12" t="n"/>
+      <c r="X113" s="12" t="inlineStr">
         <is>
           <t>지속 시간 +3초 (18 → 21)</t>
         </is>
       </c>
-      <c r="V113" s="12" t="n"/>
+      <c r="Y113" s="12" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="12" t="n">
@@ -9371,27 +9989,32 @@
         <v>0.1</v>
       </c>
       <c r="O114" s="12" t="n"/>
-      <c r="P114" s="12" t="n"/>
+      <c r="P114" s="12" t="n">
+        <v>400000</v>
+      </c>
       <c r="Q114" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R114" s="12" t="n">
+      <c r="R114" s="12" t="n"/>
+      <c r="S114" s="12" t="n"/>
+      <c r="T114" s="12" t="n"/>
+      <c r="U114" s="12" t="n">
         <v>3315</v>
       </c>
-      <c r="S114" s="12" t="inlineStr">
+      <c r="V114" s="12" t="inlineStr">
         <is>
           <t>3312</t>
         </is>
       </c>
-      <c r="T114" s="12" t="n"/>
-      <c r="U114" s="12" t="inlineStr">
+      <c r="W114" s="12" t="n"/>
+      <c r="X114" s="12" t="inlineStr">
         <is>
           <t>수확기 속도 +30%</t>
         </is>
       </c>
-      <c r="V114" s="12" t="n"/>
+      <c r="Y114" s="12" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="12" t="n">
@@ -9447,27 +10070,32 @@
         <v>0.2</v>
       </c>
       <c r="O115" s="12" t="n"/>
-      <c r="P115" s="12" t="n"/>
+      <c r="P115" s="12" t="n">
+        <v>1900000</v>
+      </c>
       <c r="Q115" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R115" s="12" t="n">
+      <c r="R115" s="12" t="n"/>
+      <c r="S115" s="12" t="n"/>
+      <c r="T115" s="12" t="n"/>
+      <c r="U115" s="12" t="n">
         <v>3318</v>
       </c>
-      <c r="S115" s="12" t="inlineStr">
+      <c r="V115" s="12" t="inlineStr">
         <is>
           <t>3317</t>
         </is>
       </c>
-      <c r="T115" s="12" t="n"/>
-      <c r="U115" s="12" t="inlineStr">
+      <c r="W115" s="12" t="n"/>
+      <c r="X115" s="12" t="inlineStr">
         <is>
           <t>콤보 계수 +60%</t>
         </is>
       </c>
-      <c r="V115" s="12" t="n"/>
+      <c r="Y115" s="12" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="12" t="n">
@@ -9523,27 +10151,32 @@
         <v>1</v>
       </c>
       <c r="O116" s="12" t="n"/>
-      <c r="P116" s="12" t="n"/>
+      <c r="P116" s="12" t="n">
+        <v>1500000</v>
+      </c>
       <c r="Q116" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R116" s="12" t="n">
+      <c r="R116" s="12" t="n"/>
+      <c r="S116" s="12" t="n"/>
+      <c r="T116" s="12" t="n"/>
+      <c r="U116" s="12" t="n">
         <v>3319</v>
       </c>
-      <c r="S116" s="12" t="inlineStr">
+      <c r="V116" s="12" t="inlineStr">
         <is>
           <t>3314</t>
         </is>
       </c>
-      <c r="T116" s="12" t="n"/>
-      <c r="U116" s="12" t="inlineStr">
+      <c r="W116" s="12" t="n"/>
+      <c r="X116" s="12" t="inlineStr">
         <is>
           <t>회전 꼬마 수확기 +1 (1 → 2)</t>
         </is>
       </c>
-      <c r="V116" s="12" t="n"/>
+      <c r="Y116" s="12" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="12" t="n">
@@ -9599,23 +10232,28 @@
         <v>0.05</v>
       </c>
       <c r="O117" s="12" t="n"/>
-      <c r="P117" s="12" t="n"/>
+      <c r="P117" s="12" t="n">
+        <v>1600000</v>
+      </c>
       <c r="Q117" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R117" s="12" t="n">
-        <v>3319</v>
-      </c>
+      <c r="R117" s="12" t="n"/>
       <c r="S117" s="12" t="n"/>
       <c r="T117" s="12" t="n"/>
-      <c r="U117" s="12" t="inlineStr">
+      <c r="U117" s="12" t="n">
+        <v>3319</v>
+      </c>
+      <c r="V117" s="12" t="n"/>
+      <c r="W117" s="12" t="n"/>
+      <c r="X117" s="12" t="inlineStr">
         <is>
           <t>회전 꼬마 수확기 공격력 5%</t>
         </is>
       </c>
-      <c r="V117" s="12" t="n"/>
+      <c r="Y117" s="12" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="12" t="n">
@@ -9671,27 +10309,32 @@
         <v>0.2</v>
       </c>
       <c r="O118" s="12" t="n"/>
-      <c r="P118" s="12" t="n"/>
+      <c r="P118" s="12" t="n">
+        <v>3700000</v>
+      </c>
       <c r="Q118" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R118" s="12" t="n">
+      <c r="R118" s="12" t="n"/>
+      <c r="S118" s="12" t="n"/>
+      <c r="T118" s="12" t="n"/>
+      <c r="U118" s="12" t="n">
         <v>3331</v>
       </c>
-      <c r="S118" s="12" t="inlineStr">
+      <c r="V118" s="12" t="inlineStr">
         <is>
           <t>3321</t>
         </is>
       </c>
-      <c r="T118" s="12" t="n"/>
-      <c r="U118" s="12" t="inlineStr">
+      <c r="W118" s="12" t="n"/>
+      <c r="X118" s="12" t="inlineStr">
         <is>
           <t>보스 피해 +60%</t>
         </is>
       </c>
-      <c r="V118" s="12" t="n"/>
+      <c r="Y118" s="12" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="12" t="n">
@@ -9749,27 +10392,32 @@
       <c r="O119" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="P119" s="12" t="n"/>
+      <c r="P119" s="12" t="n">
+        <v>3700000</v>
+      </c>
       <c r="Q119" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R119" s="12" t="n">
+      <c r="R119" s="12" t="n"/>
+      <c r="S119" s="12" t="n"/>
+      <c r="T119" s="12" t="n"/>
+      <c r="U119" s="12" t="n">
         <v>3324</v>
       </c>
-      <c r="S119" s="12" t="inlineStr">
+      <c r="V119" s="12" t="inlineStr">
         <is>
           <t>3322</t>
         </is>
       </c>
-      <c r="T119" s="12" t="n"/>
-      <c r="U119" s="12" t="inlineStr">
+      <c r="W119" s="12" t="n"/>
+      <c r="X119" s="12" t="inlineStr">
         <is>
           <t>10% 확률로 4초 분신 바</t>
         </is>
       </c>
-      <c r="V119" s="12" t="n"/>
+      <c r="Y119" s="12" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="12" t="n">
@@ -9825,27 +10473,32 @@
         <v>0.2</v>
       </c>
       <c r="O120" s="12" t="n"/>
-      <c r="P120" s="12" t="n"/>
+      <c r="P120" s="12" t="n">
+        <v>3700000</v>
+      </c>
       <c r="Q120" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R120" s="12" t="n">
+      <c r="R120" s="12" t="n"/>
+      <c r="S120" s="12" t="n"/>
+      <c r="T120" s="12" t="n"/>
+      <c r="U120" s="12" t="n">
         <v>3323</v>
       </c>
-      <c r="S120" s="12" t="inlineStr">
+      <c r="V120" s="12" t="inlineStr">
         <is>
           <t>3325</t>
         </is>
       </c>
-      <c r="T120" s="12" t="n"/>
-      <c r="U120" s="12" t="inlineStr">
+      <c r="W120" s="12" t="n"/>
+      <c r="X120" s="12" t="inlineStr">
         <is>
           <t>콤보 계수 +80%</t>
         </is>
       </c>
-      <c r="V120" s="12" t="n"/>
+      <c r="Y120" s="12" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="12" t="n">
@@ -9901,23 +10554,28 @@
         <v>1</v>
       </c>
       <c r="O121" s="12" t="n"/>
-      <c r="P121" s="12" t="n"/>
+      <c r="P121" s="12" t="n">
+        <v>3300000</v>
+      </c>
       <c r="Q121" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R121" s="12" t="n">
-        <v>3321</v>
-      </c>
+      <c r="R121" s="12" t="n"/>
       <c r="S121" s="12" t="n"/>
       <c r="T121" s="12" t="n"/>
-      <c r="U121" s="12" t="inlineStr">
+      <c r="U121" s="12" t="n">
+        <v>3321</v>
+      </c>
+      <c r="V121" s="12" t="n"/>
+      <c r="W121" s="12" t="n"/>
+      <c r="X121" s="12" t="inlineStr">
         <is>
           <t>치명타 피해 100%</t>
         </is>
       </c>
-      <c r="V121" s="12" t="n"/>
+      <c r="Y121" s="12" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="12" t="n">
@@ -9973,27 +10631,32 @@
         <v>0.02</v>
       </c>
       <c r="O122" s="12" t="n"/>
-      <c r="P122" s="12" t="n"/>
+      <c r="P122" s="12" t="n">
+        <v>12000000</v>
+      </c>
       <c r="Q122" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R122" s="12" t="n">
+      <c r="R122" s="12" t="n"/>
+      <c r="S122" s="12" t="n"/>
+      <c r="T122" s="12" t="n"/>
+      <c r="U122" s="12" t="n">
         <v>3331</v>
       </c>
-      <c r="S122" s="12" t="inlineStr">
+      <c r="V122" s="12" t="inlineStr">
         <is>
           <t>3319</t>
         </is>
       </c>
-      <c r="T122" s="12" t="n"/>
-      <c r="U122" s="12" t="inlineStr">
+      <c r="W122" s="12" t="n"/>
+      <c r="X122" s="12" t="inlineStr">
         <is>
           <t>치명타 확률 8%</t>
         </is>
       </c>
-      <c r="V122" s="12" t="n"/>
+      <c r="Y122" s="12" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="12" t="n">
@@ -10049,27 +10712,32 @@
         <v>3</v>
       </c>
       <c r="O123" s="12" t="n"/>
-      <c r="P123" s="12" t="n"/>
+      <c r="P123" s="12" t="n">
+        <v>11000000</v>
+      </c>
       <c r="Q123" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R123" s="12" t="n">
+      <c r="R123" s="12" t="n"/>
+      <c r="S123" s="12" t="n"/>
+      <c r="T123" s="12" t="n"/>
+      <c r="U123" s="12" t="n">
         <v>3325</v>
       </c>
-      <c r="S123" s="12" t="inlineStr">
+      <c r="V123" s="12" t="inlineStr">
         <is>
           <t>3323</t>
         </is>
       </c>
-      <c r="T123" s="12" t="n"/>
-      <c r="U123" s="12" t="inlineStr">
+      <c r="W123" s="12" t="n"/>
+      <c r="X123" s="12" t="inlineStr">
         <is>
           <t>지속 시간 +3초 (21 → 24)</t>
         </is>
       </c>
-      <c r="V123" s="12" t="n"/>
+      <c r="Y123" s="12" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="12" t="n">
@@ -10125,27 +10793,32 @@
         <v>3</v>
       </c>
       <c r="O124" s="12" t="n"/>
-      <c r="P124" s="12" t="n"/>
+      <c r="P124" s="12" t="n">
+        <v>11000000</v>
+      </c>
       <c r="Q124" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R124" s="12" t="n">
+      <c r="R124" s="12" t="n"/>
+      <c r="S124" s="12" t="n"/>
+      <c r="T124" s="12" t="n"/>
+      <c r="U124" s="12" t="n">
         <v>3325</v>
       </c>
-      <c r="S124" s="12" t="inlineStr">
+      <c r="V124" s="12" t="inlineStr">
         <is>
           <t>3333</t>
         </is>
       </c>
-      <c r="T124" s="12" t="n"/>
-      <c r="U124" s="12" t="inlineStr">
+      <c r="W124" s="12" t="n"/>
+      <c r="X124" s="12" t="inlineStr">
         <is>
           <t>지속 시간 +3초 (24 → 27)</t>
         </is>
       </c>
-      <c r="V124" s="12" t="inlineStr">
+      <c r="Y124" s="12" t="inlineStr">
         <is>
           <t>원문은 Lv.3과 같은 레어도 14</t>
         </is>
@@ -10205,27 +10878,32 @@
         <v>0.2</v>
       </c>
       <c r="O125" s="12" t="n"/>
-      <c r="P125" s="12" t="n"/>
+      <c r="P125" s="12" t="n">
+        <v>19000000</v>
+      </c>
       <c r="Q125" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R125" s="12" t="n">
+      <c r="R125" s="12" t="n"/>
+      <c r="S125" s="12" t="n"/>
+      <c r="T125" s="12" t="n"/>
+      <c r="U125" s="12" t="n">
         <v>3327</v>
       </c>
-      <c r="S125" s="12" t="inlineStr">
+      <c r="V125" s="12" t="inlineStr">
         <is>
           <t>3328</t>
         </is>
       </c>
-      <c r="T125" s="12" t="n"/>
-      <c r="U125" s="12" t="inlineStr">
+      <c r="W125" s="12" t="n"/>
+      <c r="X125" s="12" t="inlineStr">
         <is>
           <t>보스 피해 +80%</t>
         </is>
       </c>
-      <c r="V125" s="12" t="n"/>
+      <c r="Y125" s="12" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="12" t="n">
@@ -10281,27 +10959,32 @@
         <v>0.2</v>
       </c>
       <c r="O126" s="12" t="n"/>
-      <c r="P126" s="12" t="n"/>
+      <c r="P126" s="12" t="n">
+        <v>19000000</v>
+      </c>
       <c r="Q126" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R126" s="12" t="n">
+      <c r="R126" s="12" t="n"/>
+      <c r="S126" s="12" t="n"/>
+      <c r="T126" s="12" t="n"/>
+      <c r="U126" s="12" t="n">
         <v>3329</v>
       </c>
-      <c r="S126" s="12" t="inlineStr">
+      <c r="V126" s="12" t="inlineStr">
         <is>
           <t>3330</t>
         </is>
       </c>
-      <c r="T126" s="12" t="n"/>
-      <c r="U126" s="12" t="inlineStr">
+      <c r="W126" s="12" t="n"/>
+      <c r="X126" s="12" t="inlineStr">
         <is>
           <t>콤보 계수 +100%</t>
         </is>
       </c>
-      <c r="V126" s="12" t="n"/>
+      <c r="Y126" s="12" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="12" t="n">
@@ -10357,27 +11040,32 @@
         <v>0.05</v>
       </c>
       <c r="O127" s="12" t="n"/>
-      <c r="P127" s="12" t="n"/>
+      <c r="P127" s="12" t="n">
+        <v>19000000</v>
+      </c>
       <c r="Q127" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R127" s="12" t="n">
+      <c r="R127" s="12" t="n"/>
+      <c r="S127" s="12" t="n"/>
+      <c r="T127" s="12" t="n"/>
+      <c r="U127" s="12" t="n">
         <v>3328</v>
       </c>
-      <c r="S127" s="12" t="inlineStr">
+      <c r="V127" s="12" t="inlineStr">
         <is>
           <t>3327</t>
         </is>
       </c>
-      <c r="T127" s="12" t="n"/>
-      <c r="U127" s="12" t="inlineStr">
+      <c r="W127" s="12" t="n"/>
+      <c r="X127" s="12" t="inlineStr">
         <is>
           <t>회전 꼬마 수확기 공격력 10%</t>
         </is>
       </c>
-      <c r="V127" s="12" t="n"/>
+      <c r="Y127" s="12" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="12" t="n">
@@ -10433,27 +11121,32 @@
         <v>5</v>
       </c>
       <c r="O128" s="12" t="n"/>
-      <c r="P128" s="12" t="n"/>
+      <c r="P128" s="12" t="n">
+        <v>19000000</v>
+      </c>
       <c r="Q128" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R128" s="12" t="n">
+      <c r="R128" s="12" t="n"/>
+      <c r="S128" s="12" t="n"/>
+      <c r="T128" s="12" t="n"/>
+      <c r="U128" s="12" t="n">
         <v>3326</v>
       </c>
-      <c r="S128" s="12" t="inlineStr">
+      <c r="V128" s="12" t="inlineStr">
         <is>
           <t>3320</t>
         </is>
       </c>
-      <c r="T128" s="12" t="n"/>
-      <c r="U128" s="12" t="inlineStr">
+      <c r="W128" s="12" t="n"/>
+      <c r="X128" s="12" t="inlineStr">
         <is>
           <t>공격력 +5 (10 → 15)</t>
         </is>
       </c>
-      <c r="V128" s="12" t="n"/>
+      <c r="Y128" s="12" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="12" t="n">
@@ -10509,23 +11202,30 @@
         <v>1</v>
       </c>
       <c r="O129" s="12" t="n"/>
-      <c r="P129" s="12" t="n"/>
+      <c r="P129" s="12" t="n">
+        <v>5</v>
+      </c>
       <c r="Q129" s="12" t="inlineStr">
         <is>
           <t>Mycelite</t>
         </is>
       </c>
-      <c r="R129" s="12" t="n">
+      <c r="R129" s="12" t="n"/>
+      <c r="S129" s="12" t="n"/>
+      <c r="T129" s="12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U129" s="12" t="n">
         <v>3341</v>
       </c>
-      <c r="S129" s="12" t="n"/>
-      <c r="T129" s="12" t="n"/>
-      <c r="U129" s="12" t="inlineStr">
+      <c r="V129" s="12" t="n"/>
+      <c r="W129" s="12" t="n"/>
+      <c r="X129" s="12" t="inlineStr">
         <is>
           <t>수확기 개수 +1 / Lv (최대 5개 장착)</t>
         </is>
       </c>
-      <c r="V129" s="12" t="n"/>
+      <c r="Y129" s="12" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="12" t="n">
@@ -10581,27 +11281,32 @@
         <v>0.2</v>
       </c>
       <c r="O130" s="12" t="n"/>
-      <c r="P130" s="12" t="n"/>
+      <c r="P130" s="12" t="n">
+        <v>26000000</v>
+      </c>
       <c r="Q130" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R130" s="12" t="n">
+      <c r="R130" s="12" t="n"/>
+      <c r="S130" s="12" t="n"/>
+      <c r="T130" s="12" t="n"/>
+      <c r="U130" s="12" t="n">
         <v>3337</v>
       </c>
-      <c r="S130" s="12" t="inlineStr">
+      <c r="V130" s="12" t="inlineStr">
         <is>
           <t>3335</t>
         </is>
       </c>
-      <c r="T130" s="12" t="n"/>
-      <c r="U130" s="12" t="inlineStr">
+      <c r="W130" s="12" t="n"/>
+      <c r="X130" s="12" t="inlineStr">
         <is>
           <t>보스 피해 +100%</t>
         </is>
       </c>
-      <c r="V130" s="12" t="n"/>
+      <c r="Y130" s="12" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="12" t="n">
@@ -10659,27 +11364,32 @@
       <c r="O131" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="P131" s="12" t="n"/>
+      <c r="P131" s="12" t="n">
+        <v>26000000</v>
+      </c>
       <c r="Q131" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R131" s="12" t="n">
+      <c r="R131" s="12" t="n"/>
+      <c r="S131" s="12" t="n"/>
+      <c r="T131" s="12" t="n"/>
+      <c r="U131" s="12" t="n">
         <v>3334</v>
       </c>
-      <c r="S131" s="12" t="inlineStr">
+      <c r="V131" s="12" t="inlineStr">
         <is>
           <t>3329</t>
         </is>
       </c>
-      <c r="T131" s="12" t="n"/>
-      <c r="U131" s="12" t="inlineStr">
+      <c r="W131" s="12" t="n"/>
+      <c r="X131" s="12" t="inlineStr">
         <is>
           <t>10% 확률로 5초 분신 바</t>
         </is>
       </c>
-      <c r="V131" s="12" t="n"/>
+      <c r="Y131" s="12" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="12" t="n">
@@ -10735,27 +11445,32 @@
         <v>0.02</v>
       </c>
       <c r="O132" s="12" t="n"/>
-      <c r="P132" s="12" t="n"/>
+      <c r="P132" s="12" t="n">
+        <v>26000000</v>
+      </c>
       <c r="Q132" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R132" s="12" t="n">
+      <c r="R132" s="12" t="n"/>
+      <c r="S132" s="12" t="n"/>
+      <c r="T132" s="12" t="n"/>
+      <c r="U132" s="12" t="n">
         <v>3331</v>
       </c>
-      <c r="S132" s="12" t="inlineStr">
+      <c r="V132" s="12" t="inlineStr">
         <is>
           <t>3332</t>
         </is>
       </c>
-      <c r="T132" s="12" t="n"/>
-      <c r="U132" s="12" t="inlineStr">
+      <c r="W132" s="12" t="n"/>
+      <c r="X132" s="12" t="inlineStr">
         <is>
           <t>치명타 확률 10%</t>
         </is>
       </c>
-      <c r="V132" s="12" t="n"/>
+      <c r="Y132" s="12" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="12" t="n">
@@ -10811,23 +11526,28 @@
         <v>1</v>
       </c>
       <c r="O133" s="12" t="n"/>
-      <c r="P133" s="12" t="n"/>
+      <c r="P133" s="12" t="n">
+        <v>26000000</v>
+      </c>
       <c r="Q133" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R133" s="12" t="n">
-        <v>3333</v>
-      </c>
+      <c r="R133" s="12" t="n"/>
       <c r="S133" s="12" t="n"/>
       <c r="T133" s="12" t="n"/>
-      <c r="U133" s="12" t="inlineStr">
+      <c r="U133" s="12" t="n">
+        <v>3333</v>
+      </c>
+      <c r="V133" s="12" t="n"/>
+      <c r="W133" s="12" t="n"/>
+      <c r="X133" s="12" t="inlineStr">
         <is>
           <t>분신 바 +1 (1 → 2)</t>
         </is>
       </c>
-      <c r="V133" s="12" t="n"/>
+      <c r="Y133" s="12" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="12" t="n">
@@ -10883,27 +11603,32 @@
         <v>1</v>
       </c>
       <c r="O134" s="12" t="n"/>
-      <c r="P134" s="12" t="n"/>
+      <c r="P134" s="12" t="n">
+        <v>26000000</v>
+      </c>
       <c r="Q134" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R134" s="12" t="n">
+      <c r="R134" s="12" t="n"/>
+      <c r="S134" s="12" t="n"/>
+      <c r="T134" s="12" t="n"/>
+      <c r="U134" s="12" t="n">
         <v>3335</v>
       </c>
-      <c r="S134" s="12" t="inlineStr">
+      <c r="V134" s="12" t="inlineStr">
         <is>
           <t>3326</t>
         </is>
       </c>
-      <c r="T134" s="12" t="n"/>
-      <c r="U134" s="12" t="inlineStr">
+      <c r="W134" s="12" t="n"/>
+      <c r="X134" s="12" t="inlineStr">
         <is>
           <t>회전 꼬마 수확기 +1 (2 → 3)</t>
         </is>
       </c>
-      <c r="V134" s="12" t="n"/>
+      <c r="Y134" s="12" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="12" t="n">
@@ -10959,27 +11684,32 @@
         <v>0.05</v>
       </c>
       <c r="O135" s="12" t="n"/>
-      <c r="P135" s="12" t="n"/>
+      <c r="P135" s="12" t="n">
+        <v>26000000</v>
+      </c>
       <c r="Q135" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R135" s="12" t="n">
+      <c r="R135" s="12" t="n"/>
+      <c r="S135" s="12" t="n"/>
+      <c r="T135" s="12" t="n"/>
+      <c r="U135" s="12" t="n">
         <v>3335</v>
       </c>
-      <c r="S135" s="12" t="inlineStr">
+      <c r="V135" s="12" t="inlineStr">
         <is>
           <t>3337</t>
         </is>
       </c>
-      <c r="T135" s="12" t="n"/>
-      <c r="U135" s="12" t="inlineStr">
+      <c r="W135" s="12" t="n"/>
+      <c r="X135" s="12" t="inlineStr">
         <is>
           <t>회전 꼬마 수확기 공격력 15%</t>
         </is>
       </c>
-      <c r="V135" s="12" t="n"/>
+      <c r="Y135" s="12" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="12" t="n">
@@ -11035,27 +11765,32 @@
         <v>0.2</v>
       </c>
       <c r="O136" s="12" t="n"/>
-      <c r="P136" s="12" t="n"/>
+      <c r="P136" s="12" t="n">
+        <v>47000000</v>
+      </c>
       <c r="Q136" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R136" s="12" t="n">
+      <c r="R136" s="12" t="n"/>
+      <c r="S136" s="12" t="n"/>
+      <c r="T136" s="12" t="n"/>
+      <c r="U136" s="12" t="n">
         <v>3337</v>
       </c>
-      <c r="S136" s="12" t="inlineStr">
+      <c r="V136" s="12" t="inlineStr">
         <is>
           <t>3331</t>
         </is>
       </c>
-      <c r="T136" s="12" t="n"/>
-      <c r="U136" s="12" t="inlineStr">
+      <c r="W136" s="12" t="n"/>
+      <c r="X136" s="12" t="inlineStr">
         <is>
           <t>치명타 피해 120%</t>
         </is>
       </c>
-      <c r="V136" s="12" t="inlineStr">
+      <c r="Y136" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +20%</t>
         </is>
@@ -11115,27 +11850,32 @@
         <v>0.3</v>
       </c>
       <c r="O137" s="12" t="n"/>
-      <c r="P137" s="12" t="n"/>
+      <c r="P137" s="12" t="n">
+        <v>65000000</v>
+      </c>
       <c r="Q137" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R137" s="12" t="n">
+      <c r="R137" s="12" t="n"/>
+      <c r="S137" s="12" t="n"/>
+      <c r="T137" s="12" t="n"/>
+      <c r="U137" s="12" t="n">
         <v>3342</v>
       </c>
-      <c r="S137" s="12" t="inlineStr">
+      <c r="V137" s="12" t="inlineStr">
         <is>
           <t>3346</t>
         </is>
       </c>
-      <c r="T137" s="12" t="n"/>
-      <c r="U137" s="12" t="inlineStr">
+      <c r="W137" s="12" t="n"/>
+      <c r="X137" s="12" t="inlineStr">
         <is>
           <t>치명타 피해 150%</t>
         </is>
       </c>
-      <c r="V137" s="12" t="inlineStr">
+      <c r="Y137" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +30%</t>
         </is>
@@ -11195,27 +11935,32 @@
         <v>3</v>
       </c>
       <c r="O138" s="12" t="n"/>
-      <c r="P138" s="12" t="n"/>
+      <c r="P138" s="12" t="n">
+        <v>51000000</v>
+      </c>
       <c r="Q138" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="R138" s="12" t="n">
+      <c r="R138" s="12" t="n"/>
+      <c r="S138" s="12" t="n"/>
+      <c r="T138" s="12" t="n"/>
+      <c r="U138" s="12" t="n">
         <v>3343</v>
       </c>
-      <c r="S138" s="12" t="inlineStr">
+      <c r="V138" s="12" t="inlineStr">
         <is>
           <t>3334</t>
         </is>
       </c>
-      <c r="T138" s="12" t="n"/>
-      <c r="U138" s="12" t="inlineStr">
+      <c r="W138" s="12" t="n"/>
+      <c r="X138" s="12" t="inlineStr">
         <is>
           <t>지속 시간 +3초 (27 → 30)</t>
         </is>
       </c>
-      <c r="V138" s="12" t="n"/>
+      <c r="Y138" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/Data/Tables/Skill.xlsx
+++ b/Assets/Data/Tables/Skill.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y138"/>
+  <dimension ref="A1:Z138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -523,15 +523,16 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="7" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
     <col width="11" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -592,70 +593,75 @@
       </c>
       <c r="L1" s="5" t="inlineStr">
         <is>
+          <t>tier</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
           <t>ability</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>abilityBase</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>abilityValue</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>param</t>
         </is>
       </c>
-      <c r="P1" s="5" t="inlineStr">
+      <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>unlockPrice</t>
         </is>
       </c>
-      <c r="Q1" s="5" t="inlineStr">
+      <c r="R1" s="5" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="S1" s="5" t="inlineStr">
         <is>
           <t>levelPrice</t>
         </is>
       </c>
-      <c r="S1" s="5" t="inlineStr">
+      <c r="T1" s="5" t="inlineStr">
         <is>
           <t>levelCurrency</t>
         </is>
       </c>
-      <c r="T1" s="5" t="inlineStr">
+      <c r="U1" s="5" t="inlineStr">
         <is>
           <t>priceGrowth</t>
         </is>
       </c>
-      <c r="U1" s="5" t="inlineStr">
+      <c r="V1" s="5" t="inlineStr">
         <is>
           <t>link</t>
         </is>
       </c>
-      <c r="V1" s="5" t="inlineStr">
+      <c r="W1" s="5" t="inlineStr">
         <is>
           <t>requires</t>
         </is>
       </c>
-      <c r="W1" s="5" t="inlineStr">
+      <c r="X1" s="5" t="inlineStr">
         <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="X1" s="5" t="inlineStr">
+      <c r="Y1" s="5" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="Y1" s="6" t="inlineStr">
+      <c r="Z1" s="6" t="inlineStr">
         <is>
           <t>#memo</t>
         </is>
@@ -719,70 +725,75 @@
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="P2" s="7" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="Q2" s="7" t="inlineStr">
+      <c r="R2" s="7" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="R2" s="7" t="inlineStr">
+      <c r="S2" s="7" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
+      <c r="T2" s="7" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="T2" s="7" t="inlineStr">
+      <c r="U2" s="7" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="U2" s="7" t="inlineStr">
+      <c r="V2" s="7" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="V2" s="7" t="inlineStr">
+      <c r="W2" s="7" t="inlineStr">
         <is>
           <t>int[]</t>
         </is>
       </c>
-      <c r="W2" s="7" t="inlineStr">
+      <c r="X2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="X2" s="7" t="inlineStr">
+      <c r="Y2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="Y2" s="7" t="n"/>
+      <c r="Z2" s="7" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
@@ -842,70 +853,75 @@
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
+          <t>티어 (1 = 시작 스킬, 선으로 이어진 이전 노드에서 한 칸 멀어질 때마다 +1). 노드 배치용</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
           <t>능력 종류 키 (효과 코드가 찾는 값)</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="N3" s="8" t="inlineStr">
         <is>
           <t>배웠으면 한 번 더하는 값</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="O3" s="8" t="inlineStr">
         <is>
           <t>레벨당 더하는 값 (비율은 0.1 = 10%)</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="P3" s="8" t="inlineStr">
         <is>
           <t>레벨과 무관한 고정 수치 (해석은 ability마다)</t>
         </is>
       </c>
-      <c r="P3" s="8" t="inlineStr">
+      <c r="Q3" s="8" t="inlineStr">
         <is>
           <t>첫 레벨 가격</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="R3" s="8" t="inlineStr">
         <is>
           <t>첫 레벨 재화 (Gold / Mycelite)</t>
         </is>
       </c>
-      <c r="R3" s="8" t="inlineStr">
+      <c r="S3" s="8" t="inlineStr">
         <is>
           <t>2레벨부터의 첫 가격. 비우면 unlockPrice × priceGrowth^(레벨-1)을 같은 재화로</t>
         </is>
       </c>
-      <c r="S3" s="8" t="inlineStr">
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>2레벨부터의 재화 (levelPrice가 있을 때만)</t>
         </is>
       </c>
-      <c r="T3" s="8" t="inlineStr">
+      <c r="U3" s="8" t="inlineStr">
         <is>
           <t>레벨마다 가격 배율 (비우면 1). 노드 안 마지막/첫 ≤ ×4</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
+      <c r="V3" s="8" t="inlineStr">
         <is>
           <t>연결 노드 index. 트리에 선으로 그리고, 1레벨 이상 배우면 열린다</t>
         </is>
       </c>
-      <c r="V3" s="8" t="inlineStr">
+      <c r="W3" s="8" t="inlineStr">
         <is>
           <t>이전 레벨 노드 index (쉼표 구분). 최대 레벨까지 배워야 열린다</t>
         </is>
       </c>
-      <c r="W3" s="8" t="inlineStr">
+      <c r="X3" s="8" t="inlineStr">
         <is>
           <t>아이콘 경로 (Resources 기준)</t>
         </is>
       </c>
-      <c r="X3" s="8" t="inlineStr">
+      <c r="Y3" s="8" t="inlineStr">
         <is>
           <t>인게임 설명</t>
         </is>
       </c>
-      <c r="Y3" s="8" t="inlineStr">
+      <c r="Z3" s="8" t="inlineStr">
         <is>
           <t>기획 메모 (게임에서 읽지 않음)</t>
         </is>
@@ -955,46 +971,49 @@
       <c r="K4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="L4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="9" t="inlineStr">
         <is>
           <t>start_attack_buff</t>
         </is>
       </c>
-      <c r="M4" s="9" t="n"/>
-      <c r="N4" s="9" t="n">
+      <c r="N4" s="9" t="n"/>
+      <c r="O4" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="O4" s="9" t="n">
+      <c r="P4" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="P4" s="9" t="n">
+      <c r="Q4" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="Q4" s="9" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R4" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" s="9" t="inlineStr">
+      <c r="R4" s="9" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="S4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="9" t="inlineStr">
         <is>
           <t>Mycelite</t>
         </is>
       </c>
-      <c r="T4" s="9" t="n">
+      <c r="U4" s="9" t="n">
         <v>1.17</v>
       </c>
-      <c r="U4" s="9" t="n"/>
       <c r="V4" s="9" t="n"/>
       <c r="W4" s="9" t="n"/>
-      <c r="X4" s="9" t="inlineStr">
+      <c r="X4" s="9" t="n"/>
+      <c r="Y4" s="9" t="inlineStr">
         <is>
           <t>공격력 +2 (3초) 버프 / Lv</t>
         </is>
       </c>
-      <c r="Y4" s="9" t="inlineStr">
+      <c r="Z4" s="9" t="inlineStr">
         <is>
           <t>첫 레벨업은 골드, 이후 균사석 — currency 한 칸이라 가격 구조 정해지면 열 추가 필요. param = 버프 지속(초)</t>
         </is>
@@ -1044,46 +1063,49 @@
       <c r="K5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="L5" s="10" t="inlineStr">
+      <c r="L5" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>score_rate</t>
         </is>
       </c>
-      <c r="M5" s="10" t="n"/>
-      <c r="N5" s="10" t="n">
+      <c r="N5" s="10" t="n"/>
+      <c r="O5" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="O5" s="10" t="n"/>
-      <c r="P5" s="10" t="n">
+      <c r="P5" s="10" t="n"/>
+      <c r="Q5" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="Q5" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R5" s="10" t="n">
+      <c r="R5" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="n">
         <v>114</v>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="T5" s="10" t="n">
+      <c r="T5" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="U5" s="10" t="n">
         <v>1.14</v>
       </c>
-      <c r="U5" s="10" t="n">
+      <c r="V5" s="10" t="n">
         <v>3001</v>
       </c>
-      <c r="V5" s="10" t="n"/>
       <c r="W5" s="10" t="n"/>
-      <c r="X5" s="10" t="inlineStr">
+      <c r="X5" s="10" t="n"/>
+      <c r="Y5" s="10" t="inlineStr">
         <is>
           <t>획득 점수 +10% / Lv</t>
         </is>
       </c>
-      <c r="Y5" s="10" t="n"/>
+      <c r="Z5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="n">
@@ -1129,38 +1151,41 @@
       <c r="K6" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="L6" s="10" t="inlineStr">
+      <c r="L6" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>gold_conversion</t>
         </is>
       </c>
-      <c r="M6" s="10" t="n"/>
-      <c r="N6" s="10" t="n">
+      <c r="N6" s="10" t="n"/>
+      <c r="O6" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="O6" s="10" t="n"/>
-      <c r="P6" s="10" t="n">
+      <c r="P6" s="10" t="n"/>
+      <c r="Q6" s="10" t="n">
         <v>280</v>
       </c>
-      <c r="Q6" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R6" s="10" t="n"/>
+      <c r="R6" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S6" s="10" t="n"/>
       <c r="T6" s="10" t="n"/>
-      <c r="U6" s="10" t="n">
+      <c r="U6" s="10" t="n"/>
+      <c r="V6" s="10" t="n">
         <v>3101</v>
       </c>
-      <c r="V6" s="10" t="n"/>
       <c r="W6" s="10" t="n"/>
-      <c r="X6" s="10" t="inlineStr">
+      <c r="X6" s="10" t="n"/>
+      <c r="Y6" s="10" t="inlineStr">
         <is>
           <t>점수 골드 전환율 +10%</t>
         </is>
       </c>
-      <c r="Y6" s="10" t="n"/>
+      <c r="Z6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="n">
@@ -1206,38 +1231,41 @@
       <c r="K7" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="L7" s="10" t="inlineStr">
+      <c r="L7" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
         <is>
           <t>colony_count</t>
         </is>
       </c>
-      <c r="M7" s="10" t="n"/>
-      <c r="N7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" s="10" t="n"/>
-      <c r="P7" s="10" t="n">
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="10" t="n">
         <v>450</v>
       </c>
-      <c r="Q7" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R7" s="10" t="n"/>
+      <c r="R7" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S7" s="10" t="n"/>
       <c r="T7" s="10" t="n"/>
-      <c r="U7" s="10" t="n">
+      <c r="U7" s="10" t="n"/>
+      <c r="V7" s="10" t="n">
         <v>3101</v>
       </c>
-      <c r="V7" s="10" t="n"/>
       <c r="W7" s="10" t="n"/>
-      <c r="X7" s="10" t="inlineStr">
+      <c r="X7" s="10" t="n"/>
+      <c r="Y7" s="10" t="inlineStr">
         <is>
           <t>군락지 수 +1 (3 → 4)</t>
         </is>
       </c>
-      <c r="Y7" s="10" t="n"/>
+      <c r="Z7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="n">
@@ -1283,38 +1311,41 @@
       <c r="K8" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="L8" s="10" t="inlineStr">
+      <c r="L8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
         <is>
           <t>colony_single_mushroom</t>
         </is>
       </c>
-      <c r="M8" s="10" t="n"/>
-      <c r="N8" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" s="10" t="n"/>
-      <c r="P8" s="10" t="n">
+      <c r="N8" s="10" t="n"/>
+      <c r="O8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="10" t="n"/>
+      <c r="Q8" s="10" t="n">
         <v>1400</v>
       </c>
-      <c r="Q8" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R8" s="10" t="n"/>
+      <c r="R8" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S8" s="10" t="n"/>
       <c r="T8" s="10" t="n"/>
-      <c r="U8" s="10" t="n">
+      <c r="U8" s="10" t="n"/>
+      <c r="V8" s="10" t="n">
         <v>3103</v>
       </c>
-      <c r="V8" s="10" t="n"/>
       <c r="W8" s="10" t="n"/>
-      <c r="X8" s="10" t="inlineStr">
+      <c r="X8" s="10" t="n"/>
+      <c r="Y8" s="10" t="inlineStr">
         <is>
           <t>군락지 주변 단일 버섯 +1 (3 → 4)</t>
         </is>
       </c>
-      <c r="Y8" s="10" t="n"/>
+      <c r="Z8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="n">
@@ -1360,38 +1391,41 @@
       <c r="K9" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="L9" s="10" t="inlineStr">
+      <c r="L9" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
         <is>
           <t>normal_yield</t>
         </is>
       </c>
-      <c r="M9" s="10" t="n"/>
-      <c r="N9" s="10" t="n">
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="O9" s="10" t="n"/>
-      <c r="P9" s="10" t="n">
+      <c r="P9" s="10" t="n"/>
+      <c r="Q9" s="10" t="n">
         <v>1100</v>
       </c>
-      <c r="Q9" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R9" s="10" t="n"/>
+      <c r="R9" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S9" s="10" t="n"/>
       <c r="T9" s="10" t="n"/>
-      <c r="U9" s="10" t="n">
+      <c r="U9" s="10" t="n"/>
+      <c r="V9" s="10" t="n">
         <v>3102</v>
       </c>
-      <c r="V9" s="10" t="n"/>
       <c r="W9" s="10" t="n"/>
-      <c r="X9" s="10" t="inlineStr">
+      <c r="X9" s="10" t="n"/>
+      <c r="Y9" s="10" t="inlineStr">
         <is>
           <t>일반 버섯 수확량 +5%</t>
         </is>
       </c>
-      <c r="Y9" s="10" t="n"/>
+      <c r="Z9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n">
@@ -1437,42 +1471,45 @@
       <c r="K10" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="L10" s="10" t="inlineStr">
+      <c r="L10" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
         <is>
           <t>epic_spawn</t>
         </is>
-      </c>
-      <c r="M10" s="10" t="n">
-        <v>0.05</v>
       </c>
       <c r="N10" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="O10" s="10" t="n"/>
-      <c r="P10" s="10" t="n">
+      <c r="O10" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P10" s="10" t="n"/>
+      <c r="Q10" s="10" t="n">
         <v>2100</v>
       </c>
-      <c r="Q10" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R10" s="10" t="n"/>
+      <c r="R10" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S10" s="10" t="n"/>
-      <c r="T10" s="10" t="n">
+      <c r="T10" s="10" t="n"/>
+      <c r="U10" s="10" t="n">
         <v>1.047</v>
       </c>
-      <c r="U10" s="10" t="n">
+      <c r="V10" s="10" t="n">
         <v>3103</v>
       </c>
-      <c r="V10" s="10" t="n"/>
       <c r="W10" s="10" t="n"/>
-      <c r="X10" s="10" t="inlineStr">
+      <c r="X10" s="10" t="n"/>
+      <c r="Y10" s="10" t="inlineStr">
         <is>
           <t>에픽 버섯 스폰율 +10% / +15% / +20%</t>
         </is>
       </c>
-      <c r="Y10" s="10" t="inlineStr">
+      <c r="Z10" s="10" t="inlineStr">
         <is>
           <t>Lv.1 10, Lv.2 15, Lv.3 20 → base 5% + 5%/Lv</t>
         </is>
@@ -1522,42 +1559,45 @@
       <c r="K11" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="L11" s="10" t="inlineStr">
+      <c r="L11" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
         <is>
           <t>normal_yield</t>
         </is>
       </c>
-      <c r="M11" s="10" t="n"/>
-      <c r="N11" s="10" t="n">
+      <c r="N11" s="10" t="n"/>
+      <c r="O11" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="O11" s="10" t="n"/>
-      <c r="P11" s="10" t="n">
+      <c r="P11" s="10" t="n"/>
+      <c r="Q11" s="10" t="n">
         <v>1800</v>
       </c>
-      <c r="Q11" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R11" s="10" t="n"/>
+      <c r="R11" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S11" s="10" t="n"/>
       <c r="T11" s="10" t="n"/>
-      <c r="U11" s="10" t="n">
+      <c r="U11" s="10" t="n"/>
+      <c r="V11" s="10" t="n">
         <v>3102</v>
       </c>
-      <c r="V11" s="10" t="inlineStr">
+      <c r="W11" s="10" t="inlineStr">
         <is>
           <t>3105</t>
         </is>
       </c>
-      <c r="W11" s="10" t="n"/>
-      <c r="X11" s="10" t="inlineStr">
+      <c r="X11" s="10" t="n"/>
+      <c r="Y11" s="10" t="inlineStr">
         <is>
           <t>일반 버섯 수확량 +10%</t>
         </is>
       </c>
-      <c r="Y11" s="10" t="inlineStr">
+      <c r="Z11" s="10" t="inlineStr">
         <is>
           <t>원문 % = 누적값으로 보고 차이(+5%)만 더함</t>
         </is>
@@ -1607,42 +1647,45 @@
       <c r="K12" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="L12" s="10" t="inlineStr">
+      <c r="L12" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
         <is>
           <t>gold_conversion</t>
         </is>
       </c>
-      <c r="M12" s="10" t="n"/>
-      <c r="N12" s="10" t="n">
+      <c r="N12" s="10" t="n"/>
+      <c r="O12" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="O12" s="10" t="n"/>
-      <c r="P12" s="10" t="n">
+      <c r="P12" s="10" t="n"/>
+      <c r="Q12" s="10" t="n">
         <v>9800</v>
       </c>
-      <c r="Q12" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R12" s="10" t="n"/>
+      <c r="R12" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S12" s="10" t="n"/>
       <c r="T12" s="10" t="n"/>
-      <c r="U12" s="10" t="n">
+      <c r="U12" s="10" t="n"/>
+      <c r="V12" s="10" t="n">
         <v>3105</v>
       </c>
-      <c r="V12" s="10" t="inlineStr">
+      <c r="W12" s="10" t="inlineStr">
         <is>
           <t>3102</t>
         </is>
       </c>
-      <c r="W12" s="10" t="n"/>
-      <c r="X12" s="10" t="inlineStr">
+      <c r="X12" s="10" t="n"/>
+      <c r="Y12" s="10" t="inlineStr">
         <is>
           <t>점수 골드 전환율 +15%</t>
         </is>
       </c>
-      <c r="Y12" s="10" t="inlineStr">
+      <c r="Z12" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -1692,38 +1735,41 @@
       <c r="K13" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="L13" s="10" t="inlineStr">
+      <c r="L13" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
         <is>
           <t>colony_respawn</t>
         </is>
       </c>
-      <c r="M13" s="10" t="n"/>
-      <c r="N13" s="10" t="n">
+      <c r="N13" s="10" t="n"/>
+      <c r="O13" s="10" t="n">
         <v>-1</v>
       </c>
-      <c r="O13" s="10" t="n"/>
-      <c r="P13" s="10" t="n">
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="10" t="n">
         <v>9800</v>
       </c>
-      <c r="Q13" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R13" s="10" t="n"/>
+      <c r="R13" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S13" s="10" t="n"/>
       <c r="T13" s="10" t="n"/>
-      <c r="U13" s="10" t="n">
+      <c r="U13" s="10" t="n"/>
+      <c r="V13" s="10" t="n">
         <v>3104</v>
       </c>
-      <c r="V13" s="10" t="n"/>
       <c r="W13" s="10" t="n"/>
-      <c r="X13" s="10" t="inlineStr">
+      <c r="X13" s="10" t="n"/>
+      <c r="Y13" s="10" t="inlineStr">
         <is>
           <t>군락지 리스폰 −1초 (7 → 6)</t>
         </is>
       </c>
-      <c r="Y13" s="10" t="n"/>
+      <c r="Z13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n">
@@ -1769,42 +1815,45 @@
       <c r="K14" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="L14" s="10" t="inlineStr">
+      <c r="L14" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>gold_conversion</t>
         </is>
       </c>
-      <c r="M14" s="10" t="n"/>
-      <c r="N14" s="10" t="n">
+      <c r="N14" s="10" t="n"/>
+      <c r="O14" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="O14" s="10" t="n"/>
-      <c r="P14" s="10" t="n">
+      <c r="P14" s="10" t="n"/>
+      <c r="Q14" s="10" t="n">
         <v>21000</v>
       </c>
-      <c r="Q14" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R14" s="10" t="n"/>
+      <c r="R14" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S14" s="10" t="n"/>
       <c r="T14" s="10" t="n"/>
-      <c r="U14" s="10" t="n">
+      <c r="U14" s="10" t="n"/>
+      <c r="V14" s="10" t="n">
         <v>3107</v>
       </c>
-      <c r="V14" s="10" t="inlineStr">
+      <c r="W14" s="10" t="inlineStr">
         <is>
           <t>3108</t>
         </is>
       </c>
-      <c r="W14" s="10" t="n"/>
-      <c r="X14" s="10" t="inlineStr">
+      <c r="X14" s="10" t="n"/>
+      <c r="Y14" s="10" t="inlineStr">
         <is>
           <t>점수 골드 전환율 +20%</t>
         </is>
       </c>
-      <c r="Y14" s="10" t="inlineStr">
+      <c r="Z14" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -1854,42 +1903,45 @@
       <c r="K15" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="L15" s="10" t="inlineStr">
+      <c r="L15" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>colony_respawn</t>
         </is>
       </c>
-      <c r="M15" s="10" t="n"/>
-      <c r="N15" s="10" t="n">
+      <c r="N15" s="10" t="n"/>
+      <c r="O15" s="10" t="n">
         <v>-1</v>
       </c>
-      <c r="O15" s="10" t="n"/>
-      <c r="P15" s="10" t="n">
+      <c r="P15" s="10" t="n"/>
+      <c r="Q15" s="10" t="n">
         <v>36000</v>
       </c>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R15" s="10" t="n"/>
+      <c r="R15" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S15" s="10" t="n"/>
       <c r="T15" s="10" t="n"/>
-      <c r="U15" s="10" t="n">
+      <c r="U15" s="10" t="n"/>
+      <c r="V15" s="10" t="n">
         <v>3106</v>
       </c>
-      <c r="V15" s="10" t="inlineStr">
+      <c r="W15" s="10" t="inlineStr">
         <is>
           <t>3109</t>
         </is>
       </c>
-      <c r="W15" s="10" t="n"/>
-      <c r="X15" s="10" t="inlineStr">
+      <c r="X15" s="10" t="n"/>
+      <c r="Y15" s="10" t="inlineStr">
         <is>
           <t>군락지 리스폰 −1초 (6 → 5)</t>
         </is>
       </c>
-      <c r="Y15" s="10" t="n"/>
+      <c r="Z15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
@@ -1935,38 +1987,41 @@
       <c r="K16" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="L16" s="10" t="inlineStr">
+      <c r="L16" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
         <is>
           <t>triple_score_chance</t>
         </is>
       </c>
-      <c r="M16" s="10" t="n"/>
-      <c r="N16" s="10" t="n">
+      <c r="N16" s="10" t="n"/>
+      <c r="O16" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="O16" s="10" t="n"/>
-      <c r="P16" s="10" t="n">
+      <c r="P16" s="10" t="n"/>
+      <c r="Q16" s="10" t="n">
         <v>17000</v>
       </c>
-      <c r="Q16" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R16" s="10" t="n"/>
+      <c r="R16" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S16" s="10" t="n"/>
       <c r="T16" s="10" t="n"/>
-      <c r="U16" s="10" t="n">
+      <c r="U16" s="10" t="n"/>
+      <c r="V16" s="10" t="n">
         <v>3108</v>
       </c>
-      <c r="V16" s="10" t="n"/>
       <c r="W16" s="10" t="n"/>
-      <c r="X16" s="10" t="inlineStr">
+      <c r="X16" s="10" t="n"/>
+      <c r="Y16" s="10" t="inlineStr">
         <is>
           <t>점수 3배 확률 +3%</t>
         </is>
       </c>
-      <c r="Y16" s="10" t="n"/>
+      <c r="Z16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n">
@@ -2012,42 +2067,45 @@
       <c r="K17" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="L17" s="10" t="inlineStr">
+      <c r="L17" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
         <is>
           <t>colony_count</t>
         </is>
       </c>
-      <c r="M17" s="10" t="n"/>
-      <c r="N17" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" s="10" t="n"/>
-      <c r="P17" s="10" t="n">
+      <c r="N17" s="10" t="n"/>
+      <c r="O17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" s="10" t="n"/>
+      <c r="Q17" s="10" t="n">
         <v>36000</v>
       </c>
-      <c r="Q17" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R17" s="10" t="n"/>
+      <c r="R17" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S17" s="10" t="n"/>
       <c r="T17" s="10" t="n"/>
-      <c r="U17" s="10" t="n">
+      <c r="U17" s="10" t="n"/>
+      <c r="V17" s="10" t="n">
         <v>3109</v>
       </c>
-      <c r="V17" s="10" t="inlineStr">
+      <c r="W17" s="10" t="inlineStr">
         <is>
           <t>3103</t>
         </is>
       </c>
-      <c r="W17" s="10" t="n"/>
-      <c r="X17" s="10" t="inlineStr">
+      <c r="X17" s="10" t="n"/>
+      <c r="Y17" s="10" t="inlineStr">
         <is>
           <t>군락지 수 +1 (4 → 5)</t>
         </is>
       </c>
-      <c r="Y17" s="10" t="n"/>
+      <c r="Z17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
@@ -2093,38 +2151,41 @@
       <c r="K18" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="10" t="inlineStr">
+      <c r="L18" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
         <is>
           <t>epic_yield</t>
         </is>
       </c>
-      <c r="M18" s="10" t="n"/>
-      <c r="N18" s="10" t="n">
+      <c r="N18" s="10" t="n"/>
+      <c r="O18" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="O18" s="10" t="n"/>
-      <c r="P18" s="10" t="n">
+      <c r="P18" s="10" t="n"/>
+      <c r="Q18" s="10" t="n">
         <v>100000</v>
       </c>
-      <c r="Q18" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R18" s="10" t="n"/>
+      <c r="R18" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S18" s="10" t="n"/>
       <c r="T18" s="10" t="n"/>
-      <c r="U18" s="10" t="n">
+      <c r="U18" s="10" t="n"/>
+      <c r="V18" s="10" t="n">
         <v>3110</v>
       </c>
-      <c r="V18" s="10" t="n"/>
       <c r="W18" s="10" t="n"/>
-      <c r="X18" s="10" t="inlineStr">
+      <c r="X18" s="10" t="n"/>
+      <c r="Y18" s="10" t="inlineStr">
         <is>
           <t>에픽 버섯 수확량 +5%</t>
         </is>
       </c>
-      <c r="Y18" s="10" t="n"/>
+      <c r="Z18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n">
@@ -2170,42 +2231,45 @@
       <c r="K19" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="L19" s="10" t="inlineStr">
+      <c r="L19" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M19" s="10" t="inlineStr">
         <is>
           <t>colony_single_mushroom</t>
         </is>
       </c>
-      <c r="M19" s="10" t="n"/>
-      <c r="N19" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" s="10" t="n"/>
-      <c r="P19" s="10" t="n">
+      <c r="N19" s="10" t="n"/>
+      <c r="O19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="10" t="n"/>
+      <c r="Q19" s="10" t="n">
         <v>150000</v>
       </c>
-      <c r="Q19" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R19" s="10" t="n"/>
+      <c r="R19" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S19" s="10" t="n"/>
       <c r="T19" s="10" t="n"/>
-      <c r="U19" s="10" t="n">
+      <c r="U19" s="10" t="n"/>
+      <c r="V19" s="10" t="n">
         <v>3109</v>
       </c>
-      <c r="V19" s="10" t="inlineStr">
+      <c r="W19" s="10" t="inlineStr">
         <is>
           <t>3104</t>
         </is>
       </c>
-      <c r="W19" s="10" t="n"/>
-      <c r="X19" s="10" t="inlineStr">
+      <c r="X19" s="10" t="n"/>
+      <c r="Y19" s="10" t="inlineStr">
         <is>
           <t>군락지 주변 단일 버섯 +1 (4 → 5)</t>
         </is>
       </c>
-      <c r="Y19" s="10" t="n"/>
+      <c r="Z19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
@@ -2251,42 +2315,45 @@
       <c r="K20" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="L20" s="10" t="inlineStr">
+      <c r="L20" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
         <is>
           <t>normal_yield</t>
         </is>
       </c>
-      <c r="M20" s="10" t="n"/>
-      <c r="N20" s="10" t="n">
+      <c r="N20" s="10" t="n"/>
+      <c r="O20" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="O20" s="10" t="n"/>
-      <c r="P20" s="10" t="n">
+      <c r="P20" s="10" t="n"/>
+      <c r="Q20" s="10" t="n">
         <v>100000</v>
       </c>
-      <c r="Q20" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R20" s="10" t="n"/>
+      <c r="R20" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S20" s="10" t="n"/>
       <c r="T20" s="10" t="n"/>
-      <c r="U20" s="10" t="n">
+      <c r="U20" s="10" t="n"/>
+      <c r="V20" s="10" t="n">
         <v>3108</v>
       </c>
-      <c r="V20" s="10" t="inlineStr">
+      <c r="W20" s="10" t="inlineStr">
         <is>
           <t>3107</t>
         </is>
       </c>
-      <c r="W20" s="10" t="n"/>
-      <c r="X20" s="10" t="inlineStr">
+      <c r="X20" s="10" t="n"/>
+      <c r="Y20" s="10" t="inlineStr">
         <is>
           <t>일반 버섯 수확량 +15%</t>
         </is>
       </c>
-      <c r="Y20" s="10" t="inlineStr">
+      <c r="Z20" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -2336,42 +2403,45 @@
       <c r="K21" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="L21" s="10" t="inlineStr">
+      <c r="L21" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
         <is>
           <t>colony_count</t>
         </is>
       </c>
-      <c r="M21" s="10" t="n"/>
-      <c r="N21" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" s="10" t="n"/>
-      <c r="P21" s="10" t="n">
+      <c r="N21" s="10" t="n"/>
+      <c r="O21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="10" t="n"/>
+      <c r="Q21" s="10" t="n">
         <v>150000</v>
       </c>
-      <c r="Q21" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R21" s="10" t="n"/>
+      <c r="R21" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S21" s="10" t="n"/>
       <c r="T21" s="10" t="n"/>
-      <c r="U21" s="10" t="n">
+      <c r="U21" s="10" t="n"/>
+      <c r="V21" s="10" t="n">
         <v>3111</v>
       </c>
-      <c r="V21" s="10" t="inlineStr">
+      <c r="W21" s="10" t="inlineStr">
         <is>
           <t>3113</t>
         </is>
       </c>
-      <c r="W21" s="10" t="n"/>
-      <c r="X21" s="10" t="inlineStr">
+      <c r="X21" s="10" t="n"/>
+      <c r="Y21" s="10" t="inlineStr">
         <is>
           <t>군락지 수 +1 (5 → 6)</t>
         </is>
       </c>
-      <c r="Y21" s="10" t="n"/>
+      <c r="Z21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
@@ -2417,42 +2487,45 @@
       <c r="K22" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="L22" s="10" t="inlineStr">
+      <c r="L22" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M22" s="10" t="inlineStr">
         <is>
           <t>triple_score_chance</t>
         </is>
       </c>
-      <c r="M22" s="10" t="n"/>
-      <c r="N22" s="10" t="n">
+      <c r="N22" s="10" t="n"/>
+      <c r="O22" s="10" t="n">
         <v>0.02</v>
       </c>
-      <c r="O22" s="10" t="n"/>
-      <c r="P22" s="10" t="n">
+      <c r="P22" s="10" t="n"/>
+      <c r="Q22" s="10" t="n">
         <v>380000</v>
       </c>
-      <c r="Q22" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R22" s="10" t="n"/>
+      <c r="R22" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S22" s="10" t="n"/>
       <c r="T22" s="10" t="n"/>
-      <c r="U22" s="10" t="n">
+      <c r="U22" s="10" t="n"/>
+      <c r="V22" s="10" t="n">
         <v>3110</v>
       </c>
-      <c r="V22" s="10" t="inlineStr">
+      <c r="W22" s="10" t="inlineStr">
         <is>
           <t>3112</t>
         </is>
       </c>
-      <c r="W22" s="10" t="n"/>
-      <c r="X22" s="10" t="inlineStr">
+      <c r="X22" s="10" t="n"/>
+      <c r="Y22" s="10" t="inlineStr">
         <is>
           <t>점수 3배 확률 +5%</t>
         </is>
       </c>
-      <c r="Y22" s="10" t="inlineStr">
+      <c r="Z22" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -2502,42 +2575,45 @@
       <c r="K23" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="L23" s="10" t="inlineStr">
+      <c r="L23" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M23" s="10" t="inlineStr">
         <is>
           <t>colony_single_mushroom</t>
         </is>
       </c>
-      <c r="M23" s="10" t="n"/>
-      <c r="N23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" s="10" t="n"/>
-      <c r="P23" s="10" t="n">
+      <c r="N23" s="10" t="n"/>
+      <c r="O23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" s="10" t="n"/>
+      <c r="Q23" s="10" t="n">
         <v>390000</v>
       </c>
-      <c r="Q23" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R23" s="10" t="n"/>
+      <c r="R23" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S23" s="10" t="n"/>
       <c r="T23" s="10" t="n"/>
-      <c r="U23" s="10" t="n">
+      <c r="U23" s="10" t="n"/>
+      <c r="V23" s="10" t="n">
         <v>3111</v>
       </c>
-      <c r="V23" s="10" t="inlineStr">
+      <c r="W23" s="10" t="inlineStr">
         <is>
           <t>3115</t>
         </is>
       </c>
-      <c r="W23" s="10" t="n"/>
-      <c r="X23" s="10" t="inlineStr">
+      <c r="X23" s="10" t="n"/>
+      <c r="Y23" s="10" t="inlineStr">
         <is>
           <t>군락지 주변 단일 버섯 +1 (5 → 6)</t>
         </is>
       </c>
-      <c r="Y23" s="10" t="n"/>
+      <c r="Z23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
@@ -2583,42 +2659,45 @@
       <c r="K24" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="L24" s="10" t="inlineStr">
+      <c r="L24" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
         <is>
           <t>score_rate</t>
         </is>
       </c>
-      <c r="M24" s="10" t="n"/>
-      <c r="N24" s="10" t="n">
+      <c r="N24" s="10" t="n"/>
+      <c r="O24" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="O24" s="10" t="n"/>
-      <c r="P24" s="10" t="n">
+      <c r="P24" s="10" t="n"/>
+      <c r="Q24" s="10" t="n">
         <v>1100000</v>
       </c>
-      <c r="Q24" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R24" s="10" t="n"/>
+      <c r="R24" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S24" s="10" t="n"/>
       <c r="T24" s="10" t="n"/>
-      <c r="U24" s="10" t="n">
+      <c r="U24" s="10" t="n"/>
+      <c r="V24" s="10" t="n">
         <v>3114</v>
       </c>
-      <c r="V24" s="10" t="inlineStr">
+      <c r="W24" s="10" t="inlineStr">
         <is>
           <t>3101</t>
         </is>
       </c>
-      <c r="W24" s="10" t="n"/>
-      <c r="X24" s="10" t="inlineStr">
+      <c r="X24" s="10" t="n"/>
+      <c r="Y24" s="10" t="inlineStr">
         <is>
           <t>획득 점수 +40%</t>
         </is>
       </c>
-      <c r="Y24" s="10" t="inlineStr">
+      <c r="Z24" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%</t>
         </is>
@@ -2668,42 +2747,45 @@
       <c r="K25" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="L25" s="10" t="inlineStr">
+      <c r="L25" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
         <is>
           <t>epic_spawn</t>
         </is>
       </c>
-      <c r="M25" s="10" t="n"/>
-      <c r="N25" s="10" t="n">
+      <c r="N25" s="10" t="n"/>
+      <c r="O25" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="O25" s="10" t="n"/>
-      <c r="P25" s="10" t="n">
+      <c r="P25" s="10" t="n"/>
+      <c r="Q25" s="10" t="n">
         <v>1100000</v>
       </c>
-      <c r="Q25" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R25" s="10" t="n"/>
+      <c r="R25" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S25" s="10" t="n"/>
       <c r="T25" s="10" t="n"/>
-      <c r="U25" s="10" t="n">
+      <c r="U25" s="10" t="n"/>
+      <c r="V25" s="10" t="n">
         <v>3113</v>
       </c>
-      <c r="V25" s="10" t="inlineStr">
+      <c r="W25" s="10" t="inlineStr">
         <is>
           <t>3106</t>
         </is>
       </c>
-      <c r="W25" s="10" t="n"/>
-      <c r="X25" s="10" t="inlineStr">
+      <c r="X25" s="10" t="n"/>
+      <c r="Y25" s="10" t="inlineStr">
         <is>
           <t>에픽 버섯 스폰율 +25%</t>
         </is>
       </c>
-      <c r="Y25" s="10" t="inlineStr">
+      <c r="Z25" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -2753,38 +2835,41 @@
       <c r="K26" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="L26" s="10" t="inlineStr">
+      <c r="L26" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M26" s="10" t="inlineStr">
         <is>
           <t>gold_conversion</t>
         </is>
       </c>
-      <c r="M26" s="10" t="n"/>
-      <c r="N26" s="10" t="n">
+      <c r="N26" s="10" t="n"/>
+      <c r="O26" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="O26" s="10" t="n"/>
-      <c r="P26" s="10" t="n">
+      <c r="P26" s="10" t="n"/>
+      <c r="Q26" s="10" t="n">
         <v>1100000</v>
       </c>
-      <c r="Q26" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R26" s="10" t="n"/>
+      <c r="R26" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S26" s="10" t="n"/>
       <c r="T26" s="10" t="n"/>
-      <c r="U26" s="10" t="n">
+      <c r="U26" s="10" t="n"/>
+      <c r="V26" s="10" t="n">
         <v>3112</v>
       </c>
-      <c r="V26" s="10" t="n"/>
       <c r="W26" s="10" t="n"/>
-      <c r="X26" s="10" t="inlineStr">
+      <c r="X26" s="10" t="n"/>
+      <c r="Y26" s="10" t="inlineStr">
         <is>
           <t>점수 골드 전환율 +30%</t>
         </is>
       </c>
-      <c r="Y26" s="10" t="inlineStr">
+      <c r="Z26" s="10" t="inlineStr">
         <is>
           <t>흥정 기술의 상위. 누적값 기준 차이 +10%</t>
         </is>
@@ -2834,38 +2919,41 @@
       <c r="K27" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="L27" s="10" t="inlineStr">
+      <c r="L27" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M27" s="10" t="inlineStr">
         <is>
           <t>colony_count</t>
         </is>
       </c>
-      <c r="M27" s="10" t="n"/>
-      <c r="N27" s="10" t="n">
+      <c r="N27" s="10" t="n"/>
+      <c r="O27" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="O27" s="10" t="n"/>
-      <c r="P27" s="10" t="n">
+      <c r="P27" s="10" t="n"/>
+      <c r="Q27" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q27" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R27" s="10" t="n"/>
+      <c r="R27" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S27" s="10" t="n"/>
       <c r="T27" s="10" t="n"/>
-      <c r="U27" s="10" t="n">
+      <c r="U27" s="10" t="n"/>
+      <c r="V27" s="10" t="n">
         <v>3117</v>
       </c>
-      <c r="V27" s="10" t="n"/>
       <c r="W27" s="10" t="n"/>
-      <c r="X27" s="10" t="inlineStr">
+      <c r="X27" s="10" t="n"/>
+      <c r="Y27" s="10" t="inlineStr">
         <is>
           <t>군락지 수 +2 (6 → 8)</t>
         </is>
       </c>
-      <c r="Y27" s="10" t="inlineStr">
+      <c r="Z27" s="10" t="inlineStr">
         <is>
           <t>넓은 시야의 상위</t>
         </is>
@@ -2915,42 +3003,45 @@
       <c r="K28" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="L28" s="10" t="inlineStr">
+      <c r="L28" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M28" s="10" t="inlineStr">
         <is>
           <t>epic_yield</t>
         </is>
       </c>
-      <c r="M28" s="10" t="n"/>
-      <c r="N28" s="10" t="n">
+      <c r="N28" s="10" t="n"/>
+      <c r="O28" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="O28" s="10" t="n"/>
-      <c r="P28" s="10" t="n">
+      <c r="P28" s="10" t="n"/>
+      <c r="Q28" s="10" t="n">
         <v>2500000</v>
       </c>
-      <c r="Q28" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R28" s="10" t="n"/>
+      <c r="R28" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S28" s="10" t="n"/>
       <c r="T28" s="10" t="n"/>
-      <c r="U28" s="10" t="n">
+      <c r="U28" s="10" t="n"/>
+      <c r="V28" s="10" t="n">
         <v>3116</v>
       </c>
-      <c r="V28" s="10" t="inlineStr">
+      <c r="W28" s="10" t="inlineStr">
         <is>
           <t>3114</t>
         </is>
       </c>
-      <c r="W28" s="10" t="n"/>
-      <c r="X28" s="10" t="inlineStr">
+      <c r="X28" s="10" t="n"/>
+      <c r="Y28" s="10" t="inlineStr">
         <is>
           <t>에픽 버섯 수확량 +10%</t>
         </is>
       </c>
-      <c r="Y28" s="10" t="inlineStr">
+      <c r="Z28" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -3000,42 +3091,45 @@
       <c r="K29" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="L29" s="10" t="inlineStr">
+      <c r="L29" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="M29" s="10" t="inlineStr">
         <is>
           <t>triple_score_chance</t>
         </is>
       </c>
-      <c r="M29" s="10" t="n"/>
-      <c r="N29" s="10" t="n">
+      <c r="N29" s="10" t="n"/>
+      <c r="O29" s="10" t="n">
         <v>0.02</v>
       </c>
-      <c r="O29" s="10" t="n"/>
-      <c r="P29" s="10" t="n">
+      <c r="P29" s="10" t="n"/>
+      <c r="Q29" s="10" t="n">
         <v>2300000</v>
       </c>
-      <c r="Q29" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R29" s="10" t="n"/>
+      <c r="R29" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S29" s="10" t="n"/>
       <c r="T29" s="10" t="n"/>
-      <c r="U29" s="10" t="n">
+      <c r="U29" s="10" t="n"/>
+      <c r="V29" s="10" t="n">
         <v>3122</v>
       </c>
-      <c r="V29" s="10" t="inlineStr">
+      <c r="W29" s="10" t="inlineStr">
         <is>
           <t>3118</t>
         </is>
       </c>
-      <c r="W29" s="10" t="n"/>
-      <c r="X29" s="10" t="inlineStr">
+      <c r="X29" s="10" t="n"/>
+      <c r="Y29" s="10" t="inlineStr">
         <is>
           <t>점수 3배 확률 +7%</t>
         </is>
       </c>
-      <c r="Y29" s="10" t="inlineStr">
+      <c r="Z29" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -3085,42 +3179,45 @@
       <c r="K30" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="L30" s="10" t="inlineStr">
+      <c r="L30" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M30" s="10" t="inlineStr">
         <is>
           <t>colony_count</t>
         </is>
       </c>
-      <c r="M30" s="10" t="n"/>
-      <c r="N30" s="10" t="n">
+      <c r="N30" s="10" t="n"/>
+      <c r="O30" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="O30" s="10" t="n"/>
-      <c r="P30" s="10" t="n">
+      <c r="P30" s="10" t="n"/>
+      <c r="Q30" s="10" t="n">
         <v>3300000</v>
       </c>
-      <c r="Q30" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R30" s="10" t="n"/>
+      <c r="R30" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S30" s="10" t="n"/>
       <c r="T30" s="10" t="n"/>
-      <c r="U30" s="10" t="n">
+      <c r="U30" s="10" t="n"/>
+      <c r="V30" s="10" t="n">
         <v>3115</v>
       </c>
-      <c r="V30" s="10" t="inlineStr">
+      <c r="W30" s="10" t="inlineStr">
         <is>
           <t>3123</t>
         </is>
       </c>
-      <c r="W30" s="10" t="n"/>
-      <c r="X30" s="10" t="inlineStr">
+      <c r="X30" s="10" t="n"/>
+      <c r="Y30" s="10" t="inlineStr">
         <is>
           <t>군락지 수 +2 (8 → 10)</t>
         </is>
       </c>
-      <c r="Y30" s="10" t="inlineStr">
+      <c r="Z30" s="10" t="inlineStr">
         <is>
           <t>넓은 시야의 상위</t>
         </is>
@@ -3170,38 +3267,41 @@
       <c r="K31" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="L31" s="10" t="inlineStr">
+      <c r="L31" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="M31" s="10" t="inlineStr">
         <is>
           <t>unique_spawn</t>
         </is>
       </c>
-      <c r="M31" s="10" t="n"/>
-      <c r="N31" s="10" t="n">
+      <c r="N31" s="10" t="n"/>
+      <c r="O31" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="O31" s="10" t="n"/>
-      <c r="P31" s="10" t="n">
+      <c r="P31" s="10" t="n"/>
+      <c r="Q31" s="10" t="n">
         <v>2500000</v>
       </c>
-      <c r="Q31" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R31" s="10" t="n"/>
+      <c r="R31" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S31" s="10" t="n"/>
       <c r="T31" s="10" t="n"/>
-      <c r="U31" s="10" t="n">
+      <c r="U31" s="10" t="n"/>
+      <c r="V31" s="10" t="n">
         <v>3121</v>
       </c>
-      <c r="V31" s="10" t="n"/>
       <c r="W31" s="10" t="n"/>
-      <c r="X31" s="10" t="inlineStr">
+      <c r="X31" s="10" t="n"/>
+      <c r="Y31" s="10" t="inlineStr">
         <is>
           <t>유니크 버섯 스폰율 +5%</t>
         </is>
       </c>
-      <c r="Y31" s="10" t="n"/>
+      <c r="Z31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
@@ -3247,42 +3347,45 @@
       <c r="K32" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="L32" s="10" t="inlineStr">
+      <c r="L32" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="M32" s="10" t="inlineStr">
         <is>
           <t>epic_yield</t>
         </is>
       </c>
-      <c r="M32" s="10" t="n"/>
-      <c r="N32" s="10" t="n">
+      <c r="N32" s="10" t="n"/>
+      <c r="O32" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="O32" s="10" t="n"/>
-      <c r="P32" s="10" t="n">
+      <c r="P32" s="10" t="n"/>
+      <c r="Q32" s="10" t="n">
         <v>9700000</v>
       </c>
-      <c r="Q32" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R32" s="10" t="n"/>
+      <c r="R32" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S32" s="10" t="n"/>
       <c r="T32" s="10" t="n"/>
-      <c r="U32" s="10" t="n">
+      <c r="U32" s="10" t="n"/>
+      <c r="V32" s="10" t="n">
         <v>3122</v>
       </c>
-      <c r="V32" s="10" t="inlineStr">
+      <c r="W32" s="10" t="inlineStr">
         <is>
           <t>3124</t>
         </is>
       </c>
-      <c r="W32" s="10" t="n"/>
-      <c r="X32" s="10" t="inlineStr">
+      <c r="X32" s="10" t="n"/>
+      <c r="Y32" s="10" t="inlineStr">
         <is>
           <t>에픽 버섯 수확량 +15%</t>
         </is>
       </c>
-      <c r="Y32" s="10" t="inlineStr">
+      <c r="Z32" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -3332,38 +3435,41 @@
       <c r="K33" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="L33" s="10" t="inlineStr">
+      <c r="L33" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M33" s="10" t="inlineStr">
         <is>
           <t>unique_yield</t>
         </is>
       </c>
-      <c r="M33" s="10" t="n"/>
-      <c r="N33" s="10" t="n">
+      <c r="N33" s="10" t="n"/>
+      <c r="O33" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="O33" s="10" t="n"/>
-      <c r="P33" s="10" t="n">
+      <c r="P33" s="10" t="n"/>
+      <c r="Q33" s="10" t="n">
         <v>9700000</v>
       </c>
-      <c r="Q33" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R33" s="10" t="n"/>
+      <c r="R33" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S33" s="10" t="n"/>
       <c r="T33" s="10" t="n"/>
-      <c r="U33" s="10" t="n">
+      <c r="U33" s="10" t="n"/>
+      <c r="V33" s="10" t="n">
         <v>3118</v>
       </c>
-      <c r="V33" s="10" t="n"/>
       <c r="W33" s="10" t="n"/>
-      <c r="X33" s="10" t="inlineStr">
+      <c r="X33" s="10" t="n"/>
+      <c r="Y33" s="10" t="inlineStr">
         <is>
           <t>유니크 버섯 수확량 +5%</t>
         </is>
       </c>
-      <c r="Y33" s="10" t="n"/>
+      <c r="Z33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
@@ -3409,42 +3515,45 @@
       <c r="K34" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="L34" s="10" t="inlineStr">
+      <c r="L34" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M34" s="10" t="inlineStr">
         <is>
           <t>colony_respawn</t>
         </is>
       </c>
-      <c r="M34" s="10" t="n"/>
-      <c r="N34" s="10" t="n">
+      <c r="N34" s="10" t="n"/>
+      <c r="O34" s="10" t="n">
         <v>-2</v>
       </c>
-      <c r="O34" s="10" t="n"/>
-      <c r="P34" s="10" t="n">
+      <c r="P34" s="10" t="n"/>
+      <c r="Q34" s="10" t="n">
         <v>11000000</v>
       </c>
-      <c r="Q34" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R34" s="10" t="n"/>
+      <c r="R34" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S34" s="10" t="n"/>
       <c r="T34" s="10" t="n"/>
-      <c r="U34" s="10" t="n">
+      <c r="U34" s="10" t="n"/>
+      <c r="V34" s="10" t="n">
         <v>3119</v>
       </c>
-      <c r="V34" s="10" t="inlineStr">
+      <c r="W34" s="10" t="inlineStr">
         <is>
           <t>3111</t>
         </is>
       </c>
-      <c r="W34" s="10" t="n"/>
-      <c r="X34" s="10" t="inlineStr">
+      <c r="X34" s="10" t="n"/>
+      <c r="Y34" s="10" t="inlineStr">
         <is>
           <t>군락지 리스폰 −2초 (5 → 3)</t>
         </is>
       </c>
-      <c r="Y34" s="10" t="n"/>
+      <c r="Z34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="n">
@@ -3490,38 +3599,41 @@
       <c r="K35" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="L35" s="10" t="inlineStr">
+      <c r="L35" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="M35" s="10" t="inlineStr">
         <is>
           <t>golden_spawn</t>
         </is>
       </c>
-      <c r="M35" s="10" t="n"/>
-      <c r="N35" s="10" t="n">
+      <c r="N35" s="10" t="n"/>
+      <c r="O35" s="10" t="n">
         <v>0.01</v>
       </c>
-      <c r="O35" s="10" t="n"/>
-      <c r="P35" s="10" t="n">
+      <c r="P35" s="10" t="n"/>
+      <c r="Q35" s="10" t="n">
         <v>11000000</v>
       </c>
-      <c r="Q35" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R35" s="10" t="n"/>
+      <c r="R35" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S35" s="10" t="n"/>
       <c r="T35" s="10" t="n"/>
-      <c r="U35" s="10" t="n">
+      <c r="U35" s="10" t="n"/>
+      <c r="V35" s="10" t="n">
         <v>3121</v>
       </c>
-      <c r="V35" s="10" t="n"/>
       <c r="W35" s="10" t="n"/>
-      <c r="X35" s="10" t="inlineStr">
+      <c r="X35" s="10" t="n"/>
+      <c r="Y35" s="10" t="inlineStr">
         <is>
           <t>황금 변종 스폰율 +1%</t>
         </is>
       </c>
-      <c r="Y35" s="10" t="n"/>
+      <c r="Z35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
@@ -3567,42 +3679,45 @@
       <c r="K36" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="L36" s="10" t="inlineStr">
+      <c r="L36" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="M36" s="10" t="inlineStr">
         <is>
           <t>unique_yield</t>
         </is>
       </c>
-      <c r="M36" s="10" t="n"/>
-      <c r="N36" s="10" t="n">
+      <c r="N36" s="10" t="n"/>
+      <c r="O36" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="O36" s="10" t="n"/>
-      <c r="P36" s="10" t="n">
+      <c r="P36" s="10" t="n"/>
+      <c r="Q36" s="10" t="n">
         <v>16000000</v>
       </c>
-      <c r="Q36" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R36" s="10" t="n"/>
+      <c r="R36" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S36" s="10" t="n"/>
       <c r="T36" s="10" t="n"/>
-      <c r="U36" s="10" t="n">
+      <c r="U36" s="10" t="n"/>
+      <c r="V36" s="10" t="n">
         <v>3124</v>
       </c>
-      <c r="V36" s="10" t="inlineStr">
+      <c r="W36" s="10" t="inlineStr">
         <is>
           <t>3129</t>
         </is>
       </c>
-      <c r="W36" s="10" t="n"/>
-      <c r="X36" s="10" t="inlineStr">
+      <c r="X36" s="10" t="n"/>
+      <c r="Y36" s="10" t="inlineStr">
         <is>
           <t>유니크 버섯 수확량 +10%</t>
         </is>
       </c>
-      <c r="Y36" s="10" t="inlineStr">
+      <c r="Z36" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -3652,38 +3767,41 @@
       <c r="K37" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="L37" s="10" t="inlineStr">
+      <c r="L37" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="M37" s="10" t="inlineStr">
         <is>
           <t>legendary_yield</t>
         </is>
       </c>
-      <c r="M37" s="10" t="n"/>
-      <c r="N37" s="10" t="n">
+      <c r="N37" s="10" t="n"/>
+      <c r="O37" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="O37" s="10" t="n"/>
-      <c r="P37" s="10" t="n">
+      <c r="P37" s="10" t="n"/>
+      <c r="Q37" s="10" t="n">
         <v>17000000</v>
       </c>
-      <c r="Q37" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R37" s="10" t="n"/>
+      <c r="R37" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S37" s="10" t="n"/>
       <c r="T37" s="10" t="n"/>
-      <c r="U37" s="10" t="n">
+      <c r="U37" s="10" t="n"/>
+      <c r="V37" s="10" t="n">
         <v>3129</v>
       </c>
-      <c r="V37" s="10" t="n"/>
       <c r="W37" s="10" t="n"/>
-      <c r="X37" s="10" t="inlineStr">
+      <c r="X37" s="10" t="n"/>
+      <c r="Y37" s="10" t="inlineStr">
         <is>
           <t>보스 전용 레전더리 버섯 수확량 +3%</t>
         </is>
       </c>
-      <c r="Y37" s="10" t="n"/>
+      <c r="Z37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
@@ -3729,42 +3847,45 @@
       <c r="K38" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="L38" s="10" t="inlineStr">
+      <c r="L38" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="M38" s="10" t="inlineStr">
         <is>
           <t>unique_spawn</t>
         </is>
       </c>
-      <c r="M38" s="10" t="n"/>
-      <c r="N38" s="10" t="n">
+      <c r="N38" s="10" t="n"/>
+      <c r="O38" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="O38" s="10" t="n"/>
-      <c r="P38" s="10" t="n">
+      <c r="P38" s="10" t="n"/>
+      <c r="Q38" s="10" t="n">
         <v>17000000</v>
       </c>
-      <c r="Q38" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R38" s="10" t="n"/>
+      <c r="R38" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S38" s="10" t="n"/>
       <c r="T38" s="10" t="n"/>
-      <c r="U38" s="10" t="n">
+      <c r="U38" s="10" t="n"/>
+      <c r="V38" s="10" t="n">
         <v>3126</v>
       </c>
-      <c r="V38" s="10" t="inlineStr">
+      <c r="W38" s="10" t="inlineStr">
         <is>
           <t>3127</t>
         </is>
       </c>
-      <c r="W38" s="10" t="n"/>
-      <c r="X38" s="10" t="inlineStr">
+      <c r="X38" s="10" t="n"/>
+      <c r="Y38" s="10" t="inlineStr">
         <is>
           <t>유니크 버섯 스폰율 +10%</t>
         </is>
       </c>
-      <c r="Y38" s="10" t="inlineStr">
+      <c r="Z38" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -3814,42 +3935,45 @@
       <c r="K39" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="L39" s="10" t="inlineStr">
+      <c r="L39" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="M39" s="10" t="inlineStr">
         <is>
           <t>unique_spawn</t>
         </is>
       </c>
-      <c r="M39" s="10" t="n"/>
-      <c r="N39" s="10" t="n">
+      <c r="N39" s="10" t="n"/>
+      <c r="O39" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="O39" s="10" t="n"/>
-      <c r="P39" s="10" t="n">
+      <c r="P39" s="10" t="n"/>
+      <c r="Q39" s="10" t="n">
         <v>19000000</v>
       </c>
-      <c r="Q39" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R39" s="10" t="n"/>
+      <c r="R39" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S39" s="10" t="n"/>
       <c r="T39" s="10" t="n"/>
-      <c r="U39" s="10" t="n">
+      <c r="U39" s="10" t="n"/>
+      <c r="V39" s="10" t="n">
         <v>3130</v>
       </c>
-      <c r="V39" s="10" t="inlineStr">
+      <c r="W39" s="10" t="inlineStr">
         <is>
           <t>3134</t>
         </is>
       </c>
-      <c r="W39" s="10" t="n"/>
-      <c r="X39" s="10" t="inlineStr">
+      <c r="X39" s="10" t="n"/>
+      <c r="Y39" s="10" t="inlineStr">
         <is>
           <t>유니크 버섯 스폰율 +15%</t>
         </is>
       </c>
-      <c r="Y39" s="10" t="inlineStr">
+      <c r="Z39" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%. 원문은 Lv.2와 같은 레어도 15</t>
         </is>
@@ -3899,42 +4023,45 @@
       <c r="K40" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="L40" s="10" t="inlineStr">
+      <c r="L40" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="M40" s="10" t="inlineStr">
         <is>
           <t>golden_spawn</t>
         </is>
       </c>
-      <c r="M40" s="10" t="n"/>
-      <c r="N40" s="10" t="n">
+      <c r="N40" s="10" t="n"/>
+      <c r="O40" s="10" t="n">
         <v>0.02</v>
       </c>
-      <c r="O40" s="10" t="n"/>
-      <c r="P40" s="10" t="n">
+      <c r="P40" s="10" t="n"/>
+      <c r="Q40" s="10" t="n">
         <v>25000000</v>
       </c>
-      <c r="Q40" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R40" s="10" t="n"/>
+      <c r="R40" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S40" s="10" t="n"/>
       <c r="T40" s="10" t="n"/>
-      <c r="U40" s="10" t="n">
+      <c r="U40" s="10" t="n"/>
+      <c r="V40" s="10" t="n">
         <v>3130</v>
       </c>
-      <c r="V40" s="10" t="inlineStr">
+      <c r="W40" s="10" t="inlineStr">
         <is>
           <t>3131</t>
         </is>
       </c>
-      <c r="W40" s="10" t="n"/>
-      <c r="X40" s="10" t="inlineStr">
+      <c r="X40" s="10" t="n"/>
+      <c r="Y40" s="10" t="inlineStr">
         <is>
           <t>황금 변종 스폰율 +3%</t>
         </is>
       </c>
-      <c r="Y40" s="10" t="inlineStr">
+      <c r="Z40" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -3984,42 +4111,45 @@
       <c r="K41" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="L41" s="10" t="inlineStr">
+      <c r="L41" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="M41" s="10" t="inlineStr">
         <is>
           <t>legendary_yield</t>
         </is>
       </c>
-      <c r="M41" s="10" t="n"/>
-      <c r="N41" s="10" t="n">
+      <c r="N41" s="10" t="n"/>
+      <c r="O41" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="O41" s="10" t="n"/>
-      <c r="P41" s="10" t="n">
+      <c r="P41" s="10" t="n"/>
+      <c r="Q41" s="10" t="n">
         <v>23000000</v>
       </c>
-      <c r="Q41" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R41" s="10" t="n"/>
+      <c r="R41" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S41" s="10" t="n"/>
       <c r="T41" s="10" t="n"/>
-      <c r="U41" s="10" t="n">
+      <c r="U41" s="10" t="n"/>
+      <c r="V41" s="10" t="n">
         <v>3129</v>
       </c>
-      <c r="V41" s="10" t="inlineStr">
+      <c r="W41" s="10" t="inlineStr">
         <is>
           <t>3133</t>
         </is>
       </c>
-      <c r="W41" s="10" t="n"/>
-      <c r="X41" s="10" t="inlineStr">
+      <c r="X41" s="10" t="n"/>
+      <c r="Y41" s="10" t="inlineStr">
         <is>
           <t>보스 전용 레전더리 버섯 수확량 +6%</t>
         </is>
       </c>
-      <c r="Y41" s="10" t="inlineStr">
+      <c r="Z41" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +3%</t>
         </is>
@@ -4069,42 +4199,45 @@
       <c r="K42" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="L42" s="10" t="inlineStr">
+      <c r="L42" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M42" s="10" t="inlineStr">
         <is>
           <t>gold_conversion</t>
         </is>
       </c>
-      <c r="M42" s="10" t="n"/>
-      <c r="N42" s="10" t="n">
+      <c r="N42" s="10" t="n"/>
+      <c r="O42" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="O42" s="10" t="n"/>
-      <c r="P42" s="10" t="n">
+      <c r="P42" s="10" t="n"/>
+      <c r="Q42" s="10" t="n">
         <v>23000000</v>
       </c>
-      <c r="Q42" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R42" s="10" t="n"/>
+      <c r="R42" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S42" s="10" t="n"/>
       <c r="T42" s="10" t="n"/>
-      <c r="U42" s="10" t="n">
+      <c r="U42" s="10" t="n"/>
+      <c r="V42" s="10" t="n">
         <v>3125</v>
       </c>
-      <c r="V42" s="10" t="inlineStr">
+      <c r="W42" s="10" t="inlineStr">
         <is>
           <t>3122</t>
         </is>
       </c>
-      <c r="W42" s="10" t="n"/>
-      <c r="X42" s="10" t="inlineStr">
+      <c r="X42" s="10" t="n"/>
+      <c r="Y42" s="10" t="inlineStr">
         <is>
           <t>점수 골드 전환율 +40%</t>
         </is>
       </c>
-      <c r="Y42" s="10" t="inlineStr">
+      <c r="Z42" s="10" t="inlineStr">
         <is>
           <t>흥정 기술의 상위. 누적값 기준 차이 +10%</t>
         </is>
@@ -4154,42 +4287,45 @@
       <c r="K43" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="L43" s="10" t="inlineStr">
+      <c r="L43" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M43" s="10" t="inlineStr">
         <is>
           <t>colony_count</t>
         </is>
       </c>
-      <c r="M43" s="10" t="n"/>
-      <c r="N43" s="10" t="n">
+      <c r="N43" s="10" t="n"/>
+      <c r="O43" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="O43" s="10" t="n"/>
-      <c r="P43" s="10" t="n">
+      <c r="P43" s="10" t="n"/>
+      <c r="Q43" s="10" t="n">
         <v>25000000</v>
       </c>
-      <c r="Q43" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R43" s="10" t="n"/>
+      <c r="R43" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S43" s="10" t="n"/>
       <c r="T43" s="10" t="n"/>
-      <c r="U43" s="10" t="n">
+      <c r="U43" s="10" t="n"/>
+      <c r="V43" s="10" t="n">
         <v>3127</v>
       </c>
-      <c r="V43" s="10" t="inlineStr">
+      <c r="W43" s="10" t="inlineStr">
         <is>
           <t>3126</t>
         </is>
       </c>
-      <c r="W43" s="10" t="n"/>
-      <c r="X43" s="10" t="inlineStr">
+      <c r="X43" s="10" t="n"/>
+      <c r="Y43" s="10" t="inlineStr">
         <is>
           <t>군락지 수 +2 (10 → 12)</t>
         </is>
       </c>
-      <c r="Y43" s="10" t="inlineStr">
+      <c r="Z43" s="10" t="inlineStr">
         <is>
           <t>넓은 시야의 상위</t>
         </is>
@@ -4239,42 +4375,45 @@
       <c r="K44" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="L44" s="10" t="inlineStr">
+      <c r="L44" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M44" s="10" t="inlineStr">
         <is>
           <t>unique_yield</t>
         </is>
       </c>
-      <c r="M44" s="10" t="n"/>
-      <c r="N44" s="10" t="n">
+      <c r="N44" s="10" t="n"/>
+      <c r="O44" s="10" t="n">
         <v>0.05</v>
       </c>
-      <c r="O44" s="10" t="n"/>
-      <c r="P44" s="10" t="n">
+      <c r="P44" s="10" t="n"/>
+      <c r="Q44" s="10" t="n">
         <v>37000000</v>
       </c>
-      <c r="Q44" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R44" s="10" t="n"/>
+      <c r="R44" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S44" s="10" t="n"/>
       <c r="T44" s="10" t="n"/>
-      <c r="U44" s="10" t="n">
+      <c r="U44" s="10" t="n"/>
+      <c r="V44" s="10" t="n">
         <v>3133</v>
       </c>
-      <c r="V44" s="10" t="inlineStr">
+      <c r="W44" s="10" t="inlineStr">
         <is>
           <t>3132</t>
         </is>
       </c>
-      <c r="W44" s="10" t="n"/>
-      <c r="X44" s="10" t="inlineStr">
+      <c r="X44" s="10" t="n"/>
+      <c r="Y44" s="10" t="inlineStr">
         <is>
           <t>유니크 버섯 수확량 +15%</t>
         </is>
       </c>
-      <c r="Y44" s="10" t="inlineStr">
+      <c r="Z44" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +5%</t>
         </is>
@@ -4324,42 +4463,45 @@
       <c r="K45" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="L45" s="10" t="inlineStr">
+      <c r="L45" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M45" s="10" t="inlineStr">
         <is>
           <t>score_rate</t>
         </is>
       </c>
-      <c r="M45" s="10" t="n"/>
-      <c r="N45" s="10" t="n">
+      <c r="N45" s="10" t="n"/>
+      <c r="O45" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="O45" s="10" t="n"/>
-      <c r="P45" s="10" t="n">
+      <c r="P45" s="10" t="n"/>
+      <c r="Q45" s="10" t="n">
         <v>35000000</v>
       </c>
-      <c r="Q45" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R45" s="10" t="n"/>
+      <c r="R45" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S45" s="10" t="n"/>
       <c r="T45" s="10" t="n"/>
-      <c r="U45" s="10" t="n">
+      <c r="U45" s="10" t="n"/>
+      <c r="V45" s="10" t="n">
         <v>3128</v>
       </c>
-      <c r="V45" s="10" t="inlineStr">
+      <c r="W45" s="10" t="inlineStr">
         <is>
           <t>3120</t>
         </is>
       </c>
-      <c r="W45" s="10" t="n"/>
-      <c r="X45" s="10" t="inlineStr">
+      <c r="X45" s="10" t="n"/>
+      <c r="Y45" s="10" t="inlineStr">
         <is>
           <t>획득 점수 +50%</t>
         </is>
       </c>
-      <c r="Y45" s="10" t="inlineStr">
+      <c r="Z45" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%</t>
         </is>
@@ -4409,42 +4551,45 @@
       <c r="K46" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="L46" s="10" t="inlineStr">
+      <c r="L46" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M46" s="10" t="inlineStr">
         <is>
           <t>golden_spawn</t>
         </is>
       </c>
-      <c r="M46" s="10" t="n"/>
-      <c r="N46" s="10" t="n">
+      <c r="N46" s="10" t="n"/>
+      <c r="O46" s="10" t="n">
         <v>0.02</v>
       </c>
-      <c r="O46" s="10" t="n"/>
-      <c r="P46" s="10" t="n">
+      <c r="P46" s="10" t="n"/>
+      <c r="Q46" s="10" t="n">
         <v>37000000</v>
       </c>
-      <c r="Q46" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R46" s="10" t="n"/>
+      <c r="R46" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S46" s="10" t="n"/>
       <c r="T46" s="10" t="n"/>
-      <c r="U46" s="10" t="n">
+      <c r="U46" s="10" t="n"/>
+      <c r="V46" s="10" t="n">
         <v>3135</v>
       </c>
-      <c r="V46" s="10" t="inlineStr">
+      <c r="W46" s="10" t="inlineStr">
         <is>
           <t>3136</t>
         </is>
       </c>
-      <c r="W46" s="10" t="n"/>
-      <c r="X46" s="10" t="inlineStr">
+      <c r="X46" s="10" t="n"/>
+      <c r="Y46" s="10" t="inlineStr">
         <is>
           <t>황금 변종 스폰율 +5%</t>
         </is>
       </c>
-      <c r="Y46" s="10" t="inlineStr">
+      <c r="Z46" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -4494,42 +4639,45 @@
       <c r="K47" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="L47" s="10" t="inlineStr">
+      <c r="L47" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="M47" s="10" t="inlineStr">
         <is>
           <t>final_rush_bonus</t>
         </is>
       </c>
-      <c r="M47" s="10" t="n"/>
-      <c r="N47" s="10" t="n">
+      <c r="N47" s="10" t="n"/>
+      <c r="O47" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="O47" s="10" t="n">
+      <c r="P47" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="P47" s="10" t="n">
+      <c r="Q47" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="Q47" s="10" t="inlineStr">
+      <c r="R47" s="10" t="inlineStr">
         <is>
           <t>Mycelite</t>
         </is>
       </c>
-      <c r="R47" s="10" t="n"/>
       <c r="S47" s="10" t="n"/>
-      <c r="T47" s="10" t="n">
+      <c r="T47" s="10" t="n"/>
+      <c r="U47" s="10" t="n">
         <v>1.25</v>
       </c>
-      <c r="U47" s="10" t="n">
+      <c r="V47" s="10" t="n">
         <v>3145</v>
       </c>
-      <c r="V47" s="10" t="n"/>
       <c r="W47" s="10" t="n"/>
-      <c r="X47" s="10" t="inlineStr">
+      <c r="X47" s="10" t="n"/>
+      <c r="Y47" s="10" t="inlineStr">
         <is>
           <t>라운드 마지막 5초 점수·수확량 +10% / Lv</t>
         </is>
       </c>
-      <c r="Y47" s="10" t="inlineStr">
+      <c r="Z47" s="10" t="inlineStr">
         <is>
           <t>param = 마지막 몇 초</t>
         </is>
@@ -4579,38 +4727,41 @@
       <c r="K48" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="L48" s="10" t="inlineStr">
+      <c r="L48" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M48" s="10" t="inlineStr">
         <is>
           <t>colony_count</t>
         </is>
       </c>
-      <c r="M48" s="10" t="n"/>
-      <c r="N48" s="10" t="n">
+      <c r="N48" s="10" t="n"/>
+      <c r="O48" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="O48" s="10" t="n"/>
-      <c r="P48" s="10" t="n">
+      <c r="P48" s="10" t="n"/>
+      <c r="Q48" s="10" t="n">
         <v>51000000</v>
       </c>
-      <c r="Q48" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R48" s="10" t="n"/>
+      <c r="R48" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S48" s="10" t="n"/>
       <c r="T48" s="10" t="n"/>
-      <c r="U48" s="10" t="n">
+      <c r="U48" s="10" t="n"/>
+      <c r="V48" s="10" t="n">
         <v>3142</v>
       </c>
-      <c r="V48" s="10" t="n"/>
       <c r="W48" s="10" t="n"/>
-      <c r="X48" s="10" t="inlineStr">
+      <c r="X48" s="10" t="n"/>
+      <c r="Y48" s="10" t="inlineStr">
         <is>
           <t>군락지 수 +3 (12 → 15)</t>
         </is>
       </c>
-      <c r="Y48" s="10" t="inlineStr">
+      <c r="Z48" s="10" t="inlineStr">
         <is>
           <t>넓은 시야의 상위</t>
         </is>
@@ -4660,42 +4811,45 @@
       <c r="K49" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="L49" s="10" t="inlineStr">
+      <c r="L49" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M49" s="10" t="inlineStr">
         <is>
           <t>legendary_yield</t>
         </is>
       </c>
-      <c r="M49" s="10" t="n"/>
-      <c r="N49" s="10" t="n">
+      <c r="N49" s="10" t="n"/>
+      <c r="O49" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="O49" s="10" t="n"/>
-      <c r="P49" s="10" t="n">
+      <c r="P49" s="10" t="n"/>
+      <c r="Q49" s="10" t="n">
         <v>47000000</v>
       </c>
-      <c r="Q49" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R49" s="10" t="n"/>
+      <c r="R49" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S49" s="10" t="n"/>
       <c r="T49" s="10" t="n"/>
-      <c r="U49" s="10" t="n">
+      <c r="U49" s="10" t="n"/>
+      <c r="V49" s="10" t="n">
         <v>3140</v>
       </c>
-      <c r="V49" s="10" t="inlineStr">
+      <c r="W49" s="10" t="inlineStr">
         <is>
           <t>3137</t>
         </is>
       </c>
-      <c r="W49" s="10" t="n"/>
-      <c r="X49" s="10" t="inlineStr">
+      <c r="X49" s="10" t="n"/>
+      <c r="Y49" s="10" t="inlineStr">
         <is>
           <t>보스 전용 레전더리 버섯 수확량 +9%</t>
         </is>
       </c>
-      <c r="Y49" s="10" t="inlineStr">
+      <c r="Z49" s="10" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +3%</t>
         </is>
@@ -4745,42 +4899,45 @@
       <c r="K50" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="L50" s="10" t="inlineStr">
+      <c r="L50" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M50" s="10" t="inlineStr">
         <is>
           <t>gold_conversion</t>
         </is>
       </c>
-      <c r="M50" s="10" t="n"/>
-      <c r="N50" s="10" t="n">
+      <c r="N50" s="10" t="n"/>
+      <c r="O50" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="O50" s="10" t="n"/>
-      <c r="P50" s="10" t="n">
+      <c r="P50" s="10" t="n"/>
+      <c r="Q50" s="10" t="n">
         <v>65000000</v>
       </c>
-      <c r="Q50" s="10" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R50" s="10" t="n"/>
+      <c r="R50" s="10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S50" s="10" t="n"/>
       <c r="T50" s="10" t="n"/>
-      <c r="U50" s="10" t="n">
+      <c r="U50" s="10" t="n"/>
+      <c r="V50" s="10" t="n">
         <v>3137</v>
       </c>
-      <c r="V50" s="10" t="inlineStr">
+      <c r="W50" s="10" t="inlineStr">
         <is>
           <t>3138</t>
         </is>
       </c>
-      <c r="W50" s="10" t="n"/>
-      <c r="X50" s="10" t="inlineStr">
+      <c r="X50" s="10" t="n"/>
+      <c r="Y50" s="10" t="inlineStr">
         <is>
           <t>점수 골드 전환율 +50%</t>
         </is>
       </c>
-      <c r="Y50" s="10" t="inlineStr">
+      <c r="Z50" s="10" t="inlineStr">
         <is>
           <t>흥정 기술의 상위. 누적값 기준 차이 +10%</t>
         </is>
@@ -4830,38 +4987,41 @@
       <c r="K51" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="L51" s="11" t="inlineStr">
+      <c r="L51" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M51" s="11" t="inlineStr">
         <is>
           <t>buff_haste_duration</t>
         </is>
       </c>
-      <c r="M51" s="11" t="n"/>
-      <c r="N51" s="11" t="n">
+      <c r="N51" s="11" t="n"/>
+      <c r="O51" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="O51" s="11" t="n"/>
-      <c r="P51" s="11" t="n">
+      <c r="P51" s="11" t="n"/>
+      <c r="Q51" s="11" t="n">
         <v>170</v>
       </c>
-      <c r="Q51" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R51" s="11" t="n"/>
+      <c r="R51" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S51" s="11" t="n"/>
       <c r="T51" s="11" t="n"/>
-      <c r="U51" s="11" t="n">
+      <c r="U51" s="11" t="n"/>
+      <c r="V51" s="11" t="n">
         <v>3001</v>
       </c>
-      <c r="V51" s="11" t="n"/>
       <c r="W51" s="11" t="n"/>
-      <c r="X51" s="11" t="inlineStr">
+      <c r="X51" s="11" t="n"/>
+      <c r="Y51" s="11" t="inlineStr">
         <is>
           <t>가속(3초) 버프</t>
         </is>
       </c>
-      <c r="Y51" s="11" t="inlineStr">
+      <c r="Z51" s="11" t="inlineStr">
         <is>
           <t>value = 지속(초), 다음 노드는 +1초씩</t>
         </is>
@@ -4911,38 +5071,41 @@
       <c r="K52" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="L52" s="11" t="inlineStr">
+      <c r="L52" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M52" s="11" t="inlineStr">
         <is>
           <t>buff_pierce_duration</t>
         </is>
       </c>
-      <c r="M52" s="11" t="n"/>
-      <c r="N52" s="11" t="n">
+      <c r="N52" s="11" t="n"/>
+      <c r="O52" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="O52" s="11" t="n"/>
-      <c r="P52" s="11" t="n">
+      <c r="P52" s="11" t="n"/>
+      <c r="Q52" s="11" t="n">
         <v>170</v>
       </c>
-      <c r="Q52" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R52" s="11" t="n"/>
+      <c r="R52" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S52" s="11" t="n"/>
       <c r="T52" s="11" t="n"/>
-      <c r="U52" s="11" t="n">
+      <c r="U52" s="11" t="n"/>
+      <c r="V52" s="11" t="n">
         <v>3201</v>
       </c>
-      <c r="V52" s="11" t="n"/>
       <c r="W52" s="11" t="n"/>
-      <c r="X52" s="11" t="inlineStr">
+      <c r="X52" s="11" t="n"/>
+      <c r="Y52" s="11" t="inlineStr">
         <is>
           <t>관통(3초) 버프</t>
         </is>
       </c>
-      <c r="Y52" s="11" t="n"/>
+      <c r="Z52" s="11" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="n">
@@ -4988,42 +5151,45 @@
       <c r="K53" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="L53" s="11" t="inlineStr">
+      <c r="L53" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M53" s="11" t="inlineStr">
         <is>
           <t>buff_haste_duration</t>
         </is>
       </c>
-      <c r="M53" s="11" t="n"/>
-      <c r="N53" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O53" s="11" t="n"/>
-      <c r="P53" s="11" t="n">
+      <c r="N53" s="11" t="n"/>
+      <c r="O53" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" s="11" t="n"/>
+      <c r="Q53" s="11" t="n">
         <v>240</v>
       </c>
-      <c r="Q53" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R53" s="11" t="n"/>
+      <c r="R53" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S53" s="11" t="n"/>
       <c r="T53" s="11" t="n"/>
-      <c r="U53" s="11" t="n">
+      <c r="U53" s="11" t="n"/>
+      <c r="V53" s="11" t="n">
         <v>3202</v>
       </c>
-      <c r="V53" s="11" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>3201</t>
         </is>
       </c>
-      <c r="W53" s="11" t="n"/>
-      <c r="X53" s="11" t="inlineStr">
+      <c r="X53" s="11" t="n"/>
+      <c r="Y53" s="11" t="inlineStr">
         <is>
           <t>가속(4초) 버프</t>
         </is>
       </c>
-      <c r="Y53" s="11" t="n"/>
+      <c r="Z53" s="11" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="n">
@@ -5069,38 +5235,41 @@
       <c r="K54" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="L54" s="11" t="inlineStr">
+      <c r="L54" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M54" s="11" t="inlineStr">
         <is>
           <t>field_restoration</t>
         </is>
       </c>
-      <c r="M54" s="11" t="n"/>
-      <c r="N54" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O54" s="11" t="n"/>
-      <c r="P54" s="11" t="n">
+      <c r="N54" s="11" t="n"/>
+      <c r="O54" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" s="11" t="n"/>
+      <c r="Q54" s="11" t="n">
         <v>240</v>
       </c>
-      <c r="Q54" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R54" s="11" t="n"/>
+      <c r="R54" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S54" s="11" t="n"/>
       <c r="T54" s="11" t="n"/>
-      <c r="U54" s="11" t="n">
+      <c r="U54" s="11" t="n"/>
+      <c r="V54" s="11" t="n">
         <v>3201</v>
       </c>
-      <c r="V54" s="11" t="n"/>
       <c r="W54" s="11" t="n"/>
-      <c r="X54" s="11" t="inlineStr">
+      <c r="X54" s="11" t="n"/>
+      <c r="Y54" s="11" t="inlineStr">
         <is>
           <t>필드에 그루터기 추가</t>
         </is>
       </c>
-      <c r="Y54" s="11" t="inlineStr">
+      <c r="Z54" s="11" t="inlineStr">
         <is>
           <t>value = 단계 (1 그루터기 / 2 꽃밭 / 3 도토리 점등)</t>
         </is>
@@ -5150,40 +5319,43 @@
       <c r="K55" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="L55" s="11" t="inlineStr">
+      <c r="L55" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M55" s="11" t="inlineStr">
         <is>
           <t>poison_strike_chance</t>
         </is>
       </c>
-      <c r="M55" s="11" t="n"/>
-      <c r="N55" s="11" t="n">
+      <c r="N55" s="11" t="n"/>
+      <c r="O55" s="11" t="n">
         <v>0.03</v>
       </c>
-      <c r="O55" s="11" t="n">
+      <c r="P55" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="P55" s="11" t="n">
+      <c r="Q55" s="11" t="n">
         <v>910</v>
       </c>
-      <c r="Q55" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R55" s="11" t="n"/>
+      <c r="R55" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S55" s="11" t="n"/>
       <c r="T55" s="11" t="n"/>
-      <c r="U55" s="11" t="n">
+      <c r="U55" s="11" t="n"/>
+      <c r="V55" s="11" t="n">
         <v>3204</v>
       </c>
-      <c r="V55" s="11" t="n"/>
       <c r="W55" s="11" t="n"/>
-      <c r="X55" s="11" t="inlineStr">
+      <c r="X55" s="11" t="n"/>
+      <c r="Y55" s="11" t="inlineStr">
         <is>
           <t>단일 버섯 획득 시 3% 확률로 다음 타격 피해 +200%</t>
         </is>
       </c>
-      <c r="Y55" s="11" t="inlineStr">
+      <c r="Z55" s="11" t="inlineStr">
         <is>
           <t>param = 피해 증가 (2 = +200%)</t>
         </is>
@@ -5233,40 +5405,43 @@
       <c r="K56" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="L56" s="11" t="inlineStr">
+      <c r="L56" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M56" s="11" t="inlineStr">
         <is>
           <t>buff_fever_duration</t>
         </is>
       </c>
-      <c r="M56" s="11" t="n"/>
-      <c r="N56" s="11" t="n">
+      <c r="N56" s="11" t="n"/>
+      <c r="O56" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="O56" s="11" t="n">
+      <c r="P56" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="P56" s="11" t="n">
+      <c r="Q56" s="11" t="n">
         <v>1400</v>
       </c>
-      <c r="Q56" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R56" s="11" t="n"/>
+      <c r="R56" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S56" s="11" t="n"/>
       <c r="T56" s="11" t="n"/>
-      <c r="U56" s="11" t="n">
+      <c r="U56" s="11" t="n"/>
+      <c r="V56" s="11" t="n">
         <v>3202</v>
       </c>
-      <c r="V56" s="11" t="n"/>
       <c r="W56" s="11" t="n"/>
-      <c r="X56" s="11" t="inlineStr">
+      <c r="X56" s="11" t="n"/>
+      <c r="Y56" s="11" t="inlineStr">
         <is>
           <t>[피버] 버프 3초 · 콤보 계수 +50%</t>
         </is>
       </c>
-      <c r="Y56" s="11" t="inlineStr">
+      <c r="Z56" s="11" t="inlineStr">
         <is>
           <t>param = 콤보 계수 증가</t>
         </is>
@@ -5316,42 +5491,45 @@
       <c r="K57" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="L57" s="11" t="inlineStr">
+      <c r="L57" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M57" s="11" t="inlineStr">
         <is>
           <t>buff_haste_duration</t>
         </is>
       </c>
-      <c r="M57" s="11" t="n"/>
-      <c r="N57" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O57" s="11" t="n"/>
-      <c r="P57" s="11" t="n">
+      <c r="N57" s="11" t="n"/>
+      <c r="O57" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" s="11" t="n"/>
+      <c r="Q57" s="11" t="n">
         <v>1400</v>
       </c>
-      <c r="Q57" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R57" s="11" t="n"/>
+      <c r="R57" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S57" s="11" t="n"/>
       <c r="T57" s="11" t="n"/>
-      <c r="U57" s="11" t="n">
+      <c r="U57" s="11" t="n"/>
+      <c r="V57" s="11" t="n">
         <v>3202</v>
       </c>
-      <c r="V57" s="11" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>3203</t>
         </is>
       </c>
-      <c r="W57" s="11" t="n"/>
-      <c r="X57" s="11" t="inlineStr">
+      <c r="X57" s="11" t="n"/>
+      <c r="Y57" s="11" t="inlineStr">
         <is>
           <t>가속(5초) 버프</t>
         </is>
       </c>
-      <c r="Y57" s="11" t="n"/>
+      <c r="Z57" s="11" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="n">
@@ -5397,44 +5575,47 @@
       <c r="K58" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L58" s="11" t="inlineStr">
+      <c r="L58" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M58" s="11" t="inlineStr">
         <is>
           <t>poison_strike_chance</t>
         </is>
       </c>
-      <c r="M58" s="11" t="n"/>
-      <c r="N58" s="11" t="n">
+      <c r="N58" s="11" t="n"/>
+      <c r="O58" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="O58" s="11" t="n">
+      <c r="P58" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="P58" s="11" t="n">
+      <c r="Q58" s="11" t="n">
         <v>3200</v>
       </c>
-      <c r="Q58" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R58" s="11" t="n"/>
+      <c r="R58" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S58" s="11" t="n"/>
       <c r="T58" s="11" t="n"/>
-      <c r="U58" s="11" t="n">
+      <c r="U58" s="11" t="n"/>
+      <c r="V58" s="11" t="n">
         <v>3204</v>
       </c>
-      <c r="V58" s="11" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>3205</t>
         </is>
       </c>
-      <c r="W58" s="11" t="n"/>
-      <c r="X58" s="11" t="inlineStr">
+      <c r="X58" s="11" t="n"/>
+      <c r="Y58" s="11" t="inlineStr">
         <is>
           <t>단일 버섯 획득 시 4% 확률로 다음 타격 피해 +200%</t>
         </is>
       </c>
-      <c r="Y58" s="11" t="n"/>
+      <c r="Z58" s="11" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="n">
@@ -5480,40 +5661,43 @@
       <c r="K59" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="L59" s="11" t="inlineStr">
+      <c r="L59" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M59" s="11" t="inlineStr">
         <is>
           <t>chain_lightning_chance</t>
         </is>
       </c>
-      <c r="M59" s="11" t="n"/>
-      <c r="N59" s="11" t="n">
+      <c r="N59" s="11" t="n"/>
+      <c r="O59" s="11" t="n">
         <v>0.03</v>
       </c>
-      <c r="O59" s="11" t="n">
+      <c r="P59" s="11" t="n">
         <v>0.3</v>
       </c>
-      <c r="P59" s="11" t="n">
+      <c r="Q59" s="11" t="n">
         <v>8400</v>
       </c>
-      <c r="Q59" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R59" s="11" t="n"/>
+      <c r="R59" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S59" s="11" t="n"/>
       <c r="T59" s="11" t="n"/>
-      <c r="U59" s="11" t="n">
+      <c r="U59" s="11" t="n"/>
+      <c r="V59" s="11" t="n">
         <v>3205</v>
       </c>
-      <c r="V59" s="11" t="n"/>
       <c r="W59" s="11" t="n"/>
-      <c r="X59" s="11" t="inlineStr">
+      <c r="X59" s="11" t="n"/>
+      <c r="Y59" s="11" t="inlineStr">
         <is>
           <t>군락 파괴 시 3% 확률로 랜덤 군락에 번개(공격력 30%)</t>
         </is>
       </c>
-      <c r="Y59" s="11" t="inlineStr">
+      <c r="Z59" s="11" t="inlineStr">
         <is>
           <t>param = 번개 피해 (공격력 비율)</t>
         </is>
@@ -5563,38 +5747,41 @@
       <c r="K60" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="L60" s="11" t="inlineStr">
+      <c r="L60" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M60" s="11" t="inlineStr">
         <is>
           <t>buff_homing_duration</t>
         </is>
       </c>
-      <c r="M60" s="11" t="n"/>
-      <c r="N60" s="11" t="n">
+      <c r="N60" s="11" t="n"/>
+      <c r="O60" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="O60" s="11" t="n"/>
-      <c r="P60" s="11" t="n">
+      <c r="P60" s="11" t="n"/>
+      <c r="Q60" s="11" t="n">
         <v>5800</v>
       </c>
-      <c r="Q60" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R60" s="11" t="n"/>
+      <c r="R60" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S60" s="11" t="n"/>
       <c r="T60" s="11" t="n"/>
-      <c r="U60" s="11" t="n">
+      <c r="U60" s="11" t="n"/>
+      <c r="V60" s="11" t="n">
         <v>3211</v>
       </c>
-      <c r="V60" s="11" t="n"/>
       <c r="W60" s="11" t="n"/>
-      <c r="X60" s="11" t="inlineStr">
+      <c r="X60" s="11" t="n"/>
+      <c r="Y60" s="11" t="inlineStr">
         <is>
           <t>유도(3초) 버프</t>
         </is>
       </c>
-      <c r="Y60" s="11" t="n"/>
+      <c r="Z60" s="11" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="n">
@@ -5640,42 +5827,45 @@
       <c r="K61" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="L61" s="11" t="inlineStr">
+      <c r="L61" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M61" s="11" t="inlineStr">
         <is>
           <t>buff_pierce_duration</t>
         </is>
       </c>
-      <c r="M61" s="11" t="n"/>
-      <c r="N61" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O61" s="11" t="n"/>
-      <c r="P61" s="11" t="n">
+      <c r="N61" s="11" t="n"/>
+      <c r="O61" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P61" s="11" t="n"/>
+      <c r="Q61" s="11" t="n">
         <v>5800</v>
       </c>
-      <c r="Q61" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R61" s="11" t="n"/>
+      <c r="R61" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S61" s="11" t="n"/>
       <c r="T61" s="11" t="n"/>
-      <c r="U61" s="11" t="n">
+      <c r="U61" s="11" t="n"/>
+      <c r="V61" s="11" t="n">
         <v>3206</v>
       </c>
-      <c r="V61" s="11" t="inlineStr">
+      <c r="W61" s="11" t="inlineStr">
         <is>
           <t>3202</t>
         </is>
       </c>
-      <c r="W61" s="11" t="n"/>
-      <c r="X61" s="11" t="inlineStr">
+      <c r="X61" s="11" t="n"/>
+      <c r="Y61" s="11" t="inlineStr">
         <is>
           <t>관통(4초) 버프</t>
         </is>
       </c>
-      <c r="Y61" s="11" t="n"/>
+      <c r="Z61" s="11" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="n">
@@ -5721,42 +5911,45 @@
       <c r="K62" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="L62" s="11" t="inlineStr">
+      <c r="L62" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M62" s="11" t="inlineStr">
         <is>
           <t>buff_pierce_duration</t>
         </is>
       </c>
-      <c r="M62" s="11" t="n"/>
-      <c r="N62" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O62" s="11" t="n"/>
-      <c r="P62" s="11" t="n">
+      <c r="N62" s="11" t="n"/>
+      <c r="O62" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P62" s="11" t="n"/>
+      <c r="Q62" s="11" t="n">
         <v>8400</v>
       </c>
-      <c r="Q62" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R62" s="11" t="n"/>
+      <c r="R62" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S62" s="11" t="n"/>
       <c r="T62" s="11" t="n"/>
-      <c r="U62" s="11" t="n">
+      <c r="U62" s="11" t="n"/>
+      <c r="V62" s="11" t="n">
         <v>3207</v>
       </c>
-      <c r="V62" s="11" t="inlineStr">
+      <c r="W62" s="11" t="inlineStr">
         <is>
           <t>3211</t>
         </is>
       </c>
-      <c r="W62" s="11" t="n"/>
-      <c r="X62" s="11" t="inlineStr">
+      <c r="X62" s="11" t="n"/>
+      <c r="Y62" s="11" t="inlineStr">
         <is>
           <t>관통(5초) 버프</t>
         </is>
       </c>
-      <c r="Y62" s="11" t="inlineStr">
+      <c r="Z62" s="11" t="inlineStr">
         <is>
           <t>원문은 Lv.2와 같은 레어도 7</t>
         </is>
@@ -5806,38 +5999,41 @@
       <c r="K63" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="L63" s="11" t="inlineStr">
+      <c r="L63" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M63" s="11" t="inlineStr">
         <is>
           <t>debuff_cleanse_chance</t>
         </is>
       </c>
-      <c r="M63" s="11" t="n"/>
-      <c r="N63" s="11" t="n">
+      <c r="N63" s="11" t="n"/>
+      <c r="O63" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="O63" s="11" t="n"/>
-      <c r="P63" s="11" t="n">
+      <c r="P63" s="11" t="n"/>
+      <c r="Q63" s="11" t="n">
         <v>16000</v>
       </c>
-      <c r="Q63" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R63" s="11" t="n"/>
+      <c r="R63" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S63" s="11" t="n"/>
       <c r="T63" s="11" t="n"/>
-      <c r="U63" s="11" t="n">
+      <c r="U63" s="11" t="n"/>
+      <c r="V63" s="11" t="n">
         <v>3209</v>
       </c>
-      <c r="V63" s="11" t="n"/>
       <c r="W63" s="11" t="n"/>
-      <c r="X63" s="11" t="inlineStr">
+      <c r="X63" s="11" t="n"/>
+      <c r="Y63" s="11" t="inlineStr">
         <is>
           <t>군락 충돌로 디버프를 얻으면 10% 확률로 해제</t>
         </is>
       </c>
-      <c r="Y63" s="11" t="n"/>
+      <c r="Z63" s="11" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="n">
@@ -5883,44 +6079,47 @@
       <c r="K64" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="L64" s="11" t="inlineStr">
+      <c r="L64" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M64" s="11" t="inlineStr">
         <is>
           <t>poison_strike_chance</t>
         </is>
       </c>
-      <c r="M64" s="11" t="n"/>
-      <c r="N64" s="11" t="n">
+      <c r="N64" s="11" t="n"/>
+      <c r="O64" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="O64" s="11" t="n">
+      <c r="P64" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="P64" s="11" t="n">
+      <c r="Q64" s="11" t="n">
         <v>17000</v>
       </c>
-      <c r="Q64" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R64" s="11" t="n"/>
+      <c r="R64" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S64" s="11" t="n"/>
       <c r="T64" s="11" t="n"/>
-      <c r="U64" s="11" t="n">
+      <c r="U64" s="11" t="n"/>
+      <c r="V64" s="11" t="n">
         <v>3215</v>
       </c>
-      <c r="V64" s="11" t="inlineStr">
+      <c r="W64" s="11" t="inlineStr">
         <is>
           <t>3208</t>
         </is>
       </c>
-      <c r="W64" s="11" t="n"/>
-      <c r="X64" s="11" t="inlineStr">
+      <c r="X64" s="11" t="n"/>
+      <c r="Y64" s="11" t="inlineStr">
         <is>
           <t>단일 버섯 획득 시 5% 확률로 다음 타격 피해 +200%</t>
         </is>
       </c>
-      <c r="Y64" s="11" t="n"/>
+      <c r="Z64" s="11" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="n">
@@ -5966,42 +6165,45 @@
       <c r="K65" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="L65" s="11" t="inlineStr">
+      <c r="L65" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M65" s="11" t="inlineStr">
         <is>
           <t>field_restoration</t>
         </is>
       </c>
-      <c r="M65" s="11" t="n"/>
-      <c r="N65" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O65" s="11" t="n"/>
-      <c r="P65" s="11" t="n">
+      <c r="N65" s="11" t="n"/>
+      <c r="O65" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" s="11" t="n"/>
+      <c r="Q65" s="11" t="n">
         <v>10000</v>
       </c>
-      <c r="Q65" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R65" s="11" t="n"/>
+      <c r="R65" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S65" s="11" t="n"/>
       <c r="T65" s="11" t="n"/>
-      <c r="U65" s="11" t="n">
+      <c r="U65" s="11" t="n"/>
+      <c r="V65" s="11" t="n">
         <v>3208</v>
       </c>
-      <c r="V65" s="11" t="inlineStr">
+      <c r="W65" s="11" t="inlineStr">
         <is>
           <t>3204</t>
         </is>
       </c>
-      <c r="W65" s="11" t="n"/>
-      <c r="X65" s="11" t="inlineStr">
+      <c r="X65" s="11" t="n"/>
+      <c r="Y65" s="11" t="inlineStr">
         <is>
           <t>필드에 꽃밭 추가</t>
         </is>
       </c>
-      <c r="Y65" s="11" t="n"/>
+      <c r="Z65" s="11" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="n">
@@ -6047,38 +6249,41 @@
       <c r="K66" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="L66" s="11" t="inlineStr">
+      <c r="L66" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M66" s="11" t="inlineStr">
         <is>
           <t>buff_heal_duration</t>
         </is>
       </c>
-      <c r="M66" s="11" t="n"/>
-      <c r="N66" s="11" t="n">
+      <c r="N66" s="11" t="n"/>
+      <c r="O66" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="O66" s="11" t="n"/>
-      <c r="P66" s="11" t="n">
+      <c r="P66" s="11" t="n"/>
+      <c r="Q66" s="11" t="n">
         <v>82000</v>
       </c>
-      <c r="Q66" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R66" s="11" t="n"/>
+      <c r="R66" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S66" s="11" t="n"/>
       <c r="T66" s="11" t="n"/>
-      <c r="U66" s="11" t="n">
+      <c r="U66" s="11" t="n"/>
+      <c r="V66" s="11" t="n">
         <v>3212</v>
       </c>
-      <c r="V66" s="11" t="n"/>
       <c r="W66" s="11" t="n"/>
-      <c r="X66" s="11" t="inlineStr">
+      <c r="X66" s="11" t="n"/>
+      <c r="Y66" s="11" t="inlineStr">
         <is>
           <t>포자 디버프 제거 + 약손(3초)</t>
         </is>
       </c>
-      <c r="Y66" s="11" t="n"/>
+      <c r="Z66" s="11" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="n">
@@ -6124,42 +6329,45 @@
       <c r="K67" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="L67" s="11" t="inlineStr">
+      <c r="L67" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M67" s="11" t="inlineStr">
         <is>
           <t>buff_homing_duration</t>
         </is>
       </c>
-      <c r="M67" s="11" t="n"/>
-      <c r="N67" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O67" s="11" t="n"/>
-      <c r="P67" s="11" t="n">
+      <c r="N67" s="11" t="n"/>
+      <c r="O67" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" s="11" t="n"/>
+      <c r="Q67" s="11" t="n">
         <v>82000</v>
       </c>
-      <c r="Q67" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R67" s="11" t="n"/>
+      <c r="R67" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S67" s="11" t="n"/>
       <c r="T67" s="11" t="n"/>
-      <c r="U67" s="11" t="n">
+      <c r="U67" s="11" t="n"/>
+      <c r="V67" s="11" t="n">
         <v>3211</v>
       </c>
-      <c r="V67" s="11" t="inlineStr">
+      <c r="W67" s="11" t="inlineStr">
         <is>
           <t>3210</t>
         </is>
       </c>
-      <c r="W67" s="11" t="n"/>
-      <c r="X67" s="11" t="inlineStr">
+      <c r="X67" s="11" t="n"/>
+      <c r="Y67" s="11" t="inlineStr">
         <is>
           <t>유도(4초) 버프</t>
         </is>
       </c>
-      <c r="Y67" s="11" t="n"/>
+      <c r="Z67" s="11" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="n">
@@ -6205,42 +6413,45 @@
       <c r="K68" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="L68" s="11" t="inlineStr">
+      <c r="L68" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M68" s="11" t="inlineStr">
         <is>
           <t>debuff_cleanse_chance</t>
         </is>
       </c>
-      <c r="M68" s="11" t="n"/>
-      <c r="N68" s="11" t="n">
+      <c r="N68" s="11" t="n"/>
+      <c r="O68" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="O68" s="11" t="n"/>
-      <c r="P68" s="11" t="n">
+      <c r="P68" s="11" t="n"/>
+      <c r="Q68" s="11" t="n">
         <v>45000</v>
       </c>
-      <c r="Q68" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R68" s="11" t="n"/>
+      <c r="R68" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S68" s="11" t="n"/>
       <c r="T68" s="11" t="n"/>
-      <c r="U68" s="11" t="n">
+      <c r="U68" s="11" t="n"/>
+      <c r="V68" s="11" t="n">
         <v>3209</v>
       </c>
-      <c r="V68" s="11" t="inlineStr">
+      <c r="W68" s="11" t="inlineStr">
         <is>
           <t>3213</t>
         </is>
       </c>
-      <c r="W68" s="11" t="n"/>
-      <c r="X68" s="11" t="inlineStr">
+      <c r="X68" s="11" t="n"/>
+      <c r="Y68" s="11" t="inlineStr">
         <is>
           <t>군락 충돌로 디버프를 얻으면 20% 확률로 해제</t>
         </is>
       </c>
-      <c r="Y68" s="11" t="n"/>
+      <c r="Z68" s="11" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="n">
@@ -6286,40 +6497,43 @@
       <c r="K69" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="L69" s="11" t="inlineStr">
+      <c r="L69" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M69" s="11" t="inlineStr">
         <is>
           <t>whirlwind_chance</t>
         </is>
       </c>
-      <c r="M69" s="11" t="n"/>
-      <c r="N69" s="11" t="n">
+      <c r="N69" s="11" t="n"/>
+      <c r="O69" s="11" t="n">
         <v>0.03</v>
       </c>
-      <c r="O69" s="11" t="n">
+      <c r="P69" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="P69" s="11" t="n">
+      <c r="Q69" s="11" t="n">
         <v>310000</v>
       </c>
-      <c r="Q69" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R69" s="11" t="n"/>
+      <c r="R69" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S69" s="11" t="n"/>
       <c r="T69" s="11" t="n"/>
-      <c r="U69" s="11" t="n">
+      <c r="U69" s="11" t="n"/>
+      <c r="V69" s="11" t="n">
         <v>3214</v>
       </c>
-      <c r="V69" s="11" t="n"/>
       <c r="W69" s="11" t="n"/>
-      <c r="X69" s="11" t="inlineStr">
+      <c r="X69" s="11" t="n"/>
+      <c r="Y69" s="11" t="inlineStr">
         <is>
           <t>군락 충돌 시 3% 확률로 3초 지속 피해(공격력 5%)</t>
         </is>
       </c>
-      <c r="Y69" s="11" t="inlineStr">
+      <c r="Z69" s="11" t="inlineStr">
         <is>
           <t>param = 초당 피해 (공격력 비율). 지속 시간도 3/4/5초로 오르는데 칸이 하나라 계열 레벨 + 2초로 계산 필요</t>
         </is>
@@ -6369,40 +6583,43 @@
       <c r="K70" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="L70" s="11" t="inlineStr">
+      <c r="L70" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M70" s="11" t="inlineStr">
         <is>
           <t>buff_wisdom_rate</t>
         </is>
       </c>
-      <c r="M70" s="11" t="n"/>
-      <c r="N70" s="11" t="n">
+      <c r="N70" s="11" t="n"/>
+      <c r="O70" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="O70" s="11" t="n">
+      <c r="P70" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="P70" s="11" t="n">
+      <c r="Q70" s="11" t="n">
         <v>1000000</v>
       </c>
-      <c r="Q70" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R70" s="11" t="n"/>
+      <c r="R70" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S70" s="11" t="n"/>
       <c r="T70" s="11" t="n"/>
-      <c r="U70" s="11" t="n">
+      <c r="U70" s="11" t="n"/>
+      <c r="V70" s="11" t="n">
         <v>3211</v>
       </c>
-      <c r="V70" s="11" t="n"/>
       <c r="W70" s="11" t="n"/>
-      <c r="X70" s="11" t="inlineStr">
+      <c r="X70" s="11" t="n"/>
+      <c r="Y70" s="11" t="inlineStr">
         <is>
           <t>[지혜] 버프 3초 · 수확기 스킬 발동률 +1%</t>
         </is>
       </c>
-      <c r="Y70" s="11" t="inlineStr">
+      <c r="Z70" s="11" t="inlineStr">
         <is>
           <t>param = 버프 지속(초)</t>
         </is>
@@ -6452,44 +6669,47 @@
       <c r="K71" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="L71" s="11" t="inlineStr">
+      <c r="L71" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M71" s="11" t="inlineStr">
         <is>
           <t>buff_wisdom_rate</t>
         </is>
       </c>
-      <c r="M71" s="11" t="n"/>
-      <c r="N71" s="11" t="n">
+      <c r="N71" s="11" t="n"/>
+      <c r="O71" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="O71" s="11" t="n">
+      <c r="P71" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="P71" s="11" t="n">
+      <c r="Q71" s="11" t="n">
         <v>1100000</v>
       </c>
-      <c r="Q71" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R71" s="11" t="n"/>
+      <c r="R71" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S71" s="11" t="n"/>
       <c r="T71" s="11" t="n"/>
-      <c r="U71" s="11" t="n">
+      <c r="U71" s="11" t="n"/>
+      <c r="V71" s="11" t="n">
         <v>3217</v>
       </c>
-      <c r="V71" s="11" t="inlineStr">
+      <c r="W71" s="11" t="inlineStr">
         <is>
           <t>3220</t>
         </is>
       </c>
-      <c r="W71" s="11" t="n"/>
-      <c r="X71" s="11" t="inlineStr">
+      <c r="X71" s="11" t="n"/>
+      <c r="Y71" s="11" t="inlineStr">
         <is>
           <t>[지혜] 버프 3초 · 수확기 스킬 발동률 +2%</t>
         </is>
       </c>
-      <c r="Y71" s="11" t="inlineStr">
+      <c r="Z71" s="11" t="inlineStr">
         <is>
           <t>원문은 Lv.1과 같은 레어도 11</t>
         </is>
@@ -6539,44 +6759,47 @@
       <c r="K72" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="L72" s="11" t="inlineStr">
+      <c r="L72" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M72" s="11" t="inlineStr">
         <is>
           <t>buff_fever_duration</t>
         </is>
       </c>
-      <c r="M72" s="11" t="n"/>
-      <c r="N72" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="N72" s="11" t="n"/>
       <c r="O72" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="P72" s="11" t="n">
+      <c r="Q72" s="11" t="n">
         <v>1100000</v>
       </c>
-      <c r="Q72" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R72" s="11" t="n"/>
+      <c r="R72" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S72" s="11" t="n"/>
       <c r="T72" s="11" t="n"/>
-      <c r="U72" s="11" t="n">
+      <c r="U72" s="11" t="n"/>
+      <c r="V72" s="11" t="n">
         <v>3221</v>
       </c>
-      <c r="V72" s="11" t="inlineStr">
+      <c r="W72" s="11" t="inlineStr">
         <is>
           <t>3206</t>
         </is>
       </c>
-      <c r="W72" s="11" t="n"/>
-      <c r="X72" s="11" t="inlineStr">
+      <c r="X72" s="11" t="n"/>
+      <c r="Y72" s="11" t="inlineStr">
         <is>
           <t>[피버] 버프 4초 · 콤보 계수 +50%</t>
         </is>
       </c>
-      <c r="Y72" s="11" t="n"/>
+      <c r="Z72" s="11" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="n">
@@ -6622,40 +6845,43 @@
       <c r="K73" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="L73" s="11" t="inlineStr">
+      <c r="L73" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M73" s="11" t="inlineStr">
         <is>
           <t>spore_burst_chance</t>
         </is>
       </c>
-      <c r="M73" s="11" t="n"/>
-      <c r="N73" s="11" t="n">
+      <c r="N73" s="11" t="n"/>
+      <c r="O73" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="O73" s="11" t="n">
+      <c r="P73" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="P73" s="11" t="n">
+      <c r="Q73" s="11" t="n">
         <v>1100000</v>
       </c>
-      <c r="Q73" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R73" s="11" t="n"/>
+      <c r="R73" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S73" s="11" t="n"/>
       <c r="T73" s="11" t="n"/>
-      <c r="U73" s="11" t="n">
+      <c r="U73" s="11" t="n"/>
+      <c r="V73" s="11" t="n">
         <v>3215</v>
       </c>
-      <c r="V73" s="11" t="n"/>
       <c r="W73" s="11" t="n"/>
-      <c r="X73" s="11" t="inlineStr">
+      <c r="X73" s="11" t="n"/>
+      <c r="Y73" s="11" t="inlineStr">
         <is>
           <t>군락 충돌 시 1% 확률로 전체 피해(공격력 10%)</t>
         </is>
       </c>
-      <c r="Y73" s="11" t="inlineStr">
+      <c r="Z73" s="11" t="inlineStr">
         <is>
           <t>param = 피해 (공격력 비율)</t>
         </is>
@@ -6705,44 +6931,47 @@
       <c r="K74" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="L74" s="11" t="inlineStr">
+      <c r="L74" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M74" s="11" t="inlineStr">
         <is>
           <t>spore_burst_chance</t>
         </is>
       </c>
-      <c r="M74" s="11" t="n"/>
-      <c r="N74" s="11" t="n">
+      <c r="N74" s="11" t="n"/>
+      <c r="O74" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="O74" s="11" t="n">
+      <c r="P74" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="P74" s="11" t="n">
+      <c r="Q74" s="11" t="n">
         <v>1900000</v>
       </c>
-      <c r="Q74" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R74" s="11" t="n"/>
+      <c r="R74" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S74" s="11" t="n"/>
       <c r="T74" s="11" t="n"/>
-      <c r="U74" s="11" t="n">
+      <c r="U74" s="11" t="n"/>
+      <c r="V74" s="11" t="n">
         <v>3213</v>
       </c>
-      <c r="V74" s="11" t="inlineStr">
+      <c r="W74" s="11" t="inlineStr">
         <is>
           <t>3223</t>
         </is>
       </c>
-      <c r="W74" s="11" t="n"/>
-      <c r="X74" s="11" t="inlineStr">
+      <c r="X74" s="11" t="n"/>
+      <c r="Y74" s="11" t="inlineStr">
         <is>
           <t>군락 충돌 시 2% 확률로 전체 피해(공격력 10%)</t>
         </is>
       </c>
-      <c r="Y74" s="11" t="n"/>
+      <c r="Z74" s="11" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="11" t="n">
@@ -6788,42 +7017,45 @@
       <c r="K75" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="L75" s="11" t="inlineStr">
+      <c r="L75" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M75" s="11" t="inlineStr">
         <is>
           <t>buff_homing_duration</t>
         </is>
       </c>
-      <c r="M75" s="11" t="n"/>
-      <c r="N75" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O75" s="11" t="n"/>
-      <c r="P75" s="11" t="n">
+      <c r="N75" s="11" t="n"/>
+      <c r="O75" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" s="11" t="n"/>
+      <c r="Q75" s="11" t="n">
         <v>3700000</v>
       </c>
-      <c r="Q75" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R75" s="11" t="n"/>
+      <c r="R75" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S75" s="11" t="n"/>
       <c r="T75" s="11" t="n"/>
-      <c r="U75" s="11" t="n">
+      <c r="U75" s="11" t="n"/>
+      <c r="V75" s="11" t="n">
         <v>3221</v>
       </c>
-      <c r="V75" s="11" t="inlineStr">
+      <c r="W75" s="11" t="inlineStr">
         <is>
           <t>3217</t>
         </is>
       </c>
-      <c r="W75" s="11" t="n"/>
-      <c r="X75" s="11" t="inlineStr">
+      <c r="X75" s="11" t="n"/>
+      <c r="Y75" s="11" t="inlineStr">
         <is>
           <t>유도(5초) 버프</t>
         </is>
       </c>
-      <c r="Y75" s="11" t="n"/>
+      <c r="Z75" s="11" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="n">
@@ -6869,42 +7101,45 @@
       <c r="K76" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="L76" s="11" t="inlineStr">
+      <c r="L76" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M76" s="11" t="inlineStr">
         <is>
           <t>debuff_cleanse_chance</t>
         </is>
       </c>
-      <c r="M76" s="11" t="n"/>
-      <c r="N76" s="11" t="n">
+      <c r="N76" s="11" t="n"/>
+      <c r="O76" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="O76" s="11" t="n"/>
-      <c r="P76" s="11" t="n">
+      <c r="P76" s="11" t="n"/>
+      <c r="Q76" s="11" t="n">
         <v>3500000</v>
       </c>
-      <c r="Q76" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R76" s="11" t="n"/>
+      <c r="R76" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S76" s="11" t="n"/>
       <c r="T76" s="11" t="n"/>
-      <c r="U76" s="11" t="n">
+      <c r="U76" s="11" t="n"/>
+      <c r="V76" s="11" t="n">
         <v>3224</v>
       </c>
-      <c r="V76" s="11" t="inlineStr">
+      <c r="W76" s="11" t="inlineStr">
         <is>
           <t>3218</t>
         </is>
       </c>
-      <c r="W76" s="11" t="n"/>
-      <c r="X76" s="11" t="inlineStr">
+      <c r="X76" s="11" t="n"/>
+      <c r="Y76" s="11" t="inlineStr">
         <is>
           <t>군락 충돌로 디버프를 얻으면 30% 확률로 해제</t>
         </is>
       </c>
-      <c r="Y76" s="11" t="n"/>
+      <c r="Z76" s="11" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="n">
@@ -6950,42 +7185,45 @@
       <c r="K77" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="L77" s="11" t="inlineStr">
+      <c r="L77" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M77" s="11" t="inlineStr">
         <is>
           <t>field_restoration</t>
         </is>
       </c>
-      <c r="M77" s="11" t="n"/>
-      <c r="N77" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O77" s="11" t="n"/>
-      <c r="P77" s="11" t="n">
+      <c r="N77" s="11" t="n"/>
+      <c r="O77" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P77" s="11" t="n"/>
+      <c r="Q77" s="11" t="n">
         <v>3300000</v>
       </c>
-      <c r="Q77" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R77" s="11" t="n"/>
+      <c r="R77" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S77" s="11" t="n"/>
       <c r="T77" s="11" t="n"/>
-      <c r="U77" s="11" t="n">
+      <c r="U77" s="11" t="n"/>
+      <c r="V77" s="11" t="n">
         <v>3223</v>
       </c>
-      <c r="V77" s="11" t="inlineStr">
+      <c r="W77" s="11" t="inlineStr">
         <is>
           <t>3215</t>
         </is>
       </c>
-      <c r="W77" s="11" t="n"/>
-      <c r="X77" s="11" t="inlineStr">
+      <c r="X77" s="11" t="n"/>
+      <c r="Y77" s="11" t="inlineStr">
         <is>
           <t>필드에 도토리 점등 추가</t>
         </is>
       </c>
-      <c r="Y77" s="11" t="n"/>
+      <c r="Z77" s="11" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="11" t="n">
@@ -7031,40 +7269,43 @@
       <c r="K78" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="L78" s="11" t="inlineStr">
+      <c r="L78" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M78" s="11" t="inlineStr">
         <is>
           <t>buff_split_duration</t>
         </is>
       </c>
-      <c r="M78" s="11" t="n"/>
-      <c r="N78" s="11" t="n">
+      <c r="N78" s="11" t="n"/>
+      <c r="O78" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="O78" s="11" t="n">
+      <c r="P78" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="P78" s="11" t="n">
+      <c r="Q78" s="11" t="n">
         <v>5400000</v>
       </c>
-      <c r="Q78" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R78" s="11" t="n"/>
+      <c r="R78" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S78" s="11" t="n"/>
       <c r="T78" s="11" t="n"/>
-      <c r="U78" s="11" t="n">
+      <c r="U78" s="11" t="n"/>
+      <c r="V78" s="11" t="n">
         <v>3221</v>
       </c>
-      <c r="V78" s="11" t="n"/>
       <c r="W78" s="11" t="n"/>
-      <c r="X78" s="11" t="inlineStr">
+      <c r="X78" s="11" t="n"/>
+      <c r="Y78" s="11" t="inlineStr">
         <is>
           <t>10% 확률로 분열(3초) 버프</t>
         </is>
       </c>
-      <c r="Y78" s="11" t="inlineStr">
+      <c r="Z78" s="11" t="inlineStr">
         <is>
           <t>param = 발동 확률</t>
         </is>
@@ -7114,44 +7355,47 @@
       <c r="K79" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="L79" s="11" t="inlineStr">
+      <c r="L79" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M79" s="11" t="inlineStr">
         <is>
           <t>whirlwind_chance</t>
         </is>
       </c>
-      <c r="M79" s="11" t="n"/>
-      <c r="N79" s="11" t="n">
+      <c r="N79" s="11" t="n"/>
+      <c r="O79" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="O79" s="11" t="n">
+      <c r="P79" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="P79" s="11" t="n">
+      <c r="Q79" s="11" t="n">
         <v>5600000</v>
       </c>
-      <c r="Q79" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R79" s="11" t="n"/>
+      <c r="R79" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S79" s="11" t="n"/>
       <c r="T79" s="11" t="n"/>
-      <c r="U79" s="11" t="n">
+      <c r="U79" s="11" t="n"/>
+      <c r="V79" s="11" t="n">
         <v>3227</v>
       </c>
-      <c r="V79" s="11" t="inlineStr">
+      <c r="W79" s="11" t="inlineStr">
         <is>
           <t>3219</t>
         </is>
       </c>
-      <c r="W79" s="11" t="n"/>
-      <c r="X79" s="11" t="inlineStr">
+      <c r="X79" s="11" t="n"/>
+      <c r="Y79" s="11" t="inlineStr">
         <is>
           <t>군락 충돌 시 4% 확률로 4초 지속 피해(공격력 5%)</t>
         </is>
       </c>
-      <c r="Y79" s="11" t="n"/>
+      <c r="Z79" s="11" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="n">
@@ -7197,44 +7441,47 @@
       <c r="K80" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="L80" s="11" t="inlineStr">
+      <c r="L80" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M80" s="11" t="inlineStr">
         <is>
           <t>buff_wisdom_rate</t>
         </is>
       </c>
-      <c r="M80" s="11" t="n"/>
-      <c r="N80" s="11" t="n">
+      <c r="N80" s="11" t="n"/>
+      <c r="O80" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="O80" s="11" t="n">
+      <c r="P80" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="P80" s="11" t="n">
+      <c r="Q80" s="11" t="n">
         <v>14000000</v>
       </c>
-      <c r="Q80" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R80" s="11" t="n"/>
+      <c r="R80" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S80" s="11" t="n"/>
       <c r="T80" s="11" t="n"/>
-      <c r="U80" s="11" t="n">
+      <c r="U80" s="11" t="n"/>
+      <c r="V80" s="11" t="n">
         <v>3231</v>
       </c>
-      <c r="V80" s="11" t="inlineStr">
+      <c r="W80" s="11" t="inlineStr">
         <is>
           <t>3221</t>
         </is>
       </c>
-      <c r="W80" s="11" t="n"/>
-      <c r="X80" s="11" t="inlineStr">
+      <c r="X80" s="11" t="n"/>
+      <c r="Y80" s="11" t="inlineStr">
         <is>
           <t>[지혜] 버프 3초 · 수확기 스킬 발동률 +3%</t>
         </is>
       </c>
-      <c r="Y80" s="11" t="n"/>
+      <c r="Z80" s="11" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="11" t="n">
@@ -7280,42 +7527,45 @@
       <c r="K81" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="L81" s="11" t="inlineStr">
+      <c r="L81" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M81" s="11" t="inlineStr">
         <is>
           <t>buff_heal_duration</t>
         </is>
       </c>
-      <c r="M81" s="11" t="n"/>
-      <c r="N81" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O81" s="11" t="n"/>
-      <c r="P81" s="11" t="n">
+      <c r="N81" s="11" t="n"/>
+      <c r="O81" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" s="11" t="n"/>
+      <c r="Q81" s="11" t="n">
         <v>14000000</v>
       </c>
-      <c r="Q81" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R81" s="11" t="n"/>
+      <c r="R81" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S81" s="11" t="n"/>
       <c r="T81" s="11" t="n"/>
-      <c r="U81" s="11" t="n">
+      <c r="U81" s="11" t="n"/>
+      <c r="V81" s="11" t="n">
         <v>3220</v>
       </c>
-      <c r="V81" s="11" t="inlineStr">
+      <c r="W81" s="11" t="inlineStr">
         <is>
           <t>3216</t>
         </is>
       </c>
-      <c r="W81" s="11" t="n"/>
-      <c r="X81" s="11" t="inlineStr">
+      <c r="X81" s="11" t="n"/>
+      <c r="Y81" s="11" t="inlineStr">
         <is>
           <t>포자 디버프 제거 + 약손(4초)</t>
         </is>
       </c>
-      <c r="Y81" s="11" t="n"/>
+      <c r="Z81" s="11" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="n">
@@ -7361,44 +7611,47 @@
       <c r="K82" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="L82" s="11" t="inlineStr">
+      <c r="L82" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="M82" s="11" t="inlineStr">
         <is>
           <t>chain_lightning_chance</t>
         </is>
       </c>
-      <c r="M82" s="11" t="n"/>
-      <c r="N82" s="11" t="n">
+      <c r="N82" s="11" t="n"/>
+      <c r="O82" s="11" t="n">
         <v>0.02</v>
       </c>
-      <c r="O82" s="11" t="n">
+      <c r="P82" s="11" t="n">
         <v>0.3</v>
       </c>
-      <c r="P82" s="11" t="n">
+      <c r="Q82" s="11" t="n">
         <v>23000000</v>
       </c>
-      <c r="Q82" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R82" s="11" t="n"/>
+      <c r="R82" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S82" s="11" t="n"/>
       <c r="T82" s="11" t="n"/>
-      <c r="U82" s="11" t="n">
+      <c r="U82" s="11" t="n"/>
+      <c r="V82" s="11" t="n">
         <v>3229</v>
       </c>
-      <c r="V82" s="11" t="inlineStr">
+      <c r="W82" s="11" t="inlineStr">
         <is>
           <t>3209</t>
         </is>
       </c>
-      <c r="W82" s="11" t="n"/>
-      <c r="X82" s="11" t="inlineStr">
+      <c r="X82" s="11" t="n"/>
+      <c r="Y82" s="11" t="inlineStr">
         <is>
           <t>군락 파괴 시 5% 확률로 랜덤 군락에 번개(공격력 30%)</t>
         </is>
       </c>
-      <c r="Y82" s="11" t="inlineStr">
+      <c r="Z82" s="11" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -7448,42 +7701,45 @@
       <c r="K83" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="L83" s="11" t="inlineStr">
+      <c r="L83" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="M83" s="11" t="inlineStr">
         <is>
           <t>buff_heal_duration</t>
         </is>
       </c>
-      <c r="M83" s="11" t="n"/>
-      <c r="N83" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O83" s="11" t="n"/>
-      <c r="P83" s="11" t="n">
+      <c r="N83" s="11" t="n"/>
+      <c r="O83" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P83" s="11" t="n"/>
+      <c r="Q83" s="11" t="n">
         <v>23000000</v>
       </c>
-      <c r="Q83" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R83" s="11" t="n"/>
+      <c r="R83" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S83" s="11" t="n"/>
       <c r="T83" s="11" t="n"/>
-      <c r="U83" s="11" t="n">
+      <c r="U83" s="11" t="n"/>
+      <c r="V83" s="11" t="n">
         <v>3228</v>
       </c>
-      <c r="V83" s="11" t="inlineStr">
+      <c r="W83" s="11" t="inlineStr">
         <is>
           <t>3231</t>
         </is>
       </c>
-      <c r="W83" s="11" t="n"/>
-      <c r="X83" s="11" t="inlineStr">
+      <c r="X83" s="11" t="n"/>
+      <c r="Y83" s="11" t="inlineStr">
         <is>
           <t>포자 디버프 제거 + 약손(5초)</t>
         </is>
       </c>
-      <c r="Y83" s="11" t="n"/>
+      <c r="Z83" s="11" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="11" t="n">
@@ -7529,44 +7785,47 @@
       <c r="K84" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="L84" s="11" t="inlineStr">
+      <c r="L84" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="M84" s="11" t="inlineStr">
         <is>
           <t>chain_lightning_chance</t>
         </is>
       </c>
-      <c r="M84" s="11" t="n"/>
-      <c r="N84" s="11" t="n">
+      <c r="N84" s="11" t="n"/>
+      <c r="O84" s="11" t="n">
         <v>0.02</v>
       </c>
-      <c r="O84" s="11" t="n">
+      <c r="P84" s="11" t="n">
         <v>0.3</v>
       </c>
-      <c r="P84" s="11" t="n">
+      <c r="Q84" s="11" t="n">
         <v>35000000</v>
       </c>
-      <c r="Q84" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R84" s="11" t="n"/>
+      <c r="R84" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S84" s="11" t="n"/>
       <c r="T84" s="11" t="n"/>
-      <c r="U84" s="11" t="n">
+      <c r="U84" s="11" t="n"/>
+      <c r="V84" s="11" t="n">
         <v>3226</v>
       </c>
-      <c r="V84" s="11" t="inlineStr">
+      <c r="W84" s="11" t="inlineStr">
         <is>
           <t>3232</t>
         </is>
       </c>
-      <c r="W84" s="11" t="n"/>
-      <c r="X84" s="11" t="inlineStr">
+      <c r="X84" s="11" t="n"/>
+      <c r="Y84" s="11" t="inlineStr">
         <is>
           <t>군락 파괴 시 7% 확률로 랜덤 위치에 번개(공격력 30%)</t>
         </is>
       </c>
-      <c r="Y84" s="11" t="inlineStr">
+      <c r="Z84" s="11" t="inlineStr">
         <is>
           <t>확인 필요: 원문 Lv.3만 "랜덤 위치", Lv.1·2는 "랜덤 군락"</t>
         </is>
@@ -7616,40 +7875,43 @@
       <c r="K85" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="L85" s="11" t="inlineStr">
+      <c r="L85" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="M85" s="11" t="inlineStr">
         <is>
           <t>opening_buff_chance</t>
         </is>
       </c>
-      <c r="M85" s="11" t="n"/>
-      <c r="N85" s="11" t="n">
+      <c r="N85" s="11" t="n"/>
+      <c r="O85" s="11" t="n">
         <v>0.02</v>
       </c>
-      <c r="O85" s="11" t="n"/>
-      <c r="P85" s="11" t="n">
+      <c r="P85" s="11" t="n"/>
+      <c r="Q85" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="Q85" s="11" t="inlineStr">
+      <c r="R85" s="11" t="inlineStr">
         <is>
           <t>Mycelite</t>
         </is>
       </c>
-      <c r="R85" s="11" t="n"/>
       <c r="S85" s="11" t="n"/>
-      <c r="T85" s="11" t="n">
+      <c r="T85" s="11" t="n"/>
+      <c r="U85" s="11" t="n">
         <v>1.3</v>
       </c>
-      <c r="U85" s="11" t="n">
+      <c r="V85" s="11" t="n">
         <v>3230</v>
       </c>
-      <c r="V85" s="11" t="n"/>
       <c r="W85" s="11" t="n"/>
-      <c r="X85" s="11" t="inlineStr">
+      <c r="X85" s="11" t="n"/>
+      <c r="Y85" s="11" t="inlineStr">
         <is>
           <t>게임 시작 시 보유 버프 스킬 즉시 발동 확률 +2% / Lv</t>
         </is>
       </c>
-      <c r="Y85" s="11" t="n"/>
+      <c r="Z85" s="11" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="11" t="n">
@@ -7695,44 +7957,47 @@
       <c r="K86" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="L86" s="11" t="inlineStr">
+      <c r="L86" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="M86" s="11" t="inlineStr">
         <is>
           <t>buff_split_duration</t>
         </is>
       </c>
-      <c r="M86" s="11" t="n"/>
-      <c r="N86" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="N86" s="11" t="n"/>
       <c r="O86" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P86" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="P86" s="11" t="n">
+      <c r="Q86" s="11" t="n">
         <v>35000000</v>
       </c>
-      <c r="Q86" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R86" s="11" t="n"/>
+      <c r="R86" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S86" s="11" t="n"/>
       <c r="T86" s="11" t="n"/>
-      <c r="U86" s="11" t="n">
+      <c r="U86" s="11" t="n"/>
+      <c r="V86" s="11" t="n">
         <v>3225</v>
       </c>
-      <c r="V86" s="11" t="inlineStr">
+      <c r="W86" s="11" t="inlineStr">
         <is>
           <t>3228</t>
         </is>
       </c>
-      <c r="W86" s="11" t="n"/>
-      <c r="X86" s="11" t="inlineStr">
+      <c r="X86" s="11" t="n"/>
+      <c r="Y86" s="11" t="inlineStr">
         <is>
           <t>10% 확률로 분열(4초) 버프</t>
         </is>
       </c>
-      <c r="Y86" s="11" t="n"/>
+      <c r="Z86" s="11" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="n">
@@ -7778,44 +8043,47 @@
       <c r="K87" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="L87" s="11" t="inlineStr">
+      <c r="L87" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M87" s="11" t="inlineStr">
         <is>
           <t>buff_split_duration</t>
         </is>
       </c>
-      <c r="M87" s="11" t="n"/>
-      <c r="N87" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="N87" s="11" t="n"/>
       <c r="O87" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P87" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="P87" s="11" t="n">
+      <c r="Q87" s="11" t="n">
         <v>35000000</v>
       </c>
-      <c r="Q87" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R87" s="11" t="n"/>
+      <c r="R87" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S87" s="11" t="n"/>
       <c r="T87" s="11" t="n"/>
-      <c r="U87" s="11" t="n">
+      <c r="U87" s="11" t="n"/>
+      <c r="V87" s="11" t="n">
         <v>3231</v>
       </c>
-      <c r="V87" s="11" t="inlineStr">
+      <c r="W87" s="11" t="inlineStr">
         <is>
           <t>3236</t>
         </is>
       </c>
-      <c r="W87" s="11" t="n"/>
-      <c r="X87" s="11" t="inlineStr">
+      <c r="X87" s="11" t="n"/>
+      <c r="Y87" s="11" t="inlineStr">
         <is>
           <t>10% 확률로 분열(5초) 버프</t>
         </is>
       </c>
-      <c r="Y87" s="11" t="inlineStr">
+      <c r="Z87" s="11" t="inlineStr">
         <is>
           <t>원문은 Lv.2와 같은 레어도 16</t>
         </is>
@@ -7865,44 +8133,47 @@
       <c r="K88" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="L88" s="11" t="inlineStr">
+      <c r="L88" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M88" s="11" t="inlineStr">
         <is>
           <t>spore_burst_chance</t>
         </is>
       </c>
-      <c r="M88" s="11" t="n"/>
-      <c r="N88" s="11" t="n">
+      <c r="N88" s="11" t="n"/>
+      <c r="O88" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="O88" s="11" t="n">
+      <c r="P88" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="P88" s="11" t="n">
+      <c r="Q88" s="11" t="n">
         <v>35000000</v>
       </c>
-      <c r="Q88" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R88" s="11" t="n"/>
+      <c r="R88" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S88" s="11" t="n"/>
       <c r="T88" s="11" t="n"/>
-      <c r="U88" s="11" t="n">
+      <c r="U88" s="11" t="n"/>
+      <c r="V88" s="11" t="n">
         <v>3227</v>
       </c>
-      <c r="V88" s="11" t="inlineStr">
+      <c r="W88" s="11" t="inlineStr">
         <is>
           <t>3224</t>
         </is>
       </c>
-      <c r="W88" s="11" t="n"/>
-      <c r="X88" s="11" t="inlineStr">
+      <c r="X88" s="11" t="n"/>
+      <c r="Y88" s="11" t="inlineStr">
         <is>
           <t>군락 충돌 시 3% 확률로 전체 피해(공격력 10%)</t>
         </is>
       </c>
-      <c r="Y88" s="11" t="n"/>
+      <c r="Z88" s="11" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="11" t="n">
@@ -7948,44 +8219,47 @@
       <c r="K89" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="L89" s="11" t="inlineStr">
+      <c r="L89" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="M89" s="11" t="inlineStr">
         <is>
           <t>whirlwind_chance</t>
         </is>
       </c>
-      <c r="M89" s="11" t="n"/>
-      <c r="N89" s="11" t="n">
+      <c r="N89" s="11" t="n"/>
+      <c r="O89" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="O89" s="11" t="n">
+      <c r="P89" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="P89" s="11" t="n">
+      <c r="Q89" s="11" t="n">
         <v>35000000</v>
       </c>
-      <c r="Q89" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R89" s="11" t="n"/>
+      <c r="R89" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S89" s="11" t="n"/>
       <c r="T89" s="11" t="n"/>
-      <c r="U89" s="11" t="n">
+      <c r="U89" s="11" t="n"/>
+      <c r="V89" s="11" t="n">
         <v>3232</v>
       </c>
-      <c r="V89" s="11" t="inlineStr">
+      <c r="W89" s="11" t="inlineStr">
         <is>
           <t>3229</t>
         </is>
       </c>
-      <c r="W89" s="11" t="n"/>
-      <c r="X89" s="11" t="inlineStr">
+      <c r="X89" s="11" t="n"/>
+      <c r="Y89" s="11" t="inlineStr">
         <is>
           <t>군락 충돌 시 5% 확률로 5초 지속 피해(공격력 5%)</t>
         </is>
       </c>
-      <c r="Y89" s="11" t="n"/>
+      <c r="Z89" s="11" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="n">
@@ -8031,44 +8305,47 @@
       <c r="K90" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="L90" s="11" t="inlineStr">
+      <c r="L90" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="M90" s="11" t="inlineStr">
         <is>
           <t>buff_fever_duration</t>
         </is>
       </c>
-      <c r="M90" s="11" t="n"/>
-      <c r="N90" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="N90" s="11" t="n"/>
       <c r="O90" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P90" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="P90" s="11" t="n">
+      <c r="Q90" s="11" t="n">
         <v>65000000</v>
       </c>
-      <c r="Q90" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R90" s="11" t="n"/>
+      <c r="R90" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S90" s="11" t="n"/>
       <c r="T90" s="11" t="n"/>
-      <c r="U90" s="11" t="n">
+      <c r="U90" s="11" t="n"/>
+      <c r="V90" s="11" t="n">
         <v>3236</v>
       </c>
-      <c r="V90" s="11" t="inlineStr">
+      <c r="W90" s="11" t="inlineStr">
         <is>
           <t>3222</t>
         </is>
       </c>
-      <c r="W90" s="11" t="n"/>
-      <c r="X90" s="11" t="inlineStr">
+      <c r="X90" s="11" t="n"/>
+      <c r="Y90" s="11" t="inlineStr">
         <is>
           <t>[피버] 버프 5초 · 콤보 계수 +50%</t>
         </is>
       </c>
-      <c r="Y90" s="11" t="n"/>
+      <c r="Z90" s="11" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="12" t="n">
@@ -8114,38 +8391,41 @@
       <c r="K91" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L91" s="12" t="inlineStr">
+      <c r="L91" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M91" s="12" t="inlineStr">
         <is>
           <t>harvester_damage</t>
         </is>
       </c>
-      <c r="M91" s="12" t="n"/>
-      <c r="N91" s="12" t="n">
+      <c r="N91" s="12" t="n"/>
+      <c r="O91" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="O91" s="12" t="n"/>
-      <c r="P91" s="12" t="n">
+      <c r="P91" s="12" t="n"/>
+      <c r="Q91" s="12" t="n">
         <v>130</v>
       </c>
-      <c r="Q91" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R91" s="12" t="n"/>
+      <c r="R91" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S91" s="12" t="n"/>
       <c r="T91" s="12" t="n"/>
-      <c r="U91" s="12" t="n">
+      <c r="U91" s="12" t="n"/>
+      <c r="V91" s="12" t="n">
         <v>3001</v>
       </c>
-      <c r="V91" s="12" t="n"/>
       <c r="W91" s="12" t="n"/>
-      <c r="X91" s="12" t="inlineStr">
+      <c r="X91" s="12" t="n"/>
+      <c r="Y91" s="12" t="inlineStr">
         <is>
           <t>공격력 +2 (1 → 3)</t>
         </is>
       </c>
-      <c r="Y91" s="12" t="n"/>
+      <c r="Z91" s="12" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="12" t="n">
@@ -8191,38 +8471,41 @@
       <c r="K92" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L92" s="12" t="inlineStr">
+      <c r="L92" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M92" s="12" t="inlineStr">
         <is>
           <t>combo_rate</t>
         </is>
       </c>
-      <c r="M92" s="12" t="n"/>
-      <c r="N92" s="12" t="n">
+      <c r="N92" s="12" t="n"/>
+      <c r="O92" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="O92" s="12" t="n"/>
-      <c r="P92" s="12" t="n">
+      <c r="P92" s="12" t="n"/>
+      <c r="Q92" s="12" t="n">
         <v>240</v>
       </c>
-      <c r="Q92" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R92" s="12" t="n"/>
+      <c r="R92" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S92" s="12" t="n"/>
       <c r="T92" s="12" t="n"/>
-      <c r="U92" s="12" t="n">
+      <c r="U92" s="12" t="n"/>
+      <c r="V92" s="12" t="n">
         <v>3303</v>
       </c>
-      <c r="V92" s="12" t="n"/>
       <c r="W92" s="12" t="n"/>
-      <c r="X92" s="12" t="inlineStr">
+      <c r="X92" s="12" t="n"/>
+      <c r="Y92" s="12" t="inlineStr">
         <is>
           <t>콤보 계수 +20%</t>
         </is>
       </c>
-      <c r="Y92" s="12" t="n"/>
+      <c r="Z92" s="12" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="12" t="n">
@@ -8268,38 +8551,41 @@
       <c r="K93" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L93" s="12" t="inlineStr">
+      <c r="L93" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M93" s="12" t="inlineStr">
         <is>
           <t>harvester_speed</t>
         </is>
       </c>
-      <c r="M93" s="12" t="n"/>
-      <c r="N93" s="12" t="n">
+      <c r="N93" s="12" t="n"/>
+      <c r="O93" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="O93" s="12" t="n"/>
-      <c r="P93" s="12" t="n">
+      <c r="P93" s="12" t="n"/>
+      <c r="Q93" s="12" t="n">
         <v>170</v>
       </c>
-      <c r="Q93" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R93" s="12" t="n"/>
+      <c r="R93" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S93" s="12" t="n"/>
       <c r="T93" s="12" t="n"/>
-      <c r="U93" s="12" t="n">
+      <c r="U93" s="12" t="n"/>
+      <c r="V93" s="12" t="n">
         <v>3301</v>
       </c>
-      <c r="V93" s="12" t="n"/>
       <c r="W93" s="12" t="n"/>
-      <c r="X93" s="12" t="inlineStr">
+      <c r="X93" s="12" t="n"/>
+      <c r="Y93" s="12" t="inlineStr">
         <is>
           <t>수확기 속도 +10%</t>
         </is>
       </c>
-      <c r="Y93" s="12" t="n"/>
+      <c r="Z93" s="12" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="n">
@@ -8345,38 +8631,41 @@
       <c r="K94" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L94" s="12" t="inlineStr">
+      <c r="L94" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M94" s="12" t="inlineStr">
         <is>
           <t>crit_chance</t>
         </is>
       </c>
-      <c r="M94" s="12" t="n"/>
-      <c r="N94" s="12" t="n">
+      <c r="N94" s="12" t="n"/>
+      <c r="O94" s="12" t="n">
         <v>0.02</v>
       </c>
-      <c r="O94" s="12" t="n"/>
-      <c r="P94" s="12" t="n">
+      <c r="P94" s="12" t="n"/>
+      <c r="Q94" s="12" t="n">
         <v>240</v>
       </c>
-      <c r="Q94" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R94" s="12" t="n"/>
+      <c r="R94" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S94" s="12" t="n"/>
       <c r="T94" s="12" t="n"/>
-      <c r="U94" s="12" t="n">
+      <c r="U94" s="12" t="n"/>
+      <c r="V94" s="12" t="n">
         <v>3301</v>
       </c>
-      <c r="V94" s="12" t="n"/>
       <c r="W94" s="12" t="n"/>
-      <c r="X94" s="12" t="inlineStr">
+      <c r="X94" s="12" t="n"/>
+      <c r="Y94" s="12" t="inlineStr">
         <is>
           <t>치명타 확률 2%</t>
         </is>
       </c>
-      <c r="Y94" s="12" t="n"/>
+      <c r="Z94" s="12" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="12" t="n">
@@ -8422,38 +8711,41 @@
       <c r="K95" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L95" s="12" t="inlineStr">
+      <c r="L95" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M95" s="12" t="inlineStr">
         <is>
           <t>bar_length</t>
         </is>
       </c>
-      <c r="M95" s="12" t="n"/>
-      <c r="N95" s="12" t="n">
+      <c r="N95" s="12" t="n"/>
+      <c r="O95" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="O95" s="12" t="n"/>
-      <c r="P95" s="12" t="n">
+      <c r="P95" s="12" t="n"/>
+      <c r="Q95" s="12" t="n">
         <v>800</v>
       </c>
-      <c r="Q95" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R95" s="12" t="n"/>
+      <c r="R95" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S95" s="12" t="n"/>
       <c r="T95" s="12" t="n"/>
-      <c r="U95" s="12" t="n">
+      <c r="U95" s="12" t="n"/>
+      <c r="V95" s="12" t="n">
         <v>3302</v>
       </c>
-      <c r="V95" s="12" t="n"/>
       <c r="W95" s="12" t="n"/>
-      <c r="X95" s="12" t="inlineStr">
+      <c r="X95" s="12" t="n"/>
+      <c r="Y95" s="12" t="inlineStr">
         <is>
           <t>바 길이 +20%</t>
         </is>
       </c>
-      <c r="Y95" s="12" t="n"/>
+      <c r="Z95" s="12" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="12" t="n">
@@ -8499,42 +8791,45 @@
       <c r="K96" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L96" s="12" t="inlineStr">
+      <c r="L96" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M96" s="12" t="inlineStr">
         <is>
           <t>harvester_damage</t>
         </is>
       </c>
-      <c r="M96" s="12" t="n"/>
-      <c r="N96" s="12" t="n">
+      <c r="N96" s="12" t="n"/>
+      <c r="O96" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="O96" s="12" t="n"/>
-      <c r="P96" s="12" t="n">
+      <c r="P96" s="12" t="n"/>
+      <c r="Q96" s="12" t="n">
         <v>800</v>
       </c>
-      <c r="Q96" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R96" s="12" t="n"/>
+      <c r="R96" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S96" s="12" t="n"/>
       <c r="T96" s="12" t="n"/>
-      <c r="U96" s="12" t="n">
+      <c r="U96" s="12" t="n"/>
+      <c r="V96" s="12" t="n">
         <v>3304</v>
       </c>
-      <c r="V96" s="12" t="inlineStr">
+      <c r="W96" s="12" t="inlineStr">
         <is>
           <t>3301</t>
         </is>
       </c>
-      <c r="W96" s="12" t="n"/>
-      <c r="X96" s="12" t="inlineStr">
+      <c r="X96" s="12" t="n"/>
+      <c r="Y96" s="12" t="inlineStr">
         <is>
           <t>공격력 +2 (3 → 5)</t>
         </is>
       </c>
-      <c r="Y96" s="12" t="n"/>
+      <c r="Z96" s="12" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="12" t="n">
@@ -8580,38 +8875,41 @@
       <c r="K97" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L97" s="12" t="inlineStr">
+      <c r="L97" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M97" s="12" t="inlineStr">
         <is>
           <t>harvester_size</t>
         </is>
       </c>
-      <c r="M97" s="12" t="n"/>
-      <c r="N97" s="12" t="n">
+      <c r="N97" s="12" t="n"/>
+      <c r="O97" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="O97" s="12" t="n"/>
-      <c r="P97" s="12" t="n">
+      <c r="P97" s="12" t="n"/>
+      <c r="Q97" s="12" t="n">
         <v>1400</v>
       </c>
-      <c r="Q97" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R97" s="12" t="n"/>
+      <c r="R97" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S97" s="12" t="n"/>
       <c r="T97" s="12" t="n"/>
-      <c r="U97" s="12" t="n">
+      <c r="U97" s="12" t="n"/>
+      <c r="V97" s="12" t="n">
         <v>3303</v>
       </c>
-      <c r="V97" s="12" t="n"/>
       <c r="W97" s="12" t="n"/>
-      <c r="X97" s="12" t="inlineStr">
+      <c r="X97" s="12" t="n"/>
+      <c r="Y97" s="12" t="inlineStr">
         <is>
           <t>수확기 크기 +10%</t>
         </is>
       </c>
-      <c r="Y97" s="12" t="n"/>
+      <c r="Z97" s="12" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="12" t="n">
@@ -8657,42 +8955,45 @@
       <c r="K98" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L98" s="12" t="inlineStr">
+      <c r="L98" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M98" s="12" t="inlineStr">
         <is>
           <t>harvester_size</t>
         </is>
       </c>
-      <c r="M98" s="12" t="n"/>
-      <c r="N98" s="12" t="n">
+      <c r="N98" s="12" t="n"/>
+      <c r="O98" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="O98" s="12" t="n"/>
-      <c r="P98" s="12" t="n">
+      <c r="P98" s="12" t="n"/>
+      <c r="Q98" s="12" t="n">
         <v>1400</v>
       </c>
-      <c r="Q98" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R98" s="12" t="n"/>
+      <c r="R98" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S98" s="12" t="n"/>
       <c r="T98" s="12" t="n"/>
-      <c r="U98" s="12" t="n">
+      <c r="U98" s="12" t="n"/>
+      <c r="V98" s="12" t="n">
         <v>3303</v>
       </c>
-      <c r="V98" s="12" t="inlineStr">
+      <c r="W98" s="12" t="inlineStr">
         <is>
           <t>3307</t>
         </is>
       </c>
-      <c r="W98" s="12" t="n"/>
-      <c r="X98" s="12" t="inlineStr">
+      <c r="X98" s="12" t="n"/>
+      <c r="Y98" s="12" t="inlineStr">
         <is>
           <t>수확기 크기 +20%</t>
         </is>
       </c>
-      <c r="Y98" s="12" t="inlineStr">
+      <c r="Z98" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%. 원문은 Lv.1과 같은 레어도 5</t>
         </is>
@@ -8742,42 +9043,45 @@
       <c r="K99" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L99" s="12" t="inlineStr">
+      <c r="L99" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M99" s="12" t="inlineStr">
         <is>
           <t>harvester_damage</t>
         </is>
       </c>
-      <c r="M99" s="12" t="n"/>
-      <c r="N99" s="12" t="n">
+      <c r="N99" s="12" t="n"/>
+      <c r="O99" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="O99" s="12" t="n"/>
-      <c r="P99" s="12" t="n">
+      <c r="P99" s="12" t="n"/>
+      <c r="Q99" s="12" t="n">
         <v>3200</v>
       </c>
-      <c r="Q99" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R99" s="12" t="n"/>
+      <c r="R99" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S99" s="12" t="n"/>
       <c r="T99" s="12" t="n"/>
-      <c r="U99" s="12" t="n">
+      <c r="U99" s="12" t="n"/>
+      <c r="V99" s="12" t="n">
         <v>3304</v>
       </c>
-      <c r="V99" s="12" t="inlineStr">
+      <c r="W99" s="12" t="inlineStr">
         <is>
           <t>3306</t>
         </is>
       </c>
-      <c r="W99" s="12" t="n"/>
-      <c r="X99" s="12" t="inlineStr">
+      <c r="X99" s="12" t="n"/>
+      <c r="Y99" s="12" t="inlineStr">
         <is>
           <t>공격력 +2 (5 → 7)</t>
         </is>
       </c>
-      <c r="Y99" s="12" t="inlineStr">
+      <c r="Z99" s="12" t="inlineStr">
         <is>
           <t>확인 필요: 원문은 "+3 (5 → 7)", 화살표 기준 +2로 넣음</t>
         </is>
@@ -8827,42 +9131,45 @@
       <c r="K100" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L100" s="12" t="inlineStr">
+      <c r="L100" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M100" s="12" t="inlineStr">
         <is>
           <t>bar_length</t>
         </is>
       </c>
-      <c r="M100" s="12" t="n"/>
-      <c r="N100" s="12" t="n">
+      <c r="N100" s="12" t="n"/>
+      <c r="O100" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="O100" s="12" t="n"/>
-      <c r="P100" s="12" t="n">
+      <c r="P100" s="12" t="n"/>
+      <c r="Q100" s="12" t="n">
         <v>4500</v>
       </c>
-      <c r="Q100" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R100" s="12" t="n"/>
+      <c r="R100" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S100" s="12" t="n"/>
       <c r="T100" s="12" t="n"/>
-      <c r="U100" s="12" t="n">
+      <c r="U100" s="12" t="n"/>
+      <c r="V100" s="12" t="n">
         <v>3308</v>
       </c>
-      <c r="V100" s="12" t="inlineStr">
+      <c r="W100" s="12" t="inlineStr">
         <is>
           <t>3305</t>
         </is>
       </c>
-      <c r="W100" s="12" t="n"/>
-      <c r="X100" s="12" t="inlineStr">
+      <c r="X100" s="12" t="n"/>
+      <c r="Y100" s="12" t="inlineStr">
         <is>
           <t>바 길이 +30%</t>
         </is>
       </c>
-      <c r="Y100" s="12" t="inlineStr">
+      <c r="Z100" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%</t>
         </is>
@@ -8912,42 +9219,45 @@
       <c r="K101" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L101" s="12" t="inlineStr">
+      <c r="L101" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M101" s="12" t="inlineStr">
         <is>
           <t>harvester_size</t>
         </is>
       </c>
-      <c r="M101" s="12" t="n"/>
-      <c r="N101" s="12" t="n">
+      <c r="N101" s="12" t="n"/>
+      <c r="O101" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="O101" s="12" t="n"/>
-      <c r="P101" s="12" t="n">
+      <c r="P101" s="12" t="n"/>
+      <c r="Q101" s="12" t="n">
         <v>4300</v>
       </c>
-      <c r="Q101" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R101" s="12" t="n"/>
+      <c r="R101" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S101" s="12" t="n"/>
       <c r="T101" s="12" t="n"/>
-      <c r="U101" s="12" t="n">
+      <c r="U101" s="12" t="n"/>
+      <c r="V101" s="12" t="n">
         <v>3312</v>
       </c>
-      <c r="V101" s="12" t="inlineStr">
+      <c r="W101" s="12" t="inlineStr">
         <is>
           <t>3308</t>
         </is>
       </c>
-      <c r="W101" s="12" t="n"/>
-      <c r="X101" s="12" t="inlineStr">
+      <c r="X101" s="12" t="n"/>
+      <c r="Y101" s="12" t="inlineStr">
         <is>
           <t>수확기 크기 +30%</t>
         </is>
       </c>
-      <c r="Y101" s="12" t="inlineStr">
+      <c r="Z101" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%</t>
         </is>
@@ -8997,42 +9307,45 @@
       <c r="K102" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L102" s="12" t="inlineStr">
+      <c r="L102" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M102" s="12" t="inlineStr">
         <is>
           <t>harvester_speed</t>
         </is>
       </c>
-      <c r="M102" s="12" t="n"/>
-      <c r="N102" s="12" t="n">
+      <c r="N102" s="12" t="n"/>
+      <c r="O102" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="O102" s="12" t="n"/>
-      <c r="P102" s="12" t="n">
+      <c r="P102" s="12" t="n"/>
+      <c r="Q102" s="12" t="n">
         <v>4300</v>
       </c>
-      <c r="Q102" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R102" s="12" t="n"/>
+      <c r="R102" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S102" s="12" t="n"/>
       <c r="T102" s="12" t="n"/>
-      <c r="U102" s="12" t="n">
+      <c r="U102" s="12" t="n"/>
+      <c r="V102" s="12" t="n">
         <v>3307</v>
       </c>
-      <c r="V102" s="12" t="inlineStr">
+      <c r="W102" s="12" t="inlineStr">
         <is>
           <t>3303</t>
         </is>
       </c>
-      <c r="W102" s="12" t="n"/>
-      <c r="X102" s="12" t="inlineStr">
+      <c r="X102" s="12" t="n"/>
+      <c r="Y102" s="12" t="inlineStr">
         <is>
           <t>수확기 속도 +20%</t>
         </is>
       </c>
-      <c r="Y102" s="12" t="inlineStr">
+      <c r="Z102" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +10%</t>
         </is>
@@ -9082,42 +9395,45 @@
       <c r="K103" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L103" s="12" t="inlineStr">
+      <c r="L103" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M103" s="12" t="inlineStr">
         <is>
           <t>crit_chance</t>
         </is>
       </c>
-      <c r="M103" s="12" t="n"/>
-      <c r="N103" s="12" t="n">
+      <c r="N103" s="12" t="n"/>
+      <c r="O103" s="12" t="n">
         <v>0.02</v>
       </c>
-      <c r="O103" s="12" t="n"/>
-      <c r="P103" s="12" t="n">
+      <c r="P103" s="12" t="n"/>
+      <c r="Q103" s="12" t="n">
         <v>10000</v>
       </c>
-      <c r="Q103" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R103" s="12" t="n"/>
+      <c r="R103" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S103" s="12" t="n"/>
       <c r="T103" s="12" t="n"/>
-      <c r="U103" s="12" t="n">
+      <c r="U103" s="12" t="n"/>
+      <c r="V103" s="12" t="n">
         <v>3309</v>
       </c>
-      <c r="V103" s="12" t="inlineStr">
+      <c r="W103" s="12" t="inlineStr">
         <is>
           <t>3304</t>
         </is>
       </c>
-      <c r="W103" s="12" t="n"/>
-      <c r="X103" s="12" t="inlineStr">
+      <c r="X103" s="12" t="n"/>
+      <c r="Y103" s="12" t="inlineStr">
         <is>
           <t>치명타 확률 4%</t>
         </is>
       </c>
-      <c r="Y103" s="12" t="inlineStr">
+      <c r="Z103" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +2%</t>
         </is>
@@ -9167,38 +9483,41 @@
       <c r="K104" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L104" s="12" t="inlineStr">
+      <c r="L104" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M104" s="12" t="inlineStr">
         <is>
           <t>orbit_harvester_count</t>
         </is>
       </c>
-      <c r="M104" s="12" t="n"/>
-      <c r="N104" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O104" s="12" t="n"/>
-      <c r="P104" s="12" t="n">
+      <c r="N104" s="12" t="n"/>
+      <c r="O104" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P104" s="12" t="n"/>
+      <c r="Q104" s="12" t="n">
         <v>16000</v>
       </c>
-      <c r="Q104" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R104" s="12" t="n"/>
+      <c r="R104" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S104" s="12" t="n"/>
       <c r="T104" s="12" t="n"/>
-      <c r="U104" s="12" t="n">
+      <c r="U104" s="12" t="n"/>
+      <c r="V104" s="12" t="n">
         <v>3313</v>
       </c>
-      <c r="V104" s="12" t="n"/>
       <c r="W104" s="12" t="n"/>
-      <c r="X104" s="12" t="inlineStr">
+      <c r="X104" s="12" t="n"/>
+      <c r="Y104" s="12" t="inlineStr">
         <is>
           <t>회전 꼬마 수확기 +1 (0 → 1)</t>
         </is>
       </c>
-      <c r="Y104" s="12" t="n"/>
+      <c r="Z104" s="12" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="12" t="n">
@@ -9244,42 +9563,45 @@
       <c r="K105" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L105" s="12" t="inlineStr">
+      <c r="L105" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M105" s="12" t="inlineStr">
         <is>
           <t>bar_length</t>
         </is>
       </c>
-      <c r="M105" s="12" t="n"/>
-      <c r="N105" s="12" t="n">
+      <c r="N105" s="12" t="n"/>
+      <c r="O105" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="O105" s="12" t="n"/>
-      <c r="P105" s="12" t="n">
+      <c r="P105" s="12" t="n"/>
+      <c r="Q105" s="12" t="n">
         <v>53000</v>
       </c>
-      <c r="Q105" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R105" s="12" t="n"/>
+      <c r="R105" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S105" s="12" t="n"/>
       <c r="T105" s="12" t="n"/>
-      <c r="U105" s="12" t="n">
+      <c r="U105" s="12" t="n"/>
+      <c r="V105" s="12" t="n">
         <v>3312</v>
       </c>
-      <c r="V105" s="12" t="inlineStr">
+      <c r="W105" s="12" t="inlineStr">
         <is>
           <t>3310</t>
         </is>
       </c>
-      <c r="W105" s="12" t="n"/>
-      <c r="X105" s="12" t="inlineStr">
+      <c r="X105" s="12" t="n"/>
+      <c r="Y105" s="12" t="inlineStr">
         <is>
           <t>바 길이 +50%</t>
         </is>
       </c>
-      <c r="Y105" s="12" t="inlineStr">
+      <c r="Z105" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +20%</t>
         </is>
@@ -9329,38 +9651,41 @@
       <c r="K106" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L106" s="12" t="inlineStr">
+      <c r="L106" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M106" s="12" t="inlineStr">
         <is>
           <t>boss_damage</t>
         </is>
       </c>
-      <c r="M106" s="12" t="n"/>
-      <c r="N106" s="12" t="n">
+      <c r="N106" s="12" t="n"/>
+      <c r="O106" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="O106" s="12" t="n"/>
-      <c r="P106" s="12" t="n">
+      <c r="P106" s="12" t="n"/>
+      <c r="Q106" s="12" t="n">
         <v>37000</v>
       </c>
-      <c r="Q106" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R106" s="12" t="n"/>
+      <c r="R106" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S106" s="12" t="n"/>
       <c r="T106" s="12" t="n"/>
-      <c r="U106" s="12" t="n">
+      <c r="U106" s="12" t="n"/>
+      <c r="V106" s="12" t="n">
         <v>3313</v>
       </c>
-      <c r="V106" s="12" t="n"/>
       <c r="W106" s="12" t="n"/>
-      <c r="X106" s="12" t="inlineStr">
+      <c r="X106" s="12" t="n"/>
+      <c r="Y106" s="12" t="inlineStr">
         <is>
           <t>보스 피해 +20%</t>
         </is>
       </c>
-      <c r="Y106" s="12" t="n"/>
+      <c r="Z106" s="12" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="12" t="n">
@@ -9406,42 +9731,45 @@
       <c r="K107" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L107" s="12" t="inlineStr">
+      <c r="L107" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M107" s="12" t="inlineStr">
         <is>
           <t>combo_rate</t>
         </is>
       </c>
-      <c r="M107" s="12" t="n"/>
-      <c r="N107" s="12" t="n">
+      <c r="N107" s="12" t="n"/>
+      <c r="O107" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="O107" s="12" t="n"/>
-      <c r="P107" s="12" t="n">
+      <c r="P107" s="12" t="n"/>
+      <c r="Q107" s="12" t="n">
         <v>53000</v>
       </c>
-      <c r="Q107" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R107" s="12" t="n"/>
+      <c r="R107" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S107" s="12" t="n"/>
       <c r="T107" s="12" t="n"/>
-      <c r="U107" s="12" t="n">
+      <c r="U107" s="12" t="n"/>
+      <c r="V107" s="12" t="n">
         <v>3310</v>
       </c>
-      <c r="V107" s="12" t="inlineStr">
+      <c r="W107" s="12" t="inlineStr">
         <is>
           <t>3302</t>
         </is>
       </c>
-      <c r="W107" s="12" t="n"/>
-      <c r="X107" s="12" t="inlineStr">
+      <c r="X107" s="12" t="n"/>
+      <c r="Y107" s="12" t="inlineStr">
         <is>
           <t>콤보 계수 +40%</t>
         </is>
       </c>
-      <c r="Y107" s="12" t="inlineStr">
+      <c r="Z107" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +20%</t>
         </is>
@@ -9491,38 +9819,41 @@
       <c r="K108" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L108" s="12" t="inlineStr">
+      <c r="L108" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M108" s="12" t="inlineStr">
         <is>
           <t>round_time</t>
         </is>
       </c>
-      <c r="M108" s="12" t="n"/>
-      <c r="N108" s="12" t="n">
+      <c r="N108" s="12" t="n"/>
+      <c r="O108" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="O108" s="12" t="n"/>
-      <c r="P108" s="12" t="n">
+      <c r="P108" s="12" t="n"/>
+      <c r="Q108" s="12" t="n">
         <v>21000</v>
       </c>
-      <c r="Q108" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R108" s="12" t="n"/>
+      <c r="R108" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S108" s="12" t="n"/>
       <c r="T108" s="12" t="n"/>
-      <c r="U108" s="12" t="n">
+      <c r="U108" s="12" t="n"/>
+      <c r="V108" s="12" t="n">
         <v>3310</v>
       </c>
-      <c r="V108" s="12" t="n"/>
       <c r="W108" s="12" t="n"/>
-      <c r="X108" s="12" t="inlineStr">
+      <c r="X108" s="12" t="n"/>
+      <c r="Y108" s="12" t="inlineStr">
         <is>
           <t>지속 시간 +3초 (15 → 18)</t>
         </is>
       </c>
-      <c r="Y108" s="12" t="inlineStr">
+      <c r="Z108" s="12" t="inlineStr">
         <is>
           <t>확인 필요: 원문은 "+2초 (15 → 18)", 화살표 기준 +3으로 넣음</t>
         </is>
@@ -9572,42 +9903,45 @@
       <c r="K109" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L109" s="12" t="inlineStr">
+      <c r="L109" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M109" s="12" t="inlineStr">
         <is>
           <t>crit_chance</t>
         </is>
       </c>
-      <c r="M109" s="12" t="n"/>
-      <c r="N109" s="12" t="n">
+      <c r="N109" s="12" t="n"/>
+      <c r="O109" s="12" t="n">
         <v>0.02</v>
       </c>
-      <c r="O109" s="12" t="n"/>
-      <c r="P109" s="12" t="n">
+      <c r="P109" s="12" t="n"/>
+      <c r="Q109" s="12" t="n">
         <v>180000</v>
       </c>
-      <c r="Q109" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R109" s="12" t="n"/>
+      <c r="R109" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S109" s="12" t="n"/>
       <c r="T109" s="12" t="n"/>
-      <c r="U109" s="12" t="n">
+      <c r="U109" s="12" t="n"/>
+      <c r="V109" s="12" t="n">
         <v>3306</v>
       </c>
-      <c r="V109" s="12" t="inlineStr">
+      <c r="W109" s="12" t="inlineStr">
         <is>
           <t>3313</t>
         </is>
       </c>
-      <c r="W109" s="12" t="n"/>
-      <c r="X109" s="12" t="inlineStr">
+      <c r="X109" s="12" t="n"/>
+      <c r="Y109" s="12" t="inlineStr">
         <is>
           <t>치명타 확률 6%</t>
         </is>
       </c>
-      <c r="Y109" s="12" t="n"/>
+      <c r="Z109" s="12" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="12" t="n">
@@ -9653,42 +9987,45 @@
       <c r="K110" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L110" s="12" t="inlineStr">
+      <c r="L110" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M110" s="12" t="inlineStr">
         <is>
           <t>harvester_damage</t>
         </is>
       </c>
-      <c r="M110" s="12" t="n"/>
-      <c r="N110" s="12" t="n">
+      <c r="N110" s="12" t="n"/>
+      <c r="O110" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="O110" s="12" t="n"/>
-      <c r="P110" s="12" t="n">
+      <c r="P110" s="12" t="n"/>
+      <c r="Q110" s="12" t="n">
         <v>180000</v>
       </c>
-      <c r="Q110" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R110" s="12" t="n"/>
+      <c r="R110" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S110" s="12" t="n"/>
       <c r="T110" s="12" t="n"/>
-      <c r="U110" s="12" t="n">
+      <c r="U110" s="12" t="n"/>
+      <c r="V110" s="12" t="n">
         <v>3314</v>
       </c>
-      <c r="V110" s="12" t="inlineStr">
+      <c r="W110" s="12" t="inlineStr">
         <is>
           <t>3309</t>
         </is>
       </c>
-      <c r="W110" s="12" t="n"/>
-      <c r="X110" s="12" t="inlineStr">
+      <c r="X110" s="12" t="n"/>
+      <c r="Y110" s="12" t="inlineStr">
         <is>
           <t>공격력 +3 (7 → 10)</t>
         </is>
       </c>
-      <c r="Y110" s="12" t="n"/>
+      <c r="Z110" s="12" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="12" t="n">
@@ -9734,42 +10071,45 @@
       <c r="K111" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L111" s="12" t="inlineStr">
+      <c r="L111" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M111" s="12" t="inlineStr">
         <is>
           <t>boss_damage</t>
         </is>
       </c>
-      <c r="M111" s="12" t="n"/>
-      <c r="N111" s="12" t="n">
+      <c r="N111" s="12" t="n"/>
+      <c r="O111" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="O111" s="12" t="n"/>
-      <c r="P111" s="12" t="n">
+      <c r="P111" s="12" t="n"/>
+      <c r="Q111" s="12" t="n">
         <v>560000</v>
       </c>
-      <c r="Q111" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R111" s="12" t="n"/>
+      <c r="R111" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S111" s="12" t="n"/>
       <c r="T111" s="12" t="n"/>
-      <c r="U111" s="12" t="n">
+      <c r="U111" s="12" t="n"/>
+      <c r="V111" s="12" t="n">
         <v>3313</v>
       </c>
-      <c r="V111" s="12" t="inlineStr">
+      <c r="W111" s="12" t="inlineStr">
         <is>
           <t>3316</t>
         </is>
       </c>
-      <c r="W111" s="12" t="n"/>
-      <c r="X111" s="12" t="inlineStr">
+      <c r="X111" s="12" t="n"/>
+      <c r="Y111" s="12" t="inlineStr">
         <is>
           <t>보스 피해 +40%</t>
         </is>
       </c>
-      <c r="Y111" s="12" t="n"/>
+      <c r="Z111" s="12" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="12" t="n">
@@ -9815,40 +10155,43 @@
       <c r="K112" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L112" s="12" t="inlineStr">
+      <c r="L112" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M112" s="12" t="inlineStr">
         <is>
           <t>clone_bar_duration</t>
         </is>
       </c>
-      <c r="M112" s="12" t="n"/>
-      <c r="N112" s="12" t="n">
+      <c r="N112" s="12" t="n"/>
+      <c r="O112" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="O112" s="12" t="n">
+      <c r="P112" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="P112" s="12" t="n">
+      <c r="Q112" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="Q112" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R112" s="12" t="n"/>
+      <c r="R112" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S112" s="12" t="n"/>
       <c r="T112" s="12" t="n"/>
-      <c r="U112" s="12" t="n">
+      <c r="U112" s="12" t="n"/>
+      <c r="V112" s="12" t="n">
         <v>3324</v>
       </c>
-      <c r="V112" s="12" t="n"/>
       <c r="W112" s="12" t="n"/>
-      <c r="X112" s="12" t="inlineStr">
+      <c r="X112" s="12" t="n"/>
+      <c r="Y112" s="12" t="inlineStr">
         <is>
           <t>10% 확률로 3초 분신 바</t>
         </is>
       </c>
-      <c r="Y112" s="12" t="inlineStr">
+      <c r="Z112" s="12" t="inlineStr">
         <is>
           <t>param = 발동 확률</t>
         </is>
@@ -9898,42 +10241,45 @@
       <c r="K113" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L113" s="12" t="inlineStr">
+      <c r="L113" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M113" s="12" t="inlineStr">
         <is>
           <t>round_time</t>
         </is>
       </c>
-      <c r="M113" s="12" t="n"/>
-      <c r="N113" s="12" t="n">
+      <c r="N113" s="12" t="n"/>
+      <c r="O113" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="O113" s="12" t="n"/>
-      <c r="P113" s="12" t="n">
+      <c r="P113" s="12" t="n"/>
+      <c r="Q113" s="12" t="n">
         <v>390000</v>
       </c>
-      <c r="Q113" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R113" s="12" t="n"/>
+      <c r="R113" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S113" s="12" t="n"/>
       <c r="T113" s="12" t="n"/>
-      <c r="U113" s="12" t="n">
+      <c r="U113" s="12" t="n"/>
+      <c r="V113" s="12" t="n">
         <v>3317</v>
       </c>
-      <c r="V113" s="12" t="inlineStr">
+      <c r="W113" s="12" t="inlineStr">
         <is>
           <t>3318</t>
         </is>
       </c>
-      <c r="W113" s="12" t="n"/>
-      <c r="X113" s="12" t="inlineStr">
+      <c r="X113" s="12" t="n"/>
+      <c r="Y113" s="12" t="inlineStr">
         <is>
           <t>지속 시간 +3초 (18 → 21)</t>
         </is>
       </c>
-      <c r="Y113" s="12" t="n"/>
+      <c r="Z113" s="12" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="12" t="n">
@@ -9979,42 +10325,45 @@
       <c r="K114" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L114" s="12" t="inlineStr">
+      <c r="L114" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M114" s="12" t="inlineStr">
         <is>
           <t>harvester_speed</t>
         </is>
       </c>
-      <c r="M114" s="12" t="n"/>
-      <c r="N114" s="12" t="n">
+      <c r="N114" s="12" t="n"/>
+      <c r="O114" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="O114" s="12" t="n"/>
-      <c r="P114" s="12" t="n">
+      <c r="P114" s="12" t="n"/>
+      <c r="Q114" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="Q114" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R114" s="12" t="n"/>
+      <c r="R114" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S114" s="12" t="n"/>
       <c r="T114" s="12" t="n"/>
-      <c r="U114" s="12" t="n">
+      <c r="U114" s="12" t="n"/>
+      <c r="V114" s="12" t="n">
         <v>3315</v>
       </c>
-      <c r="V114" s="12" t="inlineStr">
+      <c r="W114" s="12" t="inlineStr">
         <is>
           <t>3312</t>
         </is>
       </c>
-      <c r="W114" s="12" t="n"/>
-      <c r="X114" s="12" t="inlineStr">
+      <c r="X114" s="12" t="n"/>
+      <c r="Y114" s="12" t="inlineStr">
         <is>
           <t>수확기 속도 +30%</t>
         </is>
       </c>
-      <c r="Y114" s="12" t="n"/>
+      <c r="Z114" s="12" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="12" t="n">
@@ -10060,42 +10409,45 @@
       <c r="K115" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="L115" s="12" t="inlineStr">
+      <c r="L115" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M115" s="12" t="inlineStr">
         <is>
           <t>combo_rate</t>
         </is>
       </c>
-      <c r="M115" s="12" t="n"/>
-      <c r="N115" s="12" t="n">
+      <c r="N115" s="12" t="n"/>
+      <c r="O115" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="O115" s="12" t="n"/>
-      <c r="P115" s="12" t="n">
+      <c r="P115" s="12" t="n"/>
+      <c r="Q115" s="12" t="n">
         <v>1900000</v>
       </c>
-      <c r="Q115" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R115" s="12" t="n"/>
+      <c r="R115" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S115" s="12" t="n"/>
       <c r="T115" s="12" t="n"/>
-      <c r="U115" s="12" t="n">
+      <c r="U115" s="12" t="n"/>
+      <c r="V115" s="12" t="n">
         <v>3318</v>
       </c>
-      <c r="V115" s="12" t="inlineStr">
+      <c r="W115" s="12" t="inlineStr">
         <is>
           <t>3317</t>
         </is>
       </c>
-      <c r="W115" s="12" t="n"/>
-      <c r="X115" s="12" t="inlineStr">
+      <c r="X115" s="12" t="n"/>
+      <c r="Y115" s="12" t="inlineStr">
         <is>
           <t>콤보 계수 +60%</t>
         </is>
       </c>
-      <c r="Y115" s="12" t="n"/>
+      <c r="Z115" s="12" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="12" t="n">
@@ -10141,42 +10493,45 @@
       <c r="K116" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="L116" s="12" t="inlineStr">
+      <c r="L116" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M116" s="12" t="inlineStr">
         <is>
           <t>orbit_harvester_count</t>
         </is>
       </c>
-      <c r="M116" s="12" t="n"/>
-      <c r="N116" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O116" s="12" t="n"/>
-      <c r="P116" s="12" t="n">
+      <c r="N116" s="12" t="n"/>
+      <c r="O116" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P116" s="12" t="n"/>
+      <c r="Q116" s="12" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q116" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R116" s="12" t="n"/>
+      <c r="R116" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S116" s="12" t="n"/>
       <c r="T116" s="12" t="n"/>
-      <c r="U116" s="12" t="n">
+      <c r="U116" s="12" t="n"/>
+      <c r="V116" s="12" t="n">
         <v>3319</v>
       </c>
-      <c r="V116" s="12" t="inlineStr">
+      <c r="W116" s="12" t="inlineStr">
         <is>
           <t>3314</t>
         </is>
       </c>
-      <c r="W116" s="12" t="n"/>
-      <c r="X116" s="12" t="inlineStr">
+      <c r="X116" s="12" t="n"/>
+      <c r="Y116" s="12" t="inlineStr">
         <is>
           <t>회전 꼬마 수확기 +1 (1 → 2)</t>
         </is>
       </c>
-      <c r="Y116" s="12" t="n"/>
+      <c r="Z116" s="12" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="12" t="n">
@@ -10222,38 +10577,41 @@
       <c r="K117" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="L117" s="12" t="inlineStr">
+      <c r="L117" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M117" s="12" t="inlineStr">
         <is>
           <t>orbit_harvester_damage</t>
         </is>
       </c>
-      <c r="M117" s="12" t="n"/>
-      <c r="N117" s="12" t="n">
+      <c r="N117" s="12" t="n"/>
+      <c r="O117" s="12" t="n">
         <v>0.05</v>
       </c>
-      <c r="O117" s="12" t="n"/>
-      <c r="P117" s="12" t="n">
+      <c r="P117" s="12" t="n"/>
+      <c r="Q117" s="12" t="n">
         <v>1600000</v>
       </c>
-      <c r="Q117" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R117" s="12" t="n"/>
+      <c r="R117" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S117" s="12" t="n"/>
       <c r="T117" s="12" t="n"/>
-      <c r="U117" s="12" t="n">
+      <c r="U117" s="12" t="n"/>
+      <c r="V117" s="12" t="n">
         <v>3319</v>
       </c>
-      <c r="V117" s="12" t="n"/>
       <c r="W117" s="12" t="n"/>
-      <c r="X117" s="12" t="inlineStr">
+      <c r="X117" s="12" t="n"/>
+      <c r="Y117" s="12" t="inlineStr">
         <is>
           <t>회전 꼬마 수확기 공격력 5%</t>
         </is>
       </c>
-      <c r="Y117" s="12" t="n"/>
+      <c r="Z117" s="12" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="12" t="n">
@@ -10299,42 +10657,45 @@
       <c r="K118" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="L118" s="12" t="inlineStr">
+      <c r="L118" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M118" s="12" t="inlineStr">
         <is>
           <t>boss_damage</t>
         </is>
       </c>
-      <c r="M118" s="12" t="n"/>
-      <c r="N118" s="12" t="n">
+      <c r="N118" s="12" t="n"/>
+      <c r="O118" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="O118" s="12" t="n"/>
-      <c r="P118" s="12" t="n">
+      <c r="P118" s="12" t="n"/>
+      <c r="Q118" s="12" t="n">
         <v>3700000</v>
       </c>
-      <c r="Q118" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R118" s="12" t="n"/>
+      <c r="R118" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S118" s="12" t="n"/>
       <c r="T118" s="12" t="n"/>
-      <c r="U118" s="12" t="n">
+      <c r="U118" s="12" t="n"/>
+      <c r="V118" s="12" t="n">
         <v>3331</v>
       </c>
-      <c r="V118" s="12" t="inlineStr">
+      <c r="W118" s="12" t="inlineStr">
         <is>
           <t>3321</t>
         </is>
       </c>
-      <c r="W118" s="12" t="n"/>
-      <c r="X118" s="12" t="inlineStr">
+      <c r="X118" s="12" t="n"/>
+      <c r="Y118" s="12" t="inlineStr">
         <is>
           <t>보스 피해 +60%</t>
         </is>
       </c>
-      <c r="Y118" s="12" t="n"/>
+      <c r="Z118" s="12" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="12" t="n">
@@ -10380,44 +10741,47 @@
       <c r="K119" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="L119" s="12" t="inlineStr">
+      <c r="L119" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M119" s="12" t="inlineStr">
         <is>
           <t>clone_bar_duration</t>
         </is>
       </c>
-      <c r="M119" s="12" t="n"/>
-      <c r="N119" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="N119" s="12" t="n"/>
       <c r="O119" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P119" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="P119" s="12" t="n">
+      <c r="Q119" s="12" t="n">
         <v>3700000</v>
       </c>
-      <c r="Q119" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R119" s="12" t="n"/>
+      <c r="R119" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S119" s="12" t="n"/>
       <c r="T119" s="12" t="n"/>
-      <c r="U119" s="12" t="n">
+      <c r="U119" s="12" t="n"/>
+      <c r="V119" s="12" t="n">
         <v>3324</v>
       </c>
-      <c r="V119" s="12" t="inlineStr">
+      <c r="W119" s="12" t="inlineStr">
         <is>
           <t>3322</t>
         </is>
       </c>
-      <c r="W119" s="12" t="n"/>
-      <c r="X119" s="12" t="inlineStr">
+      <c r="X119" s="12" t="n"/>
+      <c r="Y119" s="12" t="inlineStr">
         <is>
           <t>10% 확률로 4초 분신 바</t>
         </is>
       </c>
-      <c r="Y119" s="12" t="n"/>
+      <c r="Z119" s="12" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="12" t="n">
@@ -10463,42 +10827,45 @@
       <c r="K120" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="L120" s="12" t="inlineStr">
+      <c r="L120" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M120" s="12" t="inlineStr">
         <is>
           <t>combo_rate</t>
         </is>
       </c>
-      <c r="M120" s="12" t="n"/>
-      <c r="N120" s="12" t="n">
+      <c r="N120" s="12" t="n"/>
+      <c r="O120" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="O120" s="12" t="n"/>
-      <c r="P120" s="12" t="n">
+      <c r="P120" s="12" t="n"/>
+      <c r="Q120" s="12" t="n">
         <v>3700000</v>
       </c>
-      <c r="Q120" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R120" s="12" t="n"/>
+      <c r="R120" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S120" s="12" t="n"/>
       <c r="T120" s="12" t="n"/>
-      <c r="U120" s="12" t="n">
+      <c r="U120" s="12" t="n"/>
+      <c r="V120" s="12" t="n">
         <v>3323</v>
       </c>
-      <c r="V120" s="12" t="inlineStr">
+      <c r="W120" s="12" t="inlineStr">
         <is>
           <t>3325</t>
         </is>
       </c>
-      <c r="W120" s="12" t="n"/>
-      <c r="X120" s="12" t="inlineStr">
+      <c r="X120" s="12" t="n"/>
+      <c r="Y120" s="12" t="inlineStr">
         <is>
           <t>콤보 계수 +80%</t>
         </is>
       </c>
-      <c r="Y120" s="12" t="n"/>
+      <c r="Z120" s="12" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="12" t="n">
@@ -10544,38 +10911,41 @@
       <c r="K121" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="L121" s="12" t="inlineStr">
+      <c r="L121" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M121" s="12" t="inlineStr">
         <is>
           <t>crit_damage</t>
         </is>
       </c>
-      <c r="M121" s="12" t="n"/>
-      <c r="N121" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O121" s="12" t="n"/>
-      <c r="P121" s="12" t="n">
+      <c r="N121" s="12" t="n"/>
+      <c r="O121" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P121" s="12" t="n"/>
+      <c r="Q121" s="12" t="n">
         <v>3300000</v>
       </c>
-      <c r="Q121" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R121" s="12" t="n"/>
+      <c r="R121" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S121" s="12" t="n"/>
       <c r="T121" s="12" t="n"/>
-      <c r="U121" s="12" t="n">
+      <c r="U121" s="12" t="n"/>
+      <c r="V121" s="12" t="n">
         <v>3321</v>
       </c>
-      <c r="V121" s="12" t="n"/>
       <c r="W121" s="12" t="n"/>
-      <c r="X121" s="12" t="inlineStr">
+      <c r="X121" s="12" t="n"/>
+      <c r="Y121" s="12" t="inlineStr">
         <is>
           <t>치명타 피해 100%</t>
         </is>
       </c>
-      <c r="Y121" s="12" t="n"/>
+      <c r="Z121" s="12" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="12" t="n">
@@ -10621,42 +10991,45 @@
       <c r="K122" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L122" s="12" t="inlineStr">
+      <c r="L122" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M122" s="12" t="inlineStr">
         <is>
           <t>crit_chance</t>
         </is>
       </c>
-      <c r="M122" s="12" t="n"/>
-      <c r="N122" s="12" t="n">
+      <c r="N122" s="12" t="n"/>
+      <c r="O122" s="12" t="n">
         <v>0.02</v>
       </c>
-      <c r="O122" s="12" t="n"/>
-      <c r="P122" s="12" t="n">
+      <c r="P122" s="12" t="n"/>
+      <c r="Q122" s="12" t="n">
         <v>12000000</v>
       </c>
-      <c r="Q122" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R122" s="12" t="n"/>
+      <c r="R122" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S122" s="12" t="n"/>
       <c r="T122" s="12" t="n"/>
-      <c r="U122" s="12" t="n">
+      <c r="U122" s="12" t="n"/>
+      <c r="V122" s="12" t="n">
         <v>3331</v>
       </c>
-      <c r="V122" s="12" t="inlineStr">
+      <c r="W122" s="12" t="inlineStr">
         <is>
           <t>3319</t>
         </is>
       </c>
-      <c r="W122" s="12" t="n"/>
-      <c r="X122" s="12" t="inlineStr">
+      <c r="X122" s="12" t="n"/>
+      <c r="Y122" s="12" t="inlineStr">
         <is>
           <t>치명타 확률 8%</t>
         </is>
       </c>
-      <c r="Y122" s="12" t="n"/>
+      <c r="Z122" s="12" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="12" t="n">
@@ -10702,42 +11075,45 @@
       <c r="K123" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L123" s="12" t="inlineStr">
+      <c r="L123" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M123" s="12" t="inlineStr">
         <is>
           <t>round_time</t>
         </is>
       </c>
-      <c r="M123" s="12" t="n"/>
-      <c r="N123" s="12" t="n">
+      <c r="N123" s="12" t="n"/>
+      <c r="O123" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="O123" s="12" t="n"/>
-      <c r="P123" s="12" t="n">
+      <c r="P123" s="12" t="n"/>
+      <c r="Q123" s="12" t="n">
         <v>11000000</v>
       </c>
-      <c r="Q123" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R123" s="12" t="n"/>
+      <c r="R123" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S123" s="12" t="n"/>
       <c r="T123" s="12" t="n"/>
-      <c r="U123" s="12" t="n">
+      <c r="U123" s="12" t="n"/>
+      <c r="V123" s="12" t="n">
         <v>3325</v>
       </c>
-      <c r="V123" s="12" t="inlineStr">
+      <c r="W123" s="12" t="inlineStr">
         <is>
           <t>3323</t>
         </is>
       </c>
-      <c r="W123" s="12" t="n"/>
-      <c r="X123" s="12" t="inlineStr">
+      <c r="X123" s="12" t="n"/>
+      <c r="Y123" s="12" t="inlineStr">
         <is>
           <t>지속 시간 +3초 (21 → 24)</t>
         </is>
       </c>
-      <c r="Y123" s="12" t="n"/>
+      <c r="Z123" s="12" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="12" t="n">
@@ -10783,42 +11159,45 @@
       <c r="K124" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="L124" s="12" t="inlineStr">
+      <c r="L124" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M124" s="12" t="inlineStr">
         <is>
           <t>round_time</t>
         </is>
       </c>
-      <c r="M124" s="12" t="n"/>
-      <c r="N124" s="12" t="n">
+      <c r="N124" s="12" t="n"/>
+      <c r="O124" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="O124" s="12" t="n"/>
-      <c r="P124" s="12" t="n">
+      <c r="P124" s="12" t="n"/>
+      <c r="Q124" s="12" t="n">
         <v>11000000</v>
       </c>
-      <c r="Q124" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R124" s="12" t="n"/>
+      <c r="R124" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S124" s="12" t="n"/>
       <c r="T124" s="12" t="n"/>
-      <c r="U124" s="12" t="n">
+      <c r="U124" s="12" t="n"/>
+      <c r="V124" s="12" t="n">
         <v>3325</v>
       </c>
-      <c r="V124" s="12" t="inlineStr">
+      <c r="W124" s="12" t="inlineStr">
         <is>
           <t>3333</t>
         </is>
       </c>
-      <c r="W124" s="12" t="n"/>
-      <c r="X124" s="12" t="inlineStr">
+      <c r="X124" s="12" t="n"/>
+      <c r="Y124" s="12" t="inlineStr">
         <is>
           <t>지속 시간 +3초 (24 → 27)</t>
         </is>
       </c>
-      <c r="Y124" s="12" t="inlineStr">
+      <c r="Z124" s="12" t="inlineStr">
         <is>
           <t>원문은 Lv.3과 같은 레어도 14</t>
         </is>
@@ -10868,42 +11247,45 @@
       <c r="K125" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L125" s="12" t="inlineStr">
+      <c r="L125" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M125" s="12" t="inlineStr">
         <is>
           <t>boss_damage</t>
         </is>
       </c>
-      <c r="M125" s="12" t="n"/>
-      <c r="N125" s="12" t="n">
+      <c r="N125" s="12" t="n"/>
+      <c r="O125" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="O125" s="12" t="n"/>
-      <c r="P125" s="12" t="n">
+      <c r="P125" s="12" t="n"/>
+      <c r="Q125" s="12" t="n">
         <v>19000000</v>
       </c>
-      <c r="Q125" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R125" s="12" t="n"/>
+      <c r="R125" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S125" s="12" t="n"/>
       <c r="T125" s="12" t="n"/>
-      <c r="U125" s="12" t="n">
+      <c r="U125" s="12" t="n"/>
+      <c r="V125" s="12" t="n">
         <v>3327</v>
       </c>
-      <c r="V125" s="12" t="inlineStr">
+      <c r="W125" s="12" t="inlineStr">
         <is>
           <t>3328</t>
         </is>
       </c>
-      <c r="W125" s="12" t="n"/>
-      <c r="X125" s="12" t="inlineStr">
+      <c r="X125" s="12" t="n"/>
+      <c r="Y125" s="12" t="inlineStr">
         <is>
           <t>보스 피해 +80%</t>
         </is>
       </c>
-      <c r="Y125" s="12" t="n"/>
+      <c r="Z125" s="12" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="12" t="n">
@@ -10949,42 +11331,45 @@
       <c r="K126" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L126" s="12" t="inlineStr">
+      <c r="L126" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M126" s="12" t="inlineStr">
         <is>
           <t>combo_rate</t>
         </is>
       </c>
-      <c r="M126" s="12" t="n"/>
-      <c r="N126" s="12" t="n">
+      <c r="N126" s="12" t="n"/>
+      <c r="O126" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="O126" s="12" t="n"/>
-      <c r="P126" s="12" t="n">
+      <c r="P126" s="12" t="n"/>
+      <c r="Q126" s="12" t="n">
         <v>19000000</v>
       </c>
-      <c r="Q126" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R126" s="12" t="n"/>
+      <c r="R126" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S126" s="12" t="n"/>
       <c r="T126" s="12" t="n"/>
-      <c r="U126" s="12" t="n">
+      <c r="U126" s="12" t="n"/>
+      <c r="V126" s="12" t="n">
         <v>3329</v>
       </c>
-      <c r="V126" s="12" t="inlineStr">
+      <c r="W126" s="12" t="inlineStr">
         <is>
           <t>3330</t>
         </is>
       </c>
-      <c r="W126" s="12" t="n"/>
-      <c r="X126" s="12" t="inlineStr">
+      <c r="X126" s="12" t="n"/>
+      <c r="Y126" s="12" t="inlineStr">
         <is>
           <t>콤보 계수 +100%</t>
         </is>
       </c>
-      <c r="Y126" s="12" t="n"/>
+      <c r="Z126" s="12" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="12" t="n">
@@ -11030,42 +11415,45 @@
       <c r="K127" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L127" s="12" t="inlineStr">
+      <c r="L127" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M127" s="12" t="inlineStr">
         <is>
           <t>orbit_harvester_damage</t>
         </is>
       </c>
-      <c r="M127" s="12" t="n"/>
-      <c r="N127" s="12" t="n">
+      <c r="N127" s="12" t="n"/>
+      <c r="O127" s="12" t="n">
         <v>0.05</v>
       </c>
-      <c r="O127" s="12" t="n"/>
-      <c r="P127" s="12" t="n">
+      <c r="P127" s="12" t="n"/>
+      <c r="Q127" s="12" t="n">
         <v>19000000</v>
       </c>
-      <c r="Q127" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R127" s="12" t="n"/>
+      <c r="R127" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S127" s="12" t="n"/>
       <c r="T127" s="12" t="n"/>
-      <c r="U127" s="12" t="n">
+      <c r="U127" s="12" t="n"/>
+      <c r="V127" s="12" t="n">
         <v>3328</v>
       </c>
-      <c r="V127" s="12" t="inlineStr">
+      <c r="W127" s="12" t="inlineStr">
         <is>
           <t>3327</t>
         </is>
       </c>
-      <c r="W127" s="12" t="n"/>
-      <c r="X127" s="12" t="inlineStr">
+      <c r="X127" s="12" t="n"/>
+      <c r="Y127" s="12" t="inlineStr">
         <is>
           <t>회전 꼬마 수확기 공격력 10%</t>
         </is>
       </c>
-      <c r="Y127" s="12" t="n"/>
+      <c r="Z127" s="12" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="12" t="n">
@@ -11111,42 +11499,45 @@
       <c r="K128" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L128" s="12" t="inlineStr">
+      <c r="L128" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M128" s="12" t="inlineStr">
         <is>
           <t>harvester_damage</t>
         </is>
       </c>
-      <c r="M128" s="12" t="n"/>
-      <c r="N128" s="12" t="n">
+      <c r="N128" s="12" t="n"/>
+      <c r="O128" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="O128" s="12" t="n"/>
-      <c r="P128" s="12" t="n">
+      <c r="P128" s="12" t="n"/>
+      <c r="Q128" s="12" t="n">
         <v>19000000</v>
       </c>
-      <c r="Q128" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R128" s="12" t="n"/>
+      <c r="R128" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S128" s="12" t="n"/>
       <c r="T128" s="12" t="n"/>
-      <c r="U128" s="12" t="n">
+      <c r="U128" s="12" t="n"/>
+      <c r="V128" s="12" t="n">
         <v>3326</v>
       </c>
-      <c r="V128" s="12" t="inlineStr">
+      <c r="W128" s="12" t="inlineStr">
         <is>
           <t>3320</t>
         </is>
       </c>
-      <c r="W128" s="12" t="n"/>
-      <c r="X128" s="12" t="inlineStr">
+      <c r="X128" s="12" t="n"/>
+      <c r="Y128" s="12" t="inlineStr">
         <is>
           <t>공격력 +5 (10 → 15)</t>
         </is>
       </c>
-      <c r="Y128" s="12" t="n"/>
+      <c r="Z128" s="12" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="12" t="n">
@@ -11192,40 +11583,43 @@
       <c r="K129" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="L129" s="12" t="inlineStr">
+      <c r="L129" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="M129" s="12" t="inlineStr">
         <is>
           <t>harvester_slot</t>
         </is>
       </c>
-      <c r="M129" s="12" t="n"/>
-      <c r="N129" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O129" s="12" t="n"/>
-      <c r="P129" s="12" t="n">
+      <c r="N129" s="12" t="n"/>
+      <c r="O129" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P129" s="12" t="n"/>
+      <c r="Q129" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="Q129" s="12" t="inlineStr">
+      <c r="R129" s="12" t="inlineStr">
         <is>
           <t>Mycelite</t>
         </is>
       </c>
-      <c r="R129" s="12" t="n"/>
       <c r="S129" s="12" t="n"/>
-      <c r="T129" s="12" t="n">
+      <c r="T129" s="12" t="n"/>
+      <c r="U129" s="12" t="n">
         <v>1.3</v>
       </c>
-      <c r="U129" s="12" t="n">
+      <c r="V129" s="12" t="n">
         <v>3341</v>
       </c>
-      <c r="V129" s="12" t="n"/>
       <c r="W129" s="12" t="n"/>
-      <c r="X129" s="12" t="inlineStr">
+      <c r="X129" s="12" t="n"/>
+      <c r="Y129" s="12" t="inlineStr">
         <is>
           <t>수확기 개수 +1 / Lv (최대 5개 장착)</t>
         </is>
       </c>
-      <c r="Y129" s="12" t="n"/>
+      <c r="Z129" s="12" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="12" t="n">
@@ -11271,42 +11665,45 @@
       <c r="K130" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="L130" s="12" t="inlineStr">
+      <c r="L130" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="M130" s="12" t="inlineStr">
         <is>
           <t>boss_damage</t>
         </is>
       </c>
-      <c r="M130" s="12" t="n"/>
-      <c r="N130" s="12" t="n">
+      <c r="N130" s="12" t="n"/>
+      <c r="O130" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="O130" s="12" t="n"/>
-      <c r="P130" s="12" t="n">
+      <c r="P130" s="12" t="n"/>
+      <c r="Q130" s="12" t="n">
         <v>26000000</v>
       </c>
-      <c r="Q130" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R130" s="12" t="n"/>
+      <c r="R130" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S130" s="12" t="n"/>
       <c r="T130" s="12" t="n"/>
-      <c r="U130" s="12" t="n">
+      <c r="U130" s="12" t="n"/>
+      <c r="V130" s="12" t="n">
         <v>3337</v>
       </c>
-      <c r="V130" s="12" t="inlineStr">
+      <c r="W130" s="12" t="inlineStr">
         <is>
           <t>3335</t>
         </is>
       </c>
-      <c r="W130" s="12" t="n"/>
-      <c r="X130" s="12" t="inlineStr">
+      <c r="X130" s="12" t="n"/>
+      <c r="Y130" s="12" t="inlineStr">
         <is>
           <t>보스 피해 +100%</t>
         </is>
       </c>
-      <c r="Y130" s="12" t="n"/>
+      <c r="Z130" s="12" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="12" t="n">
@@ -11352,44 +11749,47 @@
       <c r="K131" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="L131" s="12" t="inlineStr">
+      <c r="L131" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M131" s="12" t="inlineStr">
         <is>
           <t>clone_bar_duration</t>
         </is>
       </c>
-      <c r="M131" s="12" t="n"/>
-      <c r="N131" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="N131" s="12" t="n"/>
       <c r="O131" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P131" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="P131" s="12" t="n">
+      <c r="Q131" s="12" t="n">
         <v>26000000</v>
       </c>
-      <c r="Q131" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R131" s="12" t="n"/>
+      <c r="R131" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S131" s="12" t="n"/>
       <c r="T131" s="12" t="n"/>
-      <c r="U131" s="12" t="n">
+      <c r="U131" s="12" t="n"/>
+      <c r="V131" s="12" t="n">
         <v>3334</v>
       </c>
-      <c r="V131" s="12" t="inlineStr">
+      <c r="W131" s="12" t="inlineStr">
         <is>
           <t>3329</t>
         </is>
       </c>
-      <c r="W131" s="12" t="n"/>
-      <c r="X131" s="12" t="inlineStr">
+      <c r="X131" s="12" t="n"/>
+      <c r="Y131" s="12" t="inlineStr">
         <is>
           <t>10% 확률로 5초 분신 바</t>
         </is>
       </c>
-      <c r="Y131" s="12" t="n"/>
+      <c r="Z131" s="12" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="12" t="n">
@@ -11435,42 +11835,45 @@
       <c r="K132" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="L132" s="12" t="inlineStr">
+      <c r="L132" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M132" s="12" t="inlineStr">
         <is>
           <t>crit_chance</t>
         </is>
       </c>
-      <c r="M132" s="12" t="n"/>
-      <c r="N132" s="12" t="n">
+      <c r="N132" s="12" t="n"/>
+      <c r="O132" s="12" t="n">
         <v>0.02</v>
       </c>
-      <c r="O132" s="12" t="n"/>
-      <c r="P132" s="12" t="n">
+      <c r="P132" s="12" t="n"/>
+      <c r="Q132" s="12" t="n">
         <v>26000000</v>
       </c>
-      <c r="Q132" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R132" s="12" t="n"/>
+      <c r="R132" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S132" s="12" t="n"/>
       <c r="T132" s="12" t="n"/>
-      <c r="U132" s="12" t="n">
+      <c r="U132" s="12" t="n"/>
+      <c r="V132" s="12" t="n">
         <v>3331</v>
       </c>
-      <c r="V132" s="12" t="inlineStr">
+      <c r="W132" s="12" t="inlineStr">
         <is>
           <t>3332</t>
         </is>
       </c>
-      <c r="W132" s="12" t="n"/>
-      <c r="X132" s="12" t="inlineStr">
+      <c r="X132" s="12" t="n"/>
+      <c r="Y132" s="12" t="inlineStr">
         <is>
           <t>치명타 확률 10%</t>
         </is>
       </c>
-      <c r="Y132" s="12" t="n"/>
+      <c r="Z132" s="12" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="12" t="n">
@@ -11516,38 +11919,41 @@
       <c r="K133" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="L133" s="12" t="inlineStr">
+      <c r="L133" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M133" s="12" t="inlineStr">
         <is>
           <t>clone_bar_count</t>
         </is>
       </c>
-      <c r="M133" s="12" t="n"/>
-      <c r="N133" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O133" s="12" t="n"/>
-      <c r="P133" s="12" t="n">
+      <c r="N133" s="12" t="n"/>
+      <c r="O133" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P133" s="12" t="n"/>
+      <c r="Q133" s="12" t="n">
         <v>26000000</v>
       </c>
-      <c r="Q133" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R133" s="12" t="n"/>
+      <c r="R133" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S133" s="12" t="n"/>
       <c r="T133" s="12" t="n"/>
-      <c r="U133" s="12" t="n">
+      <c r="U133" s="12" t="n"/>
+      <c r="V133" s="12" t="n">
         <v>3333</v>
       </c>
-      <c r="V133" s="12" t="n"/>
       <c r="W133" s="12" t="n"/>
-      <c r="X133" s="12" t="inlineStr">
+      <c r="X133" s="12" t="n"/>
+      <c r="Y133" s="12" t="inlineStr">
         <is>
           <t>분신 바 +1 (1 → 2)</t>
         </is>
       </c>
-      <c r="Y133" s="12" t="n"/>
+      <c r="Z133" s="12" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="12" t="n">
@@ -11593,42 +11999,45 @@
       <c r="K134" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="L134" s="12" t="inlineStr">
+      <c r="L134" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M134" s="12" t="inlineStr">
         <is>
           <t>orbit_harvester_count</t>
         </is>
       </c>
-      <c r="M134" s="12" t="n"/>
-      <c r="N134" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O134" s="12" t="n"/>
-      <c r="P134" s="12" t="n">
+      <c r="N134" s="12" t="n"/>
+      <c r="O134" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P134" s="12" t="n"/>
+      <c r="Q134" s="12" t="n">
         <v>26000000</v>
       </c>
-      <c r="Q134" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R134" s="12" t="n"/>
+      <c r="R134" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S134" s="12" t="n"/>
       <c r="T134" s="12" t="n"/>
-      <c r="U134" s="12" t="n">
+      <c r="U134" s="12" t="n"/>
+      <c r="V134" s="12" t="n">
         <v>3335</v>
       </c>
-      <c r="V134" s="12" t="inlineStr">
+      <c r="W134" s="12" t="inlineStr">
         <is>
           <t>3326</t>
         </is>
       </c>
-      <c r="W134" s="12" t="n"/>
-      <c r="X134" s="12" t="inlineStr">
+      <c r="X134" s="12" t="n"/>
+      <c r="Y134" s="12" t="inlineStr">
         <is>
           <t>회전 꼬마 수확기 +1 (2 → 3)</t>
         </is>
       </c>
-      <c r="Y134" s="12" t="n"/>
+      <c r="Z134" s="12" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="12" t="n">
@@ -11674,42 +12083,45 @@
       <c r="K135" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="L135" s="12" t="inlineStr">
+      <c r="L135" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M135" s="12" t="inlineStr">
         <is>
           <t>orbit_harvester_damage</t>
         </is>
       </c>
-      <c r="M135" s="12" t="n"/>
-      <c r="N135" s="12" t="n">
+      <c r="N135" s="12" t="n"/>
+      <c r="O135" s="12" t="n">
         <v>0.05</v>
       </c>
-      <c r="O135" s="12" t="n"/>
-      <c r="P135" s="12" t="n">
+      <c r="P135" s="12" t="n"/>
+      <c r="Q135" s="12" t="n">
         <v>26000000</v>
       </c>
-      <c r="Q135" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R135" s="12" t="n"/>
+      <c r="R135" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S135" s="12" t="n"/>
       <c r="T135" s="12" t="n"/>
-      <c r="U135" s="12" t="n">
+      <c r="U135" s="12" t="n"/>
+      <c r="V135" s="12" t="n">
         <v>3335</v>
       </c>
-      <c r="V135" s="12" t="inlineStr">
+      <c r="W135" s="12" t="inlineStr">
         <is>
           <t>3337</t>
         </is>
       </c>
-      <c r="W135" s="12" t="n"/>
-      <c r="X135" s="12" t="inlineStr">
+      <c r="X135" s="12" t="n"/>
+      <c r="Y135" s="12" t="inlineStr">
         <is>
           <t>회전 꼬마 수확기 공격력 15%</t>
         </is>
       </c>
-      <c r="Y135" s="12" t="n"/>
+      <c r="Z135" s="12" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="12" t="n">
@@ -11755,42 +12167,45 @@
       <c r="K136" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="L136" s="12" t="inlineStr">
+      <c r="L136" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="M136" s="12" t="inlineStr">
         <is>
           <t>crit_damage</t>
         </is>
       </c>
-      <c r="M136" s="12" t="n"/>
-      <c r="N136" s="12" t="n">
+      <c r="N136" s="12" t="n"/>
+      <c r="O136" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="O136" s="12" t="n"/>
-      <c r="P136" s="12" t="n">
+      <c r="P136" s="12" t="n"/>
+      <c r="Q136" s="12" t="n">
         <v>47000000</v>
       </c>
-      <c r="Q136" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R136" s="12" t="n"/>
+      <c r="R136" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S136" s="12" t="n"/>
       <c r="T136" s="12" t="n"/>
-      <c r="U136" s="12" t="n">
+      <c r="U136" s="12" t="n"/>
+      <c r="V136" s="12" t="n">
         <v>3337</v>
       </c>
-      <c r="V136" s="12" t="inlineStr">
+      <c r="W136" s="12" t="inlineStr">
         <is>
           <t>3331</t>
         </is>
       </c>
-      <c r="W136" s="12" t="n"/>
-      <c r="X136" s="12" t="inlineStr">
+      <c r="X136" s="12" t="n"/>
+      <c r="Y136" s="12" t="inlineStr">
         <is>
           <t>치명타 피해 120%</t>
         </is>
       </c>
-      <c r="Y136" s="12" t="inlineStr">
+      <c r="Z136" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +20%</t>
         </is>
@@ -11840,42 +12255,45 @@
       <c r="K137" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="L137" s="12" t="inlineStr">
+      <c r="L137" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M137" s="12" t="inlineStr">
         <is>
           <t>crit_damage</t>
         </is>
       </c>
-      <c r="M137" s="12" t="n"/>
-      <c r="N137" s="12" t="n">
+      <c r="N137" s="12" t="n"/>
+      <c r="O137" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="O137" s="12" t="n"/>
-      <c r="P137" s="12" t="n">
+      <c r="P137" s="12" t="n"/>
+      <c r="Q137" s="12" t="n">
         <v>65000000</v>
       </c>
-      <c r="Q137" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R137" s="12" t="n"/>
+      <c r="R137" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S137" s="12" t="n"/>
       <c r="T137" s="12" t="n"/>
-      <c r="U137" s="12" t="n">
+      <c r="U137" s="12" t="n"/>
+      <c r="V137" s="12" t="n">
         <v>3342</v>
       </c>
-      <c r="V137" s="12" t="inlineStr">
+      <c r="W137" s="12" t="inlineStr">
         <is>
           <t>3346</t>
         </is>
       </c>
-      <c r="W137" s="12" t="n"/>
-      <c r="X137" s="12" t="inlineStr">
+      <c r="X137" s="12" t="n"/>
+      <c r="Y137" s="12" t="inlineStr">
         <is>
           <t>치명타 피해 150%</t>
         </is>
       </c>
-      <c r="Y137" s="12" t="inlineStr">
+      <c r="Z137" s="12" t="inlineStr">
         <is>
           <t>누적값 기준 차이 +30%</t>
         </is>
@@ -11925,42 +12343,45 @@
       <c r="K138" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="L138" s="12" t="inlineStr">
+      <c r="L138" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="M138" s="12" t="inlineStr">
         <is>
           <t>round_time</t>
         </is>
       </c>
-      <c r="M138" s="12" t="n"/>
-      <c r="N138" s="12" t="n">
+      <c r="N138" s="12" t="n"/>
+      <c r="O138" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="O138" s="12" t="n"/>
-      <c r="P138" s="12" t="n">
+      <c r="P138" s="12" t="n"/>
+      <c r="Q138" s="12" t="n">
         <v>51000000</v>
       </c>
-      <c r="Q138" s="12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="R138" s="12" t="n"/>
+      <c r="R138" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="S138" s="12" t="n"/>
       <c r="T138" s="12" t="n"/>
-      <c r="U138" s="12" t="n">
+      <c r="U138" s="12" t="n"/>
+      <c r="V138" s="12" t="n">
         <v>3343</v>
       </c>
-      <c r="V138" s="12" t="inlineStr">
+      <c r="W138" s="12" t="inlineStr">
         <is>
           <t>3334</t>
         </is>
       </c>
-      <c r="W138" s="12" t="n"/>
-      <c r="X138" s="12" t="inlineStr">
+      <c r="X138" s="12" t="n"/>
+      <c r="Y138" s="12" t="inlineStr">
         <is>
           <t>지속 시간 +3초 (27 → 30)</t>
         </is>
       </c>
-      <c r="Y138" s="12" t="n"/>
+      <c r="Z138" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
